--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haavas\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB08FDD-5B17-404C-8054-364EA19B5ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37120A9E-9D0E-488D-A5FD-8502A37A14E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -22542,13 +22542,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP157"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="42" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>207</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>245</v>
       </c>
@@ -23444,7 +23444,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -23572,7 +23572,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>312</v>
       </c>
@@ -23700,7 +23700,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>341</v>
       </c>
@@ -23828,7 +23828,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>370</v>
       </c>
@@ -23956,7 +23956,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>393</v>
       </c>
@@ -24084,7 +24084,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>342</v>
       </c>
@@ -24212,7 +24212,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>433</v>
       </c>
@@ -24340,7 +24340,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>471</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>498</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>527</v>
       </c>
@@ -24724,7 +24724,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>558</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>592</v>
       </c>
@@ -24980,7 +24980,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>626</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>660</v>
       </c>
@@ -25236,7 +25236,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>693</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>725</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>750</v>
       </c>
@@ -25620,7 +25620,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>559</v>
       </c>
@@ -25748,7 +25748,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>794</v>
       </c>
@@ -25876,7 +25876,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>818</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>843</v>
       </c>
@@ -26132,7 +26132,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>871</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>898</v>
       </c>
@@ -26388,7 +26388,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>925</v>
       </c>
@@ -26516,7 +26516,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>949</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>973</v>
       </c>
@@ -26772,7 +26772,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>997</v>
       </c>
@@ -26900,7 +26900,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>1024</v>
       </c>
@@ -27028,7 +27028,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>1058</v>
       </c>
@@ -27156,7 +27156,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>1077</v>
       </c>
@@ -27284,7 +27284,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>1093</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1113</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>1148</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>1180</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>1198</v>
       </c>
@@ -27924,7 +27924,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>1237</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>1264</v>
       </c>
@@ -28180,7 +28180,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>1285</v>
       </c>
@@ -28308,7 +28308,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>1323</v>
       </c>
@@ -28436,7 +28436,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>1349</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>1384</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>1419</v>
       </c>
@@ -28820,7 +28820,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>1449</v>
       </c>
@@ -28948,7 +28948,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>1479</v>
       </c>
@@ -29076,7 +29076,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>1508</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>1544</v>
       </c>
@@ -29332,7 +29332,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>1565</v>
       </c>
@@ -29460,7 +29460,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>1604</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>1633</v>
       </c>
@@ -29716,7 +29716,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>1662</v>
       </c>
@@ -29844,7 +29844,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>1677</v>
       </c>
@@ -29972,7 +29972,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>1703</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>1739</v>
       </c>
@@ -30228,7 +30228,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>1770</v>
       </c>
@@ -30356,7 +30356,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>1798</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>1836</v>
       </c>
@@ -30612,7 +30612,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>1858</v>
       </c>
@@ -30740,7 +30740,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>1883</v>
       </c>
@@ -30868,7 +30868,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>1900</v>
       </c>
@@ -30996,7 +30996,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>1920</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>1958</v>
       </c>
@@ -31252,7 +31252,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>1995</v>
       </c>
@@ -31380,7 +31380,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>2033</v>
       </c>
@@ -31508,7 +31508,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>2072</v>
       </c>
@@ -31636,7 +31636,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>2090</v>
       </c>
@@ -31764,7 +31764,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>2126</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>2146</v>
       </c>
@@ -32020,7 +32020,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>2183</v>
       </c>
@@ -32148,7 +32148,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>2201</v>
       </c>
@@ -32276,7 +32276,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>2240</v>
       </c>
@@ -32404,7 +32404,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>2274</v>
       </c>
@@ -32532,7 +32532,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>2304</v>
       </c>
@@ -32660,7 +32660,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>2340</v>
       </c>
@@ -32788,7 +32788,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>2375</v>
       </c>
@@ -32916,7 +32916,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>2395</v>
       </c>
@@ -33044,7 +33044,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>2426</v>
       </c>
@@ -33172,7 +33172,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>2458</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>2493</v>
       </c>
@@ -33428,7 +33428,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>2524</v>
       </c>
@@ -33556,7 +33556,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>2549</v>
       </c>
@@ -33684,7 +33684,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>2573</v>
       </c>
@@ -33812,7 +33812,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>2600</v>
       </c>
@@ -33940,7 +33940,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>2616</v>
       </c>
@@ -34068,7 +34068,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>2622</v>
       </c>
@@ -34196,7 +34196,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>2628</v>
       </c>
@@ -34324,7 +34324,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>2634</v>
       </c>
@@ -34452,7 +34452,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>2640</v>
       </c>
@@ -34580,7 +34580,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>2648</v>
       </c>
@@ -34708,7 +34708,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>2656</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>2663</v>
       </c>
@@ -34964,7 +34964,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>2670</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>2677</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>2684</v>
       </c>
@@ -35348,7 +35348,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>2691</v>
       </c>
@@ -35476,7 +35476,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>2698</v>
       </c>
@@ -35604,7 +35604,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>2706</v>
       </c>
@@ -35732,7 +35732,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>2714</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>2721</v>
       </c>
@@ -35988,7 +35988,7 @@
         <v>2726</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>2727</v>
       </c>
@@ -36116,7 +36116,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>2747</v>
       </c>
@@ -36244,7 +36244,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>2767</v>
       </c>
@@ -36372,7 +36372,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>2787</v>
       </c>
@@ -36500,7 +36500,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>2807</v>
       </c>
@@ -36628,7 +36628,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>2827</v>
       </c>
@@ -36756,7 +36756,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>2847</v>
       </c>
@@ -36884,7 +36884,7 @@
         <v>2866</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>2867</v>
       </c>
@@ -37012,7 +37012,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>2887</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>2907</v>
       </c>
@@ -37268,7 +37268,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>2927</v>
       </c>
@@ -37396,7 +37396,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>2947</v>
       </c>
@@ -37524,7 +37524,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>2967</v>
       </c>
@@ -37652,7 +37652,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>2987</v>
       </c>
@@ -37780,7 +37780,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>2977</v>
       </c>
@@ -37908,7 +37908,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>2997</v>
       </c>
@@ -38036,7 +38036,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>3033</v>
       </c>
@@ -38164,43 +38164,43 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A146" s="1"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A147" s="1"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A148" s="1"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A149" s="1"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A150" s="1"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A151" s="1"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A152" s="1"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A153" s="1"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A154" s="1"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A155" s="1"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A156" s="1"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>3074</v>
       </c>
@@ -38337,22 +38337,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA72"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="10"/>
-    <col min="5" max="5" width="1.140625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="10"/>
-    <col min="7" max="7" width="27.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="1.140625" style="10" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="1.1796875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="10"/>
+    <col min="5" max="5" width="1.1796875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="10"/>
+    <col min="7" max="7" width="27.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7265625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="1.1796875" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="9.1796875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:27" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="39" t="s">
         <v>3115</v>
       </c>
@@ -38364,7 +38364,7 @@
       <c r="G2" s="40"/>
       <c r="H2" s="41"/>
     </row>
-    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="42"/>
       <c r="C3" s="43"/>
       <c r="D3" s="44"/>
@@ -38372,7 +38372,7 @@
       <c r="G3" s="43"/>
       <c r="H3" s="44"/>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B4" s="54" t="s">
         <v>3117</v>
       </c>
@@ -38384,7 +38384,7 @@
       <c r="G4" s="45"/>
       <c r="H4" s="44"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B5" s="42"/>
       <c r="C5" s="43"/>
       <c r="D5" s="44"/>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="H5" s="44"/>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B6" s="54" t="s">
         <v>3120</v>
       </c>
@@ -38412,7 +38412,7 @@
       </c>
       <c r="H6" s="44"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B7" s="54"/>
       <c r="C7" s="43"/>
       <c r="D7" s="44"/>
@@ -38428,7 +38428,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="54" t="s">
         <v>3126</v>
       </c>
@@ -38444,7 +38444,7 @@
       </c>
       <c r="H8" s="44"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B9" s="54"/>
       <c r="C9" s="43"/>
       <c r="D9" s="44"/>
@@ -38456,7 +38456,7 @@
       </c>
       <c r="H9" s="44"/>
     </row>
-    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="54" t="s">
         <v>3132</v>
       </c>
@@ -38468,7 +38468,7 @@
       <c r="G10" s="50"/>
       <c r="H10" s="44"/>
     </row>
-    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="54"/>
       <c r="C11" s="43"/>
       <c r="D11" s="44"/>
@@ -38476,7 +38476,7 @@
       <c r="G11" s="52"/>
       <c r="H11" s="53"/>
     </row>
-    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="54" t="s">
         <v>3134</v>
       </c>
@@ -38497,7 +38497,7 @@
       <c r="P12" s="76"/>
       <c r="Q12" s="76"/>
     </row>
-    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="54"/>
       <c r="C13" s="43"/>
       <c r="D13" s="44"/>
@@ -38514,7 +38514,7 @@
       <c r="P13" s="76"/>
       <c r="Q13" s="76"/>
     </row>
-    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="54" t="s">
         <v>3135</v>
       </c>
@@ -38535,7 +38535,7 @@
       <c r="P14" s="76"/>
       <c r="Q14" s="76"/>
     </row>
-    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="51"/>
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
@@ -38560,7 +38560,7 @@
       <c r="P15" s="76"/>
       <c r="Q15" s="76"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
       <c r="F16" s="118" t="s">
         <v>3137</v>
       </c>
@@ -38579,7 +38579,7 @@
       <c r="P16" s="76"/>
       <c r="Q16" s="76"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="55"/>
       <c r="C17" s="56"/>
       <c r="D17" s="57"/>
@@ -38598,7 +38598,7 @@
       <c r="P17" s="76"/>
       <c r="Q17" s="76"/>
     </row>
-    <row r="18" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B18" s="42"/>
       <c r="C18" s="58" t="s">
         <v>3131</v>
@@ -38623,7 +38623,7 @@
       <c r="P18" s="76"/>
       <c r="Q18" s="76"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="59" t="str">
         <f>VLOOKUP("France",T,lang,FALSE)</f>
         <v>France</v>
@@ -38651,7 +38651,7 @@
       <c r="P19" s="76"/>
       <c r="Q19" s="76"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="59" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
         <v>Spain</v>
@@ -38679,7 +38679,7 @@
       <c r="P20" s="76"/>
       <c r="Q20" s="76"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B21" s="59" t="str">
         <f>VLOOKUP("Argentina",T,lang,FALSE)</f>
         <v>Argentina</v>
@@ -38707,7 +38707,7 @@
       <c r="P21" s="76"/>
       <c r="Q21" s="76"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B22" s="59" t="str">
         <f>VLOOKUP("England",T,lang,FALSE)</f>
         <v>England</v>
@@ -38735,7 +38735,7 @@
       <c r="P22" s="76"/>
       <c r="Q22" s="76"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B23" s="59" t="str">
         <f>VLOOKUP("Portugal",T,lang,FALSE)</f>
         <v>Portugal</v>
@@ -38763,7 +38763,7 @@
       <c r="P23" s="76"/>
       <c r="Q23" s="76"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B24" s="59" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
         <v>Brazil</v>
@@ -38791,7 +38791,7 @@
       <c r="P24" s="76"/>
       <c r="Q24" s="76"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B25" s="59" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
         <v>Netherlands</v>
@@ -38819,7 +38819,7 @@
       <c r="P25" s="76"/>
       <c r="Q25" s="76"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B26" s="59" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
         <v>Morocco</v>
@@ -38847,7 +38847,7 @@
       <c r="P26" s="76"/>
       <c r="Q26" s="76"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B27" s="59" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
         <v>Belgium</v>
@@ -38875,7 +38875,7 @@
       <c r="P27" s="76"/>
       <c r="Q27" s="76"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B28" s="59" t="str">
         <f>VLOOKUP("Germany",T,lang,FALSE)</f>
         <v>Germany</v>
@@ -38903,7 +38903,7 @@
       <c r="P28" s="76"/>
       <c r="Q28" s="76"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29" s="59" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
         <v>Croatia</v>
@@ -38931,7 +38931,7 @@
       <c r="P29" s="76"/>
       <c r="Q29" s="76"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B30" s="59" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
         <v>Colombia</v>
@@ -38959,7 +38959,7 @@
       <c r="P30" s="76"/>
       <c r="Q30" s="76"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B31" s="59" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
         <v>Senegal</v>
@@ -38987,7 +38987,7 @@
       <c r="P31" s="76"/>
       <c r="Q31" s="76"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B32" s="59" t="str">
         <f>VLOOKUP("Mexico",T,lang,FALSE)</f>
         <v>Mexico</v>
@@ -39015,7 +39015,7 @@
       <c r="P32" s="76"/>
       <c r="Q32" s="76"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B33" s="59" t="str">
         <f>VLOOKUP("United States",T,lang,FALSE)</f>
         <v>United States</v>
@@ -39043,7 +39043,7 @@
       <c r="P33" s="76"/>
       <c r="Q33" s="76"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B34" s="59" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
         <v>Uruguay</v>
@@ -39071,7 +39071,7 @@
       <c r="P34" s="76"/>
       <c r="Q34" s="76"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B35" s="59" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
         <v>Japan</v>
@@ -39099,7 +39099,7 @@
       <c r="P35" s="76"/>
       <c r="Q35" s="76"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B36" s="59" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
         <v>Switzerland</v>
@@ -39127,7 +39127,7 @@
       <c r="P36" s="76"/>
       <c r="Q36" s="76"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B37" s="59" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
         <v>Iran</v>
@@ -39155,7 +39155,7 @@
       <c r="P37" s="76"/>
       <c r="Q37" s="76"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B38" s="59" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
         <v>Turkey</v>
@@ -39183,7 +39183,7 @@
       <c r="P38" s="76"/>
       <c r="Q38" s="76"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B39" s="59" t="str">
         <f>VLOOKUP("Ecuador",T,lang,FALSE)</f>
         <v>Ecuador</v>
@@ -39211,7 +39211,7 @@
       <c r="P39" s="76"/>
       <c r="Q39" s="76"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B40" s="59" t="str">
         <f>VLOOKUP("Austria",T,lang,FALSE)</f>
         <v>Austria</v>
@@ -39239,7 +39239,7 @@
       <c r="P40" s="76"/>
       <c r="Q40" s="76"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B41" s="59" t="str">
         <f>VLOOKUP("Korea Republic",T,lang,FALSE)</f>
         <v>Korea Republic</v>
@@ -39267,7 +39267,7 @@
       <c r="P41" s="76"/>
       <c r="Q41" s="76"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B42" s="59" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
         <v>Australia</v>
@@ -39295,7 +39295,7 @@
       <c r="P42" s="76"/>
       <c r="Q42" s="76"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B43" s="59" t="str">
         <f>VLOOKUP("Algeria",T,lang,FALSE)</f>
         <v>Algeria</v>
@@ -39319,7 +39319,7 @@
       <c r="P43" s="76"/>
       <c r="Q43" s="76"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B44" s="59" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
         <v>Egypt</v>
@@ -39347,7 +39347,7 @@
       <c r="P44" s="76"/>
       <c r="Q44" s="76"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B45" s="59" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
         <v>Canada</v>
@@ -39375,7 +39375,7 @@
       <c r="P45" s="76"/>
       <c r="Q45" s="76"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B46" s="59" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
         <v>Norway</v>
@@ -39403,7 +39403,7 @@
       <c r="P46" s="76"/>
       <c r="Q46" s="76"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B47" s="59" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
         <v>Panama</v>
@@ -39431,7 +39431,7 @@
       <c r="P47" s="76"/>
       <c r="Q47" s="76"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B48" s="59" t="str">
         <f>VLOOKUP("Ivory Coast",T,lang,FALSE)</f>
         <v>Ivory Coast</v>
@@ -39455,7 +39455,7 @@
       <c r="P48" s="76"/>
       <c r="Q48" s="76"/>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B49" s="59" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
         <v>Sweden</v>
@@ -39479,7 +39479,7 @@
       <c r="P49" s="76"/>
       <c r="Q49" s="76"/>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B50" s="59" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
         <v>Paraguay</v>
@@ -39503,7 +39503,7 @@
       <c r="P50" s="76"/>
       <c r="Q50" s="76"/>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B51" s="59" t="str">
         <f>VLOOKUP("Czech Republic",T,lang,FALSE)</f>
         <v>Czech Republic</v>
@@ -39527,7 +39527,7 @@
       <c r="P51" s="76"/>
       <c r="Q51" s="76"/>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B52" s="59" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
         <v>Scotland</v>
@@ -39551,7 +39551,7 @@
       <c r="P52" s="76"/>
       <c r="Q52" s="76"/>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B53" s="59" t="str">
         <f>VLOOKUP("Tunisia",T,lang,FALSE)</f>
         <v>Tunisia</v>
@@ -39575,7 +39575,7 @@
       <c r="P53" s="76"/>
       <c r="Q53" s="76"/>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B54" s="59" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
         <v>DR Congo</v>
@@ -39599,7 +39599,7 @@
       <c r="P54" s="76"/>
       <c r="Q54" s="76"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B55" s="59" t="str">
         <f>VLOOKUP("Uzbekistan",T,lang,FALSE)</f>
         <v>Uzbekistan</v>
@@ -39623,7 +39623,7 @@
       <c r="P55" s="76"/>
       <c r="Q55" s="76"/>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B56" s="59" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
         <v>Qatar</v>
@@ -39647,7 +39647,7 @@
       <c r="P56" s="76"/>
       <c r="Q56" s="76"/>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B57" s="59" t="str">
         <f>VLOOKUP("Iraq",T,lang,FALSE)</f>
         <v>Iraq</v>
@@ -39671,7 +39671,7 @@
       <c r="P57" s="76"/>
       <c r="Q57" s="76"/>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B58" s="59" t="str">
         <f>VLOOKUP("South Africa",T,lang,FALSE)</f>
         <v>South Africa</v>
@@ -39695,7 +39695,7 @@
       <c r="P58" s="76"/>
       <c r="Q58" s="76"/>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B59" s="59" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
         <v>Saudi Arabia</v>
@@ -39719,7 +39719,7 @@
       <c r="P59" s="76"/>
       <c r="Q59" s="76"/>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B60" s="59" t="str">
         <f>VLOOKUP("Jordan",T,lang,FALSE)</f>
         <v>Jordan</v>
@@ -39743,7 +39743,7 @@
       <c r="P60" s="76"/>
       <c r="Q60" s="76"/>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B61" s="59" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
         <v>Bosnia and Herzegovina</v>
@@ -39767,7 +39767,7 @@
       <c r="P61" s="76"/>
       <c r="Q61" s="76"/>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B62" s="59" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
         <v>Cape Verde</v>
@@ -39791,7 +39791,7 @@
       <c r="P62" s="76"/>
       <c r="Q62" s="76"/>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B63" s="59" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
         <v>Ghana</v>
@@ -39815,7 +39815,7 @@
       <c r="P63" s="76"/>
       <c r="Q63" s="76"/>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B64" s="59" t="str">
         <f>VLOOKUP("Curaçao",T,lang,FALSE)</f>
         <v>Curaçao</v>
@@ -39839,7 +39839,7 @@
       <c r="P64" s="76"/>
       <c r="Q64" s="76"/>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B65" s="59" t="str">
         <f>VLOOKUP("Haiti",T,lang,FALSE)</f>
         <v>Haiti</v>
@@ -39866,7 +39866,7 @@
       <c r="P65" s="76"/>
       <c r="Q65" s="76"/>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B66" s="59" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
         <v>New Zealand</v>
@@ -39888,7 +39888,7 @@
       <c r="P66" s="76"/>
       <c r="Q66" s="76"/>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B67" s="51"/>
       <c r="C67" s="52"/>
       <c r="D67" s="53"/>
@@ -39905,7 +39905,7 @@
       <c r="P67" s="76"/>
       <c r="Q67" s="76"/>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F68" s="76"/>
       <c r="G68" s="76"/>
       <c r="H68" s="76"/>
@@ -39919,7 +39919,7 @@
       <c r="P68" s="76"/>
       <c r="Q68" s="76"/>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F69" s="76"/>
       <c r="G69" s="76"/>
       <c r="H69" s="76"/>
@@ -39933,7 +39933,7 @@
       <c r="P69" s="76"/>
       <c r="Q69" s="76"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F70" s="76"/>
       <c r="G70" s="76"/>
       <c r="H70" s="76"/>
@@ -39947,7 +39947,7 @@
       <c r="P70" s="76"/>
       <c r="Q70" s="76"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F71" s="76"/>
       <c r="G71" s="76"/>
       <c r="H71" s="76"/>
@@ -39961,7 +39961,7 @@
       <c r="P71" s="76"/>
       <c r="Q71" s="76"/>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F72" s="76"/>
       <c r="G72" s="76"/>
       <c r="H72" s="76"/>
@@ -40011,81 +40011,81 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CR111"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" style="5" customWidth="1"/>
-    <col min="6" max="7" width="4.28515625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="3.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="8" customWidth="1"/>
-    <col min="11" max="14" width="5.42578125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="7.7109375" style="9" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" style="9" customWidth="1"/>
-    <col min="17" max="17" width="3.42578125" style="68" customWidth="1"/>
-    <col min="18" max="18" width="15.42578125" style="123" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="22.54296875" style="5" customWidth="1"/>
+    <col min="6" max="7" width="4.26953125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="22.54296875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="3.453125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" style="8" customWidth="1"/>
+    <col min="11" max="14" width="5.453125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="7.7265625" style="9" customWidth="1"/>
+    <col min="16" max="16" width="6.7265625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="3.453125" style="68" customWidth="1"/>
+    <col min="18" max="18" width="15.453125" style="123" hidden="1" customWidth="1"/>
     <col min="19" max="20" width="16" style="127" hidden="1" customWidth="1"/>
     <col min="21" max="28" width="4" style="123" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" style="124" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.42578125" style="123" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="124" hidden="1" customWidth="1"/>
-    <col min="32" max="36" width="5.42578125" style="123" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="4.26953125" style="124" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.453125" style="124" hidden="1" customWidth="1"/>
+    <col min="32" max="36" width="5.453125" style="123" hidden="1" customWidth="1"/>
     <col min="37" max="39" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="5.42578125" style="123" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="5.453125" style="123" hidden="1" customWidth="1"/>
     <col min="41" max="42" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="7.140625" style="125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="7.1796875" style="125" hidden="1" customWidth="1"/>
     <col min="44" max="44" width="10" style="125" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="15.28515625" style="125" hidden="1" customWidth="1"/>
-    <col min="46" max="50" width="4.7109375" style="126" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" style="125" hidden="1" customWidth="1"/>
-    <col min="52" max="61" width="9.140625" style="126" hidden="1" customWidth="1"/>
-    <col min="62" max="62" width="9.140625" style="112" hidden="1" customWidth="1"/>
-    <col min="63" max="63" width="3.28515625" style="2" customWidth="1"/>
-    <col min="64" max="64" width="19.7109375" style="2" customWidth="1"/>
+    <col min="45" max="45" width="15.26953125" style="125" hidden="1" customWidth="1"/>
+    <col min="46" max="50" width="4.7265625" style="126" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="9.1796875" style="125" hidden="1" customWidth="1"/>
+    <col min="52" max="61" width="9.1796875" style="126" hidden="1" customWidth="1"/>
+    <col min="62" max="62" width="9.1796875" style="112" hidden="1" customWidth="1"/>
+    <col min="63" max="63" width="3.26953125" style="2" customWidth="1"/>
+    <col min="64" max="64" width="19.7265625" style="2" customWidth="1"/>
     <col min="65" max="67" width="3" style="2" customWidth="1"/>
     <col min="68" max="69" width="2" style="111" customWidth="1"/>
-    <col min="70" max="70" width="3.28515625" style="2" customWidth="1"/>
-    <col min="71" max="71" width="19.7109375" style="2" customWidth="1"/>
+    <col min="70" max="70" width="3.26953125" style="2" customWidth="1"/>
+    <col min="71" max="71" width="19.7265625" style="2" customWidth="1"/>
     <col min="72" max="74" width="3" style="2" customWidth="1"/>
     <col min="75" max="76" width="2" style="111" customWidth="1"/>
     <col min="77" max="77" width="4" style="2" customWidth="1"/>
-    <col min="78" max="78" width="19.7109375" style="2" customWidth="1"/>
+    <col min="78" max="78" width="19.7265625" style="2" customWidth="1"/>
     <col min="79" max="81" width="3" style="2" customWidth="1"/>
     <col min="82" max="83" width="2" style="111" customWidth="1"/>
-    <col min="84" max="84" width="3.85546875" style="2" customWidth="1"/>
-    <col min="85" max="85" width="19.7109375" style="2" customWidth="1"/>
+    <col min="84" max="84" width="3.81640625" style="2" customWidth="1"/>
+    <col min="85" max="85" width="19.7265625" style="2" customWidth="1"/>
     <col min="86" max="88" width="3" style="2" customWidth="1"/>
     <col min="89" max="90" width="2" style="111" customWidth="1"/>
-    <col min="91" max="91" width="3.7109375" style="2" customWidth="1"/>
-    <col min="92" max="92" width="19.7109375" style="2" customWidth="1"/>
+    <col min="91" max="91" width="3.7265625" style="2" customWidth="1"/>
+    <col min="92" max="92" width="19.7265625" style="2" customWidth="1"/>
     <col min="93" max="95" width="3" style="2" customWidth="1"/>
     <col min="96" max="96" width="2" style="111" customWidth="1"/>
-    <col min="97" max="16384" width="9.140625" style="2"/>
+    <col min="97" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="str" cm="1">
+    <row r="1" spans="1:95" ht="46" x14ac:dyDescent="0.35">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40101,7 +40101,7 @@
       <c r="AW1" s="125"/>
       <c r="AX1" s="125"/>
     </row>
-    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S2" s="123"/>
       <c r="T2" s="123"/>
       <c r="AC2" s="123"/>
@@ -40117,7 +40117,7 @@
       <c r="AW2" s="125"/>
       <c r="AX2" s="125"/>
     </row>
-    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40152,45 +40152,45 @@
       <c r="AW3" s="125"/>
       <c r="AX3" s="125"/>
     </row>
-    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="str" cm="1">
+    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
-    </row>
-    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
+    </row>
+    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,39 +40300,39 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
-    </row>
-    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
+    </row>
+    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -40407,28 +40407,28 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
-    </row>
-    <row r="8" spans="1:95" x14ac:dyDescent="0.25">
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
+    </row>
+    <row r="8" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A8" s="16">
         <v>2</v>
       </c>
@@ -40448,8 +40448,12 @@
         <f>AE10</f>
         <v>Korea Republic</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
+      <c r="F8" s="19">
+        <v>2</v>
+      </c>
+      <c r="G8" s="20">
+        <v>1</v>
+      </c>
       <c r="H8" s="80" t="str">
         <f>AE11</f>
         <v>Czech Republic</v>
@@ -40488,11 +40492,11 @@
       </c>
       <c r="S8" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Korea Republic_win</v>
       </c>
       <c r="T8" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Czech Republic_lose</v>
       </c>
       <c r="U8" s="123">
         <f t="shared" ref="U8:U71" si="8">IF(S8="",0,IF(VLOOKUP(E8,$AE$8:$AN$77,10,FALSE)=VLOOKUP(H8,$AE$8:$AN$77,10,FALSE),1,0))</f>
@@ -40522,9 +40526,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB8" s="123" t="str">
+      <c r="AB8" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD8" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR8))</f>
@@ -40671,7 +40675,7 @@
       <c r="CP8" s="21"/>
       <c r="CQ8" s="21"/>
     </row>
-    <row r="9" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A9" s="16">
         <v>3</v>
       </c>
@@ -40932,7 +40936,7 @@
       <c r="CP9" s="21"/>
       <c r="CQ9" s="21"/>
     </row>
-    <row r="10" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A10" s="16">
         <v>4</v>
       </c>
@@ -40964,11 +40968,11 @@
       </c>
       <c r="K10" s="23">
         <f>L10+M10+N10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="23">
         <f>VLOOKUP(2,AD8:AN11,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="23">
         <f>VLOOKUP(2,AD8:AN11,4,FALSE)</f>
@@ -40980,11 +40984,11 @@
       </c>
       <c r="O10" s="23" t="str">
         <f>VLOOKUP(2,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD8:AN11,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 1</v>
       </c>
       <c r="P10" s="34">
         <f>L10*3+M10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10" s="123">
         <f>DATE(2026,6,12)+TIME(14,0,0)+gmt_delta</f>
@@ -41040,7 +41044,7 @@
       </c>
       <c r="AF10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_draw")</f>
@@ -41052,31 +41056,31 @@
       </c>
       <c r="AI10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE10,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE10,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL10" s="123">
         <f>AI10-AJ10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" s="123">
         <f>AL10-AL12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN10" s="123">
         <f>AF10*3+AG10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO10" s="123">
         <f>AN10/AN12*10+BA10</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP10" s="123">
         <f>AO10*10000000+BI10*100+AM10/AM12*10+AI10/AI12*1++IF(AQ10=0,ROW(),AQ10)/2000000</f>
-        <v>4.0007943299999997</v>
+        <v>75000006.667461008</v>
       </c>
       <c r="AQ10" s="126">
         <f>VLOOKUP(AE10,db_fifarank,2,FALSE)</f>
@@ -41084,7 +41088,7 @@
       </c>
       <c r="AR10" s="125">
         <f>AP10/AP12</f>
-        <v>5.3343917523963915E-8</v>
+        <v>0.9999999599993894</v>
       </c>
       <c r="AT10" s="126" cm="1">
         <f t="array" ref="AT10">SUMPRODUCT(($S$7:$S$78=AE10&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE10&amp;"_win")*($U$7:$U$78))</f>
@@ -41150,7 +41154,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41191,7 +41195,7 @@
       <c r="CP10" s="21"/>
       <c r="CQ10" s="21"/>
     </row>
-    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16">
         <v>5</v>
       </c>
@@ -41223,7 +41227,7 @@
       </c>
       <c r="K11" s="23">
         <f>L11+M11+N11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="23">
         <f>VLOOKUP(3,AD8:AN11,3,FALSE)</f>
@@ -41235,11 +41239,11 @@
       </c>
       <c r="N11" s="23">
         <f>VLOOKUP(3,AD8:AN11,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="23" t="str">
         <f>VLOOKUP(3,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD8:AN11,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P11" s="34">
         <f>L11*3+M11</f>
@@ -41307,23 +41311,23 @@
       </c>
       <c r="AH11" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE11 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE11,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE11,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL11" s="123">
         <f>AI11-AJ11</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM11" s="123">
         <f>AL11-AL12</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN11" s="123">
         <f>AF11*3+AG11</f>
@@ -41335,7 +41339,7 @@
       </c>
       <c r="AP11" s="123">
         <f>AO11*10000000+BI11*100+AM11/AM12*10+AI11/AI12*1++IF(AQ11=0,ROW(),AQ11)/2000000</f>
-        <v>4.0007506900000003</v>
+        <v>2.3340840233333333</v>
       </c>
       <c r="AQ11" s="126">
         <f>VLOOKUP(AE11,db_fifarank,2,FALSE)</f>
@@ -41343,7 +41347,7 @@
       </c>
       <c r="AR11" s="125">
         <f>AP11/AP12</f>
-        <v>5.3343335657372259E-8</v>
+        <v>3.1121116299596237E-8</v>
       </c>
       <c r="AT11" s="126" cm="1">
         <f t="array" ref="AT11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_win")*($U$7:$U$78))</f>
@@ -41409,7 +41413,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41454,7 +41458,7 @@
       <c r="CP11" s="21"/>
       <c r="CQ11" s="21"/>
     </row>
-    <row r="12" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A12" s="16">
         <v>6</v>
       </c>
@@ -41643,7 +41647,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41677,7 +41681,7 @@
       <c r="CP12" s="21"/>
       <c r="CQ12" s="21"/>
     </row>
-    <row r="13" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A13" s="16">
         <v>7</v>
       </c>
@@ -41760,7 +41764,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -41792,7 +41796,7 @@
       <c r="CP13" s="21"/>
       <c r="CQ13" s="21"/>
     </row>
-    <row r="14" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A14" s="16">
         <v>8</v>
       </c>
@@ -42014,7 +42018,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42055,7 +42059,7 @@
       <c r="CP14" s="21"/>
       <c r="CQ14" s="21"/>
     </row>
-    <row r="15" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A15" s="16">
         <v>9</v>
       </c>
@@ -42277,7 +42281,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42315,7 +42319,7 @@
       <c r="CH15" s="21"/>
       <c r="CI15" s="21"/>
     </row>
-    <row r="16" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A16" s="16">
         <v>10</v>
       </c>
@@ -42547,7 +42551,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42567,7 +42571,7 @@
       <c r="CH16" s="21"/>
       <c r="CI16" s="21"/>
     </row>
-    <row r="17" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A17" s="16">
         <v>11</v>
       </c>
@@ -42805,7 +42809,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -42823,7 +42827,7 @@
       <c r="CH17" s="21"/>
       <c r="CI17" s="21"/>
     </row>
-    <row r="18" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A18" s="16">
         <v>12</v>
       </c>
@@ -43005,7 +43009,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43039,7 +43043,7 @@
       <c r="CH18" s="21"/>
       <c r="CI18" s="21"/>
     </row>
-    <row r="19" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A19" s="16">
         <v>13</v>
       </c>
@@ -43109,7 +43113,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43154,7 +43158,7 @@
       <c r="CP19" s="21"/>
       <c r="CQ19" s="21"/>
     </row>
-    <row r="20" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A20" s="16">
         <v>14</v>
       </c>
@@ -43383,7 +43387,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43417,7 +43421,7 @@
       <c r="CP20" s="21"/>
       <c r="CQ20" s="21"/>
     </row>
-    <row r="21" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A21" s="16">
         <v>15</v>
       </c>
@@ -43652,7 +43656,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43684,7 +43688,7 @@
       <c r="CP21" s="21"/>
       <c r="CQ21" s="21"/>
     </row>
-    <row r="22" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A22" s="16">
         <v>16</v>
       </c>
@@ -43902,7 +43906,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -43944,7 +43948,7 @@
         <v>46217.791666666672</v>
       </c>
     </row>
-    <row r="23" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A23" s="16">
         <v>17</v>
       </c>
@@ -44162,7 +44166,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44189,7 +44193,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44204,7 +44208,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A24" s="16">
         <v>18</v>
       </c>
@@ -44406,7 +44410,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44419,7 +44423,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A25" s="16">
         <v>19</v>
       </c>
@@ -44529,7 +44533,7 @@
       <c r="CP25" s="21"/>
       <c r="CQ25" s="21"/>
     </row>
-    <row r="26" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A26" s="16">
         <v>20</v>
       </c>
@@ -44751,7 +44755,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -44793,7 +44797,7 @@
       <c r="CP26" s="21"/>
       <c r="CQ26" s="21"/>
     </row>
-    <row r="27" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A27" s="16">
         <v>21</v>
       </c>
@@ -45015,7 +45019,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45061,7 +45065,7 @@
       <c r="CP27" s="21"/>
       <c r="CQ27" s="21"/>
     </row>
-    <row r="28" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A28" s="16">
         <v>22</v>
       </c>
@@ -45286,7 +45290,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45316,7 +45320,7 @@
       <c r="CK28" s="114"/>
       <c r="CL28" s="112"/>
     </row>
-    <row r="29" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A29" s="16">
         <v>23</v>
       </c>
@@ -45547,7 +45551,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45575,7 +45579,7 @@
       <c r="CK29" s="114"/>
       <c r="CL29" s="112"/>
     </row>
-    <row r="30" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A30" s="16">
         <v>24</v>
       </c>
@@ -45757,7 +45761,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45794,7 +45798,7 @@
       <c r="CK30" s="114"/>
       <c r="CL30" s="112"/>
     </row>
-    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16">
         <v>25</v>
       </c>
@@ -45864,7 +45868,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -45900,7 +45904,7 @@
       <c r="CK31" s="114"/>
       <c r="CL31" s="112"/>
     </row>
-    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16">
         <v>26</v>
       </c>
@@ -46136,7 +46140,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46154,7 +46158,7 @@
       <c r="CK32" s="114"/>
       <c r="CL32" s="112"/>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A33" s="16">
         <v>27</v>
       </c>
@@ -46396,7 +46400,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46411,16 +46415,16 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
-    </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.25">
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
+    </row>
+    <row r="34" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A34" s="16">
         <v>28</v>
       </c>
@@ -46638,7 +46642,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46669,13 +46673,13 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
-    </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.25">
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
+    </row>
+    <row r="35" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A35" s="16">
         <v>29</v>
       </c>
@@ -46893,7 +46897,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -46929,7 +46933,7 @@
       <c r="CK35" s="114"/>
       <c r="CL35" s="112"/>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A36" s="16">
         <v>30</v>
       </c>
@@ -47118,7 +47122,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47155,7 +47159,7 @@
         <v>46222.791666666672</v>
       </c>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A37" s="16">
         <v>31</v>
       </c>
@@ -47238,7 +47242,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47265,7 +47269,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47280,7 +47284,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A38" s="16">
         <v>32</v>
       </c>
@@ -47502,7 +47506,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47532,7 +47536,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47545,7 +47549,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A39" s="16">
         <v>33</v>
       </c>
@@ -47767,7 +47771,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -47800,7 +47804,7 @@
       <c r="CP39" s="21"/>
       <c r="CQ39" s="21"/>
     </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A40" s="16">
         <v>34</v>
       </c>
@@ -48021,7 +48025,7 @@
       <c r="CK40" s="114"/>
       <c r="CL40" s="112"/>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A41" s="16">
         <v>35</v>
       </c>
@@ -48261,7 +48265,7 @@
       <c r="CK41" s="114"/>
       <c r="CL41" s="112"/>
     </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A42" s="16">
         <v>36</v>
       </c>
@@ -48443,7 +48447,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48466,7 +48470,7 @@
       <c r="BW42" s="112"/>
       <c r="CK42" s="114"/>
     </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A43" s="16">
         <v>37</v>
       </c>
@@ -48536,7 +48540,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48563,7 +48567,7 @@
       </c>
       <c r="CK43" s="114"/>
     </row>
-    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="16">
         <v>38</v>
       </c>
@@ -48792,7 +48796,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48807,16 +48811,16 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
-    </row>
-    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
+    </row>
+    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="16">
         <v>39</v>
       </c>
@@ -49051,7 +49055,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49064,13 +49068,13 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
-    </row>
-    <row r="46" spans="1:96" x14ac:dyDescent="0.25">
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
+    </row>
+    <row r="46" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A46" s="16">
         <v>40</v>
       </c>
@@ -49288,7 +49292,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="141">
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49312,7 +49316,7 @@
       <c r="CK46" s="114"/>
       <c r="CL46" s="112"/>
     </row>
-    <row r="47" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A47" s="16">
         <v>41</v>
       </c>
@@ -49530,7 +49534,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="142"/>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49577,7 +49581,7 @@
         <v>46221.875</v>
       </c>
     </row>
-    <row r="48" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A48" s="16">
         <v>42</v>
       </c>
@@ -49773,7 +49777,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49789,7 +49793,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49804,7 +49808,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A49" s="16">
         <v>43</v>
       </c>
@@ -49894,7 +49898,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49908,7 +49912,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -49921,7 +49925,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A50" s="16">
         <v>44</v>
       </c>
@@ -50143,7 +50147,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50174,7 +50178,7 @@
       <c r="CK50" s="114"/>
       <c r="CL50" s="112"/>
     </row>
-    <row r="51" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A51" s="16">
         <v>45</v>
       </c>
@@ -50396,7 +50400,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50431,7 +50435,7 @@
       <c r="CK51" s="114"/>
       <c r="CL51" s="112"/>
     </row>
-    <row r="52" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A52" s="16">
         <v>46</v>
       </c>
@@ -50656,7 +50660,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50680,7 +50684,7 @@
       <c r="CK52" s="114"/>
       <c r="CL52" s="112"/>
     </row>
-    <row r="53" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A53" s="16">
         <v>47</v>
       </c>
@@ -50911,7 +50915,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -50933,7 +50937,7 @@
       <c r="CK53" s="114"/>
       <c r="CL53" s="112"/>
     </row>
-    <row r="54" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A54" s="16">
         <v>48</v>
       </c>
@@ -51115,7 +51119,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51158,7 +51162,7 @@
       </c>
       <c r="CL54" s="112"/>
     </row>
-    <row r="55" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A55" s="16">
         <v>49</v>
       </c>
@@ -51236,7 +51240,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51263,7 +51267,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51279,7 +51283,7 @@
       </c>
       <c r="CL55" s="112"/>
     </row>
-    <row r="56" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A56" s="16">
         <v>50</v>
       </c>
@@ -51522,7 +51526,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -51536,7 +51540,7 @@
       </c>
       <c r="CL56" s="112"/>
     </row>
-    <row r="57" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A57" s="16">
         <v>51</v>
       </c>
@@ -51786,7 +51790,7 @@
       <c r="CC57" s="21"/>
       <c r="CD57" s="114"/>
     </row>
-    <row r="58" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A58" s="16">
         <v>52</v>
       </c>
@@ -52005,7 +52009,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52034,7 +52038,7 @@
       <c r="CC58" s="21"/>
       <c r="CD58" s="114"/>
     </row>
-    <row r="59" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A59" s="16">
         <v>53</v>
       </c>
@@ -52253,7 +52257,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52286,7 +52290,7 @@
       <c r="CC59" s="21"/>
       <c r="CD59" s="114"/>
     </row>
-    <row r="60" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A60" s="16">
         <v>54</v>
       </c>
@@ -52476,7 +52480,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52498,7 +52502,7 @@
       <c r="CC60" s="21"/>
       <c r="CD60" s="114"/>
     </row>
-    <row r="61" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A61" s="16">
         <v>55</v>
       </c>
@@ -52589,7 +52593,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52609,7 +52613,7 @@
       <c r="CC61" s="21"/>
       <c r="CD61" s="114"/>
     </row>
-    <row r="62" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A62" s="16">
         <v>56</v>
       </c>
@@ -52832,7 +52836,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -52861,7 +52865,7 @@
       <c r="CC62" s="21"/>
       <c r="CD62" s="114"/>
     </row>
-    <row r="63" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A63" s="16">
         <v>57</v>
       </c>
@@ -53084,7 +53088,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53117,7 +53121,7 @@
         <v>46215.041666666672</v>
       </c>
     </row>
-    <row r="64" spans="1:96" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A64" s="16">
         <v>58</v>
       </c>
@@ -53350,7 +53354,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53365,7 +53369,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A65" s="16">
         <v>59</v>
       </c>
@@ -53604,7 +53608,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53617,7 +53621,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A66" s="16">
         <v>60</v>
       </c>
@@ -53800,7 +53804,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53822,7 +53826,7 @@
       <c r="BV66" s="21"/>
       <c r="BW66" s="114"/>
     </row>
-    <row r="67" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A67" s="16">
         <v>61</v>
       </c>
@@ -53900,7 +53904,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -53926,7 +53930,7 @@
         <v>46210.833333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A68" s="16">
         <v>62</v>
       </c>
@@ -54156,7 +54160,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54170,27 +54174,27 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
-    </row>
-    <row r="69" spans="1:95" x14ac:dyDescent="0.25">
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
+    </row>
+    <row r="69" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A69" s="16">
         <v>63</v>
       </c>
@@ -54426,7 +54430,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54438,21 +54442,21 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
-    </row>
-    <row r="70" spans="1:95" x14ac:dyDescent="0.25">
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
+    </row>
+    <row r="70" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A70" s="16">
         <v>64</v>
       </c>
@@ -54671,7 +54675,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54688,7 +54692,7 @@
       <c r="BQ70" s="112"/>
       <c r="BW70" s="112"/>
     </row>
-    <row r="71" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A71" s="16">
         <v>65</v>
       </c>
@@ -54907,7 +54911,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -54921,7 +54925,7 @@
       </c>
       <c r="BQ71" s="112"/>
     </row>
-    <row r="72" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A72" s="16">
         <v>66</v>
       </c>
@@ -55105,7 +55109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A73" s="16">
         <v>67</v>
       </c>
@@ -55184,7 +55188,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A74" s="16">
         <v>68</v>
       </c>
@@ -55408,7 +55412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A75" s="16">
         <v>69</v>
       </c>
@@ -55632,7 +55636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A76" s="16">
         <v>70</v>
       </c>
@@ -55852,7 +55856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A77" s="16">
         <v>71</v>
       </c>
@@ -56072,7 +56076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A78" s="16">
         <v>72</v>
       </c>
@@ -56256,7 +56260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A79" s="73"/>
       <c r="B79" s="73"/>
       <c r="C79" s="73"/>
@@ -56274,7 +56278,7 @@
       <c r="O79" s="70"/>
       <c r="P79" s="70"/>
     </row>
-    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="73"/>
       <c r="B80" s="73"/>
       <c r="C80" s="73"/>
@@ -56314,7 +56318,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56330,22 +56334,22 @@
       </c>
       <c r="AH80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK80" s="123" t="s">
         <v>3180</v>
       </c>
       <c r="AL80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
@@ -56357,7 +56361,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>7.5069000000000004E-4</v>
+        <v>50.000750689999997</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -56365,18 +56369,18 @@
       </c>
       <c r="AR80" s="125" t="str">
         <f>IF(AD80&lt;=8,RIGHT(AK80,1),"")</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="AS80" s="129" t="str">
         <f>IF(AD80&lt;=8,AE80,"")</f>
-        <v>Czech Republic</v>
+        <v/>
       </c>
       <c r="AT80" s="130" t="str">
         <f>"Ⓐ "&amp;AE80</f>
         <v>Ⓐ Czech Republic</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="73"/>
       <c r="B81" s="73"/>
       <c r="C81" s="73"/>
@@ -56416,7 +56420,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -56451,7 +56455,7 @@
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
@@ -56459,7 +56463,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>7.2747999999999997E-4</v>
+        <v>500.00072748000002</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -56467,7 +56471,7 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
@@ -56478,7 +56482,7 @@
         <v>Ⓑ Qatar</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="73"/>
       <c r="B82" s="73"/>
       <c r="C82" s="73"/>
@@ -56518,7 +56522,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -56553,7 +56557,7 @@
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
@@ -56561,7 +56565,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>7.4917499999999993E-4</v>
+        <v>500.00074917500001</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -56569,27 +56573,27 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Scotland</v>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
         <v>Ⓒ Scotland</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56657,7 +56661,7 @@
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
@@ -56665,7 +56669,7 @@
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>7.9033500000000008E-4</v>
+        <v>500.00079033499998</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
@@ -56673,7 +56677,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>AD</v>
+        <v>CD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56684,14 +56688,14 @@
         <v>Ⓓ Australia</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56771,7 +56775,7 @@
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
@@ -56779,7 +56783,7 @@
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>7.6648999999999999E-4</v>
+        <v>500.00076648999999</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -56787,7 +56791,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADE</v>
+        <v>CDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56798,14 +56802,14 @@
         <v>Ⓔ Ivory Coast</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -56885,7 +56889,7 @@
       </c>
       <c r="AM85" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
@@ -56893,7 +56897,7 @@
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>7.5738499999999996E-4</v>
+        <v>500.00075738499999</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -56901,7 +56905,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEF</v>
+        <v>CDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56912,14 +56916,14 @@
         <v>Ⓕ Sweden</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -56999,7 +57003,7 @@
       </c>
       <c r="AM86" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
@@ -57007,7 +57011,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>7.8162000000000001E-4</v>
+        <v>500.00078162</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57015,7 +57019,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFG</v>
+        <v>CDEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57026,14 +57030,14 @@
         <v>Ⓖ Egypt</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57078,7 +57082,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -57113,7 +57117,7 @@
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
@@ -57121,7 +57125,7 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>7.10715E-4</v>
+        <v>500.00071071500003</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
@@ -57129,7 +57133,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFG</v>
+        <v>CDEFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57140,19 +57144,19 @@
         <v>Ⓗ Saudi Arabia</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57227,7 +57231,7 @@
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -57235,7 +57239,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>7.7547E-4</v>
+        <v>500.00077547000001</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -57243,7 +57247,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGI</v>
+        <v>CDEFGI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57254,7 +57258,7 @@
         <v>Ⓘ Norway</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="73"/>
       <c r="B89" s="73"/>
       <c r="C89" s="73"/>
@@ -57266,7 +57270,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57341,7 +57345,7 @@
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -57349,7 +57353,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>7.8213000000000002E-4</v>
+        <v>500.00078213</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -57357,7 +57361,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGIJ</v>
+        <v>CDEFGIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57368,7 +57372,7 @@
         <v>Ⓙ Algeria</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="73"/>
       <c r="B90" s="73"/>
       <c r="C90" s="73"/>
@@ -57380,7 +57384,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -57420,7 +57424,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57455,7 +57459,7 @@
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
@@ -57463,7 +57467,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>7.391749999999999E-4</v>
+        <v>500.00073917499998</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -57471,7 +57475,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGIJ</v>
+        <v>CDEFGIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57482,7 +57486,7 @@
         <v>Ⓚ DR Congo</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="73"/>
       <c r="B91" s="73"/>
       <c r="C91" s="73"/>
@@ -57494,7 +57498,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓗ Saudi Arabia</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -57569,7 +57573,7 @@
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57577,7 +57581,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>7.7032000000000001E-4</v>
+        <v>500.00077032000002</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -57585,7 +57589,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGIJL</v>
+        <v>CDEFGIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57596,7 +57600,7 @@
         <v>Ⓛ Panama</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="73"/>
       <c r="B92" s="73"/>
       <c r="C92" s="73"/>
@@ -57608,11 +57612,11 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,3,FALSE)</f>
@@ -57624,11 +57628,11 @@
       </c>
       <c r="N92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
@@ -57644,23 +57648,23 @@
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
@@ -57671,7 +57675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A93" s="73"/>
       <c r="B93" s="73"/>
       <c r="C93" s="73"/>
@@ -57689,7 +57693,7 @@
       <c r="O93" s="70"/>
       <c r="P93" s="70"/>
     </row>
-    <row r="95" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:46" x14ac:dyDescent="0.35">
       <c r="R95" s="123">
         <f>DATE(2026,12,9)+TIME(8,0,0)+gmt_delta</f>
         <v>46365.791666666672</v>
@@ -57703,7 +57707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="R96" s="123">
         <f>DATE(2026,12,9)+TIME(4,0,0)+gmt_delta</f>
         <v>46365.625</v>
@@ -57717,7 +57721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="R97" s="123">
         <f>DATE(2026,12,10)+TIME(8,0,0)+gmt_delta</f>
         <v>46366.791666666672</v>
@@ -57731,7 +57735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="18:29" x14ac:dyDescent="0.25">
+    <row r="98" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R98" s="123">
         <f>DATE(2026,12,10)+TIME(4,0,0)+gmt_delta</f>
         <v>46366.625</v>
@@ -57745,7 +57749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="18:29" x14ac:dyDescent="0.25">
+    <row r="102" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R102" s="123">
         <f>DATE(2026,12,13)+TIME(8,0,0)+gmt_delta</f>
         <v>46369.791666666672</v>
@@ -57771,7 +57775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="18:29" x14ac:dyDescent="0.25">
+    <row r="103" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R103" s="123">
         <f>DATE(2026,12,14)+TIME(8,0,0)+gmt_delta</f>
         <v>46370.791666666672</v>
@@ -57797,7 +57801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="18:29" x14ac:dyDescent="0.25">
+    <row r="107" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R107" s="123">
         <f>DATE(2026,12,17)+TIME(8,0,0)+gmt_delta</f>
         <v>46373.791666666672</v>
@@ -57807,7 +57811,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="18:29" x14ac:dyDescent="0.25">
+    <row r="111" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R111" s="123">
         <f>DATE(2026,12,18)+TIME(8,0,0)+gmt_delta</f>
         <v>46374.791666666672</v>
@@ -57824,11 +57828,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57844,31 +57868,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -58893,33 +58897,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A2A316-429C-49FB-9962-F944380EA825}">
   <dimension ref="B1:K500"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="81"/>
-    <col min="3" max="3" width="13.7109375" style="81" customWidth="1"/>
-    <col min="4" max="11" width="9.42578125" style="81" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="82"/>
+    <col min="1" max="1" width="2.453125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="81"/>
+    <col min="3" max="3" width="13.7265625" style="81" customWidth="1"/>
+    <col min="4" max="11" width="9.453125" style="81" customWidth="1"/>
+    <col min="12" max="16384" width="9.1796875" style="82"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.35">
       <c r="B2" s="108" t="s">
         <v>3193</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ADEFGIJL</v>
+        <v>CDEFGIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3E</v>
+        <v>3C</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -58927,7 +58931,7 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3J</v>
+        <v>3E</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
@@ -58935,7 +58939,7 @@
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
-        <v>3A</v>
+        <v>3J</v>
       </c>
       <c r="I3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,7,FALSE)</f>
@@ -58950,7 +58954,7 @@
         <v>3I</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="84" t="s">
         <v>3194</v>
       </c>
@@ -58980,7 +58984,7 @@
         <v>3202</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B6" s="88">
         <v>1</v>
       </c>
@@ -59012,7 +59016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B7" s="88">
         <v>2</v>
       </c>
@@ -59044,7 +59048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B8" s="88">
         <v>3</v>
       </c>
@@ -59076,7 +59080,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B9" s="88">
         <v>4</v>
       </c>
@@ -59108,7 +59112,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B10" s="88">
         <v>5</v>
       </c>
@@ -59140,7 +59144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B11" s="88">
         <v>6</v>
       </c>
@@ -59172,7 +59176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B12" s="88">
         <v>7</v>
       </c>
@@ -59204,7 +59208,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B13" s="88">
         <v>8</v>
       </c>
@@ -59236,7 +59240,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B14" s="88">
         <v>9</v>
       </c>
@@ -59268,7 +59272,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B15" s="88">
         <v>10</v>
       </c>
@@ -59300,7 +59304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B16" s="88">
         <v>11</v>
       </c>
@@ -59332,7 +59336,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="88">
         <v>12</v>
       </c>
@@ -59364,7 +59368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B18" s="88">
         <v>13</v>
       </c>
@@ -59396,7 +59400,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B19" s="88">
         <v>14</v>
       </c>
@@ -59428,7 +59432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B20" s="88">
         <v>15</v>
       </c>
@@ -59460,7 +59464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B21" s="88">
         <v>16</v>
       </c>
@@ -59492,7 +59496,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B22" s="88">
         <v>17</v>
       </c>
@@ -59524,7 +59528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B23" s="88">
         <v>18</v>
       </c>
@@ -59556,7 +59560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B24" s="88">
         <v>19</v>
       </c>
@@ -59588,7 +59592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B25" s="88">
         <v>20</v>
       </c>
@@ -59620,7 +59624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B26" s="88">
         <v>21</v>
       </c>
@@ -59652,7 +59656,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B27" s="88">
         <v>22</v>
       </c>
@@ -59684,7 +59688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B28" s="88">
         <v>23</v>
       </c>
@@ -59716,7 +59720,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B29" s="88">
         <v>24</v>
       </c>
@@ -59748,7 +59752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B30" s="88">
         <v>25</v>
       </c>
@@ -59780,7 +59784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B31" s="88">
         <v>26</v>
       </c>
@@ -59812,7 +59816,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B32" s="88">
         <v>27</v>
       </c>
@@ -59844,7 +59848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B33" s="88">
         <v>28</v>
       </c>
@@ -59876,7 +59880,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B34" s="88">
         <v>29</v>
       </c>
@@ -59908,7 +59912,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B35" s="88">
         <v>30</v>
       </c>
@@ -59940,7 +59944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B36" s="88">
         <v>31</v>
       </c>
@@ -59972,7 +59976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B37" s="88">
         <v>32</v>
       </c>
@@ -60004,7 +60008,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B38" s="88">
         <v>33</v>
       </c>
@@ -60036,7 +60040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B39" s="88">
         <v>34</v>
       </c>
@@ -60068,7 +60072,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B40" s="88">
         <v>35</v>
       </c>
@@ -60100,7 +60104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B41" s="88">
         <v>36</v>
       </c>
@@ -60132,7 +60136,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B42" s="88">
         <v>37</v>
       </c>
@@ -60164,7 +60168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B43" s="88">
         <v>38</v>
       </c>
@@ -60196,7 +60200,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B44" s="88">
         <v>39</v>
       </c>
@@ -60228,7 +60232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B45" s="88">
         <v>40</v>
       </c>
@@ -60260,7 +60264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B46" s="88">
         <v>41</v>
       </c>
@@ -60292,7 +60296,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B47" s="88">
         <v>42</v>
       </c>
@@ -60324,7 +60328,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B48" s="88">
         <v>43</v>
       </c>
@@ -60356,7 +60360,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B49" s="88">
         <v>44</v>
       </c>
@@ -60388,7 +60392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B50" s="88">
         <v>45</v>
       </c>
@@ -60420,7 +60424,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B51" s="88">
         <v>46</v>
       </c>
@@ -60452,7 +60456,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B52" s="88">
         <v>47</v>
       </c>
@@ -60484,7 +60488,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B53" s="88">
         <v>48</v>
       </c>
@@ -60516,7 +60520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B54" s="88">
         <v>49</v>
       </c>
@@ -60548,7 +60552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B55" s="88">
         <v>50</v>
       </c>
@@ -60580,7 +60584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B56" s="88">
         <v>51</v>
       </c>
@@ -60612,7 +60616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B57" s="88">
         <v>52</v>
       </c>
@@ -60644,7 +60648,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B58" s="88">
         <v>53</v>
       </c>
@@ -60676,7 +60680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B59" s="88">
         <v>54</v>
       </c>
@@ -60708,7 +60712,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B60" s="88">
         <v>55</v>
       </c>
@@ -60740,7 +60744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B61" s="88">
         <v>56</v>
       </c>
@@ -60772,7 +60776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B62" s="88">
         <v>57</v>
       </c>
@@ -60804,7 +60808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B63" s="88">
         <v>58</v>
       </c>
@@ -60836,7 +60840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B64" s="88">
         <v>59</v>
       </c>
@@ -60868,7 +60872,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B65" s="88">
         <v>60</v>
       </c>
@@ -60900,7 +60904,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B66" s="88">
         <v>61</v>
       </c>
@@ -60932,7 +60936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B67" s="88">
         <v>62</v>
       </c>
@@ -60964,7 +60968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B68" s="88">
         <v>63</v>
       </c>
@@ -60996,7 +61000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B69" s="88">
         <v>64</v>
       </c>
@@ -61028,7 +61032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B70" s="88">
         <v>65</v>
       </c>
@@ -61060,7 +61064,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B71" s="88">
         <v>66</v>
       </c>
@@ -61092,7 +61096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B72" s="88">
         <v>67</v>
       </c>
@@ -61124,7 +61128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B73" s="88">
         <v>68</v>
       </c>
@@ -61156,7 +61160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B74" s="88">
         <v>69</v>
       </c>
@@ -61188,7 +61192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B75" s="88">
         <v>70</v>
       </c>
@@ -61220,7 +61224,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B76" s="88">
         <v>71</v>
       </c>
@@ -61252,7 +61256,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B77" s="88">
         <v>72</v>
       </c>
@@ -61284,7 +61288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B78" s="88">
         <v>73</v>
       </c>
@@ -61316,7 +61320,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B79" s="88">
         <v>74</v>
       </c>
@@ -61348,7 +61352,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B80" s="88">
         <v>75</v>
       </c>
@@ -61380,7 +61384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B81" s="88">
         <v>76</v>
       </c>
@@ -61412,7 +61416,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B82" s="88">
         <v>77</v>
       </c>
@@ -61444,7 +61448,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B83" s="88">
         <v>78</v>
       </c>
@@ -61476,7 +61480,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84" s="88">
         <v>79</v>
       </c>
@@ -61508,7 +61512,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B85" s="88">
         <v>80</v>
       </c>
@@ -61540,7 +61544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B86" s="88">
         <v>81</v>
       </c>
@@ -61572,7 +61576,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87" s="88">
         <v>82</v>
       </c>
@@ -61604,7 +61608,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B88" s="88">
         <v>83</v>
       </c>
@@ -61636,7 +61640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89" s="88">
         <v>84</v>
       </c>
@@ -61668,7 +61672,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B90" s="88">
         <v>85</v>
       </c>
@@ -61700,7 +61704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B91" s="88">
         <v>86</v>
       </c>
@@ -61732,7 +61736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B92" s="88">
         <v>87</v>
       </c>
@@ -61764,7 +61768,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B93" s="88">
         <v>88</v>
       </c>
@@ -61796,7 +61800,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B94" s="88">
         <v>89</v>
       </c>
@@ -61828,7 +61832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B95" s="88">
         <v>90</v>
       </c>
@@ -61860,7 +61864,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B96" s="88">
         <v>91</v>
       </c>
@@ -61892,7 +61896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B97" s="88">
         <v>92</v>
       </c>
@@ -61924,7 +61928,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B98" s="88">
         <v>93</v>
       </c>
@@ -61956,7 +61960,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B99" s="88">
         <v>94</v>
       </c>
@@ -61988,7 +61992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B100" s="88">
         <v>95</v>
       </c>
@@ -62020,7 +62024,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B101" s="88">
         <v>96</v>
       </c>
@@ -62052,7 +62056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B102" s="88">
         <v>97</v>
       </c>
@@ -62084,7 +62088,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B103" s="88">
         <v>98</v>
       </c>
@@ -62116,7 +62120,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B104" s="88">
         <v>99</v>
       </c>
@@ -62148,7 +62152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B105" s="88">
         <v>100</v>
       </c>
@@ -62180,7 +62184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B106" s="88">
         <v>101</v>
       </c>
@@ -62212,7 +62216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B107" s="88">
         <v>102</v>
       </c>
@@ -62244,7 +62248,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B108" s="88">
         <v>103</v>
       </c>
@@ -62276,7 +62280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B109" s="88">
         <v>104</v>
       </c>
@@ -62308,7 +62312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B110" s="88">
         <v>105</v>
       </c>
@@ -62340,7 +62344,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B111" s="88">
         <v>106</v>
       </c>
@@ -62372,7 +62376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B112" s="88">
         <v>107</v>
       </c>
@@ -62404,7 +62408,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B113" s="88">
         <v>108</v>
       </c>
@@ -62436,7 +62440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B114" s="88">
         <v>109</v>
       </c>
@@ -62468,7 +62472,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B115" s="88">
         <v>110</v>
       </c>
@@ -62500,7 +62504,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B116" s="88">
         <v>111</v>
       </c>
@@ -62532,7 +62536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B117" s="88">
         <v>112</v>
       </c>
@@ -62564,7 +62568,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B118" s="88">
         <v>113</v>
       </c>
@@ -62596,7 +62600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B119" s="88">
         <v>114</v>
       </c>
@@ -62628,7 +62632,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B120" s="88">
         <v>115</v>
       </c>
@@ -62660,7 +62664,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B121" s="88">
         <v>116</v>
       </c>
@@ -62692,7 +62696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B122" s="88">
         <v>117</v>
       </c>
@@ -62724,7 +62728,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B123" s="88">
         <v>118</v>
       </c>
@@ -62756,7 +62760,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B124" s="88">
         <v>119</v>
       </c>
@@ -62788,7 +62792,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B125" s="88">
         <v>120</v>
       </c>
@@ -62820,7 +62824,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B126" s="88">
         <v>121</v>
       </c>
@@ -62852,7 +62856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B127" s="88">
         <v>122</v>
       </c>
@@ -62884,7 +62888,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B128" s="88">
         <v>123</v>
       </c>
@@ -62916,7 +62920,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B129" s="88">
         <v>124</v>
       </c>
@@ -62948,7 +62952,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B130" s="88">
         <v>125</v>
       </c>
@@ -62980,7 +62984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B131" s="88">
         <v>126</v>
       </c>
@@ -63012,7 +63016,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B132" s="88">
         <v>127</v>
       </c>
@@ -63044,7 +63048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B133" s="88">
         <v>128</v>
       </c>
@@ -63076,7 +63080,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B134" s="88">
         <v>129</v>
       </c>
@@ -63108,7 +63112,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B135" s="88">
         <v>130</v>
       </c>
@@ -63140,7 +63144,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B136" s="88">
         <v>131</v>
       </c>
@@ -63172,7 +63176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B137" s="88">
         <v>132</v>
       </c>
@@ -63204,7 +63208,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B138" s="88">
         <v>133</v>
       </c>
@@ -63236,7 +63240,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B139" s="88">
         <v>134</v>
       </c>
@@ -63268,7 +63272,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B140" s="88">
         <v>135</v>
       </c>
@@ -63300,7 +63304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B141" s="88">
         <v>136</v>
       </c>
@@ -63332,7 +63336,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B142" s="88">
         <v>137</v>
       </c>
@@ -63364,7 +63368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B143" s="88">
         <v>138</v>
       </c>
@@ -63396,7 +63400,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B144" s="88">
         <v>139</v>
       </c>
@@ -63428,7 +63432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B145" s="88">
         <v>140</v>
       </c>
@@ -63460,7 +63464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B146" s="88">
         <v>141</v>
       </c>
@@ -63492,7 +63496,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B147" s="88">
         <v>142</v>
       </c>
@@ -63524,7 +63528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B148" s="88">
         <v>143</v>
       </c>
@@ -63556,7 +63560,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B149" s="88">
         <v>144</v>
       </c>
@@ -63588,7 +63592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B150" s="88">
         <v>145</v>
       </c>
@@ -63620,7 +63624,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B151" s="88">
         <v>146</v>
       </c>
@@ -63652,7 +63656,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B152" s="88">
         <v>147</v>
       </c>
@@ -63684,7 +63688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B153" s="88">
         <v>148</v>
       </c>
@@ -63716,7 +63720,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B154" s="88">
         <v>149</v>
       </c>
@@ -63748,7 +63752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B155" s="88">
         <v>150</v>
       </c>
@@ -63780,7 +63784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B156" s="88">
         <v>151</v>
       </c>
@@ -63812,7 +63816,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B157" s="88">
         <v>152</v>
       </c>
@@ -63844,7 +63848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B158" s="88">
         <v>153</v>
       </c>
@@ -63876,7 +63880,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B159" s="88">
         <v>154</v>
       </c>
@@ -63908,7 +63912,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B160" s="88">
         <v>155</v>
       </c>
@@ -63940,7 +63944,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B161" s="88">
         <v>156</v>
       </c>
@@ -63972,7 +63976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B162" s="88">
         <v>157</v>
       </c>
@@ -64004,7 +64008,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B163" s="88">
         <v>158</v>
       </c>
@@ -64036,7 +64040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B164" s="88">
         <v>159</v>
       </c>
@@ -64068,7 +64072,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B165" s="88">
         <v>160</v>
       </c>
@@ -64100,7 +64104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B166" s="88">
         <v>161</v>
       </c>
@@ -64132,7 +64136,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B167" s="88">
         <v>162</v>
       </c>
@@ -64164,7 +64168,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B168" s="88">
         <v>163</v>
       </c>
@@ -64196,7 +64200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B169" s="88">
         <v>164</v>
       </c>
@@ -64228,7 +64232,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B170" s="88">
         <v>165</v>
       </c>
@@ -64260,7 +64264,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B171" s="88">
         <v>166</v>
       </c>
@@ -64292,7 +64296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B172" s="88">
         <v>167</v>
       </c>
@@ -64324,7 +64328,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B173" s="88">
         <v>168</v>
       </c>
@@ -64356,7 +64360,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B174" s="88">
         <v>169</v>
       </c>
@@ -64388,7 +64392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B175" s="88">
         <v>170</v>
       </c>
@@ -64420,7 +64424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B176" s="88">
         <v>171</v>
       </c>
@@ -64452,7 +64456,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B177" s="88">
         <v>172</v>
       </c>
@@ -64484,7 +64488,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B178" s="88">
         <v>173</v>
       </c>
@@ -64516,7 +64520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B179" s="88">
         <v>174</v>
       </c>
@@ -64548,7 +64552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B180" s="88">
         <v>175</v>
       </c>
@@ -64580,7 +64584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B181" s="88">
         <v>176</v>
       </c>
@@ -64612,7 +64616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B182" s="88">
         <v>177</v>
       </c>
@@ -64644,7 +64648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B183" s="88">
         <v>178</v>
       </c>
@@ -64676,7 +64680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B184" s="88">
         <v>179</v>
       </c>
@@ -64708,7 +64712,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B185" s="88">
         <v>180</v>
       </c>
@@ -64740,7 +64744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B186" s="88">
         <v>181</v>
       </c>
@@ -64772,7 +64776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B187" s="88">
         <v>182</v>
       </c>
@@ -64804,7 +64808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B188" s="88">
         <v>183</v>
       </c>
@@ -64836,7 +64840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B189" s="88">
         <v>184</v>
       </c>
@@ -64868,7 +64872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B190" s="88">
         <v>185</v>
       </c>
@@ -64900,7 +64904,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B191" s="88">
         <v>186</v>
       </c>
@@ -64932,7 +64936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B192" s="88">
         <v>187</v>
       </c>
@@ -64964,7 +64968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B193" s="88">
         <v>188</v>
       </c>
@@ -64996,7 +65000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B194" s="88">
         <v>189</v>
       </c>
@@ -65028,7 +65032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B195" s="88">
         <v>190</v>
       </c>
@@ -65060,7 +65064,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B196" s="88">
         <v>191</v>
       </c>
@@ -65092,7 +65096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B197" s="88">
         <v>192</v>
       </c>
@@ -65124,7 +65128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B198" s="88">
         <v>193</v>
       </c>
@@ -65156,7 +65160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B199" s="88">
         <v>194</v>
       </c>
@@ -65188,7 +65192,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B200" s="88">
         <v>195</v>
       </c>
@@ -65220,7 +65224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B201" s="88">
         <v>196</v>
       </c>
@@ -65252,7 +65256,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B202" s="88">
         <v>197</v>
       </c>
@@ -65284,7 +65288,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B203" s="88">
         <v>198</v>
       </c>
@@ -65316,7 +65320,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B204" s="88">
         <v>199</v>
       </c>
@@ -65348,7 +65352,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B205" s="88">
         <v>200</v>
       </c>
@@ -65380,7 +65384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B206" s="88">
         <v>201</v>
       </c>
@@ -65412,7 +65416,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B207" s="88">
         <v>202</v>
       </c>
@@ -65444,7 +65448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B208" s="88">
         <v>203</v>
       </c>
@@ -65476,7 +65480,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B209" s="88">
         <v>204</v>
       </c>
@@ -65508,7 +65512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B210" s="88">
         <v>205</v>
       </c>
@@ -65540,7 +65544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B211" s="88">
         <v>206</v>
       </c>
@@ -65572,7 +65576,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B212" s="88">
         <v>207</v>
       </c>
@@ -65604,7 +65608,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B213" s="88">
         <v>208</v>
       </c>
@@ -65636,7 +65640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B214" s="88">
         <v>209</v>
       </c>
@@ -65668,7 +65672,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B215" s="88">
         <v>210</v>
       </c>
@@ -65700,7 +65704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B216" s="88">
         <v>211</v>
       </c>
@@ -65732,7 +65736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B217" s="88">
         <v>212</v>
       </c>
@@ -65764,7 +65768,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B218" s="88">
         <v>213</v>
       </c>
@@ -65796,7 +65800,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B219" s="88">
         <v>214</v>
       </c>
@@ -65828,7 +65832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B220" s="88">
         <v>215</v>
       </c>
@@ -65860,7 +65864,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B221" s="88">
         <v>216</v>
       </c>
@@ -65892,7 +65896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B222" s="88">
         <v>217</v>
       </c>
@@ -65924,7 +65928,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B223" s="88">
         <v>218</v>
       </c>
@@ -65956,7 +65960,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B224" s="88">
         <v>219</v>
       </c>
@@ -65988,7 +65992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B225" s="88">
         <v>220</v>
       </c>
@@ -66020,7 +66024,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B226" s="88">
         <v>221</v>
       </c>
@@ -66052,7 +66056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B227" s="88">
         <v>222</v>
       </c>
@@ -66084,7 +66088,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B228" s="88">
         <v>223</v>
       </c>
@@ -66116,7 +66120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B229" s="88">
         <v>224</v>
       </c>
@@ -66148,7 +66152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B230" s="88">
         <v>225</v>
       </c>
@@ -66180,7 +66184,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B231" s="88">
         <v>226</v>
       </c>
@@ -66212,7 +66216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B232" s="88">
         <v>227</v>
       </c>
@@ -66244,7 +66248,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B233" s="88">
         <v>228</v>
       </c>
@@ -66276,7 +66280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B234" s="88">
         <v>229</v>
       </c>
@@ -66308,7 +66312,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B235" s="88">
         <v>230</v>
       </c>
@@ -66340,7 +66344,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B236" s="88">
         <v>231</v>
       </c>
@@ -66372,7 +66376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B237" s="88">
         <v>232</v>
       </c>
@@ -66404,7 +66408,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B238" s="88">
         <v>233</v>
       </c>
@@ -66436,7 +66440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B239" s="88">
         <v>234</v>
       </c>
@@ -66468,7 +66472,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B240" s="88">
         <v>235</v>
       </c>
@@ -66500,7 +66504,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B241" s="88">
         <v>236</v>
       </c>
@@ -66532,7 +66536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B242" s="88">
         <v>237</v>
       </c>
@@ -66564,7 +66568,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B243" s="88">
         <v>238</v>
       </c>
@@ -66596,7 +66600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B244" s="88">
         <v>239</v>
       </c>
@@ -66628,7 +66632,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B245" s="88">
         <v>240</v>
       </c>
@@ -66660,7 +66664,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B246" s="88">
         <v>241</v>
       </c>
@@ -66692,7 +66696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B247" s="88">
         <v>242</v>
       </c>
@@ -66724,7 +66728,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B248" s="88">
         <v>243</v>
       </c>
@@ -66756,7 +66760,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B249" s="88">
         <v>244</v>
       </c>
@@ -66788,7 +66792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="250" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B250" s="88">
         <v>245</v>
       </c>
@@ -66820,7 +66824,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="251" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B251" s="88">
         <v>246</v>
       </c>
@@ -66852,7 +66856,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="252" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B252" s="88">
         <v>247</v>
       </c>
@@ -66884,7 +66888,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="253" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B253" s="88">
         <v>248</v>
       </c>
@@ -66916,7 +66920,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="254" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B254" s="88">
         <v>249</v>
       </c>
@@ -66948,7 +66952,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="255" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B255" s="88">
         <v>250</v>
       </c>
@@ -66980,7 +66984,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="256" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B256" s="88">
         <v>251</v>
       </c>
@@ -67012,7 +67016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B257" s="88">
         <v>252</v>
       </c>
@@ -67044,7 +67048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B258" s="88">
         <v>253</v>
       </c>
@@ -67076,7 +67080,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B259" s="88">
         <v>254</v>
       </c>
@@ -67108,7 +67112,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B260" s="88">
         <v>255</v>
       </c>
@@ -67140,7 +67144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B261" s="88">
         <v>256</v>
       </c>
@@ -67172,7 +67176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B262" s="88">
         <v>257</v>
       </c>
@@ -67204,7 +67208,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B263" s="88">
         <v>258</v>
       </c>
@@ -67236,7 +67240,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B264" s="88">
         <v>259</v>
       </c>
@@ -67268,7 +67272,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B265" s="88">
         <v>260</v>
       </c>
@@ -67300,7 +67304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="266" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B266" s="88">
         <v>261</v>
       </c>
@@ -67332,7 +67336,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B267" s="88">
         <v>262</v>
       </c>
@@ -67364,7 +67368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="268" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B268" s="88">
         <v>263</v>
       </c>
@@ -67396,7 +67400,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B269" s="88">
         <v>264</v>
       </c>
@@ -67428,7 +67432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B270" s="88">
         <v>265</v>
       </c>
@@ -67460,7 +67464,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B271" s="88">
         <v>266</v>
       </c>
@@ -67492,7 +67496,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="272" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B272" s="88">
         <v>267</v>
       </c>
@@ -67524,7 +67528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="273" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B273" s="88">
         <v>268</v>
       </c>
@@ -67556,7 +67560,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="274" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B274" s="88">
         <v>269</v>
       </c>
@@ -67588,7 +67592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="275" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B275" s="88">
         <v>270</v>
       </c>
@@ -67620,7 +67624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="276" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B276" s="88">
         <v>271</v>
       </c>
@@ -67652,7 +67656,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="277" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B277" s="88">
         <v>272</v>
       </c>
@@ -67684,7 +67688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="278" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B278" s="88">
         <v>273</v>
       </c>
@@ -67716,7 +67720,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="279" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B279" s="88">
         <v>274</v>
       </c>
@@ -67748,7 +67752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="280" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B280" s="88">
         <v>275</v>
       </c>
@@ -67780,7 +67784,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="281" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B281" s="88">
         <v>276</v>
       </c>
@@ -67812,7 +67816,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="282" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B282" s="88">
         <v>277</v>
       </c>
@@ -67844,7 +67848,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="283" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B283" s="88">
         <v>278</v>
       </c>
@@ -67876,7 +67880,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="284" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B284" s="88">
         <v>279</v>
       </c>
@@ -67908,7 +67912,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="285" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B285" s="88">
         <v>280</v>
       </c>
@@ -67940,7 +67944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="286" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B286" s="88">
         <v>281</v>
       </c>
@@ -67972,7 +67976,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B287" s="88">
         <v>282</v>
       </c>
@@ -68004,7 +68008,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="288" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B288" s="88">
         <v>283</v>
       </c>
@@ -68036,7 +68040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B289" s="88">
         <v>284</v>
       </c>
@@ -68068,7 +68072,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B290" s="88">
         <v>285</v>
       </c>
@@ -68100,7 +68104,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B291" s="88">
         <v>286</v>
       </c>
@@ -68132,7 +68136,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B292" s="88">
         <v>287</v>
       </c>
@@ -68164,7 +68168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B293" s="88">
         <v>288</v>
       </c>
@@ -68196,7 +68200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B294" s="88">
         <v>289</v>
       </c>
@@ -68228,7 +68232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B295" s="88">
         <v>290</v>
       </c>
@@ -68260,7 +68264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B296" s="88">
         <v>291</v>
       </c>
@@ -68292,7 +68296,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B297" s="88">
         <v>292</v>
       </c>
@@ -68324,7 +68328,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B298" s="88">
         <v>293</v>
       </c>
@@ -68356,7 +68360,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B299" s="88">
         <v>294</v>
       </c>
@@ -68388,7 +68392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B300" s="88">
         <v>295</v>
       </c>
@@ -68420,7 +68424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B301" s="88">
         <v>296</v>
       </c>
@@ -68452,7 +68456,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B302" s="88">
         <v>297</v>
       </c>
@@ -68484,7 +68488,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B303" s="88">
         <v>298</v>
       </c>
@@ -68516,7 +68520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B304" s="88">
         <v>299</v>
       </c>
@@ -68548,7 +68552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B305" s="88">
         <v>300</v>
       </c>
@@ -68580,7 +68584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B306" s="88">
         <v>301</v>
       </c>
@@ -68612,7 +68616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B307" s="88">
         <v>302</v>
       </c>
@@ -68644,7 +68648,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B308" s="88">
         <v>303</v>
       </c>
@@ -68676,7 +68680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B309" s="88">
         <v>304</v>
       </c>
@@ -68708,7 +68712,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B310" s="88">
         <v>305</v>
       </c>
@@ -68740,7 +68744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B311" s="88">
         <v>306</v>
       </c>
@@ -68772,7 +68776,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B312" s="88">
         <v>307</v>
       </c>
@@ -68804,7 +68808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B313" s="88">
         <v>308</v>
       </c>
@@ -68836,7 +68840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B314" s="88">
         <v>309</v>
       </c>
@@ -68868,7 +68872,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B315" s="88">
         <v>310</v>
       </c>
@@ -68900,7 +68904,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B316" s="88">
         <v>311</v>
       </c>
@@ -68932,7 +68936,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B317" s="88">
         <v>312</v>
       </c>
@@ -68964,7 +68968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B318" s="88">
         <v>313</v>
       </c>
@@ -68996,7 +69000,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B319" s="88">
         <v>314</v>
       </c>
@@ -69028,7 +69032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B320" s="88">
         <v>315</v>
       </c>
@@ -69060,7 +69064,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="321" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B321" s="88">
         <v>316</v>
       </c>
@@ -69092,7 +69096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="322" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B322" s="88">
         <v>317</v>
       </c>
@@ -69124,7 +69128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="323" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B323" s="88">
         <v>318</v>
       </c>
@@ -69156,7 +69160,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="324" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B324" s="88">
         <v>319</v>
       </c>
@@ -69188,7 +69192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B325" s="88">
         <v>320</v>
       </c>
@@ -69220,7 +69224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="326" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B326" s="88">
         <v>321</v>
       </c>
@@ -69252,7 +69256,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="327" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B327" s="88">
         <v>322</v>
       </c>
@@ -69284,7 +69288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="328" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B328" s="88">
         <v>323</v>
       </c>
@@ -69316,7 +69320,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="329" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B329" s="88">
         <v>324</v>
       </c>
@@ -69348,7 +69352,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="330" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B330" s="88">
         <v>325</v>
       </c>
@@ -69380,7 +69384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B331" s="88">
         <v>326</v>
       </c>
@@ -69412,7 +69416,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="332" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B332" s="88">
         <v>327</v>
       </c>
@@ -69444,7 +69448,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="333" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B333" s="88">
         <v>328</v>
       </c>
@@ -69476,7 +69480,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="334" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B334" s="88">
         <v>329</v>
       </c>
@@ -69508,7 +69512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="335" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B335" s="88">
         <v>330</v>
       </c>
@@ -69540,7 +69544,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B336" s="88">
         <v>331</v>
       </c>
@@ -69572,7 +69576,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="337" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B337" s="88">
         <v>332</v>
       </c>
@@ -69604,7 +69608,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B338" s="88">
         <v>333</v>
       </c>
@@ -69636,7 +69640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="339" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B339" s="88">
         <v>334</v>
       </c>
@@ -69668,7 +69672,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="340" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B340" s="88">
         <v>335</v>
       </c>
@@ -69700,7 +69704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="341" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B341" s="88">
         <v>336</v>
       </c>
@@ -69732,7 +69736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="342" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B342" s="88">
         <v>337</v>
       </c>
@@ -69764,7 +69768,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="343" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B343" s="88">
         <v>338</v>
       </c>
@@ -69796,7 +69800,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="344" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B344" s="88">
         <v>339</v>
       </c>
@@ -69828,7 +69832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="345" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B345" s="88">
         <v>340</v>
       </c>
@@ -69860,7 +69864,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="346" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B346" s="88">
         <v>341</v>
       </c>
@@ -69892,7 +69896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="347" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B347" s="88">
         <v>342</v>
       </c>
@@ -69924,7 +69928,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="348" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B348" s="88">
         <v>343</v>
       </c>
@@ -69956,7 +69960,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="349" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B349" s="88">
         <v>344</v>
       </c>
@@ -69988,7 +69992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="350" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B350" s="88">
         <v>345</v>
       </c>
@@ -70020,7 +70024,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="351" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B351" s="88">
         <v>346</v>
       </c>
@@ -70052,7 +70056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="352" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B352" s="88">
         <v>347</v>
       </c>
@@ -70084,7 +70088,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="353" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B353" s="88">
         <v>348</v>
       </c>
@@ -70116,7 +70120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B354" s="88">
         <v>349</v>
       </c>
@@ -70148,7 +70152,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="355" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B355" s="88">
         <v>350</v>
       </c>
@@ -70180,7 +70184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B356" s="88">
         <v>351</v>
       </c>
@@ -70212,7 +70216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="357" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B357" s="88">
         <v>352</v>
       </c>
@@ -70244,7 +70248,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="358" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B358" s="88">
         <v>353</v>
       </c>
@@ -70276,7 +70280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="359" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B359" s="88">
         <v>354</v>
       </c>
@@ -70308,7 +70312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="360" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B360" s="88">
         <v>355</v>
       </c>
@@ -70340,7 +70344,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="361" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B361" s="88">
         <v>356</v>
       </c>
@@ -70372,7 +70376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="362" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B362" s="88">
         <v>357</v>
       </c>
@@ -70404,7 +70408,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="363" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B363" s="88">
         <v>358</v>
       </c>
@@ -70436,7 +70440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="364" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B364" s="88">
         <v>359</v>
       </c>
@@ -70468,7 +70472,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="365" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B365" s="88">
         <v>360</v>
       </c>
@@ -70500,7 +70504,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="366" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B366" s="88">
         <v>361</v>
       </c>
@@ -70532,7 +70536,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="367" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B367" s="88">
         <v>362</v>
       </c>
@@ -70564,7 +70568,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="368" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B368" s="88">
         <v>363</v>
       </c>
@@ -70596,7 +70600,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="369" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B369" s="88">
         <v>364</v>
       </c>
@@ -70628,7 +70632,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="370" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B370" s="88">
         <v>365</v>
       </c>
@@ -70660,7 +70664,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="371" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B371" s="88">
         <v>366</v>
       </c>
@@ -70692,7 +70696,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B372" s="88">
         <v>367</v>
       </c>
@@ -70724,7 +70728,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="373" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B373" s="88">
         <v>368</v>
       </c>
@@ -70756,7 +70760,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="374" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B374" s="88">
         <v>369</v>
       </c>
@@ -70788,7 +70792,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B375" s="88">
         <v>370</v>
       </c>
@@ -70820,7 +70824,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B376" s="88">
         <v>371</v>
       </c>
@@ -70852,7 +70856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="377" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B377" s="88">
         <v>372</v>
       </c>
@@ -70884,7 +70888,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="378" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B378" s="88">
         <v>373</v>
       </c>
@@ -70916,7 +70920,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="379" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B379" s="88">
         <v>374</v>
       </c>
@@ -70948,7 +70952,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="380" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B380" s="88">
         <v>375</v>
       </c>
@@ -70980,7 +70984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="381" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B381" s="88">
         <v>376</v>
       </c>
@@ -71012,7 +71016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B382" s="88">
         <v>377</v>
       </c>
@@ -71044,7 +71048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="383" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B383" s="88">
         <v>378</v>
       </c>
@@ -71076,7 +71080,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="384" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B384" s="88">
         <v>379</v>
       </c>
@@ -71108,7 +71112,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B385" s="88">
         <v>380</v>
       </c>
@@ -71140,7 +71144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B386" s="88">
         <v>381</v>
       </c>
@@ -71172,7 +71176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B387" s="88">
         <v>382</v>
       </c>
@@ -71204,7 +71208,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B388" s="88">
         <v>383</v>
       </c>
@@ -71236,7 +71240,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B389" s="88">
         <v>384</v>
       </c>
@@ -71268,7 +71272,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B390" s="88">
         <v>385</v>
       </c>
@@ -71300,7 +71304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B391" s="88">
         <v>386</v>
       </c>
@@ -71332,7 +71336,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B392" s="88">
         <v>387</v>
       </c>
@@ -71364,7 +71368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B393" s="88">
         <v>388</v>
       </c>
@@ -71396,7 +71400,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B394" s="88">
         <v>389</v>
       </c>
@@ -71428,7 +71432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B395" s="88">
         <v>390</v>
       </c>
@@ -71460,7 +71464,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B396" s="88">
         <v>391</v>
       </c>
@@ -71492,7 +71496,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B397" s="88">
         <v>392</v>
       </c>
@@ -71524,7 +71528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B398" s="88">
         <v>393</v>
       </c>
@@ -71556,7 +71560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B399" s="88">
         <v>394</v>
       </c>
@@ -71588,7 +71592,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B400" s="88">
         <v>395</v>
       </c>
@@ -71620,7 +71624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="401" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B401" s="88">
         <v>396</v>
       </c>
@@ -71652,7 +71656,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="402" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B402" s="88">
         <v>397</v>
       </c>
@@ -71684,7 +71688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="403" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B403" s="88">
         <v>398</v>
       </c>
@@ -71716,7 +71720,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="404" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B404" s="88">
         <v>399</v>
       </c>
@@ -71748,7 +71752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="405" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B405" s="88">
         <v>400</v>
       </c>
@@ -71780,7 +71784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B406" s="88">
         <v>401</v>
       </c>
@@ -71812,7 +71816,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="407" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B407" s="88">
         <v>402</v>
       </c>
@@ -71844,7 +71848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="408" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B408" s="88">
         <v>403</v>
       </c>
@@ -71876,7 +71880,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="409" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B409" s="88">
         <v>404</v>
       </c>
@@ -71908,7 +71912,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="410" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B410" s="88">
         <v>405</v>
       </c>
@@ -71940,7 +71944,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="411" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B411" s="88">
         <v>406</v>
       </c>
@@ -71972,7 +71976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="412" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B412" s="88">
         <v>407</v>
       </c>
@@ -72004,7 +72008,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="413" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B413" s="88">
         <v>408</v>
       </c>
@@ -72036,7 +72040,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="414" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B414" s="88">
         <v>409</v>
       </c>
@@ -72068,7 +72072,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="415" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B415" s="88">
         <v>410</v>
       </c>
@@ -72100,7 +72104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="416" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B416" s="88">
         <v>411</v>
       </c>
@@ -72132,7 +72136,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B417" s="88">
         <v>412</v>
       </c>
@@ -72164,7 +72168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B418" s="88">
         <v>413</v>
       </c>
@@ -72196,7 +72200,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B419" s="88">
         <v>414</v>
       </c>
@@ -72228,7 +72232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B420" s="88">
         <v>415</v>
       </c>
@@ -72260,7 +72264,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B421" s="88">
         <v>416</v>
       </c>
@@ -72292,7 +72296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B422" s="88">
         <v>417</v>
       </c>
@@ -72324,7 +72328,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B423" s="88">
         <v>418</v>
       </c>
@@ -72356,7 +72360,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B424" s="88">
         <v>419</v>
       </c>
@@ -72388,7 +72392,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B425" s="88">
         <v>420</v>
       </c>
@@ -72420,7 +72424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B426" s="88">
         <v>421</v>
       </c>
@@ -72452,7 +72456,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B427" s="88">
         <v>422</v>
       </c>
@@ -72484,7 +72488,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B428" s="88">
         <v>423</v>
       </c>
@@ -72516,7 +72520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B429" s="88">
         <v>424</v>
       </c>
@@ -72548,7 +72552,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B430" s="88">
         <v>425</v>
       </c>
@@ -72580,7 +72584,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B431" s="88">
         <v>426</v>
       </c>
@@ -72612,7 +72616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B432" s="88">
         <v>427</v>
       </c>
@@ -72644,7 +72648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B433" s="88">
         <v>428</v>
       </c>
@@ -72676,7 +72680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B434" s="88">
         <v>429</v>
       </c>
@@ -72708,7 +72712,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B435" s="88">
         <v>430</v>
       </c>
@@ -72740,7 +72744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B436" s="88">
         <v>431</v>
       </c>
@@ -72772,7 +72776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B437" s="88">
         <v>432</v>
       </c>
@@ -72804,7 +72808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B438" s="88">
         <v>433</v>
       </c>
@@ -72836,7 +72840,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B439" s="88">
         <v>434</v>
       </c>
@@ -72868,7 +72872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B440" s="88">
         <v>435</v>
       </c>
@@ -72900,7 +72904,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B441" s="88">
         <v>436</v>
       </c>
@@ -72932,7 +72936,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B442" s="88">
         <v>437</v>
       </c>
@@ -72964,7 +72968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B443" s="88">
         <v>438</v>
       </c>
@@ -72996,7 +73000,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B444" s="88">
         <v>439</v>
       </c>
@@ -73028,7 +73032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B445" s="88">
         <v>440</v>
       </c>
@@ -73060,7 +73064,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="446" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B446" s="88">
         <v>441</v>
       </c>
@@ -73092,7 +73096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B447" s="88">
         <v>442</v>
       </c>
@@ -73124,7 +73128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B448" s="88">
         <v>443</v>
       </c>
@@ -73156,7 +73160,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="449" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B449" s="88">
         <v>444</v>
       </c>
@@ -73188,7 +73192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="450" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B450" s="88">
         <v>445</v>
       </c>
@@ -73220,7 +73224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="451" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B451" s="88">
         <v>446</v>
       </c>
@@ -73252,7 +73256,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="452" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B452" s="88">
         <v>447</v>
       </c>
@@ -73284,7 +73288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B453" s="88">
         <v>448</v>
       </c>
@@ -73316,7 +73320,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B454" s="88">
         <v>449</v>
       </c>
@@ -73348,7 +73352,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="455" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B455" s="88">
         <v>450</v>
       </c>
@@ -73380,7 +73384,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="456" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B456" s="88">
         <v>451</v>
       </c>
@@ -73412,7 +73416,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="457" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B457" s="88">
         <v>452</v>
       </c>
@@ -73444,7 +73448,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="458" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B458" s="88">
         <v>453</v>
       </c>
@@ -73476,7 +73480,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="459" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B459" s="88">
         <v>454</v>
       </c>
@@ -73508,7 +73512,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="460" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B460" s="88">
         <v>455</v>
       </c>
@@ -73540,7 +73544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B461" s="88">
         <v>456</v>
       </c>
@@ -73572,7 +73576,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B462" s="88">
         <v>457</v>
       </c>
@@ -73604,7 +73608,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B463" s="88">
         <v>458</v>
       </c>
@@ -73636,7 +73640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B464" s="88">
         <v>459</v>
       </c>
@@ -73668,7 +73672,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B465" s="88">
         <v>460</v>
       </c>
@@ -73700,7 +73704,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B466" s="88">
         <v>461</v>
       </c>
@@ -73732,7 +73736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B467" s="88">
         <v>462</v>
       </c>
@@ -73764,7 +73768,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B468" s="88">
         <v>463</v>
       </c>
@@ -73796,7 +73800,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B469" s="88">
         <v>464</v>
       </c>
@@ -73828,7 +73832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B470" s="88">
         <v>465</v>
       </c>
@@ -73860,7 +73864,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B471" s="88">
         <v>466</v>
       </c>
@@ -73892,7 +73896,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B472" s="88">
         <v>467</v>
       </c>
@@ -73924,7 +73928,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B473" s="88">
         <v>468</v>
       </c>
@@ -73956,7 +73960,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B474" s="88">
         <v>469</v>
       </c>
@@ -73988,7 +73992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B475" s="88">
         <v>470</v>
       </c>
@@ -74020,7 +74024,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B476" s="88">
         <v>471</v>
       </c>
@@ -74052,7 +74056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B477" s="88">
         <v>472</v>
       </c>
@@ -74084,7 +74088,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B478" s="88">
         <v>473</v>
       </c>
@@ -74116,7 +74120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B479" s="88">
         <v>474</v>
       </c>
@@ -74148,7 +74152,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B480" s="88">
         <v>475</v>
       </c>
@@ -74180,7 +74184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="481" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B481" s="88">
         <v>476</v>
       </c>
@@ -74212,7 +74216,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="482" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B482" s="88">
         <v>477</v>
       </c>
@@ -74244,7 +74248,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="483" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B483" s="88">
         <v>478</v>
       </c>
@@ -74276,7 +74280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="484" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B484" s="88">
         <v>479</v>
       </c>
@@ -74308,7 +74312,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="485" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B485" s="88">
         <v>480</v>
       </c>
@@ -74340,7 +74344,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="486" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B486" s="88">
         <v>481</v>
       </c>
@@ -74372,7 +74376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B487" s="88">
         <v>482</v>
       </c>
@@ -74404,7 +74408,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="488" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B488" s="88">
         <v>483</v>
       </c>
@@ -74436,7 +74440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="489" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B489" s="88">
         <v>484</v>
       </c>
@@ -74468,7 +74472,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="490" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B490" s="88">
         <v>485</v>
       </c>
@@ -74500,7 +74504,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="491" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B491" s="88">
         <v>486</v>
       </c>
@@ -74532,7 +74536,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B492" s="88">
         <v>487</v>
       </c>
@@ -74564,7 +74568,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="493" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B493" s="88">
         <v>488</v>
       </c>
@@ -74596,7 +74600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="494" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B494" s="88">
         <v>489</v>
       </c>
@@ -74628,7 +74632,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="495" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B495" s="88">
         <v>490</v>
       </c>
@@ -74660,7 +74664,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="496" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B496" s="88">
         <v>491</v>
       </c>
@@ -74692,7 +74696,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="497" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B497" s="88">
         <v>492</v>
       </c>
@@ -74724,7 +74728,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="498" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B498" s="88">
         <v>493</v>
       </c>
@@ -74756,7 +74760,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="499" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B499" s="88">
         <v>494</v>
       </c>
@@ -74788,7 +74792,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="500" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B500" s="90">
         <v>495</v>
       </c>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haavas\git\VM2026\fasit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37120A9E-9D0E-488D-A5FD-8502A37A14E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CC741F-A440-4C2A-818C-6650BF56E49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -22542,13 +22542,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP157"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="42" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>207</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>245</v>
       </c>
@@ -23444,7 +23444,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -23572,7 +23572,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>312</v>
       </c>
@@ -23700,7 +23700,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>341</v>
       </c>
@@ -23828,7 +23828,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>370</v>
       </c>
@@ -23956,7 +23956,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>393</v>
       </c>
@@ -24084,7 +24084,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>342</v>
       </c>
@@ -24212,7 +24212,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>433</v>
       </c>
@@ -24340,7 +24340,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>471</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>498</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>527</v>
       </c>
@@ -24724,7 +24724,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>558</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>592</v>
       </c>
@@ -24980,7 +24980,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>626</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>660</v>
       </c>
@@ -25236,7 +25236,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>693</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>725</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>750</v>
       </c>
@@ -25620,7 +25620,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>559</v>
       </c>
@@ -25748,7 +25748,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>794</v>
       </c>
@@ -25876,7 +25876,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>818</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>843</v>
       </c>
@@ -26132,7 +26132,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>871</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>898</v>
       </c>
@@ -26388,7 +26388,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>925</v>
       </c>
@@ -26516,7 +26516,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>949</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>973</v>
       </c>
@@ -26772,7 +26772,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>997</v>
       </c>
@@ -26900,7 +26900,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1024</v>
       </c>
@@ -27028,7 +27028,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1058</v>
       </c>
@@ -27156,7 +27156,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1077</v>
       </c>
@@ -27284,7 +27284,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1093</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1113</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1148</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1180</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1198</v>
       </c>
@@ -27924,7 +27924,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1237</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1264</v>
       </c>
@@ -28180,7 +28180,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1285</v>
       </c>
@@ -28308,7 +28308,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1323</v>
       </c>
@@ -28436,7 +28436,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1349</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1384</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1419</v>
       </c>
@@ -28820,7 +28820,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1449</v>
       </c>
@@ -28948,7 +28948,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1479</v>
       </c>
@@ -29076,7 +29076,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1508</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1544</v>
       </c>
@@ -29332,7 +29332,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1565</v>
       </c>
@@ -29460,7 +29460,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1604</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1633</v>
       </c>
@@ -29716,7 +29716,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1662</v>
       </c>
@@ -29844,7 +29844,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1677</v>
       </c>
@@ -29972,7 +29972,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1703</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1739</v>
       </c>
@@ -30228,7 +30228,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1770</v>
       </c>
@@ -30356,7 +30356,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1798</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1836</v>
       </c>
@@ -30612,7 +30612,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1858</v>
       </c>
@@ -30740,7 +30740,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1883</v>
       </c>
@@ -30868,7 +30868,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1900</v>
       </c>
@@ -30996,7 +30996,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1920</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1958</v>
       </c>
@@ -31252,7 +31252,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1995</v>
       </c>
@@ -31380,7 +31380,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2033</v>
       </c>
@@ -31508,7 +31508,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2072</v>
       </c>
@@ -31636,7 +31636,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2090</v>
       </c>
@@ -31764,7 +31764,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2126</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2146</v>
       </c>
@@ -32020,7 +32020,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2183</v>
       </c>
@@ -32148,7 +32148,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2201</v>
       </c>
@@ -32276,7 +32276,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>2240</v>
       </c>
@@ -32404,7 +32404,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2274</v>
       </c>
@@ -32532,7 +32532,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2304</v>
       </c>
@@ -32660,7 +32660,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>2340</v>
       </c>
@@ -32788,7 +32788,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>2375</v>
       </c>
@@ -32916,7 +32916,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>2395</v>
       </c>
@@ -33044,7 +33044,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>2426</v>
       </c>
@@ -33172,7 +33172,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>2458</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>2493</v>
       </c>
@@ -33428,7 +33428,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>2524</v>
       </c>
@@ -33556,7 +33556,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>2549</v>
       </c>
@@ -33684,7 +33684,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>2573</v>
       </c>
@@ -33812,7 +33812,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>2600</v>
       </c>
@@ -33940,7 +33940,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>2616</v>
       </c>
@@ -34068,7 +34068,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>2622</v>
       </c>
@@ -34196,7 +34196,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>2628</v>
       </c>
@@ -34324,7 +34324,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>2634</v>
       </c>
@@ -34452,7 +34452,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>2640</v>
       </c>
@@ -34580,7 +34580,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>2648</v>
       </c>
@@ -34708,7 +34708,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>2656</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>2663</v>
       </c>
@@ -34964,7 +34964,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>2670</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2677</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2684</v>
       </c>
@@ -35348,7 +35348,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>2691</v>
       </c>
@@ -35476,7 +35476,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>2698</v>
       </c>
@@ -35604,7 +35604,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>2706</v>
       </c>
@@ -35732,7 +35732,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>2714</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>2721</v>
       </c>
@@ -35988,7 +35988,7 @@
         <v>2726</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2727</v>
       </c>
@@ -36116,7 +36116,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2747</v>
       </c>
@@ -36244,7 +36244,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>2767</v>
       </c>
@@ -36372,7 +36372,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>2787</v>
       </c>
@@ -36500,7 +36500,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>2807</v>
       </c>
@@ -36628,7 +36628,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>2827</v>
       </c>
@@ -36756,7 +36756,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>2847</v>
       </c>
@@ -36884,7 +36884,7 @@
         <v>2866</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>2867</v>
       </c>
@@ -37012,7 +37012,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>2887</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>2907</v>
       </c>
@@ -37268,7 +37268,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2927</v>
       </c>
@@ -37396,7 +37396,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>2947</v>
       </c>
@@ -37524,7 +37524,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>2967</v>
       </c>
@@ -37652,7 +37652,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2987</v>
       </c>
@@ -37780,7 +37780,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2977</v>
       </c>
@@ -37908,7 +37908,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>2997</v>
       </c>
@@ -38036,7 +38036,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>3033</v>
       </c>
@@ -38164,43 +38164,43 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>3074</v>
       </c>
@@ -38337,22 +38337,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA72"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.1796875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="10"/>
-    <col min="5" max="5" width="1.1796875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="10"/>
-    <col min="7" max="7" width="27.54296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="1.1796875" style="10" customWidth="1"/>
-    <col min="10" max="16384" width="9.1796875" style="10"/>
+    <col min="1" max="1" width="1.140625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="10"/>
+    <col min="5" max="5" width="1.140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="10"/>
+    <col min="7" max="7" width="27.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="1.140625" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:27" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="39" t="s">
         <v>3115</v>
       </c>
@@ -38364,7 +38364,7 @@
       <c r="G2" s="40"/>
       <c r="H2" s="41"/>
     </row>
-    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="42"/>
       <c r="C3" s="43"/>
       <c r="D3" s="44"/>
@@ -38372,7 +38372,7 @@
       <c r="G3" s="43"/>
       <c r="H3" s="44"/>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
         <v>3117</v>
       </c>
@@ -38384,7 +38384,7 @@
       <c r="G4" s="45"/>
       <c r="H4" s="44"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B5" s="42"/>
       <c r="C5" s="43"/>
       <c r="D5" s="44"/>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="H5" s="44"/>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
         <v>3120</v>
       </c>
@@ -38412,7 +38412,7 @@
       </c>
       <c r="H6" s="44"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="54"/>
       <c r="C7" s="43"/>
       <c r="D7" s="44"/>
@@ -38428,7 +38428,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
         <v>3126</v>
       </c>
@@ -38444,7 +38444,7 @@
       </c>
       <c r="H8" s="44"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="54"/>
       <c r="C9" s="43"/>
       <c r="D9" s="44"/>
@@ -38456,7 +38456,7 @@
       </c>
       <c r="H9" s="44"/>
     </row>
-    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
         <v>3132</v>
       </c>
@@ -38468,7 +38468,7 @@
       <c r="G10" s="50"/>
       <c r="H10" s="44"/>
     </row>
-    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="54"/>
       <c r="C11" s="43"/>
       <c r="D11" s="44"/>
@@ -38476,7 +38476,7 @@
       <c r="G11" s="52"/>
       <c r="H11" s="53"/>
     </row>
-    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="54" t="s">
         <v>3134</v>
       </c>
@@ -38497,7 +38497,7 @@
       <c r="P12" s="76"/>
       <c r="Q12" s="76"/>
     </row>
-    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="54"/>
       <c r="C13" s="43"/>
       <c r="D13" s="44"/>
@@ -38514,7 +38514,7 @@
       <c r="P13" s="76"/>
       <c r="Q13" s="76"/>
     </row>
-    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="54" t="s">
         <v>3135</v>
       </c>
@@ -38535,7 +38535,7 @@
       <c r="P14" s="76"/>
       <c r="Q14" s="76"/>
     </row>
-    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="51"/>
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
@@ -38560,7 +38560,7 @@
       <c r="P15" s="76"/>
       <c r="Q15" s="76"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="F16" s="118" t="s">
         <v>3137</v>
       </c>
@@ -38579,7 +38579,7 @@
       <c r="P16" s="76"/>
       <c r="Q16" s="76"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
       <c r="C17" s="56"/>
       <c r="D17" s="57"/>
@@ -38598,7 +38598,7 @@
       <c r="P17" s="76"/>
       <c r="Q17" s="76"/>
     </row>
-    <row r="18" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="42"/>
       <c r="C18" s="58" t="s">
         <v>3131</v>
@@ -38623,7 +38623,7 @@
       <c r="P18" s="76"/>
       <c r="Q18" s="76"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="59" t="str">
         <f>VLOOKUP("France",T,lang,FALSE)</f>
         <v>France</v>
@@ -38651,7 +38651,7 @@
       <c r="P19" s="76"/>
       <c r="Q19" s="76"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="59" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
         <v>Spain</v>
@@ -38679,7 +38679,7 @@
       <c r="P20" s="76"/>
       <c r="Q20" s="76"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="59" t="str">
         <f>VLOOKUP("Argentina",T,lang,FALSE)</f>
         <v>Argentina</v>
@@ -38707,7 +38707,7 @@
       <c r="P21" s="76"/>
       <c r="Q21" s="76"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="59" t="str">
         <f>VLOOKUP("England",T,lang,FALSE)</f>
         <v>England</v>
@@ -38735,7 +38735,7 @@
       <c r="P22" s="76"/>
       <c r="Q22" s="76"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="59" t="str">
         <f>VLOOKUP("Portugal",T,lang,FALSE)</f>
         <v>Portugal</v>
@@ -38763,7 +38763,7 @@
       <c r="P23" s="76"/>
       <c r="Q23" s="76"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="59" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
         <v>Brazil</v>
@@ -38791,7 +38791,7 @@
       <c r="P24" s="76"/>
       <c r="Q24" s="76"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="59" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
         <v>Netherlands</v>
@@ -38819,7 +38819,7 @@
       <c r="P25" s="76"/>
       <c r="Q25" s="76"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="59" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
         <v>Morocco</v>
@@ -38847,7 +38847,7 @@
       <c r="P26" s="76"/>
       <c r="Q26" s="76"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="59" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
         <v>Belgium</v>
@@ -38875,7 +38875,7 @@
       <c r="P27" s="76"/>
       <c r="Q27" s="76"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="59" t="str">
         <f>VLOOKUP("Germany",T,lang,FALSE)</f>
         <v>Germany</v>
@@ -38903,7 +38903,7 @@
       <c r="P28" s="76"/>
       <c r="Q28" s="76"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="59" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
         <v>Croatia</v>
@@ -38931,7 +38931,7 @@
       <c r="P29" s="76"/>
       <c r="Q29" s="76"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="59" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
         <v>Colombia</v>
@@ -38959,7 +38959,7 @@
       <c r="P30" s="76"/>
       <c r="Q30" s="76"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="59" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
         <v>Senegal</v>
@@ -38987,7 +38987,7 @@
       <c r="P31" s="76"/>
       <c r="Q31" s="76"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="59" t="str">
         <f>VLOOKUP("Mexico",T,lang,FALSE)</f>
         <v>Mexico</v>
@@ -39015,7 +39015,7 @@
       <c r="P32" s="76"/>
       <c r="Q32" s="76"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="59" t="str">
         <f>VLOOKUP("United States",T,lang,FALSE)</f>
         <v>United States</v>
@@ -39043,7 +39043,7 @@
       <c r="P33" s="76"/>
       <c r="Q33" s="76"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="59" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
         <v>Uruguay</v>
@@ -39071,7 +39071,7 @@
       <c r="P34" s="76"/>
       <c r="Q34" s="76"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="59" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
         <v>Japan</v>
@@ -39099,7 +39099,7 @@
       <c r="P35" s="76"/>
       <c r="Q35" s="76"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B36" s="59" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
         <v>Switzerland</v>
@@ -39127,7 +39127,7 @@
       <c r="P36" s="76"/>
       <c r="Q36" s="76"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="59" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
         <v>Iran</v>
@@ -39155,7 +39155,7 @@
       <c r="P37" s="76"/>
       <c r="Q37" s="76"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B38" s="59" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
         <v>Turkey</v>
@@ -39183,7 +39183,7 @@
       <c r="P38" s="76"/>
       <c r="Q38" s="76"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B39" s="59" t="str">
         <f>VLOOKUP("Ecuador",T,lang,FALSE)</f>
         <v>Ecuador</v>
@@ -39211,7 +39211,7 @@
       <c r="P39" s="76"/>
       <c r="Q39" s="76"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="59" t="str">
         <f>VLOOKUP("Austria",T,lang,FALSE)</f>
         <v>Austria</v>
@@ -39239,7 +39239,7 @@
       <c r="P40" s="76"/>
       <c r="Q40" s="76"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" s="59" t="str">
         <f>VLOOKUP("Korea Republic",T,lang,FALSE)</f>
         <v>Korea Republic</v>
@@ -39267,7 +39267,7 @@
       <c r="P41" s="76"/>
       <c r="Q41" s="76"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" s="59" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
         <v>Australia</v>
@@ -39295,7 +39295,7 @@
       <c r="P42" s="76"/>
       <c r="Q42" s="76"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="59" t="str">
         <f>VLOOKUP("Algeria",T,lang,FALSE)</f>
         <v>Algeria</v>
@@ -39319,7 +39319,7 @@
       <c r="P43" s="76"/>
       <c r="Q43" s="76"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44" s="59" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
         <v>Egypt</v>
@@ -39347,7 +39347,7 @@
       <c r="P44" s="76"/>
       <c r="Q44" s="76"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="59" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
         <v>Canada</v>
@@ -39375,7 +39375,7 @@
       <c r="P45" s="76"/>
       <c r="Q45" s="76"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B46" s="59" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
         <v>Norway</v>
@@ -39403,7 +39403,7 @@
       <c r="P46" s="76"/>
       <c r="Q46" s="76"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B47" s="59" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
         <v>Panama</v>
@@ -39431,7 +39431,7 @@
       <c r="P47" s="76"/>
       <c r="Q47" s="76"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B48" s="59" t="str">
         <f>VLOOKUP("Ivory Coast",T,lang,FALSE)</f>
         <v>Ivory Coast</v>
@@ -39455,7 +39455,7 @@
       <c r="P48" s="76"/>
       <c r="Q48" s="76"/>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="59" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
         <v>Sweden</v>
@@ -39479,7 +39479,7 @@
       <c r="P49" s="76"/>
       <c r="Q49" s="76"/>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="59" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
         <v>Paraguay</v>
@@ -39503,7 +39503,7 @@
       <c r="P50" s="76"/>
       <c r="Q50" s="76"/>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="59" t="str">
         <f>VLOOKUP("Czech Republic",T,lang,FALSE)</f>
         <v>Czech Republic</v>
@@ -39527,7 +39527,7 @@
       <c r="P51" s="76"/>
       <c r="Q51" s="76"/>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="59" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
         <v>Scotland</v>
@@ -39551,7 +39551,7 @@
       <c r="P52" s="76"/>
       <c r="Q52" s="76"/>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="59" t="str">
         <f>VLOOKUP("Tunisia",T,lang,FALSE)</f>
         <v>Tunisia</v>
@@ -39575,7 +39575,7 @@
       <c r="P53" s="76"/>
       <c r="Q53" s="76"/>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="59" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
         <v>DR Congo</v>
@@ -39599,7 +39599,7 @@
       <c r="P54" s="76"/>
       <c r="Q54" s="76"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="59" t="str">
         <f>VLOOKUP("Uzbekistan",T,lang,FALSE)</f>
         <v>Uzbekistan</v>
@@ -39623,7 +39623,7 @@
       <c r="P55" s="76"/>
       <c r="Q55" s="76"/>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="59" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
         <v>Qatar</v>
@@ -39647,7 +39647,7 @@
       <c r="P56" s="76"/>
       <c r="Q56" s="76"/>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="59" t="str">
         <f>VLOOKUP("Iraq",T,lang,FALSE)</f>
         <v>Iraq</v>
@@ -39671,7 +39671,7 @@
       <c r="P57" s="76"/>
       <c r="Q57" s="76"/>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="59" t="str">
         <f>VLOOKUP("South Africa",T,lang,FALSE)</f>
         <v>South Africa</v>
@@ -39695,7 +39695,7 @@
       <c r="P58" s="76"/>
       <c r="Q58" s="76"/>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="59" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
         <v>Saudi Arabia</v>
@@ -39719,7 +39719,7 @@
       <c r="P59" s="76"/>
       <c r="Q59" s="76"/>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="59" t="str">
         <f>VLOOKUP("Jordan",T,lang,FALSE)</f>
         <v>Jordan</v>
@@ -39743,7 +39743,7 @@
       <c r="P60" s="76"/>
       <c r="Q60" s="76"/>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="59" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
         <v>Bosnia and Herzegovina</v>
@@ -39767,7 +39767,7 @@
       <c r="P61" s="76"/>
       <c r="Q61" s="76"/>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="59" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
         <v>Cape Verde</v>
@@ -39791,7 +39791,7 @@
       <c r="P62" s="76"/>
       <c r="Q62" s="76"/>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="59" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
         <v>Ghana</v>
@@ -39815,7 +39815,7 @@
       <c r="P63" s="76"/>
       <c r="Q63" s="76"/>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="59" t="str">
         <f>VLOOKUP("Curaçao",T,lang,FALSE)</f>
         <v>Curaçao</v>
@@ -39839,7 +39839,7 @@
       <c r="P64" s="76"/>
       <c r="Q64" s="76"/>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="59" t="str">
         <f>VLOOKUP("Haiti",T,lang,FALSE)</f>
         <v>Haiti</v>
@@ -39866,7 +39866,7 @@
       <c r="P65" s="76"/>
       <c r="Q65" s="76"/>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B66" s="59" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
         <v>New Zealand</v>
@@ -39888,7 +39888,7 @@
       <c r="P66" s="76"/>
       <c r="Q66" s="76"/>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" s="51"/>
       <c r="C67" s="52"/>
       <c r="D67" s="53"/>
@@ -39905,7 +39905,7 @@
       <c r="P67" s="76"/>
       <c r="Q67" s="76"/>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F68" s="76"/>
       <c r="G68" s="76"/>
       <c r="H68" s="76"/>
@@ -39919,7 +39919,7 @@
       <c r="P68" s="76"/>
       <c r="Q68" s="76"/>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F69" s="76"/>
       <c r="G69" s="76"/>
       <c r="H69" s="76"/>
@@ -39933,7 +39933,7 @@
       <c r="P69" s="76"/>
       <c r="Q69" s="76"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F70" s="76"/>
       <c r="G70" s="76"/>
       <c r="H70" s="76"/>
@@ -39947,7 +39947,7 @@
       <c r="P70" s="76"/>
       <c r="Q70" s="76"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F71" s="76"/>
       <c r="G71" s="76"/>
       <c r="H71" s="76"/>
@@ -39961,7 +39961,7 @@
       <c r="P71" s="76"/>
       <c r="Q71" s="76"/>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F72" s="76"/>
       <c r="G72" s="76"/>
       <c r="H72" s="76"/>
@@ -40011,62 +40011,62 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CR111"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22.54296875" style="5" customWidth="1"/>
-    <col min="6" max="7" width="4.26953125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="22.54296875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="3.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="8" customWidth="1"/>
-    <col min="11" max="14" width="5.453125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="7.7265625" style="9" customWidth="1"/>
-    <col min="16" max="16" width="6.7265625" style="9" customWidth="1"/>
-    <col min="17" max="17" width="3.453125" style="68" customWidth="1"/>
-    <col min="18" max="18" width="15.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" style="5" customWidth="1"/>
+    <col min="6" max="7" width="4.28515625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="3.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="8" customWidth="1"/>
+    <col min="11" max="14" width="5.42578125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="7.7109375" style="9" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" style="9" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="68" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="19" max="20" width="16" style="127" hidden="1" customWidth="1"/>
     <col min="21" max="28" width="4" style="123" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="4.26953125" style="124" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.453125" style="123" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="13.453125" style="124" hidden="1" customWidth="1"/>
-    <col min="32" max="36" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" style="124" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="5.42578125" style="123" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="124" hidden="1" customWidth="1"/>
+    <col min="32" max="36" width="5.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="37" max="39" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="5.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="41" max="42" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="7.1796875" style="125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="7.140625" style="125" hidden="1" customWidth="1"/>
     <col min="44" max="44" width="10" style="125" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="15.26953125" style="125" hidden="1" customWidth="1"/>
-    <col min="46" max="50" width="4.7265625" style="126" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="9.1796875" style="125" hidden="1" customWidth="1"/>
-    <col min="52" max="61" width="9.1796875" style="126" hidden="1" customWidth="1"/>
-    <col min="62" max="62" width="9.1796875" style="112" hidden="1" customWidth="1"/>
-    <col min="63" max="63" width="3.26953125" style="2" customWidth="1"/>
-    <col min="64" max="64" width="19.7265625" style="2" customWidth="1"/>
+    <col min="45" max="45" width="15.28515625" style="125" hidden="1" customWidth="1"/>
+    <col min="46" max="50" width="4.7109375" style="126" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="125" hidden="1" customWidth="1"/>
+    <col min="52" max="61" width="9.140625" style="126" hidden="1" customWidth="1"/>
+    <col min="62" max="62" width="9.140625" style="112" hidden="1" customWidth="1"/>
+    <col min="63" max="63" width="3.28515625" style="2" customWidth="1"/>
+    <col min="64" max="64" width="19.7109375" style="2" customWidth="1"/>
     <col min="65" max="67" width="3" style="2" customWidth="1"/>
     <col min="68" max="69" width="2" style="111" customWidth="1"/>
-    <col min="70" max="70" width="3.26953125" style="2" customWidth="1"/>
-    <col min="71" max="71" width="19.7265625" style="2" customWidth="1"/>
+    <col min="70" max="70" width="3.28515625" style="2" customWidth="1"/>
+    <col min="71" max="71" width="19.7109375" style="2" customWidth="1"/>
     <col min="72" max="74" width="3" style="2" customWidth="1"/>
     <col min="75" max="76" width="2" style="111" customWidth="1"/>
     <col min="77" max="77" width="4" style="2" customWidth="1"/>
-    <col min="78" max="78" width="19.7265625" style="2" customWidth="1"/>
+    <col min="78" max="78" width="19.7109375" style="2" customWidth="1"/>
     <col min="79" max="81" width="3" style="2" customWidth="1"/>
     <col min="82" max="83" width="2" style="111" customWidth="1"/>
-    <col min="84" max="84" width="3.81640625" style="2" customWidth="1"/>
-    <col min="85" max="85" width="19.7265625" style="2" customWidth="1"/>
+    <col min="84" max="84" width="3.85546875" style="2" customWidth="1"/>
+    <col min="85" max="85" width="19.7109375" style="2" customWidth="1"/>
     <col min="86" max="88" width="3" style="2" customWidth="1"/>
     <col min="89" max="90" width="2" style="111" customWidth="1"/>
-    <col min="91" max="91" width="3.7265625" style="2" customWidth="1"/>
-    <col min="92" max="92" width="19.7265625" style="2" customWidth="1"/>
+    <col min="91" max="91" width="3.7109375" style="2" customWidth="1"/>
+    <col min="92" max="92" width="19.7109375" style="2" customWidth="1"/>
     <col min="93" max="95" width="3" style="2" customWidth="1"/>
     <col min="96" max="96" width="2" style="111" customWidth="1"/>
-    <col min="97" max="16384" width="9.1796875" style="2"/>
+    <col min="97" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:95" ht="46" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
@@ -40101,7 +40101,7 @@
       <c r="AW1" s="125"/>
       <c r="AX1" s="125"/>
     </row>
-    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="S2" s="123"/>
       <c r="T2" s="123"/>
       <c r="AC2" s="123"/>
@@ -40117,7 +40117,7 @@
       <c r="AW2" s="125"/>
       <c r="AX2" s="125"/>
     </row>
-    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -40152,8 +40152,8 @@
       <c r="AW3" s="125"/>
       <c r="AX3" s="125"/>
     </row>
-    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
@@ -40175,7 +40175,7 @@
       <c r="O5" s="148"/>
       <c r="P5" s="149"/>
     </row>
-    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="144"/>
       <c r="B6" s="145"/>
       <c r="C6" s="145"/>
@@ -40332,7 +40332,7 @@
       <c r="CI6" s="134"/>
       <c r="CJ6" s="135"/>
     </row>
-    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -40428,7 +40428,7 @@
       <c r="CI7" s="137"/>
       <c r="CJ7" s="138"/>
     </row>
-    <row r="8" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>2</v>
       </c>
@@ -40675,7 +40675,7 @@
       <c r="CP8" s="21"/>
       <c r="CQ8" s="21"/>
     </row>
-    <row r="9" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>3</v>
       </c>
@@ -40695,8 +40695,12 @@
         <f>AE14</f>
         <v>Canada</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="F9" s="19">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20">
+        <v>1</v>
+      </c>
       <c r="H9" s="80" t="str">
         <f>AE15</f>
         <v>Bosnia and Herzegovina</v>
@@ -40735,43 +40739,43 @@
       </c>
       <c r="S9" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Canada_draw</v>
       </c>
       <c r="T9" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Bosnia and Herzegovina_draw</v>
       </c>
       <c r="U9" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB9" s="123" t="str">
+      <c r="AB9" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD9" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR9))</f>
@@ -40936,7 +40940,7 @@
       <c r="CP9" s="21"/>
       <c r="CQ9" s="21"/>
     </row>
-    <row r="10" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>4</v>
       </c>
@@ -40956,8 +40960,12 @@
         <f>AE26</f>
         <v>United States</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
+      <c r="F10" s="19">
+        <v>4</v>
+      </c>
+      <c r="G10" s="20">
+        <v>1</v>
+      </c>
       <c r="H10" s="80" t="str">
         <f>AE27</f>
         <v>Paraguay</v>
@@ -40996,11 +41004,11 @@
       </c>
       <c r="S10" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>United States_win</v>
       </c>
       <c r="T10" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Paraguay_lose</v>
       </c>
       <c r="U10" s="123">
         <f t="shared" si="8"/>
@@ -41030,9 +41038,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB10" s="123" t="str">
+      <c r="AB10" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD10" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR10))</f>
@@ -41195,7 +41203,7 @@
       <c r="CP10" s="21"/>
       <c r="CQ10" s="21"/>
     </row>
-    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>5</v>
       </c>
@@ -41458,7 +41466,7 @@
       <c r="CP11" s="21"/>
       <c r="CQ11" s="21"/>
     </row>
-    <row r="12" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>6</v>
       </c>
@@ -41681,7 +41689,7 @@
       <c r="CP12" s="21"/>
       <c r="CQ12" s="21"/>
     </row>
-    <row r="13" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>7</v>
       </c>
@@ -41796,7 +41804,7 @@
       <c r="CP13" s="21"/>
       <c r="CQ13" s="21"/>
     </row>
-    <row r="14" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>8</v>
       </c>
@@ -41896,7 +41904,7 @@
       </c>
       <c r="AD14" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR14))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="124" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
@@ -41908,7 +41916,7 @@
       </c>
       <c r="AG14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_lose")</f>
@@ -41916,11 +41924,11 @@
       </c>
       <c r="AI14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE14,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE14,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" s="123">
         <f>AI14-AJ14</f>
@@ -41932,15 +41940,15 @@
       </c>
       <c r="AN14" s="123">
         <f>AF14*3+AG14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" s="123">
         <f>AN14/AN18*10+BA14</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP14" s="123">
         <f>AO14*10000000+BI14*100+AM14/AM18*10+AI14/AI18*1++IF(AQ14=0,ROW(),AQ14)/2000000</f>
-        <v>7.7824000000000003E-4</v>
+        <v>59805923.80174911</v>
       </c>
       <c r="AQ14" s="126">
         <f>VLOOKUP(AE14,db_fifarank,2,FALSE)</f>
@@ -41948,7 +41956,7 @@
       </c>
       <c r="AR14" s="125">
         <f>AP14/AP18</f>
-        <v>7.7759871434028365E-4</v>
+        <v>0.99999998327924866</v>
       </c>
       <c r="AS14" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J15,"1B")</f>
@@ -41960,15 +41968,15 @@
       </c>
       <c r="AU14" s="126" cm="1">
         <f t="array" ref="AU14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV14" s="126" cm="1">
         <f t="array" ref="AV14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" s="126" cm="1">
         <f t="array" ref="AW14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" s="126">
         <f>AV14-AW14</f>
@@ -41980,11 +41988,11 @@
       </c>
       <c r="AZ14" s="126">
         <f>AT14/AT18*1000+AU14/AU18*100+AY14/AY18*10+AV14/AV18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA14" s="126">
         <f>AZ14/AZ18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB14" s="126" cm="1">
         <f t="array" ref="BB14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_win")*($X$7:$X$78))</f>
@@ -41992,15 +42000,15 @@
       </c>
       <c r="BC14" s="126" cm="1">
         <f t="array" ref="BC14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD14" s="126" cm="1">
         <f t="array" ref="BD14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE14" s="126" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF14" s="126">
         <f>BD14-BE14</f>
@@ -42012,11 +42020,11 @@
       </c>
       <c r="BH14" s="126">
         <f>BB14/BB18*1000+BC14/BC18*100+BG14/BG18*10+BD14/BD18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI14" s="126">
         <f>BH14/BH18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK14" s="131">
         <v>77</v>
@@ -42059,7 +42067,7 @@
       <c r="CP14" s="21"/>
       <c r="CQ14" s="21"/>
     </row>
-    <row r="15" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>9</v>
       </c>
@@ -42087,11 +42095,11 @@
       </c>
       <c r="J15" s="30" t="str">
         <f>VLOOKUP(1,AD14:AN17,2,FALSE)</f>
-        <v>Switzerland</v>
+        <v>Canada</v>
       </c>
       <c r="K15" s="31">
         <f>L15+M15+N15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="31">
         <f>VLOOKUP(1,AD14:AN17,3,FALSE)</f>
@@ -42099,7 +42107,7 @@
       </c>
       <c r="M15" s="31">
         <f>VLOOKUP(1,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="31">
         <f>VLOOKUP(1,AD14:AN17,5,FALSE)</f>
@@ -42107,11 +42115,11 @@
       </c>
       <c r="O15" s="31" t="str">
         <f>VLOOKUP(1,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P15" s="32">
         <f>L15*3+M15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="123">
         <f>DATE(2026,6,14)+TIME(12,0,0)+gmt_delta</f>
@@ -42159,7 +42167,7 @@
       </c>
       <c r="AD15" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR15))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE15" s="124" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
@@ -42171,7 +42179,7 @@
       </c>
       <c r="AG15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_lose")</f>
@@ -42179,11 +42187,11 @@
       </c>
       <c r="AI15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE15,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE15,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" s="123">
         <f>AI15-AJ15</f>
@@ -42195,15 +42203,15 @@
       </c>
       <c r="AN15" s="123">
         <f>AF15*3+AG15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15" s="123">
         <f>AN15/AN18*10+BA15</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP15" s="123">
         <f>AO15*10000000+BI15*100+AM15/AM18*10+AI15/AI18*1++IF(AQ15=0,ROW(),AQ15)/2000000</f>
-        <v>6.9291999999999997E-4</v>
+        <v>59805923.801663786</v>
       </c>
       <c r="AQ15" s="126">
         <f>VLOOKUP(AE15,db_fifarank,2,FALSE)</f>
@@ -42211,7 +42219,7 @@
       </c>
       <c r="AR15" s="125">
         <f>AP15/AP18</f>
-        <v>6.9234901976340118E-4</v>
+        <v>0.99999998327782191</v>
       </c>
       <c r="AS15" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J16,"2B")</f>
@@ -42223,15 +42231,15 @@
       </c>
       <c r="AU15" s="126" cm="1">
         <f t="array" ref="AU15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" s="126" cm="1">
         <f t="array" ref="AV15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" s="126" cm="1">
         <f t="array" ref="AW15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" s="126">
         <f>AV15-AW15</f>
@@ -42243,11 +42251,11 @@
       </c>
       <c r="AZ15" s="126">
         <f>AT15/AT18*1000+AU15/AU18*100+AY15/AY18*10+AV15/AV18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA15" s="126">
         <f>AZ15/AZ18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB15" s="126" cm="1">
         <f t="array" ref="BB15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_win")*($X$7:$X$78))</f>
@@ -42255,15 +42263,15 @@
       </c>
       <c r="BC15" s="126" cm="1">
         <f t="array" ref="BC15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" s="126" cm="1">
         <f t="array" ref="BD15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE15" s="126" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF15" s="126">
         <f>BD15-BE15</f>
@@ -42275,11 +42283,11 @@
       </c>
       <c r="BH15" s="126">
         <f>BB15/BB18*1000+BC15/BC18*100+BG15/BG18*10+BD15/BD18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI15" s="126">
         <f>BH15/BH18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
@@ -42319,7 +42327,7 @@
       <c r="CH15" s="21"/>
       <c r="CI15" s="21"/>
     </row>
-    <row r="16" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>10</v>
       </c>
@@ -42347,11 +42355,11 @@
       </c>
       <c r="J16" s="33" t="str">
         <f>VLOOKUP(2,AD14:AN17,2,FALSE)</f>
-        <v>Canada</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="K16" s="23">
         <f>L16+M16+N16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="23">
         <f>VLOOKUP(2,AD14:AN17,3,FALSE)</f>
@@ -42359,7 +42367,7 @@
       </c>
       <c r="M16" s="23">
         <f>VLOOKUP(2,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="23">
         <f>VLOOKUP(2,AD14:AN17,5,FALSE)</f>
@@ -42367,11 +42375,11 @@
       </c>
       <c r="O16" s="23" t="str">
         <f>VLOOKUP(2,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P16" s="34">
         <f>L16*3+M16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="123">
         <f>DATE(2026,6,14)+TIME(6,0,0)+gmt_delta</f>
@@ -42419,7 +42427,7 @@
       </c>
       <c r="AD16" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR16))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE16" s="124" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
@@ -42471,7 +42479,7 @@
       </c>
       <c r="AR16" s="125">
         <f>AP16/AP18</f>
-        <v>7.268805416173282E-4</v>
+        <v>1.2164012218045725E-11</v>
       </c>
       <c r="AT16" s="126" cm="1">
         <f t="array" ref="AT16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($U$7:$U$78))</f>
@@ -42571,7 +42579,7 @@
       <c r="CH16" s="21"/>
       <c r="CI16" s="21"/>
     </row>
-    <row r="17" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>11</v>
       </c>
@@ -42599,7 +42607,7 @@
       </c>
       <c r="J17" s="33" t="str">
         <f>VLOOKUP(3,AD14:AN17,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>Switzerland</v>
       </c>
       <c r="K17" s="23">
         <f>L17+M17+N17</f>
@@ -42671,7 +42679,7 @@
       </c>
       <c r="AD17" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR17))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" s="124" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
@@ -42723,7 +42731,7 @@
       </c>
       <c r="AR17" s="125">
         <f>AP17/AP18</f>
-        <v>8.2402043035108958E-4</v>
+        <v>1.3789603667760363E-11</v>
       </c>
       <c r="AT17" s="126" cm="1">
         <f t="array" ref="AT17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($U$7:$U$78))</f>
@@ -42827,7 +42835,7 @@
       <c r="CH17" s="21"/>
       <c r="CI17" s="21"/>
     </row>
-    <row r="18" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>12</v>
       </c>
@@ -42855,7 +42863,7 @@
       </c>
       <c r="J18" s="35" t="str">
         <f>VLOOKUP(4,AD14:AN17,2,FALSE)</f>
-        <v>Bosnia and Herzegovina</v>
+        <v>Qatar</v>
       </c>
       <c r="K18" s="36">
         <f>L18+M18+N18</f>
@@ -42931,7 +42939,7 @@
       </c>
       <c r="AG18" s="123">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH18" s="123">
         <f t="shared" si="13"/>
@@ -42939,7 +42947,7 @@
       </c>
       <c r="AI18" s="123">
         <f>MAX(AI14:AI17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL18" s="123">
         <f>MIN(AL14:AL17)</f>
@@ -42951,15 +42959,15 @@
       </c>
       <c r="AN18" s="123">
         <f>MAX(AN14:AN17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO18" s="123">
         <f>MAX(AO14:AO17)+1</f>
-        <v>1</v>
+        <v>6.9805825242718447</v>
       </c>
       <c r="AP18" s="123">
         <f>MAX(AP14:AP17)+1</f>
-        <v>1.0008246999999999</v>
+        <v>59805924.80174911</v>
       </c>
       <c r="AT18" s="126">
         <f>MAX(AT14:AT17)-MIN(AT14:AT17)+1</f>
@@ -42967,15 +42975,15 @@
       </c>
       <c r="AU18" s="126">
         <f>MAX(AU14:AU17)-MIN(AU14:AU17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV18" s="126">
         <f>MAX(AV14:AV17)-MIN(AV14:AV17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" s="126">
         <f>MAX(AW14:AW17)-MIN(AW14:AW17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY18" s="126">
         <f>MAX(AY14:AY17)-MIN(AY14:AY17)+1</f>
@@ -42983,7 +42991,7 @@
       </c>
       <c r="AZ18" s="126">
         <f>MAX(AZ14:AZ17)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB18" s="126">
         <f>MAX(BB14:BB17)-MIN(BB14:BB17)+1</f>
@@ -42991,15 +42999,15 @@
       </c>
       <c r="BC18" s="126">
         <f>MAX(BC14:BC17)-MIN(BC14:BC17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD18" s="126">
         <f>MAX(BD14:BD17)-MIN(BD14:BD17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE18" s="126">
         <f>MAX(BE14:BE17)-MIN(BE14:BE17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG18" s="126">
         <f>MAX(BG14:BG17)-MIN(BG14:BG17)+1</f>
@@ -43007,7 +43015,7 @@
       </c>
       <c r="BH18" s="126">
         <f>MAX(BH14:BH17)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BK18" s="131">
         <v>73</v>
@@ -43043,7 +43051,7 @@
       <c r="CH18" s="21"/>
       <c r="CI18" s="21"/>
     </row>
-    <row r="19" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>13</v>
       </c>
@@ -43158,7 +43166,7 @@
       <c r="CP19" s="21"/>
       <c r="CQ19" s="21"/>
     </row>
-    <row r="20" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>14</v>
       </c>
@@ -43421,7 +43429,7 @@
       <c r="CP20" s="21"/>
       <c r="CQ20" s="21"/>
     </row>
-    <row r="21" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>15</v>
       </c>
@@ -43688,7 +43696,7 @@
       <c r="CP21" s="21"/>
       <c r="CQ21" s="21"/>
     </row>
-    <row r="22" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>16</v>
       </c>
@@ -43948,7 +43956,7 @@
         <v>46217.791666666672</v>
       </c>
     </row>
-    <row r="23" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>17</v>
       </c>
@@ -44208,7 +44216,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>18</v>
       </c>
@@ -44423,7 +44431,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>19</v>
       </c>
@@ -44533,7 +44541,7 @@
       <c r="CP25" s="21"/>
       <c r="CQ25" s="21"/>
     </row>
-    <row r="26" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>20</v>
       </c>
@@ -44641,7 +44649,7 @@
       </c>
       <c r="AF26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_draw")</f>
@@ -44653,31 +44661,31 @@
       </c>
       <c r="AI26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE26,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE26,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL26" s="123">
         <f>AI26-AJ26</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM26" s="123">
         <f>AL26-AL30</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN26" s="123">
         <f>AF26*3+AG26</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO26" s="123">
         <f>AN26/AN30*10+BA26</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP26" s="123">
         <f>AO26*10000000+BI26*100+AM26/AM30*10+AI26/AI30*1++IF(AQ26=0,ROW(),AQ26)/2000000</f>
-        <v>8.3656500000000005E-4</v>
+        <v>75000009.37226513</v>
       </c>
       <c r="AQ26" s="126">
         <f>VLOOKUP(AE26,db_fifarank,2,FALSE)</f>
@@ -44685,7 +44693,7 @@
       </c>
       <c r="AR26" s="125">
         <f>AP26/AP30</f>
-        <v>8.3586574397389256E-4</v>
+        <v>0.99999998666666856</v>
       </c>
       <c r="AS26" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J27,"1D")</f>
@@ -44797,7 +44805,7 @@
       <c r="CP26" s="21"/>
       <c r="CQ26" s="21"/>
     </row>
-    <row r="27" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>21</v>
       </c>
@@ -44829,11 +44837,11 @@
       </c>
       <c r="K27" s="31">
         <f>L27+M27+N27</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="31">
         <f>VLOOKUP(1,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="31">
         <f>VLOOKUP(1,AD26:AN29,4,FALSE)</f>
@@ -44845,11 +44853,11 @@
       </c>
       <c r="O27" s="31" t="str">
         <f>VLOOKUP(1,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>4 - 1</v>
       </c>
       <c r="P27" s="32">
         <f>L27*3+M27</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" s="123">
         <f>DATE(2026,6,17)+TIME(12,0,0)+gmt_delta</f>
@@ -44913,19 +44921,19 @@
       </c>
       <c r="AH27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE27,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE27,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL27" s="123">
         <f>AI27-AJ27</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM27" s="123">
         <f>AL27-AL30</f>
@@ -44941,7 +44949,7 @@
       </c>
       <c r="AP27" s="123">
         <f>AO27*10000000+BI27*100+AM27/AM30*10+AI27/AI30*1++IF(AQ27=0,ROW(),AQ27)/2000000</f>
-        <v>7.5175000000000003E-4</v>
+        <v>0.20075175000000001</v>
       </c>
       <c r="AQ27" s="126">
         <f>VLOOKUP(AE27,db_fifarank,2,FALSE)</f>
@@ -44949,7 +44957,7 @@
       </c>
       <c r="AR27" s="125">
         <f>AP27/AP30</f>
-        <v>7.5112163792696765E-4</v>
+        <v>2.6766896298222066E-9</v>
       </c>
       <c r="AS27" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J28,"2D")</f>
@@ -45065,7 +45073,7 @@
       <c r="CP27" s="21"/>
       <c r="CQ27" s="21"/>
     </row>
-    <row r="28" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>22</v>
       </c>
@@ -45197,7 +45205,7 @@
       </c>
       <c r="AM28" s="123">
         <f>AL28-AL30</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN28" s="123">
         <f>AF28*3+AG28</f>
@@ -45209,7 +45217,7 @@
       </c>
       <c r="AP28" s="123">
         <f>AO28*10000000+BI28*100+AM28/AM30*10+AI28/AI30*1++IF(AQ28=0,ROW(),AQ28)/2000000</f>
-        <v>7.9033500000000008E-4</v>
+        <v>4.2865046207142852</v>
       </c>
       <c r="AQ28" s="126">
         <f>VLOOKUP(AE28,db_fifarank,2,FALSE)</f>
@@ -45217,7 +45225,7 @@
       </c>
       <c r="AR28" s="125">
         <f>AP28/AP30</f>
-        <v>7.8967438604723647E-4</v>
+        <v>5.715338703872269E-8</v>
       </c>
       <c r="AT28" s="126" cm="1">
         <f t="array" ref="AT28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($U$7:$U$78))</f>
@@ -45320,7 +45328,7 @@
       <c r="CK28" s="114"/>
       <c r="CL28" s="112"/>
     </row>
-    <row r="29" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>23</v>
       </c>
@@ -45452,7 +45460,7 @@
       </c>
       <c r="AM29" s="123">
         <f>AL29-AL30</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN29" s="123">
         <f>AF29*3+AG29</f>
@@ -45464,7 +45472,7 @@
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>7.9951999999999996E-4</v>
+        <v>4.2865138057142858</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -45472,7 +45480,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>7.9885170862037803E-4</v>
+        <v>5.715350950537243E-8</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -45579,7 +45587,7 @@
       <c r="CK29" s="114"/>
       <c r="CL29" s="112"/>
     </row>
-    <row r="30" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>24</v>
       </c>
@@ -45611,7 +45619,7 @@
       </c>
       <c r="K30" s="36">
         <f>L30+M30+N30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="36">
         <f>VLOOKUP(4,AD26:AN29,3,FALSE)</f>
@@ -45623,11 +45631,11 @@
       </c>
       <c r="N30" s="36">
         <f>VLOOKUP(4,AD26:AN29,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="36" t="str">
         <f>VLOOKUP(4,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 4</v>
       </c>
       <c r="P30" s="37">
         <f>L30*3+M30</f>
@@ -45679,7 +45687,7 @@
       </c>
       <c r="AF30" s="123">
         <f t="shared" ref="AF30:AH30" si="15">MAX(AF26:AF29)-MIN(AF26:AF29)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG30" s="123">
         <f t="shared" si="15"/>
@@ -45687,31 +45695,31 @@
       </c>
       <c r="AH30" s="123">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI30" s="123">
         <f>MAX(AI26:AI29)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL30" s="123">
         <f>MIN(AL26:AL29)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM30" s="123">
         <f>MAX(AM26:AM29)+1</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN30" s="123">
         <f>MAX(AN26:AN29)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO30" s="123">
         <f>MAX(AO26:AO29)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP30" s="123">
         <f>MAX(AP26:AP29)+1</f>
-        <v>1.000836565</v>
+        <v>75000010.37226513</v>
       </c>
       <c r="AT30" s="126">
         <f>MAX(AT26:AT29)-MIN(AT26:AT29)+1</f>
@@ -45798,7 +45806,7 @@
       <c r="CK30" s="114"/>
       <c r="CL30" s="112"/>
     </row>
-    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>25</v>
       </c>
@@ -45904,7 +45912,7 @@
       <c r="CK31" s="114"/>
       <c r="CL31" s="112"/>
     </row>
-    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>26</v>
       </c>
@@ -46158,7 +46166,7 @@
       <c r="CK32" s="114"/>
       <c r="CL32" s="112"/>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>27</v>
       </c>
@@ -46424,7 +46432,7 @@
       <c r="CP33" s="134"/>
       <c r="CQ33" s="135"/>
     </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>28</v>
       </c>
@@ -46679,7 +46687,7 @@
       <c r="CP34" s="137"/>
       <c r="CQ34" s="138"/>
     </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>29</v>
       </c>
@@ -46933,7 +46941,7 @@
       <c r="CK35" s="114"/>
       <c r="CL35" s="112"/>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>30</v>
       </c>
@@ -47159,7 +47167,7 @@
         <v>46222.791666666672</v>
       </c>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>31</v>
       </c>
@@ -47284,7 +47292,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>32</v>
       </c>
@@ -47549,7 +47557,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>33</v>
       </c>
@@ -47804,7 +47812,7 @@
       <c r="CP39" s="21"/>
       <c r="CQ39" s="21"/>
     </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>34</v>
       </c>
@@ -48025,7 +48033,7 @@
       <c r="CK40" s="114"/>
       <c r="CL40" s="112"/>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>35</v>
       </c>
@@ -48265,7 +48273,7 @@
       <c r="CK41" s="114"/>
       <c r="CL41" s="112"/>
     </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>36</v>
       </c>
@@ -48470,7 +48478,7 @@
       <c r="BW42" s="112"/>
       <c r="CK42" s="114"/>
     </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <v>37</v>
       </c>
@@ -48567,7 +48575,7 @@
       </c>
       <c r="CK43" s="114"/>
     </row>
-    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <v>38</v>
       </c>
@@ -48820,7 +48828,7 @@
       <c r="CP44" s="134"/>
       <c r="CQ44" s="135"/>
     </row>
-    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <v>39</v>
       </c>
@@ -49074,7 +49082,7 @@
       <c r="CP45" s="137"/>
       <c r="CQ45" s="138"/>
     </row>
-    <row r="46" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <v>40</v>
       </c>
@@ -49316,7 +49324,7 @@
       <c r="CK46" s="114"/>
       <c r="CL46" s="112"/>
     </row>
-    <row r="47" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <v>41</v>
       </c>
@@ -49581,7 +49589,7 @@
         <v>46221.875</v>
       </c>
     </row>
-    <row r="48" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <v>42</v>
       </c>
@@ -49808,7 +49816,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <v>43</v>
       </c>
@@ -49925,7 +49933,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
         <v>44</v>
       </c>
@@ -50178,7 +50186,7 @@
       <c r="CK50" s="114"/>
       <c r="CL50" s="112"/>
     </row>
-    <row r="51" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <v>45</v>
       </c>
@@ -50435,7 +50443,7 @@
       <c r="CK51" s="114"/>
       <c r="CL51" s="112"/>
     </row>
-    <row r="52" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <v>46</v>
       </c>
@@ -50684,7 +50692,7 @@
       <c r="CK52" s="114"/>
       <c r="CL52" s="112"/>
     </row>
-    <row r="53" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>47</v>
       </c>
@@ -50937,7 +50945,7 @@
       <c r="CK53" s="114"/>
       <c r="CL53" s="112"/>
     </row>
-    <row r="54" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>48</v>
       </c>
@@ -51162,7 +51170,7 @@
       </c>
       <c r="CL54" s="112"/>
     </row>
-    <row r="55" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>49</v>
       </c>
@@ -51283,7 +51291,7 @@
       </c>
       <c r="CL55" s="112"/>
     </row>
-    <row r="56" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>50</v>
       </c>
@@ -51540,7 +51548,7 @@
       </c>
       <c r="CL56" s="112"/>
     </row>
-    <row r="57" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>51</v>
       </c>
@@ -51790,7 +51798,7 @@
       <c r="CC57" s="21"/>
       <c r="CD57" s="114"/>
     </row>
-    <row r="58" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
         <v>52</v>
       </c>
@@ -52038,7 +52046,7 @@
       <c r="CC58" s="21"/>
       <c r="CD58" s="114"/>
     </row>
-    <row r="59" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <v>53</v>
       </c>
@@ -52290,7 +52298,7 @@
       <c r="CC59" s="21"/>
       <c r="CD59" s="114"/>
     </row>
-    <row r="60" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <v>54</v>
       </c>
@@ -52502,7 +52510,7 @@
       <c r="CC60" s="21"/>
       <c r="CD60" s="114"/>
     </row>
-    <row r="61" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <v>55</v>
       </c>
@@ -52613,7 +52621,7 @@
       <c r="CC61" s="21"/>
       <c r="CD61" s="114"/>
     </row>
-    <row r="62" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
         <v>56</v>
       </c>
@@ -52865,7 +52873,7 @@
       <c r="CC62" s="21"/>
       <c r="CD62" s="114"/>
     </row>
-    <row r="63" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <v>57</v>
       </c>
@@ -53121,7 +53129,7 @@
         <v>46215.041666666672</v>
       </c>
     </row>
-    <row r="64" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
         <v>58</v>
       </c>
@@ -53369,7 +53377,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
         <v>59</v>
       </c>
@@ -53621,7 +53629,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A66" s="16">
         <v>60</v>
       </c>
@@ -53826,7 +53834,7 @@
       <c r="BV66" s="21"/>
       <c r="BW66" s="114"/>
     </row>
-    <row r="67" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <v>61</v>
       </c>
@@ -53930,7 +53938,7 @@
         <v>46210.833333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
         <v>62</v>
       </c>
@@ -54194,7 +54202,7 @@
       <c r="CP68" s="153"/>
       <c r="CQ68" s="153"/>
     </row>
-    <row r="69" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <v>63</v>
       </c>
@@ -54456,7 +54464,7 @@
       <c r="CP69" s="153"/>
       <c r="CQ69" s="153"/>
     </row>
-    <row r="70" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <v>64</v>
       </c>
@@ -54692,7 +54700,7 @@
       <c r="BQ70" s="112"/>
       <c r="BW70" s="112"/>
     </row>
-    <row r="71" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <v>65</v>
       </c>
@@ -54925,7 +54933,7 @@
       </c>
       <c r="BQ71" s="112"/>
     </row>
-    <row r="72" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A72" s="16">
         <v>66</v>
       </c>
@@ -55109,7 +55117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A73" s="16">
         <v>67</v>
       </c>
@@ -55188,7 +55196,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A74" s="16">
         <v>68</v>
       </c>
@@ -55412,7 +55420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A75" s="16">
         <v>69</v>
       </c>
@@ -55636,7 +55644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A76" s="16">
         <v>70</v>
       </c>
@@ -55856,7 +55864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A77" s="16">
         <v>71</v>
       </c>
@@ -56076,7 +56084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A78" s="16">
         <v>72</v>
       </c>
@@ -56260,7 +56268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A79" s="73"/>
       <c r="B79" s="73"/>
       <c r="C79" s="73"/>
@@ -56278,7 +56286,7 @@
       <c r="O79" s="70"/>
       <c r="P79" s="70"/>
     </row>
-    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="73"/>
       <c r="B80" s="73"/>
       <c r="C80" s="73"/>
@@ -56380,7 +56388,7 @@
         <v>Ⓐ Czech Republic</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="73"/>
       <c r="B81" s="73"/>
       <c r="C81" s="73"/>
@@ -56392,7 +56400,7 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Australia</v>
+        <v>Ⓑ Switzerland</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
@@ -56420,11 +56428,11 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
-        <v>Qatar</v>
+        <v>Switzerland</v>
       </c>
       <c r="AF81" s="123">
         <f t="shared" ref="AF81:AF91" si="39">VLOOKUP($AE81,$AE$8:$AQ$78,2,FALSE)</f>
@@ -56463,26 +56471,26 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>500.00072748000002</v>
+        <v>500.00082470000001</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
-        <v>1454.96</v>
+        <v>1649.4</v>
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="AT81" s="130" t="str">
         <f>"Ⓑ "&amp;AE81</f>
-        <v>Ⓑ Qatar</v>
-      </c>
-    </row>
-    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Ⓑ Switzerland</v>
+      </c>
+    </row>
+    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="73"/>
       <c r="B82" s="73"/>
       <c r="C82" s="73"/>
@@ -56494,7 +56502,7 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓓ Australia</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
@@ -56522,7 +56530,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -56573,18 +56581,18 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Scotland</v>
+        <v/>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
         <v>Ⓒ Scotland</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
       <c r="C83" s="154" t="s">
@@ -56598,7 +56606,7 @@
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
@@ -56626,7 +56634,7 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
@@ -56677,7 +56685,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CD</v>
+        <v>BD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56688,7 +56696,7 @@
         <v>Ⓓ Australia</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
       <c r="C84" s="157"/>
@@ -56700,7 +56708,7 @@
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓖ Egypt</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56740,7 +56748,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56791,7 +56799,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDE</v>
+        <v>BDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56802,7 +56810,7 @@
         <v>Ⓔ Ivory Coast</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
       <c r="C85" s="157"/>
@@ -56814,7 +56822,7 @@
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓘ Norway</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56854,7 +56862,7 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
@@ -56905,7 +56913,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEF</v>
+        <v>BDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56916,7 +56924,7 @@
         <v>Ⓕ Sweden</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
       <c r="C86" s="157"/>
@@ -56928,7 +56936,7 @@
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -56968,7 +56976,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57019,7 +57027,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFG</v>
+        <v>BDEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57030,7 +57038,7 @@
         <v>Ⓖ Egypt</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
       <c r="C87" s="157"/>
@@ -57042,7 +57050,7 @@
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓔ Ivory Coast</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57133,7 +57141,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFG</v>
+        <v>BDEFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57144,7 +57152,7 @@
         <v>Ⓗ Saudi Arabia</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
       <c r="C88" s="160"/>
@@ -57156,7 +57164,7 @@
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓕ Sweden</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57196,7 +57204,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -57247,7 +57255,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGI</v>
+        <v>BDEFGI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57258,7 +57266,7 @@
         <v>Ⓘ Norway</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="73"/>
       <c r="B89" s="73"/>
       <c r="C89" s="73"/>
@@ -57270,7 +57278,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57310,7 +57318,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -57361,7 +57369,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJ</v>
+        <v>BDEFGIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57372,7 +57380,7 @@
         <v>Ⓙ Algeria</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="73"/>
       <c r="B90" s="73"/>
       <c r="C90" s="73"/>
@@ -57384,7 +57392,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -57424,7 +57432,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57475,7 +57483,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJ</v>
+        <v>BDEFGIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57486,7 +57494,7 @@
         <v>Ⓚ DR Congo</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="73"/>
       <c r="B91" s="73"/>
       <c r="C91" s="73"/>
@@ -57538,7 +57546,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -57589,7 +57597,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJL</v>
+        <v>BDEFGIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57600,7 +57608,7 @@
         <v>Ⓛ Panama</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="73"/>
       <c r="B92" s="73"/>
       <c r="C92" s="73"/>
@@ -57675,7 +57683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A93" s="73"/>
       <c r="B93" s="73"/>
       <c r="C93" s="73"/>
@@ -57693,7 +57701,7 @@
       <c r="O93" s="70"/>
       <c r="P93" s="70"/>
     </row>
-    <row r="95" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:46" x14ac:dyDescent="0.25">
       <c r="R95" s="123">
         <f>DATE(2026,12,9)+TIME(8,0,0)+gmt_delta</f>
         <v>46365.791666666672</v>
@@ -57707,7 +57715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R96" s="123">
         <f>DATE(2026,12,9)+TIME(4,0,0)+gmt_delta</f>
         <v>46365.625</v>
@@ -57721,7 +57729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R97" s="123">
         <f>DATE(2026,12,10)+TIME(8,0,0)+gmt_delta</f>
         <v>46366.791666666672</v>
@@ -57735,7 +57743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="98" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R98" s="123">
         <f>DATE(2026,12,10)+TIME(4,0,0)+gmt_delta</f>
         <v>46366.625</v>
@@ -57749,7 +57757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="102" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R102" s="123">
         <f>DATE(2026,12,13)+TIME(8,0,0)+gmt_delta</f>
         <v>46369.791666666672</v>
@@ -57775,7 +57783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="103" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R103" s="123">
         <f>DATE(2026,12,14)+TIME(8,0,0)+gmt_delta</f>
         <v>46370.791666666672</v>
@@ -57801,7 +57809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="107" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R107" s="123">
         <f>DATE(2026,12,17)+TIME(8,0,0)+gmt_delta</f>
         <v>46373.791666666672</v>
@@ -57811,7 +57819,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="111" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R111" s="123">
         <f>DATE(2026,12,18)+TIME(8,0,0)+gmt_delta</f>
         <v>46374.791666666672</v>
@@ -58897,33 +58905,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A2A316-429C-49FB-9962-F944380EA825}">
   <dimension ref="B1:K500"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.453125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="81"/>
-    <col min="3" max="3" width="13.7265625" style="81" customWidth="1"/>
-    <col min="4" max="11" width="9.453125" style="81" customWidth="1"/>
-    <col min="12" max="16384" width="9.1796875" style="82"/>
+    <col min="1" max="1" width="2.42578125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="81"/>
+    <col min="3" max="3" width="13.7109375" style="81" customWidth="1"/>
+    <col min="4" max="11" width="9.42578125" style="81" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="82"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B2" s="108" t="s">
         <v>3193</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>CDEFGIJL</v>
+        <v>BDEFGIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3C</v>
+        <v>3E</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -58931,7 +58939,7 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3E</v>
+        <v>3B</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
@@ -58954,7 +58962,7 @@
         <v>3I</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="84" t="s">
         <v>3194</v>
       </c>
@@ -58984,7 +58992,7 @@
         <v>3202</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="88">
         <v>1</v>
       </c>
@@ -59016,7 +59024,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="88">
         <v>2</v>
       </c>
@@ -59048,7 +59056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="88">
         <v>3</v>
       </c>
@@ -59080,7 +59088,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="88">
         <v>4</v>
       </c>
@@ -59112,7 +59120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="88">
         <v>5</v>
       </c>
@@ -59144,7 +59152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="88">
         <v>6</v>
       </c>
@@ -59176,7 +59184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="88">
         <v>7</v>
       </c>
@@ -59208,7 +59216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="88">
         <v>8</v>
       </c>
@@ -59240,7 +59248,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="88">
         <v>9</v>
       </c>
@@ -59272,7 +59280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="88">
         <v>10</v>
       </c>
@@ -59304,7 +59312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="88">
         <v>11</v>
       </c>
@@ -59336,7 +59344,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="88">
         <v>12</v>
       </c>
@@ -59368,7 +59376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="88">
         <v>13</v>
       </c>
@@ -59400,7 +59408,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="88">
         <v>14</v>
       </c>
@@ -59432,7 +59440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="88">
         <v>15</v>
       </c>
@@ -59464,7 +59472,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="88">
         <v>16</v>
       </c>
@@ -59496,7 +59504,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="88">
         <v>17</v>
       </c>
@@ -59528,7 +59536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="88">
         <v>18</v>
       </c>
@@ -59560,7 +59568,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="88">
         <v>19</v>
       </c>
@@ -59592,7 +59600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="88">
         <v>20</v>
       </c>
@@ -59624,7 +59632,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="88">
         <v>21</v>
       </c>
@@ -59656,7 +59664,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="88">
         <v>22</v>
       </c>
@@ -59688,7 +59696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="88">
         <v>23</v>
       </c>
@@ -59720,7 +59728,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="88">
         <v>24</v>
       </c>
@@ -59752,7 +59760,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="88">
         <v>25</v>
       </c>
@@ -59784,7 +59792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="88">
         <v>26</v>
       </c>
@@ -59816,7 +59824,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="88">
         <v>27</v>
       </c>
@@ -59848,7 +59856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="88">
         <v>28</v>
       </c>
@@ -59880,7 +59888,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="88">
         <v>29</v>
       </c>
@@ -59912,7 +59920,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="88">
         <v>30</v>
       </c>
@@ -59944,7 +59952,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="88">
         <v>31</v>
       </c>
@@ -59976,7 +59984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="88">
         <v>32</v>
       </c>
@@ -60008,7 +60016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="88">
         <v>33</v>
       </c>
@@ -60040,7 +60048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="88">
         <v>34</v>
       </c>
@@ -60072,7 +60080,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="88">
         <v>35</v>
       </c>
@@ -60104,7 +60112,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="88">
         <v>36</v>
       </c>
@@ -60136,7 +60144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="88">
         <v>37</v>
       </c>
@@ -60168,7 +60176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="88">
         <v>38</v>
       </c>
@@ -60200,7 +60208,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="88">
         <v>39</v>
       </c>
@@ -60232,7 +60240,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="88">
         <v>40</v>
       </c>
@@ -60264,7 +60272,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="88">
         <v>41</v>
       </c>
@@ -60296,7 +60304,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="88">
         <v>42</v>
       </c>
@@ -60328,7 +60336,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="88">
         <v>43</v>
       </c>
@@ -60360,7 +60368,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="88">
         <v>44</v>
       </c>
@@ -60392,7 +60400,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="88">
         <v>45</v>
       </c>
@@ -60424,7 +60432,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="88">
         <v>46</v>
       </c>
@@ -60456,7 +60464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="88">
         <v>47</v>
       </c>
@@ -60488,7 +60496,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" s="88">
         <v>48</v>
       </c>
@@ -60520,7 +60528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" s="88">
         <v>49</v>
       </c>
@@ -60552,7 +60560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" s="88">
         <v>50</v>
       </c>
@@ -60584,7 +60592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="88">
         <v>51</v>
       </c>
@@ -60616,7 +60624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" s="88">
         <v>52</v>
       </c>
@@ -60648,7 +60656,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="88">
         <v>53</v>
       </c>
@@ -60680,7 +60688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="88">
         <v>54</v>
       </c>
@@ -60712,7 +60720,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="88">
         <v>55</v>
       </c>
@@ -60744,7 +60752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="88">
         <v>56</v>
       </c>
@@ -60776,7 +60784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="88">
         <v>57</v>
       </c>
@@ -60808,7 +60816,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="88">
         <v>58</v>
       </c>
@@ -60840,7 +60848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="88">
         <v>59</v>
       </c>
@@ -60872,7 +60880,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="88">
         <v>60</v>
       </c>
@@ -60904,7 +60912,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="88">
         <v>61</v>
       </c>
@@ -60936,7 +60944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" s="88">
         <v>62</v>
       </c>
@@ -60968,7 +60976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" s="88">
         <v>63</v>
       </c>
@@ -61000,7 +61008,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" s="88">
         <v>64</v>
       </c>
@@ -61032,7 +61040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" s="88">
         <v>65</v>
       </c>
@@ -61064,7 +61072,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" s="88">
         <v>66</v>
       </c>
@@ -61096,7 +61104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" s="88">
         <v>67</v>
       </c>
@@ -61128,7 +61136,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" s="88">
         <v>68</v>
       </c>
@@ -61160,7 +61168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" s="88">
         <v>69</v>
       </c>
@@ -61192,7 +61200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" s="88">
         <v>70</v>
       </c>
@@ -61224,7 +61232,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" s="88">
         <v>71</v>
       </c>
@@ -61256,7 +61264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" s="88">
         <v>72</v>
       </c>
@@ -61288,7 +61296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" s="88">
         <v>73</v>
       </c>
@@ -61320,7 +61328,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="88">
         <v>74</v>
       </c>
@@ -61352,7 +61360,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" s="88">
         <v>75</v>
       </c>
@@ -61384,7 +61392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" s="88">
         <v>76</v>
       </c>
@@ -61416,7 +61424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" s="88">
         <v>77</v>
       </c>
@@ -61448,7 +61456,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" s="88">
         <v>78</v>
       </c>
@@ -61480,7 +61488,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" s="88">
         <v>79</v>
       </c>
@@ -61512,7 +61520,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" s="88">
         <v>80</v>
       </c>
@@ -61544,7 +61552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" s="88">
         <v>81</v>
       </c>
@@ -61576,7 +61584,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" s="88">
         <v>82</v>
       </c>
@@ -61608,7 +61616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" s="88">
         <v>83</v>
       </c>
@@ -61640,7 +61648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" s="88">
         <v>84</v>
       </c>
@@ -61672,7 +61680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" s="88">
         <v>85</v>
       </c>
@@ -61704,7 +61712,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" s="88">
         <v>86</v>
       </c>
@@ -61736,7 +61744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" s="88">
         <v>87</v>
       </c>
@@ -61768,7 +61776,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" s="88">
         <v>88</v>
       </c>
@@ -61800,7 +61808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" s="88">
         <v>89</v>
       </c>
@@ -61832,7 +61840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" s="88">
         <v>90</v>
       </c>
@@ -61864,7 +61872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" s="88">
         <v>91</v>
       </c>
@@ -61896,7 +61904,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" s="88">
         <v>92</v>
       </c>
@@ -61928,7 +61936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" s="88">
         <v>93</v>
       </c>
@@ -61960,7 +61968,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" s="88">
         <v>94</v>
       </c>
@@ -61992,7 +62000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" s="88">
         <v>95</v>
       </c>
@@ -62024,7 +62032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="88">
         <v>96</v>
       </c>
@@ -62056,7 +62064,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" s="88">
         <v>97</v>
       </c>
@@ -62088,7 +62096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" s="88">
         <v>98</v>
       </c>
@@ -62120,7 +62128,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" s="88">
         <v>99</v>
       </c>
@@ -62152,7 +62160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" s="88">
         <v>100</v>
       </c>
@@ -62184,7 +62192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" s="88">
         <v>101</v>
       </c>
@@ -62216,7 +62224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" s="88">
         <v>102</v>
       </c>
@@ -62248,7 +62256,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" s="88">
         <v>103</v>
       </c>
@@ -62280,7 +62288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" s="88">
         <v>104</v>
       </c>
@@ -62312,7 +62320,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" s="88">
         <v>105</v>
       </c>
@@ -62344,7 +62352,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" s="88">
         <v>106</v>
       </c>
@@ -62376,7 +62384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" s="88">
         <v>107</v>
       </c>
@@ -62408,7 +62416,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" s="88">
         <v>108</v>
       </c>
@@ -62440,7 +62448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" s="88">
         <v>109</v>
       </c>
@@ -62472,7 +62480,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" s="88">
         <v>110</v>
       </c>
@@ -62504,7 +62512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" s="88">
         <v>111</v>
       </c>
@@ -62536,7 +62544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" s="88">
         <v>112</v>
       </c>
@@ -62568,7 +62576,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" s="88">
         <v>113</v>
       </c>
@@ -62600,7 +62608,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" s="88">
         <v>114</v>
       </c>
@@ -62632,7 +62640,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" s="88">
         <v>115</v>
       </c>
@@ -62664,7 +62672,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" s="88">
         <v>116</v>
       </c>
@@ -62696,7 +62704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" s="88">
         <v>117</v>
       </c>
@@ -62728,7 +62736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" s="88">
         <v>118</v>
       </c>
@@ -62760,7 +62768,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" s="88">
         <v>119</v>
       </c>
@@ -62792,7 +62800,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" s="88">
         <v>120</v>
       </c>
@@ -62824,7 +62832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" s="88">
         <v>121</v>
       </c>
@@ -62856,7 +62864,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" s="88">
         <v>122</v>
       </c>
@@ -62888,7 +62896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" s="88">
         <v>123</v>
       </c>
@@ -62920,7 +62928,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" s="88">
         <v>124</v>
       </c>
@@ -62952,7 +62960,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" s="88">
         <v>125</v>
       </c>
@@ -62984,7 +62992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" s="88">
         <v>126</v>
       </c>
@@ -63016,7 +63024,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" s="88">
         <v>127</v>
       </c>
@@ -63048,7 +63056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" s="88">
         <v>128</v>
       </c>
@@ -63080,7 +63088,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" s="88">
         <v>129</v>
       </c>
@@ -63112,7 +63120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" s="88">
         <v>130</v>
       </c>
@@ -63144,7 +63152,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" s="88">
         <v>131</v>
       </c>
@@ -63176,7 +63184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" s="88">
         <v>132</v>
       </c>
@@ -63208,7 +63216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" s="88">
         <v>133</v>
       </c>
@@ -63240,7 +63248,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" s="88">
         <v>134</v>
       </c>
@@ -63272,7 +63280,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" s="88">
         <v>135</v>
       </c>
@@ -63304,7 +63312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" s="88">
         <v>136</v>
       </c>
@@ -63336,7 +63344,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" s="88">
         <v>137</v>
       </c>
@@ -63368,7 +63376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" s="88">
         <v>138</v>
       </c>
@@ -63400,7 +63408,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" s="88">
         <v>139</v>
       </c>
@@ -63432,7 +63440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" s="88">
         <v>140</v>
       </c>
@@ -63464,7 +63472,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" s="88">
         <v>141</v>
       </c>
@@ -63496,7 +63504,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" s="88">
         <v>142</v>
       </c>
@@ -63528,7 +63536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" s="88">
         <v>143</v>
       </c>
@@ -63560,7 +63568,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" s="88">
         <v>144</v>
       </c>
@@ -63592,7 +63600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" s="88">
         <v>145</v>
       </c>
@@ -63624,7 +63632,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" s="88">
         <v>146</v>
       </c>
@@ -63656,7 +63664,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" s="88">
         <v>147</v>
       </c>
@@ -63688,7 +63696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" s="88">
         <v>148</v>
       </c>
@@ -63720,7 +63728,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" s="88">
         <v>149</v>
       </c>
@@ -63752,7 +63760,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" s="88">
         <v>150</v>
       </c>
@@ -63784,7 +63792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" s="88">
         <v>151</v>
       </c>
@@ -63816,7 +63824,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" s="88">
         <v>152</v>
       </c>
@@ -63848,7 +63856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" s="88">
         <v>153</v>
       </c>
@@ -63880,7 +63888,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" s="88">
         <v>154</v>
       </c>
@@ -63912,7 +63920,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" s="88">
         <v>155</v>
       </c>
@@ -63944,7 +63952,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" s="88">
         <v>156</v>
       </c>
@@ -63976,7 +63984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" s="88">
         <v>157</v>
       </c>
@@ -64008,7 +64016,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" s="88">
         <v>158</v>
       </c>
@@ -64040,7 +64048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" s="88">
         <v>159</v>
       </c>
@@ -64072,7 +64080,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" s="88">
         <v>160</v>
       </c>
@@ -64104,7 +64112,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" s="88">
         <v>161</v>
       </c>
@@ -64136,7 +64144,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" s="88">
         <v>162</v>
       </c>
@@ -64168,7 +64176,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" s="88">
         <v>163</v>
       </c>
@@ -64200,7 +64208,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" s="88">
         <v>164</v>
       </c>
@@ -64232,7 +64240,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B170" s="88">
         <v>165</v>
       </c>
@@ -64264,7 +64272,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" s="88">
         <v>166</v>
       </c>
@@ -64296,7 +64304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" s="88">
         <v>167</v>
       </c>
@@ -64328,7 +64336,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" s="88">
         <v>168</v>
       </c>
@@ -64360,7 +64368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" s="88">
         <v>169</v>
       </c>
@@ -64392,7 +64400,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" s="88">
         <v>170</v>
       </c>
@@ -64424,7 +64432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" s="88">
         <v>171</v>
       </c>
@@ -64456,7 +64464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" s="88">
         <v>172</v>
       </c>
@@ -64488,7 +64496,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" s="88">
         <v>173</v>
       </c>
@@ -64520,7 +64528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" s="88">
         <v>174</v>
       </c>
@@ -64552,7 +64560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" s="88">
         <v>175</v>
       </c>
@@ -64584,7 +64592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" s="88">
         <v>176</v>
       </c>
@@ -64616,7 +64624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" s="88">
         <v>177</v>
       </c>
@@ -64648,7 +64656,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" s="88">
         <v>178</v>
       </c>
@@ -64680,7 +64688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" s="88">
         <v>179</v>
       </c>
@@ -64712,7 +64720,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" s="88">
         <v>180</v>
       </c>
@@ -64744,7 +64752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" s="88">
         <v>181</v>
       </c>
@@ -64776,7 +64784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" s="88">
         <v>182</v>
       </c>
@@ -64808,7 +64816,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" s="88">
         <v>183</v>
       </c>
@@ -64840,7 +64848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" s="88">
         <v>184</v>
       </c>
@@ -64872,7 +64880,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" s="88">
         <v>185</v>
       </c>
@@ -64904,7 +64912,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" s="88">
         <v>186</v>
       </c>
@@ -64936,7 +64944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" s="88">
         <v>187</v>
       </c>
@@ -64968,7 +64976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" s="88">
         <v>188</v>
       </c>
@@ -65000,7 +65008,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" s="88">
         <v>189</v>
       </c>
@@ -65032,7 +65040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" s="88">
         <v>190</v>
       </c>
@@ -65064,7 +65072,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" s="88">
         <v>191</v>
       </c>
@@ -65096,7 +65104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" s="88">
         <v>192</v>
       </c>
@@ -65128,7 +65136,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" s="88">
         <v>193</v>
       </c>
@@ -65160,7 +65168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" s="88">
         <v>194</v>
       </c>
@@ -65192,7 +65200,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" s="88">
         <v>195</v>
       </c>
@@ -65224,7 +65232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" s="88">
         <v>196</v>
       </c>
@@ -65256,7 +65264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" s="88">
         <v>197</v>
       </c>
@@ -65288,7 +65296,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" s="88">
         <v>198</v>
       </c>
@@ -65320,7 +65328,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" s="88">
         <v>199</v>
       </c>
@@ -65352,7 +65360,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" s="88">
         <v>200</v>
       </c>
@@ -65384,7 +65392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" s="88">
         <v>201</v>
       </c>
@@ -65416,7 +65424,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" s="88">
         <v>202</v>
       </c>
@@ -65448,7 +65456,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" s="88">
         <v>203</v>
       </c>
@@ -65480,7 +65488,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" s="88">
         <v>204</v>
       </c>
@@ -65512,7 +65520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" s="88">
         <v>205</v>
       </c>
@@ -65544,7 +65552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211" s="88">
         <v>206</v>
       </c>
@@ -65576,7 +65584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" s="88">
         <v>207</v>
       </c>
@@ -65608,7 +65616,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" s="88">
         <v>208</v>
       </c>
@@ -65640,7 +65648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" s="88">
         <v>209</v>
       </c>
@@ -65672,7 +65680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" s="88">
         <v>210</v>
       </c>
@@ -65704,7 +65712,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" s="88">
         <v>211</v>
       </c>
@@ -65736,7 +65744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" s="88">
         <v>212</v>
       </c>
@@ -65768,7 +65776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" s="88">
         <v>213</v>
       </c>
@@ -65800,7 +65808,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" s="88">
         <v>214</v>
       </c>
@@ -65832,7 +65840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" s="88">
         <v>215</v>
       </c>
@@ -65864,7 +65872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" s="88">
         <v>216</v>
       </c>
@@ -65896,7 +65904,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" s="88">
         <v>217</v>
       </c>
@@ -65928,7 +65936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" s="88">
         <v>218</v>
       </c>
@@ -65960,7 +65968,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" s="88">
         <v>219</v>
       </c>
@@ -65992,7 +66000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" s="88">
         <v>220</v>
       </c>
@@ -66024,7 +66032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226" s="88">
         <v>221</v>
       </c>
@@ -66056,7 +66064,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" s="88">
         <v>222</v>
       </c>
@@ -66088,7 +66096,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" s="88">
         <v>223</v>
       </c>
@@ -66120,7 +66128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" s="88">
         <v>224</v>
       </c>
@@ -66152,7 +66160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" s="88">
         <v>225</v>
       </c>
@@ -66184,7 +66192,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" s="88">
         <v>226</v>
       </c>
@@ -66216,7 +66224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" s="88">
         <v>227</v>
       </c>
@@ -66248,7 +66256,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" s="88">
         <v>228</v>
       </c>
@@ -66280,7 +66288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" s="88">
         <v>229</v>
       </c>
@@ -66312,7 +66320,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" s="88">
         <v>230</v>
       </c>
@@ -66344,7 +66352,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" s="88">
         <v>231</v>
       </c>
@@ -66376,7 +66384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" s="88">
         <v>232</v>
       </c>
@@ -66408,7 +66416,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" s="88">
         <v>233</v>
       </c>
@@ -66440,7 +66448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" s="88">
         <v>234</v>
       </c>
@@ -66472,7 +66480,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" s="88">
         <v>235</v>
       </c>
@@ -66504,7 +66512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" s="88">
         <v>236</v>
       </c>
@@ -66536,7 +66544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" s="88">
         <v>237</v>
       </c>
@@ -66568,7 +66576,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" s="88">
         <v>238</v>
       </c>
@@ -66600,7 +66608,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" s="88">
         <v>239</v>
       </c>
@@ -66632,7 +66640,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" s="88">
         <v>240</v>
       </c>
@@ -66664,7 +66672,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" s="88">
         <v>241</v>
       </c>
@@ -66696,7 +66704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247" s="88">
         <v>242</v>
       </c>
@@ -66728,7 +66736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" s="88">
         <v>243</v>
       </c>
@@ -66760,7 +66768,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" s="88">
         <v>244</v>
       </c>
@@ -66792,7 +66800,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="250" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" s="88">
         <v>245</v>
       </c>
@@ -66824,7 +66832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="251" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" s="88">
         <v>246</v>
       </c>
@@ -66856,7 +66864,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="252" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" s="88">
         <v>247</v>
       </c>
@@ -66888,7 +66896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="253" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" s="88">
         <v>248</v>
       </c>
@@ -66920,7 +66928,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="254" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" s="88">
         <v>249</v>
       </c>
@@ -66952,7 +66960,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="255" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255" s="88">
         <v>250</v>
       </c>
@@ -66984,7 +66992,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="256" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B256" s="88">
         <v>251</v>
       </c>
@@ -67016,7 +67024,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="257" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" s="88">
         <v>252</v>
       </c>
@@ -67048,7 +67056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" s="88">
         <v>253</v>
       </c>
@@ -67080,7 +67088,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="259" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" s="88">
         <v>254</v>
       </c>
@@ -67112,7 +67120,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260" s="88">
         <v>255</v>
       </c>
@@ -67144,7 +67152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" s="88">
         <v>256</v>
       </c>
@@ -67176,7 +67184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262" s="88">
         <v>257</v>
       </c>
@@ -67208,7 +67216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" s="88">
         <v>258</v>
       </c>
@@ -67240,7 +67248,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" s="88">
         <v>259</v>
       </c>
@@ -67272,7 +67280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" s="88">
         <v>260</v>
       </c>
@@ -67304,7 +67312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="266" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" s="88">
         <v>261</v>
       </c>
@@ -67336,7 +67344,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" s="88">
         <v>262</v>
       </c>
@@ -67368,7 +67376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="268" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" s="88">
         <v>263</v>
       </c>
@@ -67400,7 +67408,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" s="88">
         <v>264</v>
       </c>
@@ -67432,7 +67440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" s="88">
         <v>265</v>
       </c>
@@ -67464,7 +67472,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" s="88">
         <v>266</v>
       </c>
@@ -67496,7 +67504,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="272" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" s="88">
         <v>267</v>
       </c>
@@ -67528,7 +67536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="273" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" s="88">
         <v>268</v>
       </c>
@@ -67560,7 +67568,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="274" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" s="88">
         <v>269</v>
       </c>
@@ -67592,7 +67600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="275" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" s="88">
         <v>270</v>
       </c>
@@ -67624,7 +67632,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="276" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" s="88">
         <v>271</v>
       </c>
@@ -67656,7 +67664,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="277" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" s="88">
         <v>272</v>
       </c>
@@ -67688,7 +67696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="278" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" s="88">
         <v>273</v>
       </c>
@@ -67720,7 +67728,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="279" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" s="88">
         <v>274</v>
       </c>
@@ -67752,7 +67760,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="280" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" s="88">
         <v>275</v>
       </c>
@@ -67784,7 +67792,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="281" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" s="88">
         <v>276</v>
       </c>
@@ -67816,7 +67824,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="282" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" s="88">
         <v>277</v>
       </c>
@@ -67848,7 +67856,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="283" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" s="88">
         <v>278</v>
       </c>
@@ -67880,7 +67888,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="284" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284" s="88">
         <v>279</v>
       </c>
@@ -67912,7 +67920,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="285" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" s="88">
         <v>280</v>
       </c>
@@ -67944,7 +67952,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="286" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" s="88">
         <v>281</v>
       </c>
@@ -67976,7 +67984,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287" s="88">
         <v>282</v>
       </c>
@@ -68008,7 +68016,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="288" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" s="88">
         <v>283</v>
       </c>
@@ -68040,7 +68048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" s="88">
         <v>284</v>
       </c>
@@ -68072,7 +68080,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" s="88">
         <v>285</v>
       </c>
@@ -68104,7 +68112,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" s="88">
         <v>286</v>
       </c>
@@ -68136,7 +68144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" s="88">
         <v>287</v>
       </c>
@@ -68168,7 +68176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B293" s="88">
         <v>288</v>
       </c>
@@ -68200,7 +68208,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" s="88">
         <v>289</v>
       </c>
@@ -68232,7 +68240,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" s="88">
         <v>290</v>
       </c>
@@ -68264,7 +68272,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="296" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296" s="88">
         <v>291</v>
       </c>
@@ -68296,7 +68304,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297" s="88">
         <v>292</v>
       </c>
@@ -68328,7 +68336,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298" s="88">
         <v>293</v>
       </c>
@@ -68360,7 +68368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299" s="88">
         <v>294</v>
       </c>
@@ -68392,7 +68400,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300" s="88">
         <v>295</v>
       </c>
@@ -68424,7 +68432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="301" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B301" s="88">
         <v>296</v>
       </c>
@@ -68456,7 +68464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="302" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B302" s="88">
         <v>297</v>
       </c>
@@ -68488,7 +68496,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B303" s="88">
         <v>298</v>
       </c>
@@ -68520,7 +68528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="304" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B304" s="88">
         <v>299</v>
       </c>
@@ -68552,7 +68560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B305" s="88">
         <v>300</v>
       </c>
@@ -68584,7 +68592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B306" s="88">
         <v>301</v>
       </c>
@@ -68616,7 +68624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B307" s="88">
         <v>302</v>
       </c>
@@ -68648,7 +68656,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B308" s="88">
         <v>303</v>
       </c>
@@ -68680,7 +68688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B309" s="88">
         <v>304</v>
       </c>
@@ -68712,7 +68720,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B310" s="88">
         <v>305</v>
       </c>
@@ -68744,7 +68752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="311" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B311" s="88">
         <v>306</v>
       </c>
@@ -68776,7 +68784,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="312" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B312" s="88">
         <v>307</v>
       </c>
@@ -68808,7 +68816,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B313" s="88">
         <v>308</v>
       </c>
@@ -68840,7 +68848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B314" s="88">
         <v>309</v>
       </c>
@@ -68872,7 +68880,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B315" s="88">
         <v>310</v>
       </c>
@@ -68904,7 +68912,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B316" s="88">
         <v>311</v>
       </c>
@@ -68936,7 +68944,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B317" s="88">
         <v>312</v>
       </c>
@@ -68968,7 +68976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="318" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B318" s="88">
         <v>313</v>
       </c>
@@ -69000,7 +69008,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="319" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B319" s="88">
         <v>314</v>
       </c>
@@ -69032,7 +69040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B320" s="88">
         <v>315</v>
       </c>
@@ -69064,7 +69072,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="321" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B321" s="88">
         <v>316</v>
       </c>
@@ -69096,7 +69104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="322" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B322" s="88">
         <v>317</v>
       </c>
@@ -69128,7 +69136,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="323" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B323" s="88">
         <v>318</v>
       </c>
@@ -69160,7 +69168,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="324" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B324" s="88">
         <v>319</v>
       </c>
@@ -69192,7 +69200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" s="88">
         <v>320</v>
       </c>
@@ -69224,7 +69232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="326" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B326" s="88">
         <v>321</v>
       </c>
@@ -69256,7 +69264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="327" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B327" s="88">
         <v>322</v>
       </c>
@@ -69288,7 +69296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="328" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B328" s="88">
         <v>323</v>
       </c>
@@ -69320,7 +69328,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="329" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B329" s="88">
         <v>324</v>
       </c>
@@ -69352,7 +69360,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="330" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B330" s="88">
         <v>325</v>
       </c>
@@ -69384,7 +69392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="331" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B331" s="88">
         <v>326</v>
       </c>
@@ -69416,7 +69424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="332" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B332" s="88">
         <v>327</v>
       </c>
@@ -69448,7 +69456,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="333" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B333" s="88">
         <v>328</v>
       </c>
@@ -69480,7 +69488,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="334" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B334" s="88">
         <v>329</v>
       </c>
@@ -69512,7 +69520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="335" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B335" s="88">
         <v>330</v>
       </c>
@@ -69544,7 +69552,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" s="88">
         <v>331</v>
       </c>
@@ -69576,7 +69584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="337" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B337" s="88">
         <v>332</v>
       </c>
@@ -69608,7 +69616,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" s="88">
         <v>333</v>
       </c>
@@ -69640,7 +69648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="339" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B339" s="88">
         <v>334</v>
       </c>
@@ -69672,7 +69680,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="340" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B340" s="88">
         <v>335</v>
       </c>
@@ -69704,7 +69712,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="341" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B341" s="88">
         <v>336</v>
       </c>
@@ -69736,7 +69744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="342" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B342" s="88">
         <v>337</v>
       </c>
@@ -69768,7 +69776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="343" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="343" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B343" s="88">
         <v>338</v>
       </c>
@@ -69800,7 +69808,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="344" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="344" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B344" s="88">
         <v>339</v>
       </c>
@@ -69832,7 +69840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="345" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B345" s="88">
         <v>340</v>
       </c>
@@ -69864,7 +69872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="346" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B346" s="88">
         <v>341</v>
       </c>
@@ -69896,7 +69904,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="347" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B347" s="88">
         <v>342</v>
       </c>
@@ -69928,7 +69936,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="348" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B348" s="88">
         <v>343</v>
       </c>
@@ -69960,7 +69968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="349" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B349" s="88">
         <v>344</v>
       </c>
@@ -69992,7 +70000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="350" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B350" s="88">
         <v>345</v>
       </c>
@@ -70024,7 +70032,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="351" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B351" s="88">
         <v>346</v>
       </c>
@@ -70056,7 +70064,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="352" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B352" s="88">
         <v>347</v>
       </c>
@@ -70088,7 +70096,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="353" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="353" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B353" s="88">
         <v>348</v>
       </c>
@@ -70120,7 +70128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" s="88">
         <v>349</v>
       </c>
@@ -70152,7 +70160,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="355" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B355" s="88">
         <v>350</v>
       </c>
@@ -70184,7 +70192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" s="88">
         <v>351</v>
       </c>
@@ -70216,7 +70224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="357" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B357" s="88">
         <v>352</v>
       </c>
@@ -70248,7 +70256,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="358" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B358" s="88">
         <v>353</v>
       </c>
@@ -70280,7 +70288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="359" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B359" s="88">
         <v>354</v>
       </c>
@@ -70312,7 +70320,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="360" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B360" s="88">
         <v>355</v>
       </c>
@@ -70344,7 +70352,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="361" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="361" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B361" s="88">
         <v>356</v>
       </c>
@@ -70376,7 +70384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="362" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B362" s="88">
         <v>357</v>
       </c>
@@ -70408,7 +70416,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="363" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="363" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B363" s="88">
         <v>358</v>
       </c>
@@ -70440,7 +70448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="364" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B364" s="88">
         <v>359</v>
       </c>
@@ -70472,7 +70480,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="365" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B365" s="88">
         <v>360</v>
       </c>
@@ -70504,7 +70512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="366" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B366" s="88">
         <v>361</v>
       </c>
@@ -70536,7 +70544,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="367" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B367" s="88">
         <v>362</v>
       </c>
@@ -70568,7 +70576,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="368" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B368" s="88">
         <v>363</v>
       </c>
@@ -70600,7 +70608,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="369" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B369" s="88">
         <v>364</v>
       </c>
@@ -70632,7 +70640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="370" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B370" s="88">
         <v>365</v>
       </c>
@@ -70664,7 +70672,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="371" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="371" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B371" s="88">
         <v>366</v>
       </c>
@@ -70696,7 +70704,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" s="88">
         <v>367</v>
       </c>
@@ -70728,7 +70736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="373" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="373" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B373" s="88">
         <v>368</v>
       </c>
@@ -70760,7 +70768,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="374" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="374" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B374" s="88">
         <v>369</v>
       </c>
@@ -70792,7 +70800,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B375" s="88">
         <v>370</v>
       </c>
@@ -70824,7 +70832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B376" s="88">
         <v>371</v>
       </c>
@@ -70856,7 +70864,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="377" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B377" s="88">
         <v>372</v>
       </c>
@@ -70888,7 +70896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="378" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B378" s="88">
         <v>373</v>
       </c>
@@ -70920,7 +70928,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="379" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B379" s="88">
         <v>374</v>
       </c>
@@ -70952,7 +70960,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="380" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B380" s="88">
         <v>375</v>
       </c>
@@ -70984,7 +70992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="381" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B381" s="88">
         <v>376</v>
       </c>
@@ -71016,7 +71024,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" s="88">
         <v>377</v>
       </c>
@@ -71048,7 +71056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="383" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="383" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B383" s="88">
         <v>378</v>
       </c>
@@ -71080,7 +71088,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="384" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="384" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B384" s="88">
         <v>379</v>
       </c>
@@ -71112,7 +71120,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="385" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B385" s="88">
         <v>380</v>
       </c>
@@ -71144,7 +71152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="386" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B386" s="88">
         <v>381</v>
       </c>
@@ -71176,7 +71184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="387" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B387" s="88">
         <v>382</v>
       </c>
@@ -71208,7 +71216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="388" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B388" s="88">
         <v>383</v>
       </c>
@@ -71240,7 +71248,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="389" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B389" s="88">
         <v>384</v>
       </c>
@@ -71272,7 +71280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="390" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B390" s="88">
         <v>385</v>
       </c>
@@ -71304,7 +71312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="391" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B391" s="88">
         <v>386</v>
       </c>
@@ -71336,7 +71344,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="392" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B392" s="88">
         <v>387</v>
       </c>
@@ -71368,7 +71376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="393" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B393" s="88">
         <v>388</v>
       </c>
@@ -71400,7 +71408,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="394" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B394" s="88">
         <v>389</v>
       </c>
@@ -71432,7 +71440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="395" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B395" s="88">
         <v>390</v>
       </c>
@@ -71464,7 +71472,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B396" s="88">
         <v>391</v>
       </c>
@@ -71496,7 +71504,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B397" s="88">
         <v>392</v>
       </c>
@@ -71528,7 +71536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B398" s="88">
         <v>393</v>
       </c>
@@ -71560,7 +71568,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="399" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B399" s="88">
         <v>394</v>
       </c>
@@ -71592,7 +71600,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B400" s="88">
         <v>395</v>
       </c>
@@ -71624,7 +71632,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="401" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B401" s="88">
         <v>396</v>
       </c>
@@ -71656,7 +71664,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="402" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="402" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B402" s="88">
         <v>397</v>
       </c>
@@ -71688,7 +71696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="403" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B403" s="88">
         <v>398</v>
       </c>
@@ -71720,7 +71728,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="404" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B404" s="88">
         <v>399</v>
       </c>
@@ -71752,7 +71760,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="405" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="405" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B405" s="88">
         <v>400</v>
       </c>
@@ -71784,7 +71792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="406" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B406" s="88">
         <v>401</v>
       </c>
@@ -71816,7 +71824,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="407" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="407" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B407" s="88">
         <v>402</v>
       </c>
@@ -71848,7 +71856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="408" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="408" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B408" s="88">
         <v>403</v>
       </c>
@@ -71880,7 +71888,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="409" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="409" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B409" s="88">
         <v>404</v>
       </c>
@@ -71912,7 +71920,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="410" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B410" s="88">
         <v>405</v>
       </c>
@@ -71944,7 +71952,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="411" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="411" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B411" s="88">
         <v>406</v>
       </c>
@@ -71976,7 +71984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="412" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B412" s="88">
         <v>407</v>
       </c>
@@ -72008,7 +72016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="413" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B413" s="88">
         <v>408</v>
       </c>
@@ -72040,7 +72048,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="414" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="414" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B414" s="88">
         <v>409</v>
       </c>
@@ -72072,7 +72080,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="415" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="415" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B415" s="88">
         <v>410</v>
       </c>
@@ -72104,7 +72112,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="416" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="416" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B416" s="88">
         <v>411</v>
       </c>
@@ -72136,7 +72144,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="417" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B417" s="88">
         <v>412</v>
       </c>
@@ -72168,7 +72176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="418" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B418" s="88">
         <v>413</v>
       </c>
@@ -72200,7 +72208,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="419" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B419" s="88">
         <v>414</v>
       </c>
@@ -72232,7 +72240,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="420" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B420" s="88">
         <v>415</v>
       </c>
@@ -72264,7 +72272,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B421" s="88">
         <v>416</v>
       </c>
@@ -72296,7 +72304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B422" s="88">
         <v>417</v>
       </c>
@@ -72328,7 +72336,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B423" s="88">
         <v>418</v>
       </c>
@@ -72360,7 +72368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B424" s="88">
         <v>419</v>
       </c>
@@ -72392,7 +72400,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B425" s="88">
         <v>420</v>
       </c>
@@ -72424,7 +72432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B426" s="88">
         <v>421</v>
       </c>
@@ -72456,7 +72464,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B427" s="88">
         <v>422</v>
       </c>
@@ -72488,7 +72496,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B428" s="88">
         <v>423</v>
       </c>
@@ -72520,7 +72528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B429" s="88">
         <v>424</v>
       </c>
@@ -72552,7 +72560,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B430" s="88">
         <v>425</v>
       </c>
@@ -72584,7 +72592,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B431" s="88">
         <v>426</v>
       </c>
@@ -72616,7 +72624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B432" s="88">
         <v>427</v>
       </c>
@@ -72648,7 +72656,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B433" s="88">
         <v>428</v>
       </c>
@@ -72680,7 +72688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B434" s="88">
         <v>429</v>
       </c>
@@ -72712,7 +72720,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B435" s="88">
         <v>430</v>
       </c>
@@ -72744,7 +72752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B436" s="88">
         <v>431</v>
       </c>
@@ -72776,7 +72784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B437" s="88">
         <v>432</v>
       </c>
@@ -72808,7 +72816,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B438" s="88">
         <v>433</v>
       </c>
@@ -72840,7 +72848,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B439" s="88">
         <v>434</v>
       </c>
@@ -72872,7 +72880,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B440" s="88">
         <v>435</v>
       </c>
@@ -72904,7 +72912,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B441" s="88">
         <v>436</v>
       </c>
@@ -72936,7 +72944,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B442" s="88">
         <v>437</v>
       </c>
@@ -72968,7 +72976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B443" s="88">
         <v>438</v>
       </c>
@@ -73000,7 +73008,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B444" s="88">
         <v>439</v>
       </c>
@@ -73032,7 +73040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B445" s="88">
         <v>440</v>
       </c>
@@ -73064,7 +73072,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="446" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="446" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B446" s="88">
         <v>441</v>
       </c>
@@ -73096,7 +73104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="447" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B447" s="88">
         <v>442</v>
       </c>
@@ -73128,7 +73136,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B448" s="88">
         <v>443</v>
       </c>
@@ -73160,7 +73168,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="449" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="449" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B449" s="88">
         <v>444</v>
       </c>
@@ -73192,7 +73200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="450" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B450" s="88">
         <v>445</v>
       </c>
@@ -73224,7 +73232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="451" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B451" s="88">
         <v>446</v>
       </c>
@@ -73256,7 +73264,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="452" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B452" s="88">
         <v>447</v>
       </c>
@@ -73288,7 +73296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B453" s="88">
         <v>448</v>
       </c>
@@ -73320,7 +73328,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="454" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B454" s="88">
         <v>449</v>
       </c>
@@ -73352,7 +73360,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="455" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B455" s="88">
         <v>450</v>
       </c>
@@ -73384,7 +73392,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="456" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B456" s="88">
         <v>451</v>
       </c>
@@ -73416,7 +73424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="457" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B457" s="88">
         <v>452</v>
       </c>
@@ -73448,7 +73456,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="458" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B458" s="88">
         <v>453</v>
       </c>
@@ -73480,7 +73488,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="459" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B459" s="88">
         <v>454</v>
       </c>
@@ -73512,7 +73520,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="460" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B460" s="88">
         <v>455</v>
       </c>
@@ -73544,7 +73552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B461" s="88">
         <v>456</v>
       </c>
@@ -73576,7 +73584,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="462" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B462" s="88">
         <v>457</v>
       </c>
@@ -73608,7 +73616,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="463" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B463" s="88">
         <v>458</v>
       </c>
@@ -73640,7 +73648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="464" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B464" s="88">
         <v>459</v>
       </c>
@@ -73672,7 +73680,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B465" s="88">
         <v>460</v>
       </c>
@@ -73704,7 +73712,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B466" s="88">
         <v>461</v>
       </c>
@@ -73736,7 +73744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B467" s="88">
         <v>462</v>
       </c>
@@ -73768,7 +73776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B468" s="88">
         <v>463</v>
       </c>
@@ -73800,7 +73808,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B469" s="88">
         <v>464</v>
       </c>
@@ -73832,7 +73840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B470" s="88">
         <v>465</v>
       </c>
@@ -73864,7 +73872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B471" s="88">
         <v>466</v>
       </c>
@@ -73896,7 +73904,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B472" s="88">
         <v>467</v>
       </c>
@@ -73928,7 +73936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B473" s="88">
         <v>468</v>
       </c>
@@ -73960,7 +73968,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B474" s="88">
         <v>469</v>
       </c>
@@ -73992,7 +74000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B475" s="88">
         <v>470</v>
       </c>
@@ -74024,7 +74032,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B476" s="88">
         <v>471</v>
       </c>
@@ -74056,7 +74064,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B477" s="88">
         <v>472</v>
       </c>
@@ -74088,7 +74096,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B478" s="88">
         <v>473</v>
       </c>
@@ -74120,7 +74128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B479" s="88">
         <v>474</v>
       </c>
@@ -74152,7 +74160,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B480" s="88">
         <v>475</v>
       </c>
@@ -74184,7 +74192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="481" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B481" s="88">
         <v>476</v>
       </c>
@@ -74216,7 +74224,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="482" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="482" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B482" s="88">
         <v>477</v>
       </c>
@@ -74248,7 +74256,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="483" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="483" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B483" s="88">
         <v>478</v>
       </c>
@@ -74280,7 +74288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="484" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="484" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B484" s="88">
         <v>479</v>
       </c>
@@ -74312,7 +74320,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="485" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="485" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B485" s="88">
         <v>480</v>
       </c>
@@ -74344,7 +74352,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="486" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="486" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B486" s="88">
         <v>481</v>
       </c>
@@ -74376,7 +74384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B487" s="88">
         <v>482</v>
       </c>
@@ -74408,7 +74416,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="488" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B488" s="88">
         <v>483</v>
       </c>
@@ -74440,7 +74448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="489" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="489" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B489" s="88">
         <v>484</v>
       </c>
@@ -74472,7 +74480,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="490" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B490" s="88">
         <v>485</v>
       </c>
@@ -74504,7 +74512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="491" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B491" s="88">
         <v>486</v>
       </c>
@@ -74536,7 +74544,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B492" s="88">
         <v>487</v>
       </c>
@@ -74568,7 +74576,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="493" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B493" s="88">
         <v>488</v>
       </c>
@@ -74600,7 +74608,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="494" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B494" s="88">
         <v>489</v>
       </c>
@@ -74632,7 +74640,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="495" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B495" s="88">
         <v>490</v>
       </c>
@@ -74664,7 +74672,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="496" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B496" s="88">
         <v>491</v>
       </c>
@@ -74696,7 +74704,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="497" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="497" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B497" s="88">
         <v>492</v>
       </c>
@@ -74728,7 +74736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="498" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="498" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B498" s="88">
         <v>493</v>
       </c>
@@ -74760,7 +74768,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="499" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="499" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B499" s="88">
         <v>494</v>
       </c>
@@ -74792,7 +74800,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="500" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B500" s="90">
         <v>495</v>
       </c>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haavas\git\VM2026\fasit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37120A9E-9D0E-488D-A5FD-8502A37A14E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C3DA3A-E235-4A4A-991B-04BFACAAD419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -22542,13 +22542,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP157"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="42" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>207</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>245</v>
       </c>
@@ -23444,7 +23444,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -23572,7 +23572,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>312</v>
       </c>
@@ -23700,7 +23700,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>341</v>
       </c>
@@ -23828,7 +23828,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>370</v>
       </c>
@@ -23956,7 +23956,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>393</v>
       </c>
@@ -24084,7 +24084,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>342</v>
       </c>
@@ -24212,7 +24212,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>433</v>
       </c>
@@ -24340,7 +24340,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>471</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>498</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>527</v>
       </c>
@@ -24724,7 +24724,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>558</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>592</v>
       </c>
@@ -24980,7 +24980,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>626</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>660</v>
       </c>
@@ -25236,7 +25236,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>693</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>725</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>750</v>
       </c>
@@ -25620,7 +25620,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>559</v>
       </c>
@@ -25748,7 +25748,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>794</v>
       </c>
@@ -25876,7 +25876,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>818</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>843</v>
       </c>
@@ -26132,7 +26132,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>871</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>898</v>
       </c>
@@ -26388,7 +26388,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>925</v>
       </c>
@@ -26516,7 +26516,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>949</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>973</v>
       </c>
@@ -26772,7 +26772,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>997</v>
       </c>
@@ -26900,7 +26900,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1024</v>
       </c>
@@ -27028,7 +27028,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1058</v>
       </c>
@@ -27156,7 +27156,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1077</v>
       </c>
@@ -27284,7 +27284,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1093</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1113</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1148</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1180</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1198</v>
       </c>
@@ -27924,7 +27924,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1237</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1264</v>
       </c>
@@ -28180,7 +28180,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1285</v>
       </c>
@@ -28308,7 +28308,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1323</v>
       </c>
@@ -28436,7 +28436,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1349</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1384</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1419</v>
       </c>
@@ -28820,7 +28820,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1449</v>
       </c>
@@ -28948,7 +28948,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1479</v>
       </c>
@@ -29076,7 +29076,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1508</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1544</v>
       </c>
@@ -29332,7 +29332,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1565</v>
       </c>
@@ -29460,7 +29460,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1604</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1633</v>
       </c>
@@ -29716,7 +29716,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1662</v>
       </c>
@@ -29844,7 +29844,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1677</v>
       </c>
@@ -29972,7 +29972,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1703</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1739</v>
       </c>
@@ -30228,7 +30228,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1770</v>
       </c>
@@ -30356,7 +30356,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1798</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1836</v>
       </c>
@@ -30612,7 +30612,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1858</v>
       </c>
@@ -30740,7 +30740,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1883</v>
       </c>
@@ -30868,7 +30868,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1900</v>
       </c>
@@ -30996,7 +30996,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1920</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1958</v>
       </c>
@@ -31252,7 +31252,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1995</v>
       </c>
@@ -31380,7 +31380,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2033</v>
       </c>
@@ -31508,7 +31508,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2072</v>
       </c>
@@ -31636,7 +31636,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2090</v>
       </c>
@@ -31764,7 +31764,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2126</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2146</v>
       </c>
@@ -32020,7 +32020,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2183</v>
       </c>
@@ -32148,7 +32148,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2201</v>
       </c>
@@ -32276,7 +32276,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>2240</v>
       </c>
@@ -32404,7 +32404,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2274</v>
       </c>
@@ -32532,7 +32532,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2304</v>
       </c>
@@ -32660,7 +32660,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>2340</v>
       </c>
@@ -32788,7 +32788,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>2375</v>
       </c>
@@ -32916,7 +32916,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>2395</v>
       </c>
@@ -33044,7 +33044,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>2426</v>
       </c>
@@ -33172,7 +33172,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>2458</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>2493</v>
       </c>
@@ -33428,7 +33428,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>2524</v>
       </c>
@@ -33556,7 +33556,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>2549</v>
       </c>
@@ -33684,7 +33684,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>2573</v>
       </c>
@@ -33812,7 +33812,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>2600</v>
       </c>
@@ -33940,7 +33940,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>2616</v>
       </c>
@@ -34068,7 +34068,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>2622</v>
       </c>
@@ -34196,7 +34196,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>2628</v>
       </c>
@@ -34324,7 +34324,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>2634</v>
       </c>
@@ -34452,7 +34452,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>2640</v>
       </c>
@@ -34580,7 +34580,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>2648</v>
       </c>
@@ -34708,7 +34708,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>2656</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>2663</v>
       </c>
@@ -34964,7 +34964,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>2670</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2677</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2684</v>
       </c>
@@ -35348,7 +35348,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>2691</v>
       </c>
@@ -35476,7 +35476,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>2698</v>
       </c>
@@ -35604,7 +35604,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>2706</v>
       </c>
@@ -35732,7 +35732,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>2714</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>2721</v>
       </c>
@@ -35988,7 +35988,7 @@
         <v>2726</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2727</v>
       </c>
@@ -36116,7 +36116,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2747</v>
       </c>
@@ -36244,7 +36244,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>2767</v>
       </c>
@@ -36372,7 +36372,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>2787</v>
       </c>
@@ -36500,7 +36500,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>2807</v>
       </c>
@@ -36628,7 +36628,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>2827</v>
       </c>
@@ -36756,7 +36756,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>2847</v>
       </c>
@@ -36884,7 +36884,7 @@
         <v>2866</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>2867</v>
       </c>
@@ -37012,7 +37012,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>2887</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>2907</v>
       </c>
@@ -37268,7 +37268,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2927</v>
       </c>
@@ -37396,7 +37396,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>2947</v>
       </c>
@@ -37524,7 +37524,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>2967</v>
       </c>
@@ -37652,7 +37652,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2987</v>
       </c>
@@ -37780,7 +37780,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2977</v>
       </c>
@@ -37908,7 +37908,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>2997</v>
       </c>
@@ -38036,7 +38036,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>3033</v>
       </c>
@@ -38164,43 +38164,43 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>3074</v>
       </c>
@@ -38337,22 +38337,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA72"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.1796875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="10"/>
-    <col min="5" max="5" width="1.1796875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="10"/>
-    <col min="7" max="7" width="27.54296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="1.1796875" style="10" customWidth="1"/>
-    <col min="10" max="16384" width="9.1796875" style="10"/>
+    <col min="1" max="1" width="1.140625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="10"/>
+    <col min="5" max="5" width="1.140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="10"/>
+    <col min="7" max="7" width="27.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="1.140625" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:27" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="39" t="s">
         <v>3115</v>
       </c>
@@ -38364,7 +38364,7 @@
       <c r="G2" s="40"/>
       <c r="H2" s="41"/>
     </row>
-    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="42"/>
       <c r="C3" s="43"/>
       <c r="D3" s="44"/>
@@ -38372,7 +38372,7 @@
       <c r="G3" s="43"/>
       <c r="H3" s="44"/>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
         <v>3117</v>
       </c>
@@ -38384,7 +38384,7 @@
       <c r="G4" s="45"/>
       <c r="H4" s="44"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B5" s="42"/>
       <c r="C5" s="43"/>
       <c r="D5" s="44"/>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="H5" s="44"/>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
         <v>3120</v>
       </c>
@@ -38412,7 +38412,7 @@
       </c>
       <c r="H6" s="44"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="54"/>
       <c r="C7" s="43"/>
       <c r="D7" s="44"/>
@@ -38428,7 +38428,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
         <v>3126</v>
       </c>
@@ -38444,7 +38444,7 @@
       </c>
       <c r="H8" s="44"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="54"/>
       <c r="C9" s="43"/>
       <c r="D9" s="44"/>
@@ -38456,7 +38456,7 @@
       </c>
       <c r="H9" s="44"/>
     </row>
-    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
         <v>3132</v>
       </c>
@@ -38468,7 +38468,7 @@
       <c r="G10" s="50"/>
       <c r="H10" s="44"/>
     </row>
-    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="54"/>
       <c r="C11" s="43"/>
       <c r="D11" s="44"/>
@@ -38476,7 +38476,7 @@
       <c r="G11" s="52"/>
       <c r="H11" s="53"/>
     </row>
-    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="54" t="s">
         <v>3134</v>
       </c>
@@ -38497,7 +38497,7 @@
       <c r="P12" s="76"/>
       <c r="Q12" s="76"/>
     </row>
-    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="54"/>
       <c r="C13" s="43"/>
       <c r="D13" s="44"/>
@@ -38514,7 +38514,7 @@
       <c r="P13" s="76"/>
       <c r="Q13" s="76"/>
     </row>
-    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="54" t="s">
         <v>3135</v>
       </c>
@@ -38535,7 +38535,7 @@
       <c r="P14" s="76"/>
       <c r="Q14" s="76"/>
     </row>
-    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="51"/>
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
@@ -38560,7 +38560,7 @@
       <c r="P15" s="76"/>
       <c r="Q15" s="76"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="F16" s="118" t="s">
         <v>3137</v>
       </c>
@@ -38579,7 +38579,7 @@
       <c r="P16" s="76"/>
       <c r="Q16" s="76"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
       <c r="C17" s="56"/>
       <c r="D17" s="57"/>
@@ -38598,7 +38598,7 @@
       <c r="P17" s="76"/>
       <c r="Q17" s="76"/>
     </row>
-    <row r="18" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="42"/>
       <c r="C18" s="58" t="s">
         <v>3131</v>
@@ -38623,7 +38623,7 @@
       <c r="P18" s="76"/>
       <c r="Q18" s="76"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="59" t="str">
         <f>VLOOKUP("France",T,lang,FALSE)</f>
         <v>France</v>
@@ -38651,7 +38651,7 @@
       <c r="P19" s="76"/>
       <c r="Q19" s="76"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="59" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
         <v>Spain</v>
@@ -38679,7 +38679,7 @@
       <c r="P20" s="76"/>
       <c r="Q20" s="76"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="59" t="str">
         <f>VLOOKUP("Argentina",T,lang,FALSE)</f>
         <v>Argentina</v>
@@ -38707,7 +38707,7 @@
       <c r="P21" s="76"/>
       <c r="Q21" s="76"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="59" t="str">
         <f>VLOOKUP("England",T,lang,FALSE)</f>
         <v>England</v>
@@ -38735,7 +38735,7 @@
       <c r="P22" s="76"/>
       <c r="Q22" s="76"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="59" t="str">
         <f>VLOOKUP("Portugal",T,lang,FALSE)</f>
         <v>Portugal</v>
@@ -38763,7 +38763,7 @@
       <c r="P23" s="76"/>
       <c r="Q23" s="76"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="59" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
         <v>Brazil</v>
@@ -38791,7 +38791,7 @@
       <c r="P24" s="76"/>
       <c r="Q24" s="76"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="59" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
         <v>Netherlands</v>
@@ -38819,7 +38819,7 @@
       <c r="P25" s="76"/>
       <c r="Q25" s="76"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="59" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
         <v>Morocco</v>
@@ -38847,7 +38847,7 @@
       <c r="P26" s="76"/>
       <c r="Q26" s="76"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="59" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
         <v>Belgium</v>
@@ -38875,7 +38875,7 @@
       <c r="P27" s="76"/>
       <c r="Q27" s="76"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="59" t="str">
         <f>VLOOKUP("Germany",T,lang,FALSE)</f>
         <v>Germany</v>
@@ -38903,7 +38903,7 @@
       <c r="P28" s="76"/>
       <c r="Q28" s="76"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="59" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
         <v>Croatia</v>
@@ -38931,7 +38931,7 @@
       <c r="P29" s="76"/>
       <c r="Q29" s="76"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="59" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
         <v>Colombia</v>
@@ -38959,7 +38959,7 @@
       <c r="P30" s="76"/>
       <c r="Q30" s="76"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="59" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
         <v>Senegal</v>
@@ -38987,7 +38987,7 @@
       <c r="P31" s="76"/>
       <c r="Q31" s="76"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="59" t="str">
         <f>VLOOKUP("Mexico",T,lang,FALSE)</f>
         <v>Mexico</v>
@@ -39015,7 +39015,7 @@
       <c r="P32" s="76"/>
       <c r="Q32" s="76"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="59" t="str">
         <f>VLOOKUP("United States",T,lang,FALSE)</f>
         <v>United States</v>
@@ -39043,7 +39043,7 @@
       <c r="P33" s="76"/>
       <c r="Q33" s="76"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="59" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
         <v>Uruguay</v>
@@ -39071,7 +39071,7 @@
       <c r="P34" s="76"/>
       <c r="Q34" s="76"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="59" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
         <v>Japan</v>
@@ -39099,7 +39099,7 @@
       <c r="P35" s="76"/>
       <c r="Q35" s="76"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B36" s="59" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
         <v>Switzerland</v>
@@ -39127,7 +39127,7 @@
       <c r="P36" s="76"/>
       <c r="Q36" s="76"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="59" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
         <v>Iran</v>
@@ -39155,7 +39155,7 @@
       <c r="P37" s="76"/>
       <c r="Q37" s="76"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B38" s="59" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
         <v>Turkey</v>
@@ -39183,7 +39183,7 @@
       <c r="P38" s="76"/>
       <c r="Q38" s="76"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B39" s="59" t="str">
         <f>VLOOKUP("Ecuador",T,lang,FALSE)</f>
         <v>Ecuador</v>
@@ -39211,7 +39211,7 @@
       <c r="P39" s="76"/>
       <c r="Q39" s="76"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="59" t="str">
         <f>VLOOKUP("Austria",T,lang,FALSE)</f>
         <v>Austria</v>
@@ -39239,7 +39239,7 @@
       <c r="P40" s="76"/>
       <c r="Q40" s="76"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" s="59" t="str">
         <f>VLOOKUP("Korea Republic",T,lang,FALSE)</f>
         <v>Korea Republic</v>
@@ -39267,7 +39267,7 @@
       <c r="P41" s="76"/>
       <c r="Q41" s="76"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" s="59" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
         <v>Australia</v>
@@ -39295,7 +39295,7 @@
       <c r="P42" s="76"/>
       <c r="Q42" s="76"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="59" t="str">
         <f>VLOOKUP("Algeria",T,lang,FALSE)</f>
         <v>Algeria</v>
@@ -39319,7 +39319,7 @@
       <c r="P43" s="76"/>
       <c r="Q43" s="76"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44" s="59" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
         <v>Egypt</v>
@@ -39347,7 +39347,7 @@
       <c r="P44" s="76"/>
       <c r="Q44" s="76"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="59" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
         <v>Canada</v>
@@ -39375,7 +39375,7 @@
       <c r="P45" s="76"/>
       <c r="Q45" s="76"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B46" s="59" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
         <v>Norway</v>
@@ -39403,7 +39403,7 @@
       <c r="P46" s="76"/>
       <c r="Q46" s="76"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B47" s="59" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
         <v>Panama</v>
@@ -39431,7 +39431,7 @@
       <c r="P47" s="76"/>
       <c r="Q47" s="76"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B48" s="59" t="str">
         <f>VLOOKUP("Ivory Coast",T,lang,FALSE)</f>
         <v>Ivory Coast</v>
@@ -39455,7 +39455,7 @@
       <c r="P48" s="76"/>
       <c r="Q48" s="76"/>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="59" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
         <v>Sweden</v>
@@ -39479,7 +39479,7 @@
       <c r="P49" s="76"/>
       <c r="Q49" s="76"/>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="59" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
         <v>Paraguay</v>
@@ -39503,7 +39503,7 @@
       <c r="P50" s="76"/>
       <c r="Q50" s="76"/>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="59" t="str">
         <f>VLOOKUP("Czech Republic",T,lang,FALSE)</f>
         <v>Czech Republic</v>
@@ -39527,7 +39527,7 @@
       <c r="P51" s="76"/>
       <c r="Q51" s="76"/>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="59" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
         <v>Scotland</v>
@@ -39551,7 +39551,7 @@
       <c r="P52" s="76"/>
       <c r="Q52" s="76"/>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="59" t="str">
         <f>VLOOKUP("Tunisia",T,lang,FALSE)</f>
         <v>Tunisia</v>
@@ -39575,7 +39575,7 @@
       <c r="P53" s="76"/>
       <c r="Q53" s="76"/>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="59" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
         <v>DR Congo</v>
@@ -39599,7 +39599,7 @@
       <c r="P54" s="76"/>
       <c r="Q54" s="76"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="59" t="str">
         <f>VLOOKUP("Uzbekistan",T,lang,FALSE)</f>
         <v>Uzbekistan</v>
@@ -39623,7 +39623,7 @@
       <c r="P55" s="76"/>
       <c r="Q55" s="76"/>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="59" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
         <v>Qatar</v>
@@ -39647,7 +39647,7 @@
       <c r="P56" s="76"/>
       <c r="Q56" s="76"/>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="59" t="str">
         <f>VLOOKUP("Iraq",T,lang,FALSE)</f>
         <v>Iraq</v>
@@ -39671,7 +39671,7 @@
       <c r="P57" s="76"/>
       <c r="Q57" s="76"/>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="59" t="str">
         <f>VLOOKUP("South Africa",T,lang,FALSE)</f>
         <v>South Africa</v>
@@ -39695,7 +39695,7 @@
       <c r="P58" s="76"/>
       <c r="Q58" s="76"/>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="59" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
         <v>Saudi Arabia</v>
@@ -39719,7 +39719,7 @@
       <c r="P59" s="76"/>
       <c r="Q59" s="76"/>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="59" t="str">
         <f>VLOOKUP("Jordan",T,lang,FALSE)</f>
         <v>Jordan</v>
@@ -39743,7 +39743,7 @@
       <c r="P60" s="76"/>
       <c r="Q60" s="76"/>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="59" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
         <v>Bosnia and Herzegovina</v>
@@ -39767,7 +39767,7 @@
       <c r="P61" s="76"/>
       <c r="Q61" s="76"/>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="59" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
         <v>Cape Verde</v>
@@ -39791,7 +39791,7 @@
       <c r="P62" s="76"/>
       <c r="Q62" s="76"/>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="59" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
         <v>Ghana</v>
@@ -39815,7 +39815,7 @@
       <c r="P63" s="76"/>
       <c r="Q63" s="76"/>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="59" t="str">
         <f>VLOOKUP("Curaçao",T,lang,FALSE)</f>
         <v>Curaçao</v>
@@ -39839,7 +39839,7 @@
       <c r="P64" s="76"/>
       <c r="Q64" s="76"/>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="59" t="str">
         <f>VLOOKUP("Haiti",T,lang,FALSE)</f>
         <v>Haiti</v>
@@ -39866,7 +39866,7 @@
       <c r="P65" s="76"/>
       <c r="Q65" s="76"/>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B66" s="59" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
         <v>New Zealand</v>
@@ -39888,7 +39888,7 @@
       <c r="P66" s="76"/>
       <c r="Q66" s="76"/>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" s="51"/>
       <c r="C67" s="52"/>
       <c r="D67" s="53"/>
@@ -39905,7 +39905,7 @@
       <c r="P67" s="76"/>
       <c r="Q67" s="76"/>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F68" s="76"/>
       <c r="G68" s="76"/>
       <c r="H68" s="76"/>
@@ -39919,7 +39919,7 @@
       <c r="P68" s="76"/>
       <c r="Q68" s="76"/>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F69" s="76"/>
       <c r="G69" s="76"/>
       <c r="H69" s="76"/>
@@ -39933,7 +39933,7 @@
       <c r="P69" s="76"/>
       <c r="Q69" s="76"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F70" s="76"/>
       <c r="G70" s="76"/>
       <c r="H70" s="76"/>
@@ -39947,7 +39947,7 @@
       <c r="P70" s="76"/>
       <c r="Q70" s="76"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F71" s="76"/>
       <c r="G71" s="76"/>
       <c r="H71" s="76"/>
@@ -39961,7 +39961,7 @@
       <c r="P71" s="76"/>
       <c r="Q71" s="76"/>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F72" s="76"/>
       <c r="G72" s="76"/>
       <c r="H72" s="76"/>
@@ -40011,81 +40011,81 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CR111"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22.54296875" style="5" customWidth="1"/>
-    <col min="6" max="7" width="4.26953125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="22.54296875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="3.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="8" customWidth="1"/>
-    <col min="11" max="14" width="5.453125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="7.7265625" style="9" customWidth="1"/>
-    <col min="16" max="16" width="6.7265625" style="9" customWidth="1"/>
-    <col min="17" max="17" width="3.453125" style="68" customWidth="1"/>
-    <col min="18" max="18" width="15.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" style="5" customWidth="1"/>
+    <col min="6" max="7" width="4.28515625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="3.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="8" customWidth="1"/>
+    <col min="11" max="14" width="5.42578125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="7.7109375" style="9" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" style="9" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="68" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="19" max="20" width="16" style="127" hidden="1" customWidth="1"/>
     <col min="21" max="28" width="4" style="123" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="4.26953125" style="124" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.453125" style="123" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="13.453125" style="124" hidden="1" customWidth="1"/>
-    <col min="32" max="36" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" style="124" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="5.42578125" style="123" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="124" hidden="1" customWidth="1"/>
+    <col min="32" max="36" width="5.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="37" max="39" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="5.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="41" max="42" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="7.1796875" style="125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="7.140625" style="125" hidden="1" customWidth="1"/>
     <col min="44" max="44" width="10" style="125" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="15.26953125" style="125" hidden="1" customWidth="1"/>
-    <col min="46" max="50" width="4.7265625" style="126" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="9.1796875" style="125" hidden="1" customWidth="1"/>
-    <col min="52" max="61" width="9.1796875" style="126" hidden="1" customWidth="1"/>
-    <col min="62" max="62" width="9.1796875" style="112" hidden="1" customWidth="1"/>
-    <col min="63" max="63" width="3.26953125" style="2" customWidth="1"/>
-    <col min="64" max="64" width="19.7265625" style="2" customWidth="1"/>
+    <col min="45" max="45" width="15.28515625" style="125" hidden="1" customWidth="1"/>
+    <col min="46" max="50" width="4.7109375" style="126" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="125" hidden="1" customWidth="1"/>
+    <col min="52" max="61" width="9.140625" style="126" hidden="1" customWidth="1"/>
+    <col min="62" max="62" width="9.140625" style="112" hidden="1" customWidth="1"/>
+    <col min="63" max="63" width="3.28515625" style="2" customWidth="1"/>
+    <col min="64" max="64" width="19.7109375" style="2" customWidth="1"/>
     <col min="65" max="67" width="3" style="2" customWidth="1"/>
     <col min="68" max="69" width="2" style="111" customWidth="1"/>
-    <col min="70" max="70" width="3.26953125" style="2" customWidth="1"/>
-    <col min="71" max="71" width="19.7265625" style="2" customWidth="1"/>
+    <col min="70" max="70" width="3.28515625" style="2" customWidth="1"/>
+    <col min="71" max="71" width="19.7109375" style="2" customWidth="1"/>
     <col min="72" max="74" width="3" style="2" customWidth="1"/>
     <col min="75" max="76" width="2" style="111" customWidth="1"/>
     <col min="77" max="77" width="4" style="2" customWidth="1"/>
-    <col min="78" max="78" width="19.7265625" style="2" customWidth="1"/>
+    <col min="78" max="78" width="19.7109375" style="2" customWidth="1"/>
     <col min="79" max="81" width="3" style="2" customWidth="1"/>
     <col min="82" max="83" width="2" style="111" customWidth="1"/>
-    <col min="84" max="84" width="3.81640625" style="2" customWidth="1"/>
-    <col min="85" max="85" width="19.7265625" style="2" customWidth="1"/>
+    <col min="84" max="84" width="3.85546875" style="2" customWidth="1"/>
+    <col min="85" max="85" width="19.7109375" style="2" customWidth="1"/>
     <col min="86" max="88" width="3" style="2" customWidth="1"/>
     <col min="89" max="90" width="2" style="111" customWidth="1"/>
-    <col min="91" max="91" width="3.7265625" style="2" customWidth="1"/>
-    <col min="92" max="92" width="19.7265625" style="2" customWidth="1"/>
+    <col min="91" max="91" width="3.7109375" style="2" customWidth="1"/>
+    <col min="92" max="92" width="19.7109375" style="2" customWidth="1"/>
     <col min="93" max="95" width="3" style="2" customWidth="1"/>
     <col min="96" max="96" width="2" style="111" customWidth="1"/>
-    <col min="97" max="16384" width="9.1796875" style="2"/>
+    <col min="97" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:95" ht="46" x14ac:dyDescent="0.35">
-      <c r="A1" s="139" t="str" cm="1">
+    <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40101,7 +40101,7 @@
       <c r="AW1" s="125"/>
       <c r="AX1" s="125"/>
     </row>
-    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="S2" s="123"/>
       <c r="T2" s="123"/>
       <c r="AC2" s="123"/>
@@ -40117,7 +40117,7 @@
       <c r="AW2" s="125"/>
       <c r="AX2" s="125"/>
     </row>
-    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40152,45 +40152,45 @@
       <c r="AW3" s="125"/>
       <c r="AX3" s="125"/>
     </row>
-    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A5" s="141" t="str" cm="1">
+    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:95" x14ac:dyDescent="0.25">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
-    </row>
-    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
+    </row>
+    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,39 +40300,39 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
-    </row>
-    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
+    </row>
+    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -40407,28 +40407,28 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
-    </row>
-    <row r="8" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
+    </row>
+    <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>2</v>
       </c>
@@ -40675,7 +40675,7 @@
       <c r="CP8" s="21"/>
       <c r="CQ8" s="21"/>
     </row>
-    <row r="9" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>3</v>
       </c>
@@ -40695,8 +40695,12 @@
         <f>AE14</f>
         <v>Canada</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="F9" s="19">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20">
+        <v>1</v>
+      </c>
       <c r="H9" s="80" t="str">
         <f>AE15</f>
         <v>Bosnia and Herzegovina</v>
@@ -40735,43 +40739,43 @@
       </c>
       <c r="S9" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Canada_draw</v>
       </c>
       <c r="T9" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Bosnia and Herzegovina_draw</v>
       </c>
       <c r="U9" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB9" s="123" t="str">
+      <c r="AB9" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD9" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR9))</f>
@@ -40936,7 +40940,7 @@
       <c r="CP9" s="21"/>
       <c r="CQ9" s="21"/>
     </row>
-    <row r="10" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>4</v>
       </c>
@@ -41154,7 +41158,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41195,7 +41199,7 @@
       <c r="CP10" s="21"/>
       <c r="CQ10" s="21"/>
     </row>
-    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>5</v>
       </c>
@@ -41413,7 +41417,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41458,7 +41462,7 @@
       <c r="CP11" s="21"/>
       <c r="CQ11" s="21"/>
     </row>
-    <row r="12" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>6</v>
       </c>
@@ -41647,7 +41651,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41681,7 +41685,7 @@
       <c r="CP12" s="21"/>
       <c r="CQ12" s="21"/>
     </row>
-    <row r="13" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>7</v>
       </c>
@@ -41764,7 +41768,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -41796,7 +41800,7 @@
       <c r="CP13" s="21"/>
       <c r="CQ13" s="21"/>
     </row>
-    <row r="14" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>8</v>
       </c>
@@ -41896,7 +41900,7 @@
       </c>
       <c r="AD14" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR14))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="124" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
@@ -41908,7 +41912,7 @@
       </c>
       <c r="AG14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_lose")</f>
@@ -41916,11 +41920,11 @@
       </c>
       <c r="AI14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE14,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE14,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" s="123">
         <f>AI14-AJ14</f>
@@ -41932,15 +41936,15 @@
       </c>
       <c r="AN14" s="123">
         <f>AF14*3+AG14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" s="123">
         <f>AN14/AN18*10+BA14</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP14" s="123">
         <f>AO14*10000000+BI14*100+AM14/AM18*10+AI14/AI18*1++IF(AQ14=0,ROW(),AQ14)/2000000</f>
-        <v>7.7824000000000003E-4</v>
+        <v>59805923.80174911</v>
       </c>
       <c r="AQ14" s="126">
         <f>VLOOKUP(AE14,db_fifarank,2,FALSE)</f>
@@ -41948,7 +41952,7 @@
       </c>
       <c r="AR14" s="125">
         <f>AP14/AP18</f>
-        <v>7.7759871434028365E-4</v>
+        <v>0.99999998327924866</v>
       </c>
       <c r="AS14" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J15,"1B")</f>
@@ -41960,15 +41964,15 @@
       </c>
       <c r="AU14" s="126" cm="1">
         <f t="array" ref="AU14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV14" s="126" cm="1">
         <f t="array" ref="AV14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" s="126" cm="1">
         <f t="array" ref="AW14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" s="126">
         <f>AV14-AW14</f>
@@ -41980,11 +41984,11 @@
       </c>
       <c r="AZ14" s="126">
         <f>AT14/AT18*1000+AU14/AU18*100+AY14/AY18*10+AV14/AV18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA14" s="126">
         <f>AZ14/AZ18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB14" s="126" cm="1">
         <f t="array" ref="BB14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_win")*($X$7:$X$78))</f>
@@ -41992,15 +41996,15 @@
       </c>
       <c r="BC14" s="126" cm="1">
         <f t="array" ref="BC14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD14" s="126" cm="1">
         <f t="array" ref="BD14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE14" s="126" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF14" s="126">
         <f>BD14-BE14</f>
@@ -42012,13 +42016,13 @@
       </c>
       <c r="BH14" s="126">
         <f>BB14/BB18*1000+BC14/BC18*100+BG14/BG18*10+BD14/BD18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI14" s="126">
         <f>BH14/BH18</f>
-        <v>0</v>
-      </c>
-      <c r="BK14" s="131">
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42059,7 +42063,7 @@
       <c r="CP14" s="21"/>
       <c r="CQ14" s="21"/>
     </row>
-    <row r="15" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>9</v>
       </c>
@@ -42087,11 +42091,11 @@
       </c>
       <c r="J15" s="30" t="str">
         <f>VLOOKUP(1,AD14:AN17,2,FALSE)</f>
-        <v>Switzerland</v>
+        <v>Canada</v>
       </c>
       <c r="K15" s="31">
         <f>L15+M15+N15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="31">
         <f>VLOOKUP(1,AD14:AN17,3,FALSE)</f>
@@ -42099,7 +42103,7 @@
       </c>
       <c r="M15" s="31">
         <f>VLOOKUP(1,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="31">
         <f>VLOOKUP(1,AD14:AN17,5,FALSE)</f>
@@ -42107,11 +42111,11 @@
       </c>
       <c r="O15" s="31" t="str">
         <f>VLOOKUP(1,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P15" s="32">
         <f>L15*3+M15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="123">
         <f>DATE(2026,6,14)+TIME(12,0,0)+gmt_delta</f>
@@ -42159,7 +42163,7 @@
       </c>
       <c r="AD15" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR15))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE15" s="124" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
@@ -42171,7 +42175,7 @@
       </c>
       <c r="AG15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_lose")</f>
@@ -42179,11 +42183,11 @@
       </c>
       <c r="AI15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE15,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE15,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" s="123">
         <f>AI15-AJ15</f>
@@ -42195,15 +42199,15 @@
       </c>
       <c r="AN15" s="123">
         <f>AF15*3+AG15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15" s="123">
         <f>AN15/AN18*10+BA15</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP15" s="123">
         <f>AO15*10000000+BI15*100+AM15/AM18*10+AI15/AI18*1++IF(AQ15=0,ROW(),AQ15)/2000000</f>
-        <v>6.9291999999999997E-4</v>
+        <v>59805923.801663786</v>
       </c>
       <c r="AQ15" s="126">
         <f>VLOOKUP(AE15,db_fifarank,2,FALSE)</f>
@@ -42211,7 +42215,7 @@
       </c>
       <c r="AR15" s="125">
         <f>AP15/AP18</f>
-        <v>6.9234901976340118E-4</v>
+        <v>0.99999998327782191</v>
       </c>
       <c r="AS15" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J16,"2B")</f>
@@ -42223,15 +42227,15 @@
       </c>
       <c r="AU15" s="126" cm="1">
         <f t="array" ref="AU15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" s="126" cm="1">
         <f t="array" ref="AV15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" s="126" cm="1">
         <f t="array" ref="AW15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" s="126">
         <f>AV15-AW15</f>
@@ -42243,11 +42247,11 @@
       </c>
       <c r="AZ15" s="126">
         <f>AT15/AT18*1000+AU15/AU18*100+AY15/AY18*10+AV15/AV18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA15" s="126">
         <f>AZ15/AZ18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB15" s="126" cm="1">
         <f t="array" ref="BB15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_win")*($X$7:$X$78))</f>
@@ -42255,15 +42259,15 @@
       </c>
       <c r="BC15" s="126" cm="1">
         <f t="array" ref="BC15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" s="126" cm="1">
         <f t="array" ref="BD15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE15" s="126" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF15" s="126">
         <f>BD15-BE15</f>
@@ -42275,13 +42279,13 @@
       </c>
       <c r="BH15" s="126">
         <f>BB15/BB18*1000+BC15/BC18*100+BG15/BG18*10+BD15/BD18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI15" s="126">
         <f>BH15/BH18</f>
-        <v>0</v>
-      </c>
-      <c r="BK15" s="132"/>
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42319,7 +42323,7 @@
       <c r="CH15" s="21"/>
       <c r="CI15" s="21"/>
     </row>
-    <row r="16" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>10</v>
       </c>
@@ -42347,11 +42351,11 @@
       </c>
       <c r="J16" s="33" t="str">
         <f>VLOOKUP(2,AD14:AN17,2,FALSE)</f>
-        <v>Canada</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="K16" s="23">
         <f>L16+M16+N16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="23">
         <f>VLOOKUP(2,AD14:AN17,3,FALSE)</f>
@@ -42359,7 +42363,7 @@
       </c>
       <c r="M16" s="23">
         <f>VLOOKUP(2,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="23">
         <f>VLOOKUP(2,AD14:AN17,5,FALSE)</f>
@@ -42367,11 +42371,11 @@
       </c>
       <c r="O16" s="23" t="str">
         <f>VLOOKUP(2,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P16" s="34">
         <f>L16*3+M16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="123">
         <f>DATE(2026,6,14)+TIME(6,0,0)+gmt_delta</f>
@@ -42419,7 +42423,7 @@
       </c>
       <c r="AD16" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR16))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE16" s="124" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
@@ -42471,7 +42475,7 @@
       </c>
       <c r="AR16" s="125">
         <f>AP16/AP18</f>
-        <v>7.268805416173282E-4</v>
+        <v>1.2164012218045725E-11</v>
       </c>
       <c r="AT16" s="126" cm="1">
         <f t="array" ref="AT16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($U$7:$U$78))</f>
@@ -42551,7 +42555,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42571,7 +42575,7 @@
       <c r="CH16" s="21"/>
       <c r="CI16" s="21"/>
     </row>
-    <row r="17" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>11</v>
       </c>
@@ -42599,7 +42603,7 @@
       </c>
       <c r="J17" s="33" t="str">
         <f>VLOOKUP(3,AD14:AN17,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>Switzerland</v>
       </c>
       <c r="K17" s="23">
         <f>L17+M17+N17</f>
@@ -42671,7 +42675,7 @@
       </c>
       <c r="AD17" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR17))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" s="124" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
@@ -42723,7 +42727,7 @@
       </c>
       <c r="AR17" s="125">
         <f>AP17/AP18</f>
-        <v>8.2402043035108958E-4</v>
+        <v>1.3789603667760363E-11</v>
       </c>
       <c r="AT17" s="126" cm="1">
         <f t="array" ref="AT17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($U$7:$U$78))</f>
@@ -42809,7 +42813,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -42827,7 +42831,7 @@
       <c r="CH17" s="21"/>
       <c r="CI17" s="21"/>
     </row>
-    <row r="18" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>12</v>
       </c>
@@ -42855,7 +42859,7 @@
       </c>
       <c r="J18" s="35" t="str">
         <f>VLOOKUP(4,AD14:AN17,2,FALSE)</f>
-        <v>Bosnia and Herzegovina</v>
+        <v>Qatar</v>
       </c>
       <c r="K18" s="36">
         <f>L18+M18+N18</f>
@@ -42931,7 +42935,7 @@
       </c>
       <c r="AG18" s="123">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH18" s="123">
         <f t="shared" si="13"/>
@@ -42939,7 +42943,7 @@
       </c>
       <c r="AI18" s="123">
         <f>MAX(AI14:AI17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL18" s="123">
         <f>MIN(AL14:AL17)</f>
@@ -42951,15 +42955,15 @@
       </c>
       <c r="AN18" s="123">
         <f>MAX(AN14:AN17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO18" s="123">
         <f>MAX(AO14:AO17)+1</f>
-        <v>1</v>
+        <v>6.9805825242718447</v>
       </c>
       <c r="AP18" s="123">
         <f>MAX(AP14:AP17)+1</f>
-        <v>1.0008246999999999</v>
+        <v>59805924.80174911</v>
       </c>
       <c r="AT18" s="126">
         <f>MAX(AT14:AT17)-MIN(AT14:AT17)+1</f>
@@ -42967,15 +42971,15 @@
       </c>
       <c r="AU18" s="126">
         <f>MAX(AU14:AU17)-MIN(AU14:AU17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV18" s="126">
         <f>MAX(AV14:AV17)-MIN(AV14:AV17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" s="126">
         <f>MAX(AW14:AW17)-MIN(AW14:AW17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY18" s="126">
         <f>MAX(AY14:AY17)-MIN(AY14:AY17)+1</f>
@@ -42983,7 +42987,7 @@
       </c>
       <c r="AZ18" s="126">
         <f>MAX(AZ14:AZ17)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB18" s="126">
         <f>MAX(BB14:BB17)-MIN(BB14:BB17)+1</f>
@@ -42991,15 +42995,15 @@
       </c>
       <c r="BC18" s="126">
         <f>MAX(BC14:BC17)-MIN(BC14:BC17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD18" s="126">
         <f>MAX(BD14:BD17)-MIN(BD14:BD17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE18" s="126">
         <f>MAX(BE14:BE17)-MIN(BE14:BE17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG18" s="126">
         <f>MAX(BG14:BG17)-MIN(BG14:BG17)+1</f>
@@ -43007,9 +43011,9 @@
       </c>
       <c r="BH18" s="126">
         <f>MAX(BH14:BH17)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK18" s="131">
+        <v>51.5</v>
+      </c>
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43043,7 +43047,7 @@
       <c r="CH18" s="21"/>
       <c r="CI18" s="21"/>
     </row>
-    <row r="19" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>13</v>
       </c>
@@ -43113,7 +43117,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43158,7 +43162,7 @@
       <c r="CP19" s="21"/>
       <c r="CQ19" s="21"/>
     </row>
-    <row r="20" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>14</v>
       </c>
@@ -43387,7 +43391,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43421,7 +43425,7 @@
       <c r="CP20" s="21"/>
       <c r="CQ20" s="21"/>
     </row>
-    <row r="21" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>15</v>
       </c>
@@ -43656,7 +43660,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43688,7 +43692,7 @@
       <c r="CP21" s="21"/>
       <c r="CQ21" s="21"/>
     </row>
-    <row r="22" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>16</v>
       </c>
@@ -43906,7 +43910,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -43948,7 +43952,7 @@
         <v>46217.791666666672</v>
       </c>
     </row>
-    <row r="23" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>17</v>
       </c>
@@ -44166,7 +44170,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44193,7 +44197,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44208,7 +44212,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>18</v>
       </c>
@@ -44410,7 +44414,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44423,7 +44427,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>19</v>
       </c>
@@ -44533,7 +44537,7 @@
       <c r="CP25" s="21"/>
       <c r="CQ25" s="21"/>
     </row>
-    <row r="26" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>20</v>
       </c>
@@ -44755,7 +44759,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -44797,7 +44801,7 @@
       <c r="CP26" s="21"/>
       <c r="CQ26" s="21"/>
     </row>
-    <row r="27" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>21</v>
       </c>
@@ -45019,7 +45023,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45065,7 +45069,7 @@
       <c r="CP27" s="21"/>
       <c r="CQ27" s="21"/>
     </row>
-    <row r="28" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>22</v>
       </c>
@@ -45290,7 +45294,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45320,7 +45324,7 @@
       <c r="CK28" s="114"/>
       <c r="CL28" s="112"/>
     </row>
-    <row r="29" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>23</v>
       </c>
@@ -45551,7 +45555,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45579,7 +45583,7 @@
       <c r="CK29" s="114"/>
       <c r="CL29" s="112"/>
     </row>
-    <row r="30" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>24</v>
       </c>
@@ -45761,7 +45765,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45798,7 +45802,7 @@
       <c r="CK30" s="114"/>
       <c r="CL30" s="112"/>
     </row>
-    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>25</v>
       </c>
@@ -45868,7 +45872,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -45904,7 +45908,7 @@
       <c r="CK31" s="114"/>
       <c r="CL31" s="112"/>
     </row>
-    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>26</v>
       </c>
@@ -46140,7 +46144,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46158,7 +46162,7 @@
       <c r="CK32" s="114"/>
       <c r="CL32" s="112"/>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>27</v>
       </c>
@@ -46400,7 +46404,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46415,16 +46419,16 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
-    </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
+    </row>
+    <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>28</v>
       </c>
@@ -46642,7 +46646,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46673,13 +46677,13 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
-    </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
+    </row>
+    <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>29</v>
       </c>
@@ -46897,7 +46901,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -46933,7 +46937,7 @@
       <c r="CK35" s="114"/>
       <c r="CL35" s="112"/>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>30</v>
       </c>
@@ -47122,7 +47126,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47159,7 +47163,7 @@
         <v>46222.791666666672</v>
       </c>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>31</v>
       </c>
@@ -47242,7 +47246,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47269,7 +47273,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47284,7 +47288,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>32</v>
       </c>
@@ -47506,7 +47510,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47536,7 +47540,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47549,7 +47553,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>33</v>
       </c>
@@ -47771,7 +47775,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -47804,7 +47808,7 @@
       <c r="CP39" s="21"/>
       <c r="CQ39" s="21"/>
     </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>34</v>
       </c>
@@ -48025,7 +48029,7 @@
       <c r="CK40" s="114"/>
       <c r="CL40" s="112"/>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>35</v>
       </c>
@@ -48265,7 +48269,7 @@
       <c r="CK41" s="114"/>
       <c r="CL41" s="112"/>
     </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>36</v>
       </c>
@@ -48447,7 +48451,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48470,7 +48474,7 @@
       <c r="BW42" s="112"/>
       <c r="CK42" s="114"/>
     </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <v>37</v>
       </c>
@@ -48540,7 +48544,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="132"/>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48567,7 +48571,7 @@
       </c>
       <c r="CK43" s="114"/>
     </row>
-    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <v>38</v>
       </c>
@@ -48796,7 +48800,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48811,16 +48815,16 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
-    </row>
-    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
+    </row>
+    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <v>39</v>
       </c>
@@ -49055,7 +49059,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49068,13 +49072,13 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
-    </row>
-    <row r="46" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
+    </row>
+    <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <v>40</v>
       </c>
@@ -49292,7 +49296,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49316,7 +49320,7 @@
       <c r="CK46" s="114"/>
       <c r="CL46" s="112"/>
     </row>
-    <row r="47" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <v>41</v>
       </c>
@@ -49534,7 +49538,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49581,7 +49585,7 @@
         <v>46221.875</v>
       </c>
     </row>
-    <row r="48" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <v>42</v>
       </c>
@@ -49777,7 +49781,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49793,7 +49797,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49808,7 +49812,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <v>43</v>
       </c>
@@ -49898,7 +49902,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49912,7 +49916,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -49925,7 +49929,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
         <v>44</v>
       </c>
@@ -50147,7 +50151,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="131">
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50178,7 +50182,7 @@
       <c r="CK50" s="114"/>
       <c r="CL50" s="112"/>
     </row>
-    <row r="51" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <v>45</v>
       </c>
@@ -50400,7 +50404,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="132"/>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50435,7 +50439,7 @@
       <c r="CK51" s="114"/>
       <c r="CL51" s="112"/>
     </row>
-    <row r="52" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <v>46</v>
       </c>
@@ -50660,7 +50664,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50684,7 +50688,7 @@
       <c r="CK52" s="114"/>
       <c r="CL52" s="112"/>
     </row>
-    <row r="53" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>47</v>
       </c>
@@ -50915,7 +50919,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -50937,7 +50941,7 @@
       <c r="CK53" s="114"/>
       <c r="CL53" s="112"/>
     </row>
-    <row r="54" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>48</v>
       </c>
@@ -51119,7 +51123,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="131">
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51162,7 +51166,7 @@
       </c>
       <c r="CL54" s="112"/>
     </row>
-    <row r="55" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>49</v>
       </c>
@@ -51240,7 +51244,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51267,7 +51271,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51283,7 +51287,7 @@
       </c>
       <c r="CL55" s="112"/>
     </row>
-    <row r="56" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>50</v>
       </c>
@@ -51526,7 +51530,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -51540,7 +51544,7 @@
       </c>
       <c r="CL56" s="112"/>
     </row>
-    <row r="57" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>51</v>
       </c>
@@ -51790,7 +51794,7 @@
       <c r="CC57" s="21"/>
       <c r="CD57" s="114"/>
     </row>
-    <row r="58" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
         <v>52</v>
       </c>
@@ -52009,7 +52013,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52038,7 +52042,7 @@
       <c r="CC58" s="21"/>
       <c r="CD58" s="114"/>
     </row>
-    <row r="59" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <v>53</v>
       </c>
@@ -52257,7 +52261,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52290,7 +52294,7 @@
       <c r="CC59" s="21"/>
       <c r="CD59" s="114"/>
     </row>
-    <row r="60" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <v>54</v>
       </c>
@@ -52480,7 +52484,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52502,7 +52506,7 @@
       <c r="CC60" s="21"/>
       <c r="CD60" s="114"/>
     </row>
-    <row r="61" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <v>55</v>
       </c>
@@ -52593,7 +52597,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52613,7 +52617,7 @@
       <c r="CC61" s="21"/>
       <c r="CD61" s="114"/>
     </row>
-    <row r="62" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
         <v>56</v>
       </c>
@@ -52836,7 +52840,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -52865,7 +52869,7 @@
       <c r="CC62" s="21"/>
       <c r="CD62" s="114"/>
     </row>
-    <row r="63" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <v>57</v>
       </c>
@@ -53088,7 +53092,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53121,7 +53125,7 @@
         <v>46215.041666666672</v>
       </c>
     </row>
-    <row r="64" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
         <v>58</v>
       </c>
@@ -53354,7 +53358,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53369,7 +53373,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
         <v>59</v>
       </c>
@@ -53608,7 +53612,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53621,7 +53625,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A66" s="16">
         <v>60</v>
       </c>
@@ -53804,7 +53808,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53826,7 +53830,7 @@
       <c r="BV66" s="21"/>
       <c r="BW66" s="114"/>
     </row>
-    <row r="67" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <v>61</v>
       </c>
@@ -53904,7 +53908,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -53930,7 +53934,7 @@
         <v>46210.833333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
         <v>62</v>
       </c>
@@ -54160,7 +54164,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54174,27 +54178,27 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
-    </row>
-    <row r="69" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
+    </row>
+    <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <v>63</v>
       </c>
@@ -54430,7 +54434,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54442,21 +54446,21 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
-    </row>
-    <row r="70" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
+    </row>
+    <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <v>64</v>
       </c>
@@ -54675,7 +54679,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54692,7 +54696,7 @@
       <c r="BQ70" s="112"/>
       <c r="BW70" s="112"/>
     </row>
-    <row r="71" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <v>65</v>
       </c>
@@ -54911,7 +54915,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -54925,7 +54929,7 @@
       </c>
       <c r="BQ71" s="112"/>
     </row>
-    <row r="72" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A72" s="16">
         <v>66</v>
       </c>
@@ -55109,7 +55113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A73" s="16">
         <v>67</v>
       </c>
@@ -55188,7 +55192,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A74" s="16">
         <v>68</v>
       </c>
@@ -55412,7 +55416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A75" s="16">
         <v>69</v>
       </c>
@@ -55636,7 +55640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A76" s="16">
         <v>70</v>
       </c>
@@ -55856,7 +55860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A77" s="16">
         <v>71</v>
       </c>
@@ -56076,7 +56080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A78" s="16">
         <v>72</v>
       </c>
@@ -56260,7 +56264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A79" s="73"/>
       <c r="B79" s="73"/>
       <c r="C79" s="73"/>
@@ -56278,7 +56282,7 @@
       <c r="O79" s="70"/>
       <c r="P79" s="70"/>
     </row>
-    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="73"/>
       <c r="B80" s="73"/>
       <c r="C80" s="73"/>
@@ -56380,7 +56384,7 @@
         <v>Ⓐ Czech Republic</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="73"/>
       <c r="B81" s="73"/>
       <c r="C81" s="73"/>
@@ -56392,7 +56396,7 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Australia</v>
+        <v>Ⓑ Switzerland</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
@@ -56420,11 +56424,11 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
-        <v>Qatar</v>
+        <v>Switzerland</v>
       </c>
       <c r="AF81" s="123">
         <f t="shared" ref="AF81:AF91" si="39">VLOOKUP($AE81,$AE$8:$AQ$78,2,FALSE)</f>
@@ -56463,26 +56467,26 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>500.00072748000002</v>
+        <v>500.00082470000001</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
-        <v>1454.96</v>
+        <v>1649.4</v>
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="AT81" s="130" t="str">
         <f>"Ⓑ "&amp;AE81</f>
-        <v>Ⓑ Qatar</v>
-      </c>
-    </row>
-    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Ⓑ Switzerland</v>
+      </c>
+    </row>
+    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="73"/>
       <c r="B82" s="73"/>
       <c r="C82" s="73"/>
@@ -56494,7 +56498,7 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓓ Australia</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
@@ -56522,7 +56526,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -56573,32 +56577,32 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Scotland</v>
+        <v/>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
         <v>Ⓒ Scotland</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
@@ -56626,7 +56630,7 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
@@ -56677,7 +56681,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CD</v>
+        <v>BD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56688,19 +56692,19 @@
         <v>Ⓓ Australia</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓖ Egypt</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56740,7 +56744,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56791,7 +56795,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDE</v>
+        <v>BDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56802,19 +56806,19 @@
         <v>Ⓔ Ivory Coast</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓘ Norway</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56854,7 +56858,7 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
@@ -56905,7 +56909,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEF</v>
+        <v>BDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56916,19 +56920,19 @@
         <v>Ⓕ Sweden</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -56968,7 +56972,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57019,7 +57023,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFG</v>
+        <v>BDEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57030,19 +57034,19 @@
         <v>Ⓖ Egypt</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓔ Ivory Coast</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57133,7 +57137,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFG</v>
+        <v>BDEFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57144,19 +57148,19 @@
         <v>Ⓗ Saudi Arabia</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓕ Sweden</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57196,7 +57200,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -57247,7 +57251,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGI</v>
+        <v>BDEFGI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57258,7 +57262,7 @@
         <v>Ⓘ Norway</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="73"/>
       <c r="B89" s="73"/>
       <c r="C89" s="73"/>
@@ -57270,7 +57274,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57310,7 +57314,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -57361,7 +57365,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJ</v>
+        <v>BDEFGIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57372,7 +57376,7 @@
         <v>Ⓙ Algeria</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="73"/>
       <c r="B90" s="73"/>
       <c r="C90" s="73"/>
@@ -57384,7 +57388,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -57424,7 +57428,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57475,7 +57479,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJ</v>
+        <v>BDEFGIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57486,7 +57490,7 @@
         <v>Ⓚ DR Congo</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="73"/>
       <c r="B91" s="73"/>
       <c r="C91" s="73"/>
@@ -57538,7 +57542,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -57589,7 +57593,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJL</v>
+        <v>BDEFGIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57600,7 +57604,7 @@
         <v>Ⓛ Panama</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="73"/>
       <c r="B92" s="73"/>
       <c r="C92" s="73"/>
@@ -57675,7 +57679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A93" s="73"/>
       <c r="B93" s="73"/>
       <c r="C93" s="73"/>
@@ -57693,7 +57697,7 @@
       <c r="O93" s="70"/>
       <c r="P93" s="70"/>
     </row>
-    <row r="95" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:46" x14ac:dyDescent="0.25">
       <c r="R95" s="123">
         <f>DATE(2026,12,9)+TIME(8,0,0)+gmt_delta</f>
         <v>46365.791666666672</v>
@@ -57707,7 +57711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R96" s="123">
         <f>DATE(2026,12,9)+TIME(4,0,0)+gmt_delta</f>
         <v>46365.625</v>
@@ -57721,7 +57725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R97" s="123">
         <f>DATE(2026,12,10)+TIME(8,0,0)+gmt_delta</f>
         <v>46366.791666666672</v>
@@ -57735,7 +57739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="98" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R98" s="123">
         <f>DATE(2026,12,10)+TIME(4,0,0)+gmt_delta</f>
         <v>46366.625</v>
@@ -57749,7 +57753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="102" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R102" s="123">
         <f>DATE(2026,12,13)+TIME(8,0,0)+gmt_delta</f>
         <v>46369.791666666672</v>
@@ -57775,7 +57779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="103" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R103" s="123">
         <f>DATE(2026,12,14)+TIME(8,0,0)+gmt_delta</f>
         <v>46370.791666666672</v>
@@ -57801,7 +57805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="107" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R107" s="123">
         <f>DATE(2026,12,17)+TIME(8,0,0)+gmt_delta</f>
         <v>46373.791666666672</v>
@@ -57811,7 +57815,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="111" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R111" s="123">
         <f>DATE(2026,12,18)+TIME(8,0,0)+gmt_delta</f>
         <v>46374.791666666672</v>
@@ -57828,6 +57832,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57843,36 +57877,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -58897,33 +58901,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A2A316-429C-49FB-9962-F944380EA825}">
   <dimension ref="B1:K500"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.453125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="81"/>
-    <col min="3" max="3" width="13.7265625" style="81" customWidth="1"/>
-    <col min="4" max="11" width="9.453125" style="81" customWidth="1"/>
-    <col min="12" max="16384" width="9.1796875" style="82"/>
+    <col min="1" max="1" width="2.42578125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="81"/>
+    <col min="3" max="3" width="13.7109375" style="81" customWidth="1"/>
+    <col min="4" max="11" width="9.42578125" style="81" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="82"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B2" s="108" t="s">
         <v>3193</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>CDEFGIJL</v>
+        <v>BDEFGIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3C</v>
+        <v>3E</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -58931,7 +58935,7 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3E</v>
+        <v>3B</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
@@ -58954,7 +58958,7 @@
         <v>3I</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="84" t="s">
         <v>3194</v>
       </c>
@@ -58984,7 +58988,7 @@
         <v>3202</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="88">
         <v>1</v>
       </c>
@@ -59016,7 +59020,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="88">
         <v>2</v>
       </c>
@@ -59048,7 +59052,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="88">
         <v>3</v>
       </c>
@@ -59080,7 +59084,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="88">
         <v>4</v>
       </c>
@@ -59112,7 +59116,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="88">
         <v>5</v>
       </c>
@@ -59144,7 +59148,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="88">
         <v>6</v>
       </c>
@@ -59176,7 +59180,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="88">
         <v>7</v>
       </c>
@@ -59208,7 +59212,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="88">
         <v>8</v>
       </c>
@@ -59240,7 +59244,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="88">
         <v>9</v>
       </c>
@@ -59272,7 +59276,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="88">
         <v>10</v>
       </c>
@@ -59304,7 +59308,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="88">
         <v>11</v>
       </c>
@@ -59336,7 +59340,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="88">
         <v>12</v>
       </c>
@@ -59368,7 +59372,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="88">
         <v>13</v>
       </c>
@@ -59400,7 +59404,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="88">
         <v>14</v>
       </c>
@@ -59432,7 +59436,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="88">
         <v>15</v>
       </c>
@@ -59464,7 +59468,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="88">
         <v>16</v>
       </c>
@@ -59496,7 +59500,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="88">
         <v>17</v>
       </c>
@@ -59528,7 +59532,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="88">
         <v>18</v>
       </c>
@@ -59560,7 +59564,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="88">
         <v>19</v>
       </c>
@@ -59592,7 +59596,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="88">
         <v>20</v>
       </c>
@@ -59624,7 +59628,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="88">
         <v>21</v>
       </c>
@@ -59656,7 +59660,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="88">
         <v>22</v>
       </c>
@@ -59688,7 +59692,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="88">
         <v>23</v>
       </c>
@@ -59720,7 +59724,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="88">
         <v>24</v>
       </c>
@@ -59752,7 +59756,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="88">
         <v>25</v>
       </c>
@@ -59784,7 +59788,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="88">
         <v>26</v>
       </c>
@@ -59816,7 +59820,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="88">
         <v>27</v>
       </c>
@@ -59848,7 +59852,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="88">
         <v>28</v>
       </c>
@@ -59880,7 +59884,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="88">
         <v>29</v>
       </c>
@@ -59912,7 +59916,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="88">
         <v>30</v>
       </c>
@@ -59944,7 +59948,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="88">
         <v>31</v>
       </c>
@@ -59976,7 +59980,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="88">
         <v>32</v>
       </c>
@@ -60008,7 +60012,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="88">
         <v>33</v>
       </c>
@@ -60040,7 +60044,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="88">
         <v>34</v>
       </c>
@@ -60072,7 +60076,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="88">
         <v>35</v>
       </c>
@@ -60104,7 +60108,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="88">
         <v>36</v>
       </c>
@@ -60136,7 +60140,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="88">
         <v>37</v>
       </c>
@@ -60168,7 +60172,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="88">
         <v>38</v>
       </c>
@@ -60200,7 +60204,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="88">
         <v>39</v>
       </c>
@@ -60232,7 +60236,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="88">
         <v>40</v>
       </c>
@@ -60264,7 +60268,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="88">
         <v>41</v>
       </c>
@@ -60296,7 +60300,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="88">
         <v>42</v>
       </c>
@@ -60328,7 +60332,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="88">
         <v>43</v>
       </c>
@@ -60360,7 +60364,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="88">
         <v>44</v>
       </c>
@@ -60392,7 +60396,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="88">
         <v>45</v>
       </c>
@@ -60424,7 +60428,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="88">
         <v>46</v>
       </c>
@@ -60456,7 +60460,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="88">
         <v>47</v>
       </c>
@@ -60488,7 +60492,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" s="88">
         <v>48</v>
       </c>
@@ -60520,7 +60524,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" s="88">
         <v>49</v>
       </c>
@@ -60552,7 +60556,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" s="88">
         <v>50</v>
       </c>
@@ -60584,7 +60588,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="88">
         <v>51</v>
       </c>
@@ -60616,7 +60620,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" s="88">
         <v>52</v>
       </c>
@@ -60648,7 +60652,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="88">
         <v>53</v>
       </c>
@@ -60680,7 +60684,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="88">
         <v>54</v>
       </c>
@@ -60712,7 +60716,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="88">
         <v>55</v>
       </c>
@@ -60744,7 +60748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="88">
         <v>56</v>
       </c>
@@ -60776,7 +60780,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="88">
         <v>57</v>
       </c>
@@ -60808,7 +60812,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="88">
         <v>58</v>
       </c>
@@ -60840,7 +60844,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="88">
         <v>59</v>
       </c>
@@ -60872,7 +60876,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="88">
         <v>60</v>
       </c>
@@ -60904,7 +60908,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="88">
         <v>61</v>
       </c>
@@ -60936,7 +60940,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" s="88">
         <v>62</v>
       </c>
@@ -60968,7 +60972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" s="88">
         <v>63</v>
       </c>
@@ -61000,7 +61004,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" s="88">
         <v>64</v>
       </c>
@@ -61032,7 +61036,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" s="88">
         <v>65</v>
       </c>
@@ -61064,7 +61068,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" s="88">
         <v>66</v>
       </c>
@@ -61096,7 +61100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" s="88">
         <v>67</v>
       </c>
@@ -61128,7 +61132,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" s="88">
         <v>68</v>
       </c>
@@ -61160,7 +61164,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" s="88">
         <v>69</v>
       </c>
@@ -61192,7 +61196,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" s="88">
         <v>70</v>
       </c>
@@ -61224,7 +61228,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" s="88">
         <v>71</v>
       </c>
@@ -61256,7 +61260,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" s="88">
         <v>72</v>
       </c>
@@ -61288,7 +61292,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" s="88">
         <v>73</v>
       </c>
@@ -61320,7 +61324,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="88">
         <v>74</v>
       </c>
@@ -61352,7 +61356,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" s="88">
         <v>75</v>
       </c>
@@ -61384,7 +61388,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" s="88">
         <v>76</v>
       </c>
@@ -61416,7 +61420,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" s="88">
         <v>77</v>
       </c>
@@ -61448,7 +61452,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" s="88">
         <v>78</v>
       </c>
@@ -61480,7 +61484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" s="88">
         <v>79</v>
       </c>
@@ -61512,7 +61516,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" s="88">
         <v>80</v>
       </c>
@@ -61544,7 +61548,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" s="88">
         <v>81</v>
       </c>
@@ -61576,7 +61580,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" s="88">
         <v>82</v>
       </c>
@@ -61608,7 +61612,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" s="88">
         <v>83</v>
       </c>
@@ -61640,7 +61644,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" s="88">
         <v>84</v>
       </c>
@@ -61672,7 +61676,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" s="88">
         <v>85</v>
       </c>
@@ -61704,7 +61708,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" s="88">
         <v>86</v>
       </c>
@@ -61736,7 +61740,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" s="88">
         <v>87</v>
       </c>
@@ -61768,7 +61772,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" s="88">
         <v>88</v>
       </c>
@@ -61800,7 +61804,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" s="88">
         <v>89</v>
       </c>
@@ -61832,7 +61836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" s="88">
         <v>90</v>
       </c>
@@ -61864,7 +61868,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" s="88">
         <v>91</v>
       </c>
@@ -61896,7 +61900,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" s="88">
         <v>92</v>
       </c>
@@ -61928,7 +61932,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" s="88">
         <v>93</v>
       </c>
@@ -61960,7 +61964,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" s="88">
         <v>94</v>
       </c>
@@ -61992,7 +61996,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" s="88">
         <v>95</v>
       </c>
@@ -62024,7 +62028,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="88">
         <v>96</v>
       </c>
@@ -62056,7 +62060,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" s="88">
         <v>97</v>
       </c>
@@ -62088,7 +62092,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" s="88">
         <v>98</v>
       </c>
@@ -62120,7 +62124,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" s="88">
         <v>99</v>
       </c>
@@ -62152,7 +62156,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" s="88">
         <v>100</v>
       </c>
@@ -62184,7 +62188,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" s="88">
         <v>101</v>
       </c>
@@ -62216,7 +62220,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" s="88">
         <v>102</v>
       </c>
@@ -62248,7 +62252,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" s="88">
         <v>103</v>
       </c>
@@ -62280,7 +62284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" s="88">
         <v>104</v>
       </c>
@@ -62312,7 +62316,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" s="88">
         <v>105</v>
       </c>
@@ -62344,7 +62348,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" s="88">
         <v>106</v>
       </c>
@@ -62376,7 +62380,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" s="88">
         <v>107</v>
       </c>
@@ -62408,7 +62412,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" s="88">
         <v>108</v>
       </c>
@@ -62440,7 +62444,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" s="88">
         <v>109</v>
       </c>
@@ -62472,7 +62476,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" s="88">
         <v>110</v>
       </c>
@@ -62504,7 +62508,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" s="88">
         <v>111</v>
       </c>
@@ -62536,7 +62540,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" s="88">
         <v>112</v>
       </c>
@@ -62568,7 +62572,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" s="88">
         <v>113</v>
       </c>
@@ -62600,7 +62604,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" s="88">
         <v>114</v>
       </c>
@@ -62632,7 +62636,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" s="88">
         <v>115</v>
       </c>
@@ -62664,7 +62668,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" s="88">
         <v>116</v>
       </c>
@@ -62696,7 +62700,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" s="88">
         <v>117</v>
       </c>
@@ -62728,7 +62732,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" s="88">
         <v>118</v>
       </c>
@@ -62760,7 +62764,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" s="88">
         <v>119</v>
       </c>
@@ -62792,7 +62796,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" s="88">
         <v>120</v>
       </c>
@@ -62824,7 +62828,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" s="88">
         <v>121</v>
       </c>
@@ -62856,7 +62860,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" s="88">
         <v>122</v>
       </c>
@@ -62888,7 +62892,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" s="88">
         <v>123</v>
       </c>
@@ -62920,7 +62924,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" s="88">
         <v>124</v>
       </c>
@@ -62952,7 +62956,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" s="88">
         <v>125</v>
       </c>
@@ -62984,7 +62988,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" s="88">
         <v>126</v>
       </c>
@@ -63016,7 +63020,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" s="88">
         <v>127</v>
       </c>
@@ -63048,7 +63052,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" s="88">
         <v>128</v>
       </c>
@@ -63080,7 +63084,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" s="88">
         <v>129</v>
       </c>
@@ -63112,7 +63116,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" s="88">
         <v>130</v>
       </c>
@@ -63144,7 +63148,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" s="88">
         <v>131</v>
       </c>
@@ -63176,7 +63180,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" s="88">
         <v>132</v>
       </c>
@@ -63208,7 +63212,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" s="88">
         <v>133</v>
       </c>
@@ -63240,7 +63244,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" s="88">
         <v>134</v>
       </c>
@@ -63272,7 +63276,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" s="88">
         <v>135</v>
       </c>
@@ -63304,7 +63308,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" s="88">
         <v>136</v>
       </c>
@@ -63336,7 +63340,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" s="88">
         <v>137</v>
       </c>
@@ -63368,7 +63372,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" s="88">
         <v>138</v>
       </c>
@@ -63400,7 +63404,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" s="88">
         <v>139</v>
       </c>
@@ -63432,7 +63436,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" s="88">
         <v>140</v>
       </c>
@@ -63464,7 +63468,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" s="88">
         <v>141</v>
       </c>
@@ -63496,7 +63500,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" s="88">
         <v>142</v>
       </c>
@@ -63528,7 +63532,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" s="88">
         <v>143</v>
       </c>
@@ -63560,7 +63564,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" s="88">
         <v>144</v>
       </c>
@@ -63592,7 +63596,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" s="88">
         <v>145</v>
       </c>
@@ -63624,7 +63628,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" s="88">
         <v>146</v>
       </c>
@@ -63656,7 +63660,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" s="88">
         <v>147</v>
       </c>
@@ -63688,7 +63692,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" s="88">
         <v>148</v>
       </c>
@@ -63720,7 +63724,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" s="88">
         <v>149</v>
       </c>
@@ -63752,7 +63756,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" s="88">
         <v>150</v>
       </c>
@@ -63784,7 +63788,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" s="88">
         <v>151</v>
       </c>
@@ -63816,7 +63820,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" s="88">
         <v>152</v>
       </c>
@@ -63848,7 +63852,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" s="88">
         <v>153</v>
       </c>
@@ -63880,7 +63884,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" s="88">
         <v>154</v>
       </c>
@@ -63912,7 +63916,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" s="88">
         <v>155</v>
       </c>
@@ -63944,7 +63948,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" s="88">
         <v>156</v>
       </c>
@@ -63976,7 +63980,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" s="88">
         <v>157</v>
       </c>
@@ -64008,7 +64012,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" s="88">
         <v>158</v>
       </c>
@@ -64040,7 +64044,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" s="88">
         <v>159</v>
       </c>
@@ -64072,7 +64076,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" s="88">
         <v>160</v>
       </c>
@@ -64104,7 +64108,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" s="88">
         <v>161</v>
       </c>
@@ -64136,7 +64140,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" s="88">
         <v>162</v>
       </c>
@@ -64168,7 +64172,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" s="88">
         <v>163</v>
       </c>
@@ -64200,7 +64204,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" s="88">
         <v>164</v>
       </c>
@@ -64232,7 +64236,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B170" s="88">
         <v>165</v>
       </c>
@@ -64264,7 +64268,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" s="88">
         <v>166</v>
       </c>
@@ -64296,7 +64300,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" s="88">
         <v>167</v>
       </c>
@@ -64328,7 +64332,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" s="88">
         <v>168</v>
       </c>
@@ -64360,7 +64364,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" s="88">
         <v>169</v>
       </c>
@@ -64392,7 +64396,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" s="88">
         <v>170</v>
       </c>
@@ -64424,7 +64428,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" s="88">
         <v>171</v>
       </c>
@@ -64456,7 +64460,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" s="88">
         <v>172</v>
       </c>
@@ -64488,7 +64492,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" s="88">
         <v>173</v>
       </c>
@@ -64520,7 +64524,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" s="88">
         <v>174</v>
       </c>
@@ -64552,7 +64556,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" s="88">
         <v>175</v>
       </c>
@@ -64584,7 +64588,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" s="88">
         <v>176</v>
       </c>
@@ -64616,7 +64620,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" s="88">
         <v>177</v>
       </c>
@@ -64648,7 +64652,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" s="88">
         <v>178</v>
       </c>
@@ -64680,7 +64684,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" s="88">
         <v>179</v>
       </c>
@@ -64712,7 +64716,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" s="88">
         <v>180</v>
       </c>
@@ -64744,7 +64748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" s="88">
         <v>181</v>
       </c>
@@ -64776,7 +64780,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" s="88">
         <v>182</v>
       </c>
@@ -64808,7 +64812,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" s="88">
         <v>183</v>
       </c>
@@ -64840,7 +64844,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" s="88">
         <v>184</v>
       </c>
@@ -64872,7 +64876,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" s="88">
         <v>185</v>
       </c>
@@ -64904,7 +64908,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" s="88">
         <v>186</v>
       </c>
@@ -64936,7 +64940,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" s="88">
         <v>187</v>
       </c>
@@ -64968,7 +64972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" s="88">
         <v>188</v>
       </c>
@@ -65000,7 +65004,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" s="88">
         <v>189</v>
       </c>
@@ -65032,7 +65036,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" s="88">
         <v>190</v>
       </c>
@@ -65064,7 +65068,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" s="88">
         <v>191</v>
       </c>
@@ -65096,7 +65100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" s="88">
         <v>192</v>
       </c>
@@ -65128,7 +65132,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" s="88">
         <v>193</v>
       </c>
@@ -65160,7 +65164,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" s="88">
         <v>194</v>
       </c>
@@ -65192,7 +65196,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" s="88">
         <v>195</v>
       </c>
@@ -65224,7 +65228,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" s="88">
         <v>196</v>
       </c>
@@ -65256,7 +65260,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" s="88">
         <v>197</v>
       </c>
@@ -65288,7 +65292,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" s="88">
         <v>198</v>
       </c>
@@ -65320,7 +65324,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" s="88">
         <v>199</v>
       </c>
@@ -65352,7 +65356,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" s="88">
         <v>200</v>
       </c>
@@ -65384,7 +65388,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" s="88">
         <v>201</v>
       </c>
@@ -65416,7 +65420,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" s="88">
         <v>202</v>
       </c>
@@ -65448,7 +65452,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" s="88">
         <v>203</v>
       </c>
@@ -65480,7 +65484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" s="88">
         <v>204</v>
       </c>
@@ -65512,7 +65516,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" s="88">
         <v>205</v>
       </c>
@@ -65544,7 +65548,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211" s="88">
         <v>206</v>
       </c>
@@ -65576,7 +65580,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" s="88">
         <v>207</v>
       </c>
@@ -65608,7 +65612,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" s="88">
         <v>208</v>
       </c>
@@ -65640,7 +65644,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" s="88">
         <v>209</v>
       </c>
@@ -65672,7 +65676,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" s="88">
         <v>210</v>
       </c>
@@ -65704,7 +65708,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" s="88">
         <v>211</v>
       </c>
@@ -65736,7 +65740,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" s="88">
         <v>212</v>
       </c>
@@ -65768,7 +65772,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" s="88">
         <v>213</v>
       </c>
@@ -65800,7 +65804,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" s="88">
         <v>214</v>
       </c>
@@ -65832,7 +65836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" s="88">
         <v>215</v>
       </c>
@@ -65864,7 +65868,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" s="88">
         <v>216</v>
       </c>
@@ -65896,7 +65900,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" s="88">
         <v>217</v>
       </c>
@@ -65928,7 +65932,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" s="88">
         <v>218</v>
       </c>
@@ -65960,7 +65964,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" s="88">
         <v>219</v>
       </c>
@@ -65992,7 +65996,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" s="88">
         <v>220</v>
       </c>
@@ -66024,7 +66028,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226" s="88">
         <v>221</v>
       </c>
@@ -66056,7 +66060,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" s="88">
         <v>222</v>
       </c>
@@ -66088,7 +66092,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" s="88">
         <v>223</v>
       </c>
@@ -66120,7 +66124,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" s="88">
         <v>224</v>
       </c>
@@ -66152,7 +66156,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" s="88">
         <v>225</v>
       </c>
@@ -66184,7 +66188,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" s="88">
         <v>226</v>
       </c>
@@ -66216,7 +66220,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" s="88">
         <v>227</v>
       </c>
@@ -66248,7 +66252,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" s="88">
         <v>228</v>
       </c>
@@ -66280,7 +66284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" s="88">
         <v>229</v>
       </c>
@@ -66312,7 +66316,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" s="88">
         <v>230</v>
       </c>
@@ -66344,7 +66348,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" s="88">
         <v>231</v>
       </c>
@@ -66376,7 +66380,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" s="88">
         <v>232</v>
       </c>
@@ -66408,7 +66412,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" s="88">
         <v>233</v>
       </c>
@@ -66440,7 +66444,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" s="88">
         <v>234</v>
       </c>
@@ -66472,7 +66476,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" s="88">
         <v>235</v>
       </c>
@@ -66504,7 +66508,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" s="88">
         <v>236</v>
       </c>
@@ -66536,7 +66540,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" s="88">
         <v>237</v>
       </c>
@@ -66568,7 +66572,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" s="88">
         <v>238</v>
       </c>
@@ -66600,7 +66604,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" s="88">
         <v>239</v>
       </c>
@@ -66632,7 +66636,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" s="88">
         <v>240</v>
       </c>
@@ -66664,7 +66668,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" s="88">
         <v>241</v>
       </c>
@@ -66696,7 +66700,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247" s="88">
         <v>242</v>
       </c>
@@ -66728,7 +66732,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" s="88">
         <v>243</v>
       </c>
@@ -66760,7 +66764,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" s="88">
         <v>244</v>
       </c>
@@ -66792,7 +66796,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="250" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" s="88">
         <v>245</v>
       </c>
@@ -66824,7 +66828,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="251" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" s="88">
         <v>246</v>
       </c>
@@ -66856,7 +66860,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="252" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" s="88">
         <v>247</v>
       </c>
@@ -66888,7 +66892,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="253" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" s="88">
         <v>248</v>
       </c>
@@ -66920,7 +66924,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="254" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" s="88">
         <v>249</v>
       </c>
@@ -66952,7 +66956,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="255" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255" s="88">
         <v>250</v>
       </c>
@@ -66984,7 +66988,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="256" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B256" s="88">
         <v>251</v>
       </c>
@@ -67016,7 +67020,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="257" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" s="88">
         <v>252</v>
       </c>
@@ -67048,7 +67052,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" s="88">
         <v>253</v>
       </c>
@@ -67080,7 +67084,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="259" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" s="88">
         <v>254</v>
       </c>
@@ -67112,7 +67116,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260" s="88">
         <v>255</v>
       </c>
@@ -67144,7 +67148,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" s="88">
         <v>256</v>
       </c>
@@ -67176,7 +67180,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262" s="88">
         <v>257</v>
       </c>
@@ -67208,7 +67212,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" s="88">
         <v>258</v>
       </c>
@@ -67240,7 +67244,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" s="88">
         <v>259</v>
       </c>
@@ -67272,7 +67276,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" s="88">
         <v>260</v>
       </c>
@@ -67304,7 +67308,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="266" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" s="88">
         <v>261</v>
       </c>
@@ -67336,7 +67340,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" s="88">
         <v>262</v>
       </c>
@@ -67368,7 +67372,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="268" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" s="88">
         <v>263</v>
       </c>
@@ -67400,7 +67404,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" s="88">
         <v>264</v>
       </c>
@@ -67432,7 +67436,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" s="88">
         <v>265</v>
       </c>
@@ -67464,7 +67468,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" s="88">
         <v>266</v>
       </c>
@@ -67496,7 +67500,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="272" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" s="88">
         <v>267</v>
       </c>
@@ -67528,7 +67532,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="273" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" s="88">
         <v>268</v>
       </c>
@@ -67560,7 +67564,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="274" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" s="88">
         <v>269</v>
       </c>
@@ -67592,7 +67596,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="275" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" s="88">
         <v>270</v>
       </c>
@@ -67624,7 +67628,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="276" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" s="88">
         <v>271</v>
       </c>
@@ -67656,7 +67660,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="277" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" s="88">
         <v>272</v>
       </c>
@@ -67688,7 +67692,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="278" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" s="88">
         <v>273</v>
       </c>
@@ -67720,7 +67724,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="279" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" s="88">
         <v>274</v>
       </c>
@@ -67752,7 +67756,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="280" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" s="88">
         <v>275</v>
       </c>
@@ -67784,7 +67788,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="281" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" s="88">
         <v>276</v>
       </c>
@@ -67816,7 +67820,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="282" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" s="88">
         <v>277</v>
       </c>
@@ -67848,7 +67852,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="283" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" s="88">
         <v>278</v>
       </c>
@@ -67880,7 +67884,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="284" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284" s="88">
         <v>279</v>
       </c>
@@ -67912,7 +67916,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="285" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" s="88">
         <v>280</v>
       </c>
@@ -67944,7 +67948,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="286" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" s="88">
         <v>281</v>
       </c>
@@ -67976,7 +67980,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287" s="88">
         <v>282</v>
       </c>
@@ -68008,7 +68012,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="288" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" s="88">
         <v>283</v>
       </c>
@@ -68040,7 +68044,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" s="88">
         <v>284</v>
       </c>
@@ -68072,7 +68076,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" s="88">
         <v>285</v>
       </c>
@@ -68104,7 +68108,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" s="88">
         <v>286</v>
       </c>
@@ -68136,7 +68140,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" s="88">
         <v>287</v>
       </c>
@@ -68168,7 +68172,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B293" s="88">
         <v>288</v>
       </c>
@@ -68200,7 +68204,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" s="88">
         <v>289</v>
       </c>
@@ -68232,7 +68236,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" s="88">
         <v>290</v>
       </c>
@@ -68264,7 +68268,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="296" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296" s="88">
         <v>291</v>
       </c>
@@ -68296,7 +68300,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297" s="88">
         <v>292</v>
       </c>
@@ -68328,7 +68332,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298" s="88">
         <v>293</v>
       </c>
@@ -68360,7 +68364,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299" s="88">
         <v>294</v>
       </c>
@@ -68392,7 +68396,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300" s="88">
         <v>295</v>
       </c>
@@ -68424,7 +68428,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="301" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B301" s="88">
         <v>296</v>
       </c>
@@ -68456,7 +68460,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="302" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B302" s="88">
         <v>297</v>
       </c>
@@ -68488,7 +68492,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B303" s="88">
         <v>298</v>
       </c>
@@ -68520,7 +68524,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="304" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B304" s="88">
         <v>299</v>
       </c>
@@ -68552,7 +68556,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B305" s="88">
         <v>300</v>
       </c>
@@ -68584,7 +68588,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B306" s="88">
         <v>301</v>
       </c>
@@ -68616,7 +68620,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B307" s="88">
         <v>302</v>
       </c>
@@ -68648,7 +68652,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B308" s="88">
         <v>303</v>
       </c>
@@ -68680,7 +68684,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B309" s="88">
         <v>304</v>
       </c>
@@ -68712,7 +68716,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B310" s="88">
         <v>305</v>
       </c>
@@ -68744,7 +68748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="311" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B311" s="88">
         <v>306</v>
       </c>
@@ -68776,7 +68780,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="312" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B312" s="88">
         <v>307</v>
       </c>
@@ -68808,7 +68812,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B313" s="88">
         <v>308</v>
       </c>
@@ -68840,7 +68844,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B314" s="88">
         <v>309</v>
       </c>
@@ -68872,7 +68876,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B315" s="88">
         <v>310</v>
       </c>
@@ -68904,7 +68908,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B316" s="88">
         <v>311</v>
       </c>
@@ -68936,7 +68940,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B317" s="88">
         <v>312</v>
       </c>
@@ -68968,7 +68972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="318" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B318" s="88">
         <v>313</v>
       </c>
@@ -69000,7 +69004,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="319" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B319" s="88">
         <v>314</v>
       </c>
@@ -69032,7 +69036,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B320" s="88">
         <v>315</v>
       </c>
@@ -69064,7 +69068,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="321" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B321" s="88">
         <v>316</v>
       </c>
@@ -69096,7 +69100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="322" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B322" s="88">
         <v>317</v>
       </c>
@@ -69128,7 +69132,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="323" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B323" s="88">
         <v>318</v>
       </c>
@@ -69160,7 +69164,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="324" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B324" s="88">
         <v>319</v>
       </c>
@@ -69192,7 +69196,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" s="88">
         <v>320</v>
       </c>
@@ -69224,7 +69228,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="326" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B326" s="88">
         <v>321</v>
       </c>
@@ -69256,7 +69260,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="327" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B327" s="88">
         <v>322</v>
       </c>
@@ -69288,7 +69292,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="328" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B328" s="88">
         <v>323</v>
       </c>
@@ -69320,7 +69324,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="329" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B329" s="88">
         <v>324</v>
       </c>
@@ -69352,7 +69356,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="330" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B330" s="88">
         <v>325</v>
       </c>
@@ -69384,7 +69388,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="331" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B331" s="88">
         <v>326</v>
       </c>
@@ -69416,7 +69420,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="332" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B332" s="88">
         <v>327</v>
       </c>
@@ -69448,7 +69452,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="333" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B333" s="88">
         <v>328</v>
       </c>
@@ -69480,7 +69484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="334" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B334" s="88">
         <v>329</v>
       </c>
@@ -69512,7 +69516,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="335" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B335" s="88">
         <v>330</v>
       </c>
@@ -69544,7 +69548,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" s="88">
         <v>331</v>
       </c>
@@ -69576,7 +69580,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="337" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B337" s="88">
         <v>332</v>
       </c>
@@ -69608,7 +69612,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" s="88">
         <v>333</v>
       </c>
@@ -69640,7 +69644,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="339" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B339" s="88">
         <v>334</v>
       </c>
@@ -69672,7 +69676,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="340" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B340" s="88">
         <v>335</v>
       </c>
@@ -69704,7 +69708,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="341" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B341" s="88">
         <v>336</v>
       </c>
@@ -69736,7 +69740,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="342" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B342" s="88">
         <v>337</v>
       </c>
@@ -69768,7 +69772,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="343" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="343" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B343" s="88">
         <v>338</v>
       </c>
@@ -69800,7 +69804,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="344" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="344" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B344" s="88">
         <v>339</v>
       </c>
@@ -69832,7 +69836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="345" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B345" s="88">
         <v>340</v>
       </c>
@@ -69864,7 +69868,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="346" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B346" s="88">
         <v>341</v>
       </c>
@@ -69896,7 +69900,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="347" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B347" s="88">
         <v>342</v>
       </c>
@@ -69928,7 +69932,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="348" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B348" s="88">
         <v>343</v>
       </c>
@@ -69960,7 +69964,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="349" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B349" s="88">
         <v>344</v>
       </c>
@@ -69992,7 +69996,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="350" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B350" s="88">
         <v>345</v>
       </c>
@@ -70024,7 +70028,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="351" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B351" s="88">
         <v>346</v>
       </c>
@@ -70056,7 +70060,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="352" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B352" s="88">
         <v>347</v>
       </c>
@@ -70088,7 +70092,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="353" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="353" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B353" s="88">
         <v>348</v>
       </c>
@@ -70120,7 +70124,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" s="88">
         <v>349</v>
       </c>
@@ -70152,7 +70156,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="355" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B355" s="88">
         <v>350</v>
       </c>
@@ -70184,7 +70188,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" s="88">
         <v>351</v>
       </c>
@@ -70216,7 +70220,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="357" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B357" s="88">
         <v>352</v>
       </c>
@@ -70248,7 +70252,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="358" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B358" s="88">
         <v>353</v>
       </c>
@@ -70280,7 +70284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="359" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B359" s="88">
         <v>354</v>
       </c>
@@ -70312,7 +70316,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="360" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B360" s="88">
         <v>355</v>
       </c>
@@ -70344,7 +70348,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="361" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="361" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B361" s="88">
         <v>356</v>
       </c>
@@ -70376,7 +70380,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="362" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B362" s="88">
         <v>357</v>
       </c>
@@ -70408,7 +70412,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="363" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="363" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B363" s="88">
         <v>358</v>
       </c>
@@ -70440,7 +70444,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="364" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B364" s="88">
         <v>359</v>
       </c>
@@ -70472,7 +70476,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="365" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B365" s="88">
         <v>360</v>
       </c>
@@ -70504,7 +70508,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="366" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B366" s="88">
         <v>361</v>
       </c>
@@ -70536,7 +70540,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="367" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B367" s="88">
         <v>362</v>
       </c>
@@ -70568,7 +70572,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="368" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B368" s="88">
         <v>363</v>
       </c>
@@ -70600,7 +70604,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="369" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B369" s="88">
         <v>364</v>
       </c>
@@ -70632,7 +70636,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="370" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B370" s="88">
         <v>365</v>
       </c>
@@ -70664,7 +70668,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="371" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="371" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B371" s="88">
         <v>366</v>
       </c>
@@ -70696,7 +70700,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" s="88">
         <v>367</v>
       </c>
@@ -70728,7 +70732,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="373" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="373" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B373" s="88">
         <v>368</v>
       </c>
@@ -70760,7 +70764,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="374" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="374" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B374" s="88">
         <v>369</v>
       </c>
@@ -70792,7 +70796,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B375" s="88">
         <v>370</v>
       </c>
@@ -70824,7 +70828,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B376" s="88">
         <v>371</v>
       </c>
@@ -70856,7 +70860,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="377" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B377" s="88">
         <v>372</v>
       </c>
@@ -70888,7 +70892,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="378" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B378" s="88">
         <v>373</v>
       </c>
@@ -70920,7 +70924,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="379" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B379" s="88">
         <v>374</v>
       </c>
@@ -70952,7 +70956,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="380" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B380" s="88">
         <v>375</v>
       </c>
@@ -70984,7 +70988,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="381" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B381" s="88">
         <v>376</v>
       </c>
@@ -71016,7 +71020,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" s="88">
         <v>377</v>
       </c>
@@ -71048,7 +71052,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="383" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="383" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B383" s="88">
         <v>378</v>
       </c>
@@ -71080,7 +71084,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="384" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="384" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B384" s="88">
         <v>379</v>
       </c>
@@ -71112,7 +71116,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="385" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B385" s="88">
         <v>380</v>
       </c>
@@ -71144,7 +71148,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="386" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B386" s="88">
         <v>381</v>
       </c>
@@ -71176,7 +71180,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="387" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B387" s="88">
         <v>382</v>
       </c>
@@ -71208,7 +71212,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="388" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B388" s="88">
         <v>383</v>
       </c>
@@ -71240,7 +71244,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="389" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B389" s="88">
         <v>384</v>
       </c>
@@ -71272,7 +71276,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="390" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B390" s="88">
         <v>385</v>
       </c>
@@ -71304,7 +71308,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="391" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B391" s="88">
         <v>386</v>
       </c>
@@ -71336,7 +71340,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="392" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B392" s="88">
         <v>387</v>
       </c>
@@ -71368,7 +71372,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="393" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B393" s="88">
         <v>388</v>
       </c>
@@ -71400,7 +71404,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="394" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B394" s="88">
         <v>389</v>
       </c>
@@ -71432,7 +71436,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="395" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B395" s="88">
         <v>390</v>
       </c>
@@ -71464,7 +71468,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B396" s="88">
         <v>391</v>
       </c>
@@ -71496,7 +71500,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B397" s="88">
         <v>392</v>
       </c>
@@ -71528,7 +71532,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B398" s="88">
         <v>393</v>
       </c>
@@ -71560,7 +71564,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="399" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B399" s="88">
         <v>394</v>
       </c>
@@ -71592,7 +71596,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B400" s="88">
         <v>395</v>
       </c>
@@ -71624,7 +71628,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="401" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B401" s="88">
         <v>396</v>
       </c>
@@ -71656,7 +71660,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="402" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="402" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B402" s="88">
         <v>397</v>
       </c>
@@ -71688,7 +71692,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="403" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B403" s="88">
         <v>398</v>
       </c>
@@ -71720,7 +71724,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="404" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B404" s="88">
         <v>399</v>
       </c>
@@ -71752,7 +71756,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="405" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="405" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B405" s="88">
         <v>400</v>
       </c>
@@ -71784,7 +71788,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="406" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B406" s="88">
         <v>401</v>
       </c>
@@ -71816,7 +71820,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="407" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="407" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B407" s="88">
         <v>402</v>
       </c>
@@ -71848,7 +71852,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="408" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="408" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B408" s="88">
         <v>403</v>
       </c>
@@ -71880,7 +71884,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="409" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="409" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B409" s="88">
         <v>404</v>
       </c>
@@ -71912,7 +71916,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="410" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B410" s="88">
         <v>405</v>
       </c>
@@ -71944,7 +71948,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="411" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="411" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B411" s="88">
         <v>406</v>
       </c>
@@ -71976,7 +71980,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="412" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B412" s="88">
         <v>407</v>
       </c>
@@ -72008,7 +72012,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="413" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B413" s="88">
         <v>408</v>
       </c>
@@ -72040,7 +72044,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="414" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="414" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B414" s="88">
         <v>409</v>
       </c>
@@ -72072,7 +72076,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="415" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="415" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B415" s="88">
         <v>410</v>
       </c>
@@ -72104,7 +72108,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="416" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="416" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B416" s="88">
         <v>411</v>
       </c>
@@ -72136,7 +72140,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="417" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B417" s="88">
         <v>412</v>
       </c>
@@ -72168,7 +72172,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="418" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B418" s="88">
         <v>413</v>
       </c>
@@ -72200,7 +72204,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="419" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B419" s="88">
         <v>414</v>
       </c>
@@ -72232,7 +72236,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="420" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B420" s="88">
         <v>415</v>
       </c>
@@ -72264,7 +72268,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B421" s="88">
         <v>416</v>
       </c>
@@ -72296,7 +72300,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B422" s="88">
         <v>417</v>
       </c>
@@ -72328,7 +72332,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B423" s="88">
         <v>418</v>
       </c>
@@ -72360,7 +72364,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B424" s="88">
         <v>419</v>
       </c>
@@ -72392,7 +72396,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B425" s="88">
         <v>420</v>
       </c>
@@ -72424,7 +72428,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B426" s="88">
         <v>421</v>
       </c>
@@ -72456,7 +72460,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B427" s="88">
         <v>422</v>
       </c>
@@ -72488,7 +72492,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B428" s="88">
         <v>423</v>
       </c>
@@ -72520,7 +72524,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B429" s="88">
         <v>424</v>
       </c>
@@ -72552,7 +72556,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B430" s="88">
         <v>425</v>
       </c>
@@ -72584,7 +72588,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B431" s="88">
         <v>426</v>
       </c>
@@ -72616,7 +72620,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B432" s="88">
         <v>427</v>
       </c>
@@ -72648,7 +72652,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B433" s="88">
         <v>428</v>
       </c>
@@ -72680,7 +72684,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B434" s="88">
         <v>429</v>
       </c>
@@ -72712,7 +72716,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B435" s="88">
         <v>430</v>
       </c>
@@ -72744,7 +72748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B436" s="88">
         <v>431</v>
       </c>
@@ -72776,7 +72780,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B437" s="88">
         <v>432</v>
       </c>
@@ -72808,7 +72812,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B438" s="88">
         <v>433</v>
       </c>
@@ -72840,7 +72844,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B439" s="88">
         <v>434</v>
       </c>
@@ -72872,7 +72876,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B440" s="88">
         <v>435</v>
       </c>
@@ -72904,7 +72908,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B441" s="88">
         <v>436</v>
       </c>
@@ -72936,7 +72940,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B442" s="88">
         <v>437</v>
       </c>
@@ -72968,7 +72972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B443" s="88">
         <v>438</v>
       </c>
@@ -73000,7 +73004,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B444" s="88">
         <v>439</v>
       </c>
@@ -73032,7 +73036,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B445" s="88">
         <v>440</v>
       </c>
@@ -73064,7 +73068,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="446" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="446" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B446" s="88">
         <v>441</v>
       </c>
@@ -73096,7 +73100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="447" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B447" s="88">
         <v>442</v>
       </c>
@@ -73128,7 +73132,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B448" s="88">
         <v>443</v>
       </c>
@@ -73160,7 +73164,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="449" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="449" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B449" s="88">
         <v>444</v>
       </c>
@@ -73192,7 +73196,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="450" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B450" s="88">
         <v>445</v>
       </c>
@@ -73224,7 +73228,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="451" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B451" s="88">
         <v>446</v>
       </c>
@@ -73256,7 +73260,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="452" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B452" s="88">
         <v>447</v>
       </c>
@@ -73288,7 +73292,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B453" s="88">
         <v>448</v>
       </c>
@@ -73320,7 +73324,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="454" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B454" s="88">
         <v>449</v>
       </c>
@@ -73352,7 +73356,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="455" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B455" s="88">
         <v>450</v>
       </c>
@@ -73384,7 +73388,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="456" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B456" s="88">
         <v>451</v>
       </c>
@@ -73416,7 +73420,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="457" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B457" s="88">
         <v>452</v>
       </c>
@@ -73448,7 +73452,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="458" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B458" s="88">
         <v>453</v>
       </c>
@@ -73480,7 +73484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="459" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B459" s="88">
         <v>454</v>
       </c>
@@ -73512,7 +73516,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="460" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B460" s="88">
         <v>455</v>
       </c>
@@ -73544,7 +73548,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B461" s="88">
         <v>456</v>
       </c>
@@ -73576,7 +73580,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="462" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B462" s="88">
         <v>457</v>
       </c>
@@ -73608,7 +73612,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="463" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B463" s="88">
         <v>458</v>
       </c>
@@ -73640,7 +73644,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="464" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B464" s="88">
         <v>459</v>
       </c>
@@ -73672,7 +73676,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B465" s="88">
         <v>460</v>
       </c>
@@ -73704,7 +73708,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B466" s="88">
         <v>461</v>
       </c>
@@ -73736,7 +73740,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B467" s="88">
         <v>462</v>
       </c>
@@ -73768,7 +73772,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B468" s="88">
         <v>463</v>
       </c>
@@ -73800,7 +73804,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B469" s="88">
         <v>464</v>
       </c>
@@ -73832,7 +73836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B470" s="88">
         <v>465</v>
       </c>
@@ -73864,7 +73868,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B471" s="88">
         <v>466</v>
       </c>
@@ -73896,7 +73900,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B472" s="88">
         <v>467</v>
       </c>
@@ -73928,7 +73932,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B473" s="88">
         <v>468</v>
       </c>
@@ -73960,7 +73964,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B474" s="88">
         <v>469</v>
       </c>
@@ -73992,7 +73996,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B475" s="88">
         <v>470</v>
       </c>
@@ -74024,7 +74028,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B476" s="88">
         <v>471</v>
       </c>
@@ -74056,7 +74060,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B477" s="88">
         <v>472</v>
       </c>
@@ -74088,7 +74092,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B478" s="88">
         <v>473</v>
       </c>
@@ -74120,7 +74124,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B479" s="88">
         <v>474</v>
       </c>
@@ -74152,7 +74156,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B480" s="88">
         <v>475</v>
       </c>
@@ -74184,7 +74188,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="481" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B481" s="88">
         <v>476</v>
       </c>
@@ -74216,7 +74220,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="482" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="482" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B482" s="88">
         <v>477</v>
       </c>
@@ -74248,7 +74252,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="483" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="483" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B483" s="88">
         <v>478</v>
       </c>
@@ -74280,7 +74284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="484" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="484" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B484" s="88">
         <v>479</v>
       </c>
@@ -74312,7 +74316,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="485" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="485" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B485" s="88">
         <v>480</v>
       </c>
@@ -74344,7 +74348,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="486" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="486" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B486" s="88">
         <v>481</v>
       </c>
@@ -74376,7 +74380,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B487" s="88">
         <v>482</v>
       </c>
@@ -74408,7 +74412,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="488" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B488" s="88">
         <v>483</v>
       </c>
@@ -74440,7 +74444,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="489" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="489" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B489" s="88">
         <v>484</v>
       </c>
@@ -74472,7 +74476,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="490" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B490" s="88">
         <v>485</v>
       </c>
@@ -74504,7 +74508,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="491" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B491" s="88">
         <v>486</v>
       </c>
@@ -74536,7 +74540,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B492" s="88">
         <v>487</v>
       </c>
@@ -74568,7 +74572,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="493" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B493" s="88">
         <v>488</v>
       </c>
@@ -74600,7 +74604,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="494" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B494" s="88">
         <v>489</v>
       </c>
@@ -74632,7 +74636,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="495" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B495" s="88">
         <v>490</v>
       </c>
@@ -74664,7 +74668,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="496" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B496" s="88">
         <v>491</v>
       </c>
@@ -74696,7 +74700,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="497" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="497" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B497" s="88">
         <v>492</v>
       </c>
@@ -74728,7 +74732,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="498" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="498" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B498" s="88">
         <v>493</v>
       </c>
@@ -74760,7 +74764,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="499" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="499" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B499" s="88">
         <v>494</v>
       </c>
@@ -74792,7 +74796,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="500" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B500" s="90">
         <v>495</v>
       </c>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CC741F-A440-4C2A-818C-6650BF56E49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0D5E99-B6CD-40F6-AA03-0EF977303C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="str" cm="1">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="141" t="str" cm="1">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41421,7 +41421,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41655,7 +41655,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41772,7 +41772,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -41824,8 +41824,12 @@
         <f>AE16</f>
         <v>Qatar</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="19">
+        <v>1</v>
+      </c>
+      <c r="G14" s="20">
+        <v>1</v>
+      </c>
       <c r="H14" s="80" t="str">
         <f>AE17</f>
         <v>Switzerland</v>
@@ -41864,47 +41868,47 @@
       </c>
       <c r="S14" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Qatar_draw</v>
       </c>
       <c r="T14" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Switzerland_draw</v>
       </c>
       <c r="U14" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="123" t="str">
+      <c r="AB14" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD14" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR14))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" s="124" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
@@ -41944,11 +41948,11 @@
       </c>
       <c r="AO14" s="123">
         <f>AN14/AN18*10+BA14</f>
-        <v>5.9805825242718447</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP14" s="123">
         <f>AO14*10000000+BI14*100+AM14/AM18*10+AI14/AI18*1++IF(AQ14=0,ROW(),AQ14)/2000000</f>
-        <v>59805923.80174911</v>
+        <v>59902060.304699808</v>
       </c>
       <c r="AQ14" s="126">
         <f>VLOOKUP(AE14,db_fifarank,2,FALSE)</f>
@@ -41956,7 +41960,7 @@
       </c>
       <c r="AR14" s="125">
         <f>AP14/AP18</f>
-        <v>0.99999998327924866</v>
+        <v>0.99999998330530815</v>
       </c>
       <c r="AS14" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J15,"1B")</f>
@@ -41988,11 +41992,11 @@
       </c>
       <c r="AZ14" s="126">
         <f>AT14/AT18*1000+AU14/AU18*100+AY14/AY18*10+AV14/AV18</f>
-        <v>50.5</v>
+        <v>101</v>
       </c>
       <c r="BA14" s="126">
         <f>AZ14/AZ18</f>
-        <v>0.98058252427184467</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB14" s="126" cm="1">
         <f t="array" ref="BB14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_win")*($X$7:$X$78))</f>
@@ -42020,13 +42024,13 @@
       </c>
       <c r="BH14" s="126">
         <f>BB14/BB18*1000+BC14/BC18*100+BG14/BG18*10+BD14/BD18</f>
-        <v>50.5</v>
+        <v>101</v>
       </c>
       <c r="BI14" s="126">
         <f>BH14/BH18</f>
-        <v>0.98058252427184467</v>
-      </c>
-      <c r="BK14" s="131">
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42095,7 +42099,7 @@
       </c>
       <c r="J15" s="30" t="str">
         <f>VLOOKUP(1,AD14:AN17,2,FALSE)</f>
-        <v>Canada</v>
+        <v>Switzerland</v>
       </c>
       <c r="K15" s="31">
         <f>L15+M15+N15</f>
@@ -42167,7 +42171,7 @@
       </c>
       <c r="AD15" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR15))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE15" s="124" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
@@ -42207,11 +42211,11 @@
       </c>
       <c r="AO15" s="123">
         <f>AN15/AN18*10+BA15</f>
-        <v>5.9805825242718447</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP15" s="123">
         <f>AO15*10000000+BI15*100+AM15/AM18*10+AI15/AI18*1++IF(AQ15=0,ROW(),AQ15)/2000000</f>
-        <v>59805923.801663786</v>
+        <v>59902060.304614484</v>
       </c>
       <c r="AQ15" s="126">
         <f>VLOOKUP(AE15,db_fifarank,2,FALSE)</f>
@@ -42219,7 +42223,7 @@
       </c>
       <c r="AR15" s="125">
         <f>AP15/AP18</f>
-        <v>0.99999998327782191</v>
+        <v>0.99999998330388373</v>
       </c>
       <c r="AS15" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J16,"2B")</f>
@@ -42251,11 +42255,11 @@
       </c>
       <c r="AZ15" s="126">
         <f>AT15/AT18*1000+AU15/AU18*100+AY15/AY18*10+AV15/AV18</f>
-        <v>50.5</v>
+        <v>101</v>
       </c>
       <c r="BA15" s="126">
         <f>AZ15/AZ18</f>
-        <v>0.98058252427184467</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB15" s="126" cm="1">
         <f t="array" ref="BB15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_win")*($X$7:$X$78))</f>
@@ -42283,13 +42287,13 @@
       </c>
       <c r="BH15" s="126">
         <f>BB15/BB18*1000+BC15/BC18*100+BG15/BG18*10+BD15/BD18</f>
-        <v>50.5</v>
+        <v>101</v>
       </c>
       <c r="BI15" s="126">
         <f>BH15/BH18</f>
-        <v>0.98058252427184467</v>
-      </c>
-      <c r="BK15" s="132"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42355,7 +42359,7 @@
       </c>
       <c r="J16" s="33" t="str">
         <f>VLOOKUP(2,AD14:AN17,2,FALSE)</f>
-        <v>Bosnia and Herzegovina</v>
+        <v>Canada</v>
       </c>
       <c r="K16" s="23">
         <f>L16+M16+N16</f>
@@ -42427,7 +42431,7 @@
       </c>
       <c r="AD16" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR16))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE16" s="124" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
@@ -42439,7 +42443,7 @@
       </c>
       <c r="AG16" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE16 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE16 &amp; "_lose")</f>
@@ -42447,11 +42451,11 @@
       </c>
       <c r="AI16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE16,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE16,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL16" s="123">
         <f>AI16-AJ16</f>
@@ -42463,15 +42467,15 @@
       </c>
       <c r="AN16" s="123">
         <f>AF16*3+AG16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" s="123">
         <f>AN16/AN18*10+BA16</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP16" s="123">
         <f>AO16*10000000+BI16*100+AM16/AM18*10+AI16/AI18*1++IF(AQ16=0,ROW(),AQ16)/2000000</f>
-        <v>7.2747999999999997E-4</v>
+        <v>59902060.304649048</v>
       </c>
       <c r="AQ16" s="126">
         <f>VLOOKUP(AE16,db_fifarank,2,FALSE)</f>
@@ -42479,7 +42483,7 @@
       </c>
       <c r="AR16" s="125">
         <f>AP16/AP18</f>
-        <v>1.2164012218045725E-11</v>
+        <v>0.99999998330446072</v>
       </c>
       <c r="AT16" s="126" cm="1">
         <f t="array" ref="AT16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($U$7:$U$78))</f>
@@ -42487,15 +42491,15 @@
       </c>
       <c r="AU16" s="126" cm="1">
         <f t="array" ref="AU16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" s="126" cm="1">
         <f t="array" ref="AV16">SUMPRODUCT(($E$7:$E$78=AE16)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" s="126" cm="1">
         <f t="array" ref="AW16">SUMPRODUCT(($E$7:$E$78=AE16)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" s="126">
         <f>AV16-AW16</f>
@@ -42507,11 +42511,11 @@
       </c>
       <c r="AZ16" s="126">
         <f>AT16/AT18*1000+AU16/AU18*100+AY16/AY18*10+AV16/AV18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA16" s="126">
         <f>AZ16/AZ18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB16" s="126" cm="1">
         <f t="array" ref="BB16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($X$7:$X$78))</f>
@@ -42519,15 +42523,15 @@
       </c>
       <c r="BC16" s="126" cm="1">
         <f t="array" ref="BC16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD16" s="126" cm="1">
         <f t="array" ref="BD16">SUMPRODUCT(($E$7:$E$78=AE16)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE16" s="126" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(($E$7:$E$78=AE16)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF16" s="126">
         <f>BD16-BE16</f>
@@ -42539,11 +42543,11 @@
       </c>
       <c r="BH16" s="126">
         <f>BB16/BB18*1000+BC16/BC18*100+BG16/BG18*10+BD16/BD18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI16" s="126">
         <f>BH16/BH18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BK16" s="21"/>
       <c r="BL16" s="21"/>
@@ -42559,7 +42563,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42607,11 +42611,11 @@
       </c>
       <c r="J17" s="33" t="str">
         <f>VLOOKUP(3,AD14:AN17,2,FALSE)</f>
-        <v>Switzerland</v>
+        <v>Qatar</v>
       </c>
       <c r="K17" s="23">
         <f>L17+M17+N17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="23">
         <f>VLOOKUP(3,AD14:AN17,3,FALSE)</f>
@@ -42619,7 +42623,7 @@
       </c>
       <c r="M17" s="23">
         <f>VLOOKUP(3,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="23">
         <f>VLOOKUP(3,AD14:AN17,5,FALSE)</f>
@@ -42627,11 +42631,11 @@
       </c>
       <c r="O17" s="23" t="str">
         <f>VLOOKUP(3,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P17" s="34">
         <f>L17*3+M17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="123">
         <f>DATE(2026,6,14)+TIME(9,0,0)+gmt_delta</f>
@@ -42679,7 +42683,7 @@
       </c>
       <c r="AD17" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR17))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="124" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
@@ -42691,7 +42695,7 @@
       </c>
       <c r="AG17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_lose")</f>
@@ -42699,11 +42703,11 @@
       </c>
       <c r="AI17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE17,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE17,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" s="123">
         <f>AI17-AJ17</f>
@@ -42715,15 +42719,15 @@
       </c>
       <c r="AN17" s="123">
         <f>AF17*3+AG17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO17" s="123">
         <f>AN17/AN18*10+BA17</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP17" s="123">
         <f>AO17*10000000+BI17*100+AM17/AM18*10+AI17/AI18*1++IF(AQ17=0,ROW(),AQ17)/2000000</f>
-        <v>8.2470000000000004E-4</v>
+        <v>59902060.304746263</v>
       </c>
       <c r="AQ17" s="126">
         <f>VLOOKUP(AE17,db_fifarank,2,FALSE)</f>
@@ -42731,7 +42735,7 @@
       </c>
       <c r="AR17" s="125">
         <f>AP17/AP18</f>
-        <v>1.3789603667760363E-11</v>
+        <v>0.99999998330608364</v>
       </c>
       <c r="AT17" s="126" cm="1">
         <f t="array" ref="AT17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($U$7:$U$78))</f>
@@ -42739,15 +42743,15 @@
       </c>
       <c r="AU17" s="126" cm="1">
         <f t="array" ref="AU17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV17" s="126" cm="1">
         <f t="array" ref="AV17">SUMPRODUCT(($E$7:$E$78=AE17)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" s="126" cm="1">
         <f t="array" ref="AW17">SUMPRODUCT(($E$7:$E$78=AE17)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" s="126">
         <f>AV17-AW17</f>
@@ -42759,11 +42763,11 @@
       </c>
       <c r="AZ17" s="126">
         <f>AT17/AT18*1000+AU17/AU18*100+AY17/AY18*10+AV17/AV18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA17" s="126">
         <f>AZ17/AZ18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB17" s="126" cm="1">
         <f t="array" ref="BB17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($X$7:$X$78))</f>
@@ -42771,15 +42775,15 @@
       </c>
       <c r="BC17" s="126" cm="1">
         <f t="array" ref="BC17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD17" s="126" cm="1">
         <f t="array" ref="BD17">SUMPRODUCT(($E$7:$E$78=AE17)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE17" s="126" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(($E$7:$E$78=AE17)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF17" s="126">
         <f>BD17-BE17</f>
@@ -42791,11 +42795,11 @@
       </c>
       <c r="BH17" s="126">
         <f>BB17/BB18*1000+BC17/BC18*100+BG17/BG18*10+BD17/BD18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI17" s="126">
         <f>BH17/BH18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BK17" s="21" t="str" cm="1">
         <f t="array" ref="BK17">INDEX(T,24+MONTH(BP17),lang) &amp; " " &amp; DAY(BP17) &amp; ", " &amp; YEAR(BP17) &amp; "   " &amp; (IF(HOUR(BP17)&lt;10,0,"")&amp;HOUR(BP17)) &amp; ":" &amp;  (IF(MINUTE(BP17)&lt;10,0,"")&amp;MINUTE(BP17))</f>
@@ -42817,7 +42821,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -42863,11 +42867,11 @@
       </c>
       <c r="J18" s="35" t="str">
         <f>VLOOKUP(4,AD14:AN17,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="K18" s="36">
         <f>L18+M18+N18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="36">
         <f>VLOOKUP(4,AD14:AN17,3,FALSE)</f>
@@ -42875,7 +42879,7 @@
       </c>
       <c r="M18" s="36">
         <f>VLOOKUP(4,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="36">
         <f>VLOOKUP(4,AD14:AN17,5,FALSE)</f>
@@ -42883,11 +42887,11 @@
       </c>
       <c r="O18" s="36" t="str">
         <f>VLOOKUP(4,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P18" s="37">
         <f>L18*3+M18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="123">
         <f>DATE(2026,6,14)+TIME(15,0,0)+gmt_delta</f>
@@ -42939,7 +42943,7 @@
       </c>
       <c r="AG18" s="123">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH18" s="123">
         <f t="shared" si="13"/>
@@ -42963,11 +42967,11 @@
       </c>
       <c r="AO18" s="123">
         <f>MAX(AO14:AO17)+1</f>
-        <v>6.9805825242718447</v>
+        <v>6.9901960784313726</v>
       </c>
       <c r="AP18" s="123">
         <f>MAX(AP14:AP17)+1</f>
-        <v>59805924.80174911</v>
+        <v>59902061.304746263</v>
       </c>
       <c r="AT18" s="126">
         <f>MAX(AT14:AT17)-MIN(AT14:AT17)+1</f>
@@ -42975,15 +42979,15 @@
       </c>
       <c r="AU18" s="126">
         <f>MAX(AU14:AU17)-MIN(AU14:AU17)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV18" s="126">
         <f>MAX(AV14:AV17)-MIN(AV14:AV17)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW18" s="126">
         <f>MAX(AW14:AW17)-MIN(AW14:AW17)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY18" s="126">
         <f>MAX(AY14:AY17)-MIN(AY14:AY17)+1</f>
@@ -42991,7 +42995,7 @@
       </c>
       <c r="AZ18" s="126">
         <f>MAX(AZ14:AZ17)+1</f>
-        <v>51.5</v>
+        <v>102</v>
       </c>
       <c r="BB18" s="126">
         <f>MAX(BB14:BB17)-MIN(BB14:BB17)+1</f>
@@ -42999,15 +43003,15 @@
       </c>
       <c r="BC18" s="126">
         <f>MAX(BC14:BC17)-MIN(BC14:BC17)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD18" s="126">
         <f>MAX(BD14:BD17)-MIN(BD14:BD17)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE18" s="126">
         <f>MAX(BE14:BE17)-MIN(BE14:BE17)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG18" s="126">
         <f>MAX(BG14:BG17)-MIN(BG14:BG17)+1</f>
@@ -43015,9 +43019,9 @@
       </c>
       <c r="BH18" s="126">
         <f>MAX(BH14:BH17)+1</f>
-        <v>51.5</v>
-      </c>
-      <c r="BK18" s="131">
+        <v>102</v>
+      </c>
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43121,7 +43125,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43395,7 +43399,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43664,7 +43668,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43914,7 +43918,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44174,7 +44178,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44201,7 +44205,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44418,7 +44422,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44763,7 +44767,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45027,7 +45031,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45298,7 +45302,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45559,7 +45563,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45769,7 +45773,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45876,7 +45880,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46148,7 +46152,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46408,7 +46412,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46423,14 +46427,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46650,7 +46654,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46681,11 +46685,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46905,7 +46909,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47130,7 +47134,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47250,7 +47254,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47277,7 +47281,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47514,7 +47518,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47544,7 +47548,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47779,7 +47783,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48455,7 +48459,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48548,7 +48552,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="132"/>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48804,7 +48808,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48819,14 +48823,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49063,7 +49067,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49076,11 +49080,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49300,7 +49304,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49542,7 +49546,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49785,7 +49789,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49801,7 +49805,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49906,7 +49910,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49920,7 +49924,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50155,7 +50159,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="131">
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50408,7 +50412,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="132"/>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50668,7 +50672,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50923,7 +50927,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51127,7 +51131,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="131">
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51248,7 +51252,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51275,7 +51279,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51534,7 +51538,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52017,7 +52021,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52265,7 +52269,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52488,7 +52492,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52601,7 +52605,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52844,7 +52848,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53096,7 +53100,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53362,7 +53366,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53616,7 +53620,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53812,7 +53816,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53912,7 +53916,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54168,7 +54172,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54182,25 +54186,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54438,7 +54442,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54450,19 +54454,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54683,7 +54687,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54919,7 +54923,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56400,11 +56404,11 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Switzerland</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,3,FALSE)</f>
@@ -56412,7 +56416,7 @@
       </c>
       <c r="M81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,5,FALSE)</f>
@@ -56420,11 +56424,11 @@
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
@@ -56432,7 +56436,7 @@
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
-        <v>Switzerland</v>
+        <v>Qatar</v>
       </c>
       <c r="AF81" s="123">
         <f t="shared" ref="AF81:AF91" si="39">VLOOKUP($AE81,$AE$8:$AQ$78,2,FALSE)</f>
@@ -56440,7 +56444,7 @@
       </c>
       <c r="AG81" s="123">
         <f>VLOOKUP($AE81,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH81" s="123">
         <f t="shared" ref="AH81:AH90" si="40">VLOOKUP($AE81,$AE$8:$AQ$78,4,FALSE)</f>
@@ -56448,11 +56452,11 @@
       </c>
       <c r="AI81" s="123">
         <f t="shared" ref="AI81:AI90" si="41">VLOOKUP($AE81,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ81" s="123">
         <f t="shared" ref="AJ81:AJ90" si="42">VLOOKUP($AE81,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK81" s="123" t="s">
         <v>3181</v>
@@ -56467,15 +56471,15 @@
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>500.00082470000001</v>
+        <v>5550.00072748</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
-        <v>1649.4</v>
+        <v>1454.96</v>
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
@@ -56483,11 +56487,11 @@
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
-        <v>Switzerland</v>
+        <v>Qatar</v>
       </c>
       <c r="AT81" s="130" t="str">
         <f>"Ⓑ "&amp;AE81</f>
-        <v>Ⓑ Switzerland</v>
+        <v>Ⓑ Qatar</v>
       </c>
     </row>
     <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -56595,13 +56599,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56699,11 +56703,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56813,11 +56817,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -56927,11 +56931,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57041,11 +57045,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57155,11 +57159,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57652,7 +57656,7 @@
       </c>
       <c r="AG92" s="123">
         <f>MAX(AG80:AG91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
@@ -57676,7 +57680,7 @@
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
@@ -57836,6 +57840,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57851,36 +57885,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0D5E99-B6CD-40F6-AA03-0EF977303C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F675E4CC-8726-492F-86EC-B032AE700334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="str" cm="1">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="str" cm="1">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41421,7 +41421,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41655,7 +41655,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41709,8 +41709,12 @@
         <f>AE20</f>
         <v>Brazil</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
+      <c r="F13" s="19">
+        <v>1</v>
+      </c>
+      <c r="G13" s="20">
+        <v>1</v>
+      </c>
       <c r="H13" s="80" t="str">
         <f>AE21</f>
         <v>Morocco</v>
@@ -41721,43 +41725,43 @@
       </c>
       <c r="S13" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Brazil_draw</v>
       </c>
       <c r="T13" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Morocco_draw</v>
       </c>
       <c r="U13" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB13" s="123" t="str">
+      <c r="AB13" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK13" s="21" t="str" cm="1">
         <f t="array" ref="BK13">INDEX(T,24+MONTH(BP13),lang) &amp; " " &amp; DAY(BP13) &amp; ", " &amp; YEAR(BP13) &amp; "   " &amp; (IF(HOUR(BP13)&lt;10,0,"")&amp;HOUR(BP13)) &amp; ":" &amp;  (IF(MINUTE(BP13)&lt;10,0,"")&amp;MINUTE(BP13))</f>
@@ -41772,7 +41776,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42030,7 +42034,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42293,7 +42297,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42563,7 +42567,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42821,7 +42825,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43021,7 +43025,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43125,7 +43129,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43282,7 +43286,7 @@
       </c>
       <c r="AG20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_lose")</f>
@@ -43290,11 +43294,11 @@
       </c>
       <c r="AI20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE20,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE20,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" s="123">
         <f>AI20-AJ20</f>
@@ -43306,15 +43310,15 @@
       </c>
       <c r="AN20" s="123">
         <f>AF20*3+AG20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO20" s="123">
         <f>AN20/AN24*10+BA20</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP20" s="123">
         <f>AO20*10000000+BI20*100+AM20/AM24*10+AI20/AI24*1++IF(AQ20=0,ROW(),AQ20)/2000000</f>
-        <v>8.8058000000000006E-4</v>
+        <v>59805923.801851444</v>
       </c>
       <c r="AQ20" s="126">
         <f>VLOOKUP(AE20,db_fifarank,2,FALSE)</f>
@@ -43322,7 +43326,7 @@
       </c>
       <c r="AR20" s="125">
         <f>AP20/AP24</f>
-        <v>8.7980526108319542E-4</v>
+        <v>0.99999998327924866</v>
       </c>
       <c r="AS20" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J21,"1C")</f>
@@ -43334,15 +43338,15 @@
       </c>
       <c r="AU20" s="126" cm="1">
         <f t="array" ref="AU20">SUMPRODUCT(($S$7:$S$78=AE20&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE20&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" s="126" cm="1">
         <f t="array" ref="AV20">SUMPRODUCT(($E$7:$E$78=AE20)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW20" s="126" cm="1">
         <f t="array" ref="AW20">SUMPRODUCT(($E$7:$E$78=AE20)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX20" s="126">
         <f>AV20-AW20</f>
@@ -43354,11 +43358,11 @@
       </c>
       <c r="AZ20" s="126">
         <f>AT20/AT24*1000+AU20/AU24*100+AY20/AY24*10+AV20/AV24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA20" s="126">
         <f>AZ20/AZ24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB20" s="126" cm="1">
         <f t="array" ref="BB20">SUMPRODUCT(($S$7:$S$78=AE20&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE20&amp;"_win")*($X$7:$X$78))</f>
@@ -43366,15 +43370,15 @@
       </c>
       <c r="BC20" s="126" cm="1">
         <f t="array" ref="BC20">SUMPRODUCT(($S$7:$S$78=AE20&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE20&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD20" s="126" cm="1">
         <f t="array" ref="BD20">SUMPRODUCT(($E$7:$E$78=AE20)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE20" s="126" cm="1">
         <f t="array" ref="BE20">SUMPRODUCT(($E$7:$E$78=AE20)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF20" s="126">
         <f>BD20-BE20</f>
@@ -43386,11 +43390,11 @@
       </c>
       <c r="BH20" s="126">
         <f>BB20/BB24*1000+BC20/BC24*100+BG20/BG24*10+BD20/BD24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI20" s="126">
         <f>BH20/BH24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK20" s="21"/>
       <c r="BL20" s="21"/>
@@ -43399,7 +43403,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43465,7 +43469,7 @@
       </c>
       <c r="K21" s="31">
         <f>L21+M21+N21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="31">
         <f>VLOOKUP(1,AD20:AN23,3,FALSE)</f>
@@ -43473,7 +43477,7 @@
       </c>
       <c r="M21" s="31">
         <f>VLOOKUP(1,AD20:AN23,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="31">
         <f>VLOOKUP(1,AD20:AN23,5,FALSE)</f>
@@ -43481,11 +43485,11 @@
       </c>
       <c r="O21" s="31" t="str">
         <f>VLOOKUP(1,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P21" s="32">
         <f>L21*3+M21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="123">
         <f>DATE(2026,6,15)+TIME(14,0,0)+gmt_delta</f>
@@ -43545,7 +43549,7 @@
       </c>
       <c r="AG21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_lose")</f>
@@ -43553,11 +43557,11 @@
       </c>
       <c r="AI21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE21,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE21,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" s="123">
         <f>AI21-AJ21</f>
@@ -43569,15 +43573,15 @@
       </c>
       <c r="AN21" s="123">
         <f>AF21*3+AG21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21" s="123">
         <f>AN21/AN24*10+BA21</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP21" s="123">
         <f>AO21*10000000+BI21*100+AM21/AM24*10+AI21/AI24*1++IF(AQ21=0,ROW(),AQ21)/2000000</f>
-        <v>8.7793499999999994E-4</v>
+        <v>59805923.801848799</v>
       </c>
       <c r="AQ21" s="126">
         <f>VLOOKUP(AE21,db_fifarank,2,FALSE)</f>
@@ -43585,7 +43589,7 @@
       </c>
       <c r="AR21" s="125">
         <f>AP21/AP24</f>
-        <v>8.771625881681108E-4</v>
+        <v>0.99999998327920436</v>
       </c>
       <c r="AS21" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J22,"2C")</f>
@@ -43597,15 +43601,15 @@
       </c>
       <c r="AU21" s="126" cm="1">
         <f t="array" ref="AU21">SUMPRODUCT(($S$7:$S$78=AE21&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE21&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV21" s="126" cm="1">
         <f t="array" ref="AV21">SUMPRODUCT(($E$7:$E$78=AE21)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW21" s="126" cm="1">
         <f t="array" ref="AW21">SUMPRODUCT(($E$7:$E$78=AE21)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX21" s="126">
         <f>AV21-AW21</f>
@@ -43617,11 +43621,11 @@
       </c>
       <c r="AZ21" s="126">
         <f>AT21/AT24*1000+AU21/AU24*100+AY21/AY24*10+AV21/AV24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA21" s="126">
         <f>AZ21/AZ24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB21" s="126" cm="1">
         <f t="array" ref="BB21">SUMPRODUCT(($S$7:$S$78=AE21&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE21&amp;"_win")*($X$7:$X$78))</f>
@@ -43629,15 +43633,15 @@
       </c>
       <c r="BC21" s="126" cm="1">
         <f t="array" ref="BC21">SUMPRODUCT(($S$7:$S$78=AE21&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE21&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD21" s="126" cm="1">
         <f t="array" ref="BD21">SUMPRODUCT(($E$7:$E$78=AE21)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE21" s="126" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(($E$7:$E$78=AE21)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF21" s="126">
         <f>BD21-BE21</f>
@@ -43649,11 +43653,11 @@
       </c>
       <c r="BH21" s="126">
         <f>BB21/BB24*1000+BC21/BC24*100+BG21/BG24*10+BD21/BD24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI21" s="126">
         <f>BH21/BH24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK21" s="21" t="str" cm="1">
         <f t="array" ref="BK21">INDEX(T,24+MONTH(BP21),lang) &amp; " " &amp; DAY(BP21) &amp; ", " &amp; YEAR(BP21) &amp; "   " &amp; (IF(HOUR(BP21)&lt;10,0,"")&amp;HOUR(BP21)) &amp; ":" &amp;  (IF(MINUTE(BP21)&lt;10,0,"")&amp;MINUTE(BP21))</f>
@@ -43668,7 +43672,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43732,7 +43736,7 @@
       </c>
       <c r="K22" s="23">
         <f>L22+M22+N22</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="23">
         <f>VLOOKUP(2,AD20:AN23,3,FALSE)</f>
@@ -43740,7 +43744,7 @@
       </c>
       <c r="M22" s="23">
         <f>VLOOKUP(2,AD20:AN23,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="23">
         <f>VLOOKUP(2,AD20:AN23,5,FALSE)</f>
@@ -43748,11 +43752,11 @@
       </c>
       <c r="O22" s="23" t="str">
         <f>VLOOKUP(2,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P22" s="34">
         <f>L22*3+M22</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="123">
         <f>DATE(2026,6,15)+TIME(8,0,0)+gmt_delta</f>
@@ -43852,7 +43856,7 @@
       </c>
       <c r="AR22" s="125">
         <f>AP22/AP24</f>
-        <v>6.4528677337310309E-4</v>
+        <v>1.0799180886172099E-11</v>
       </c>
       <c r="AT22" s="126" cm="1">
         <f t="array" ref="AT22">SUMPRODUCT(($S$7:$S$78=AE22&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE22&amp;"_win")*($U$7:$U$78))</f>
@@ -43918,7 +43922,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44112,7 +44116,7 @@
       </c>
       <c r="AR23" s="125">
         <f>AP23/AP24</f>
-        <v>7.4851587189352792E-4</v>
+        <v>1.2526768919336355E-11</v>
       </c>
       <c r="AT23" s="126" cm="1">
         <f t="array" ref="AT23">SUMPRODUCT(($S$7:$S$78=AE23&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE23&amp;"_win")*($U$7:$U$78))</f>
@@ -44178,7 +44182,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44205,7 +44209,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44324,7 +44328,7 @@
       </c>
       <c r="AG24" s="123">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH24" s="123">
         <f t="shared" si="14"/>
@@ -44332,7 +44336,7 @@
       </c>
       <c r="AI24" s="123">
         <f>MAX(AI20:AI23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" s="123">
         <f>MIN(AL20:AL23)</f>
@@ -44344,15 +44348,15 @@
       </c>
       <c r="AN24" s="123">
         <f>MAX(AN20:AN23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO24" s="123">
         <f>MAX(AO20:AO23)+1</f>
-        <v>1</v>
+        <v>6.9805825242718447</v>
       </c>
       <c r="AP24" s="123">
         <f>MAX(AP20:AP23)+1</f>
-        <v>1.00088058</v>
+        <v>59805924.801851444</v>
       </c>
       <c r="AT24" s="126">
         <f>MAX(AT20:AT23)-MIN(AT20:AT23)+1</f>
@@ -44360,15 +44364,15 @@
       </c>
       <c r="AU24" s="126">
         <f>MAX(AU20:AU23)-MIN(AU20:AU23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV24" s="126">
         <f>MAX(AV20:AV23)-MIN(AV20:AV23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW24" s="126">
         <f>MAX(AW20:AW23)-MIN(AW20:AW23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY24" s="126">
         <f>MAX(AY20:AY23)-MIN(AY20:AY23)+1</f>
@@ -44376,7 +44380,7 @@
       </c>
       <c r="AZ24" s="126">
         <f>MAX(AZ20:AZ23)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB24" s="126">
         <f>MAX(BB20:BB23)-MIN(BB20:BB23)+1</f>
@@ -44384,15 +44388,15 @@
       </c>
       <c r="BC24" s="126">
         <f>MAX(BC20:BC23)-MIN(BC20:BC23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD24" s="126">
         <f>MAX(BD20:BD23)-MIN(BD20:BD23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE24" s="126">
         <f>MAX(BE20:BE23)-MIN(BE20:BE23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG24" s="126">
         <f>MAX(BG20:BG23)-MIN(BG20:BG23)+1</f>
@@ -44400,7 +44404,7 @@
       </c>
       <c r="BH24" s="126">
         <f>MAX(BH20:BH23)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BL24" s="21"/>
       <c r="BM24" s="21"/>
@@ -44422,7 +44426,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44767,7 +44771,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45031,7 +45035,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45302,7 +45306,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45563,7 +45567,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45773,7 +45777,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45880,7 +45884,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46152,7 +46156,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46412,7 +46416,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46427,14 +46431,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46654,7 +46658,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46685,11 +46689,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46909,7 +46913,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47134,7 +47138,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47254,7 +47258,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47281,7 +47285,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47518,7 +47522,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47548,7 +47552,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47783,7 +47787,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48459,7 +48463,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48552,7 +48556,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48808,7 +48812,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48823,14 +48827,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49067,7 +49071,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49080,11 +49084,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49304,7 +49308,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="141">
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49546,7 +49550,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="142"/>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49789,7 +49793,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49805,7 +49809,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49910,7 +49914,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49924,7 +49928,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50159,7 +50163,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50412,7 +50416,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50672,7 +50676,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50927,7 +50931,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51131,7 +51135,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51252,7 +51256,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51279,7 +51283,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51538,7 +51542,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52021,7 +52025,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52269,7 +52273,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52492,7 +52496,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52605,7 +52609,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52848,7 +52852,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53100,7 +53104,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53366,7 +53370,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53620,7 +53624,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53816,7 +53820,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53916,7 +53920,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54172,7 +54176,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54186,25 +54190,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54442,7 +54446,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54454,19 +54458,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54687,7 +54691,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54923,7 +54927,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56599,13 +56603,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56703,11 +56707,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56817,11 +56821,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -56931,11 +56935,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57045,11 +57049,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57159,11 +57163,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57840,11 +57844,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57860,31 +57884,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F675E4CC-8726-492F-86EC-B032AE700334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61460C1D-C14F-477A-BD40-D63ABDED72A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="str" cm="1">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="141" t="str" cm="1">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41223,8 +41223,12 @@
         <f>AE22</f>
         <v>Haiti</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
+      <c r="F11" s="19">
+        <v>0</v>
+      </c>
+      <c r="G11" s="20">
+        <v>1</v>
+      </c>
       <c r="H11" s="80" t="str">
         <f>AE23</f>
         <v>Scotland</v>
@@ -41263,11 +41267,11 @@
       </c>
       <c r="S11" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Haiti_lose</v>
       </c>
       <c r="T11" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Scotland_win</v>
       </c>
       <c r="U11" s="123">
         <f t="shared" si="8"/>
@@ -41297,9 +41301,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB11" s="123" t="str">
+      <c r="AB11" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD11" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR11))</f>
@@ -41421,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41486,8 +41490,12 @@
         <f>AE28</f>
         <v>Australia</v>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="20"/>
+      <c r="F12" s="19">
+        <v>2</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0</v>
+      </c>
       <c r="H12" s="80" t="str">
         <f>AE29</f>
         <v>Turkey</v>
@@ -41526,11 +41534,11 @@
       </c>
       <c r="S12" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Australia_win</v>
       </c>
       <c r="T12" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Turkey_lose</v>
       </c>
       <c r="U12" s="123">
         <f t="shared" si="8"/>
@@ -41560,9 +41568,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="123" t="str">
+      <c r="AB12" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF12" s="123">
         <f t="shared" ref="AF12:AH12" si="12">MAX(AF8:AF11)-MIN(AF8:AF11)+1</f>
@@ -41655,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41776,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42034,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="131">
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42297,7 +42305,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="132"/>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42567,7 +42575,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42825,7 +42833,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43025,7 +43033,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="131">
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43129,7 +43137,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43274,7 +43282,7 @@
       </c>
       <c r="AD20" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR20))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE20" s="124" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
@@ -43306,7 +43314,7 @@
       </c>
       <c r="AM20" s="123">
         <f>AL20-AL24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" s="123">
         <f>AF20*3+AG20</f>
@@ -43314,11 +43322,11 @@
       </c>
       <c r="AO20" s="123">
         <f>AN20/AN24*10+BA20</f>
-        <v>5.9805825242718447</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP20" s="123">
         <f>AO20*10000000+BI20*100+AM20/AM24*10+AI20/AI24*1++IF(AQ20=0,ROW(),AQ20)/2000000</f>
-        <v>59805923.801851444</v>
+        <v>34805927.13518478</v>
       </c>
       <c r="AQ20" s="126">
         <f>VLOOKUP(AE20,db_fifarank,2,FALSE)</f>
@@ -43326,7 +43334,7 @@
       </c>
       <c r="AR20" s="125">
         <f>AP20/AP24</f>
-        <v>0.99999998327924866</v>
+        <v>0.46407897793145042</v>
       </c>
       <c r="AS20" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J21,"1C")</f>
@@ -43403,7 +43411,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43465,7 +43473,7 @@
       </c>
       <c r="J21" s="30" t="str">
         <f>VLOOKUP(1,AD20:AN23,2,FALSE)</f>
-        <v>Brazil</v>
+        <v>Scotland</v>
       </c>
       <c r="K21" s="31">
         <f>L21+M21+N21</f>
@@ -43473,11 +43481,11 @@
       </c>
       <c r="L21" s="31">
         <f>VLOOKUP(1,AD20:AN23,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="31">
         <f>VLOOKUP(1,AD20:AN23,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="31">
         <f>VLOOKUP(1,AD20:AN23,5,FALSE)</f>
@@ -43485,11 +43493,11 @@
       </c>
       <c r="O21" s="31" t="str">
         <f>VLOOKUP(1,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD20:AN23,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>1 - 0</v>
       </c>
       <c r="P21" s="32">
         <f>L21*3+M21</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R21" s="123">
         <f>DATE(2026,6,15)+TIME(14,0,0)+gmt_delta</f>
@@ -43537,7 +43545,7 @@
       </c>
       <c r="AD21" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR21))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE21" s="124" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
@@ -43569,7 +43577,7 @@
       </c>
       <c r="AM21" s="123">
         <f>AL21-AL24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" s="123">
         <f>AF21*3+AG21</f>
@@ -43577,11 +43585,11 @@
       </c>
       <c r="AO21" s="123">
         <f>AN21/AN24*10+BA21</f>
-        <v>5.9805825242718447</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP21" s="123">
         <f>AO21*10000000+BI21*100+AM21/AM24*10+AI21/AI24*1++IF(AQ21=0,ROW(),AQ21)/2000000</f>
-        <v>59805923.801848799</v>
+        <v>34805927.135182135</v>
       </c>
       <c r="AQ21" s="126">
         <f>VLOOKUP(AE21,db_fifarank,2,FALSE)</f>
@@ -43589,7 +43597,7 @@
       </c>
       <c r="AR21" s="125">
         <f>AP21/AP24</f>
-        <v>0.99999998327920436</v>
+        <v>0.46407897793141517</v>
       </c>
       <c r="AS21" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J22,"2C")</f>
@@ -43672,7 +43680,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43732,7 +43740,7 @@
       </c>
       <c r="J22" s="33" t="str">
         <f>VLOOKUP(2,AD20:AN23,2,FALSE)</f>
-        <v>Morocco</v>
+        <v>Brazil</v>
       </c>
       <c r="K22" s="23">
         <f>L22+M22+N22</f>
@@ -43820,7 +43828,7 @@
       </c>
       <c r="AH22" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE22 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE22,$G$7:$G$78)</f>
@@ -43828,11 +43836,11 @@
       </c>
       <c r="AJ22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE22,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" s="123">
         <f>AI22-AJ22</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM22" s="123">
         <f>AL22-AL24</f>
@@ -43856,7 +43864,7 @@
       </c>
       <c r="AR22" s="125">
         <f>AP22/AP24</f>
-        <v>1.0799180886172099E-11</v>
+        <v>8.6113990622283044E-12</v>
       </c>
       <c r="AT22" s="126" cm="1">
         <f t="array" ref="AT22">SUMPRODUCT(($S$7:$S$78=AE22&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE22&amp;"_win")*($U$7:$U$78))</f>
@@ -43922,7 +43930,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -43992,11 +44000,11 @@
       </c>
       <c r="J23" s="33" t="str">
         <f>VLOOKUP(3,AD20:AN23,2,FALSE)</f>
-        <v>Scotland</v>
+        <v>Morocco</v>
       </c>
       <c r="K23" s="23">
         <f>L23+M23+N23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="23">
         <f>VLOOKUP(3,AD20:AN23,3,FALSE)</f>
@@ -44004,7 +44012,7 @@
       </c>
       <c r="M23" s="23">
         <f>VLOOKUP(3,AD20:AN23,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="23">
         <f>VLOOKUP(3,AD20:AN23,5,FALSE)</f>
@@ -44012,11 +44020,11 @@
       </c>
       <c r="O23" s="23" t="str">
         <f>VLOOKUP(3,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P23" s="34">
         <f>L23*3+M23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="123">
         <f>DATE(2026,6,16)+TIME(8,0,0)+gmt_delta</f>
@@ -44064,7 +44072,7 @@
       </c>
       <c r="AD23" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR23))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" s="124" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
@@ -44072,7 +44080,7 @@
       </c>
       <c r="AF23" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE23 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE23 &amp; "_draw")</f>
@@ -44084,7 +44092,7 @@
       </c>
       <c r="AI23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE23,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE23,$F$7:$F$78)</f>
@@ -44092,23 +44100,23 @@
       </c>
       <c r="AL23" s="123">
         <f>AI23-AJ23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" s="123">
         <f>AL23-AL24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN23" s="123">
         <f>AF23*3+AG23</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO23" s="123">
         <f>AN23/AN24*10+BA23</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP23" s="123">
         <f>AO23*10000000+BI23*100+AM23/AM24*10+AI23/AI24*1++IF(AQ23=0,ROW(),AQ23)/2000000</f>
-        <v>7.4917499999999993E-4</v>
+        <v>75000007.167415842</v>
       </c>
       <c r="AQ23" s="126">
         <f>VLOOKUP(AE23,db_fifarank,2,FALSE)</f>
@@ -44116,7 +44124,7 @@
       </c>
       <c r="AR23" s="125">
         <f>AP23/AP24</f>
-        <v>1.2526768919336355E-11</v>
+        <v>0.99999998666666812</v>
       </c>
       <c r="AT23" s="126" cm="1">
         <f t="array" ref="AT23">SUMPRODUCT(($S$7:$S$78=AE23&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE23&amp;"_win")*($U$7:$U$78))</f>
@@ -44182,7 +44190,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44209,7 +44217,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44256,7 +44264,7 @@
       </c>
       <c r="K24" s="36">
         <f>L24+M24+N24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="36">
         <f>VLOOKUP(4,AD20:AN23,3,FALSE)</f>
@@ -44268,11 +44276,11 @@
       </c>
       <c r="N24" s="36">
         <f>VLOOKUP(4,AD20:AN23,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="36" t="str">
         <f>VLOOKUP(4,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 1</v>
       </c>
       <c r="P24" s="37">
         <f>L24*3+M24</f>
@@ -44324,7 +44332,7 @@
       </c>
       <c r="AF24" s="123">
         <f t="shared" ref="AF24:AH24" si="14">MAX(AF20:AF23)-MIN(AF20:AF23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG24" s="123">
         <f t="shared" si="14"/>
@@ -44332,7 +44340,7 @@
       </c>
       <c r="AH24" s="123">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI24" s="123">
         <f>MAX(AI20:AI23)+1</f>
@@ -44340,23 +44348,23 @@
       </c>
       <c r="AL24" s="123">
         <f>MIN(AL20:AL23)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM24" s="123">
         <f>MAX(AM20:AM23)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN24" s="123">
         <f>MAX(AN20:AN23)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO24" s="123">
         <f>MAX(AO20:AO23)+1</f>
-        <v>6.9805825242718447</v>
+        <v>8.5</v>
       </c>
       <c r="AP24" s="123">
         <f>MAX(AP20:AP23)+1</f>
-        <v>59805924.801851444</v>
+        <v>75000008.167415842</v>
       </c>
       <c r="AT24" s="126">
         <f>MAX(AT20:AT23)-MIN(AT20:AT23)+1</f>
@@ -44426,7 +44434,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44771,7 +44779,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45035,7 +45043,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45109,15 +45117,15 @@
       </c>
       <c r="J28" s="33" t="str">
         <f>VLOOKUP(2,AD26:AN29,2,FALSE)</f>
-        <v>Turkey</v>
+        <v>Australia</v>
       </c>
       <c r="K28" s="23">
         <f>L28+M28+N28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="23">
         <f>VLOOKUP(2,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="23">
         <f>VLOOKUP(2,AD26:AN29,4,FALSE)</f>
@@ -45129,11 +45137,11 @@
       </c>
       <c r="O28" s="23" t="str">
         <f>VLOOKUP(2,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 0</v>
       </c>
       <c r="P28" s="34">
         <f>L28*3+M28</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" s="123">
         <f>DATE(2026,6,17)+TIME(9,0,0)+gmt_delta</f>
@@ -45181,7 +45189,7 @@
       </c>
       <c r="AD28" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR28))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28" s="124" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
@@ -45189,7 +45197,7 @@
       </c>
       <c r="AF28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_draw")</f>
@@ -45201,7 +45209,7 @@
       </c>
       <c r="AI28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE28,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE28,$F$7:$F$78)</f>
@@ -45209,23 +45217,23 @@
       </c>
       <c r="AL28" s="123">
         <f>AI28-AJ28</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM28" s="123">
         <f>AL28-AL30</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN28" s="123">
         <f>AF28*3+AG28</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO28" s="123">
         <f>AN28/AN30*10+BA28</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP28" s="123">
         <f>AO28*10000000+BI28*100+AM28/AM30*10+AI28/AI30*1++IF(AQ28=0,ROW(),AQ28)/2000000</f>
-        <v>4.2865046207142852</v>
+        <v>75000007.543647483</v>
       </c>
       <c r="AQ28" s="126">
         <f>VLOOKUP(AE28,db_fifarank,2,FALSE)</f>
@@ -45233,7 +45241,7 @@
       </c>
       <c r="AR28" s="125">
         <f>AP28/AP30</f>
-        <v>5.715338703872269E-8</v>
+        <v>0.99999996228510324</v>
       </c>
       <c r="AT28" s="126" cm="1">
         <f t="array" ref="AT28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($U$7:$U$78))</f>
@@ -45306,7 +45314,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45364,11 +45372,11 @@
       </c>
       <c r="J29" s="33" t="str">
         <f>VLOOKUP(3,AD26:AN29,2,FALSE)</f>
-        <v>Australia</v>
+        <v>Turkey</v>
       </c>
       <c r="K29" s="23">
         <f>L29+M29+N29</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="23">
         <f>VLOOKUP(3,AD26:AN29,3,FALSE)</f>
@@ -45380,11 +45388,11 @@
       </c>
       <c r="N29" s="23">
         <f>VLOOKUP(3,AD26:AN29,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="23" t="str">
         <f>VLOOKUP(3,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 2</v>
       </c>
       <c r="P29" s="34">
         <f>L29*3+M29</f>
@@ -45436,7 +45444,7 @@
       </c>
       <c r="AD29" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR29))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" s="124" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
@@ -45452,7 +45460,7 @@
       </c>
       <c r="AH29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE29,$G$7:$G$78)</f>
@@ -45460,15 +45468,15 @@
       </c>
       <c r="AJ29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE29,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL29" s="123">
         <f>AI29-AJ29</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM29" s="123">
         <f>AL29-AL30</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN29" s="123">
         <f>AF29*3+AG29</f>
@@ -45480,7 +45488,7 @@
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>4.2865138057142858</v>
+        <v>1.4293709485714283</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -45488,7 +45496,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>5.715350950537243E-8</v>
+        <v>1.9058276678585728E-8</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -45567,7 +45575,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45777,7 +45785,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45884,7 +45892,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46156,7 +46164,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46416,7 +46424,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46431,14 +46439,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46658,7 +46666,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46689,11 +46697,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46913,7 +46921,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47138,7 +47146,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47258,7 +47266,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47285,7 +47293,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47522,7 +47530,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47552,7 +47560,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47787,7 +47795,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48463,7 +48471,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48556,7 +48564,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="132"/>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48812,7 +48820,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48827,14 +48835,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49071,7 +49079,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49084,11 +49092,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49308,7 +49316,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49550,7 +49558,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49793,7 +49801,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49809,7 +49817,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49914,7 +49922,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49928,7 +49936,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50163,7 +50171,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="131">
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50416,7 +50424,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="132"/>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50676,7 +50684,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50931,7 +50939,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51135,7 +51143,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="131">
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51256,7 +51264,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51283,7 +51291,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51542,7 +51550,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52025,7 +52033,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52273,7 +52281,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52496,7 +52504,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52609,7 +52617,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52852,7 +52860,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53104,7 +53112,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53370,7 +53378,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53624,7 +53632,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53820,7 +53828,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53920,7 +53928,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54176,7 +54184,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54190,25 +54198,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54446,7 +54454,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54458,19 +54466,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54691,7 +54699,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54927,7 +54935,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56334,7 +56342,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56369,7 +56377,7 @@
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,10,FALSE)</f>
@@ -56377,7 +56385,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>50.000750689999997</v>
+        <v>383.33408402333333</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -56408,7 +56416,7 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓒ Morocco</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
@@ -56436,7 +56444,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -56471,7 +56479,7 @@
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
@@ -56479,7 +56487,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>5550.00072748</v>
+        <v>5716.667394146667</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -56510,11 +56518,11 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Australia</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,3,FALSE)</f>
@@ -56522,7 +56530,7 @@
       </c>
       <c r="M82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,5,FALSE)</f>
@@ -56530,19 +56538,19 @@
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
-        <v>Scotland</v>
+        <v>Morocco</v>
       </c>
       <c r="AF82" s="123">
         <f t="shared" si="39"/>
@@ -56550,7 +56558,7 @@
       </c>
       <c r="AG82" s="123">
         <f t="shared" ref="AG82:AG91" si="49">VLOOKUP($AE82,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH82" s="123">
         <f t="shared" si="40"/>
@@ -56558,11 +56566,11 @@
       </c>
       <c r="AI82" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ82" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK82" s="123" t="s">
         <v>3182</v>
@@ -56573,43 +56581,43 @@
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>500.00074917500001</v>
+        <v>5716.667544601667</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
-        <v>1498.35</v>
+        <v>1755.87</v>
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>B</v>
+        <v>BC</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Morocco</v>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓒ Morocco</v>
       </c>
     </row>
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56642,11 +56650,11 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
-        <v>Australia</v>
+        <v>Turkey</v>
       </c>
       <c r="AF83" s="123">
         <f t="shared" si="39"/>
@@ -56658,7 +56666,7 @@
       </c>
       <c r="AH83" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI83" s="123">
         <f t="shared" si="41"/>
@@ -56666,18 +56674,18 @@
       </c>
       <c r="AJ83" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK83" s="123" t="s">
         <v>3184</v>
       </c>
       <c r="AL83" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
@@ -56685,33 +56693,33 @@
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>500.00079033499998</v>
+        <v>7.9951999999999996E-4</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
-        <v>1580.67</v>
+        <v>1599.04</v>
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BD</v>
+        <v>BC</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Australia</v>
+        <v/>
       </c>
       <c r="AT83" s="130" t="str">
         <f>"Ⓓ "&amp;AE83</f>
-        <v>Ⓓ Australia</v>
+        <v>Ⓓ Turkey</v>
       </c>
     </row>
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56791,7 +56799,7 @@
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
@@ -56799,7 +56807,7 @@
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>500.00076648999999</v>
+        <v>666.66743315666668</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -56807,7 +56815,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDE</v>
+        <v>BCE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56821,11 +56829,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -56905,7 +56913,7 @@
       </c>
       <c r="AM85" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
@@ -56913,7 +56921,7 @@
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>500.00075738499999</v>
+        <v>666.66742405166667</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -56921,7 +56929,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDEF</v>
+        <v>BCEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56935,11 +56943,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57019,7 +57027,7 @@
       </c>
       <c r="AM86" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
@@ -57027,7 +57035,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>500.00078162</v>
+        <v>666.66744828666663</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57035,7 +57043,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDEFG</v>
+        <v>BCEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57049,11 +57057,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57098,7 +57106,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -57133,7 +57141,7 @@
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
@@ -57141,7 +57149,7 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>500.00071071500003</v>
+        <v>666.6673773816666</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
@@ -57149,7 +57157,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDEFG</v>
+        <v>BCEFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57163,11 +57171,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57247,7 +57255,7 @@
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -57255,7 +57263,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>500.00077547000001</v>
+        <v>666.66744213666664</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -57263,7 +57271,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDEFGI</v>
+        <v>BCEFGI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57286,7 +57294,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57361,7 +57369,7 @@
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -57369,7 +57377,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>500.00078213</v>
+        <v>666.66744879666658</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -57377,7 +57385,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDEFGIJ</v>
+        <v>BCEFGIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57400,7 +57408,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓗ Saudi Arabia</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -57440,7 +57448,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57475,7 +57483,7 @@
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
@@ -57483,7 +57491,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>500.00073917499998</v>
+        <v>666.66740584166666</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -57491,7 +57499,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDEFGIJ</v>
+        <v>BCEFGIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57514,11 +57522,11 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,3,FALSE)</f>
@@ -57530,11 +57538,11 @@
       </c>
       <c r="N91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
@@ -57589,7 +57597,7 @@
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57597,7 +57605,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>500.00077032000002</v>
+        <v>666.66743698666664</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -57605,7 +57613,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BDEFGIJL</v>
+        <v>BCEFGIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57628,7 +57636,7 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓓ Turkey</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
@@ -57648,7 +57656,7 @@
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 2</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
@@ -57676,11 +57684,11 @@
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
@@ -57844,6 +57852,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57859,36 +57897,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -58931,11 +58939,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BDEFGIJL</v>
+        <v>BCEFGIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -58951,7 +58959,7 @@
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
-        <v>3D</v>
+        <v>3C</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61460C1D-C14F-477A-BD40-D63ABDED72A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7612EA-D857-45B2-9F00-4F766F3341ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42363,8 +42363,12 @@
         <f>AE32</f>
         <v>Germany</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+      <c r="F16" s="19">
+        <v>7</v>
+      </c>
+      <c r="G16" s="20">
+        <v>1</v>
+      </c>
       <c r="H16" s="80" t="str">
         <f>AE33</f>
         <v>Curaçao</v>
@@ -42403,11 +42407,11 @@
       </c>
       <c r="S16" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Germany_win</v>
       </c>
       <c r="T16" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Curaçao_lose</v>
       </c>
       <c r="U16" s="123">
         <f t="shared" si="8"/>
@@ -42437,9 +42441,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="123" t="str">
+      <c r="AB16" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD16" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR16))</f>
@@ -42615,8 +42619,12 @@
         <f>AE38</f>
         <v>Netherlands</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
+      <c r="F17" s="19">
+        <v>2</v>
+      </c>
+      <c r="G17" s="20">
+        <v>2</v>
+      </c>
       <c r="H17" s="80" t="str">
         <f>AE39</f>
         <v>Japan</v>
@@ -42655,43 +42663,43 @@
       </c>
       <c r="S17" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Netherlands_draw</v>
       </c>
       <c r="T17" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Japan_draw</v>
       </c>
       <c r="U17" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="123" t="str">
+      <c r="AB17" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD17" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR17))</f>
@@ -46036,7 +46044,7 @@
       </c>
       <c r="AF32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_draw")</f>
@@ -46048,31 +46056,31 @@
       </c>
       <c r="AI32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE32,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE32,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL32" s="123">
         <f>AI32-AJ32</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM32" s="123">
         <f>AL32-AL36</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AN32" s="123">
         <f>AF32*3+AG32</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO32" s="123">
         <f>AN32/AN36*10+BA32</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP32" s="123">
         <f>AO32*10000000+BI32*100+AM32/AM36*10+AI32/AI36*1++IF(AQ32=0,ROW(),AQ32)/2000000</f>
-        <v>8.6518499999999998E-4</v>
+        <v>75000010.106634423</v>
       </c>
       <c r="AQ32" s="126">
         <f>VLOOKUP(AE32,db_fifarank,2,FALSE)</f>
@@ -46080,7 +46088,7 @@
       </c>
       <c r="AR32" s="125">
         <f>AP32/AP36</f>
-        <v>8.6443710198591821E-4</v>
+        <v>0.99999998666666867</v>
       </c>
       <c r="AS32" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J33,"1E")</f>
@@ -46214,11 +46222,11 @@
       </c>
       <c r="K33" s="31">
         <f>L33+M33+N33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="31">
         <f>VLOOKUP(1,AD32:AN35,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="31">
         <f>VLOOKUP(1,AD32:AN35,4,FALSE)</f>
@@ -46230,11 +46238,11 @@
       </c>
       <c r="O33" s="31" t="str">
         <f>VLOOKUP(1,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>7 - 1</v>
       </c>
       <c r="P33" s="32">
         <f>L33*3+M33</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R33" s="123">
         <f>DATE(2026,6,18)+TIME(11,0,0)+gmt_delta</f>
@@ -46298,19 +46306,19 @@
       </c>
       <c r="AH33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE33,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE33,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL33" s="123">
         <f>AI33-AJ33</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AM33" s="123">
         <f>AL33-AL36</f>
@@ -46326,7 +46334,7 @@
       </c>
       <c r="AP33" s="123">
         <f>AO33*10000000+BI33*100+AM33/AM36*10+AI33/AI36*1++IF(AQ33=0,ROW(),AQ33)/2000000</f>
-        <v>6.4732500000000003E-4</v>
+        <v>0.125647325</v>
       </c>
       <c r="AQ33" s="126">
         <f>VLOOKUP(AE33,db_fifarank,2,FALSE)</f>
@@ -46334,7 +46342,7 @@
       </c>
       <c r="AR33" s="125">
         <f>AP33/AP36</f>
-        <v>6.4676542825295696E-4</v>
+        <v>1.6752974185744538E-9</v>
       </c>
       <c r="AS33" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J34,"2E")</f>
@@ -46580,7 +46588,7 @@
       </c>
       <c r="AM34" s="123">
         <f>AL34-AL36</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
@@ -46592,7 +46600,7 @@
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>7.6648999999999999E-4</v>
+        <v>4.616151105384616</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -46600,7 +46608,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>7.6582741760569868E-4</v>
+        <v>6.1548672290480187E-8</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -46835,7 +46843,7 @@
       </c>
       <c r="AM35" s="123">
         <f>AL35-AL36</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
@@ -46847,7 +46855,7 @@
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>7.9739000000000003E-4</v>
+        <v>4.6161820053846156</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -46855,7 +46863,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>7.9670070649924736E-4</v>
+        <v>6.154908429041916E-8</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -46989,7 +46997,7 @@
       </c>
       <c r="K36" s="36">
         <f>L36+M36+N36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="36">
         <f>VLOOKUP(4,AD32:AN35,3,FALSE)</f>
@@ -47001,11 +47009,11 @@
       </c>
       <c r="N36" s="36">
         <f>VLOOKUP(4,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="36" t="str">
         <f>VLOOKUP(4,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 7</v>
       </c>
       <c r="P36" s="37">
         <f>L36*3+M36</f>
@@ -47057,7 +47065,7 @@
       </c>
       <c r="AF36" s="123">
         <f t="shared" ref="AF36:AH36" si="16">MAX(AF32:AF35)-MIN(AF32:AF35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG36" s="123">
         <f t="shared" si="16"/>
@@ -47065,31 +47073,31 @@
       </c>
       <c r="AH36" s="123">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI36" s="123">
         <f>MAX(AI32:AI35)+1</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AL36" s="123">
         <f>MIN(AL32:AL35)</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AM36" s="123">
         <f>MAX(AM32:AM35)+1</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AN36" s="123">
         <f>MAX(AN32:AN35)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO36" s="123">
         <f>MAX(AO32:AO35)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP36" s="123">
         <f>MAX(AP32:AP35)+1</f>
-        <v>1.0008651850000001</v>
+        <v>75000011.106634423</v>
       </c>
       <c r="AT36" s="126">
         <f>MAX(AT32:AT35)-MIN(AT32:AT35)+1</f>
@@ -47420,7 +47428,7 @@
       </c>
       <c r="AG38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_lose")</f>
@@ -47428,11 +47436,11 @@
       </c>
       <c r="AI38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE38,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE38,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" s="123">
         <f>AI38-AJ38</f>
@@ -47444,15 +47452,15 @@
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>0</v>
+        <v>5.9806451612903224</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>8.7893499999999996E-4</v>
+        <v>59806550.344964951</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -47460,7 +47468,7 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>8.7816315167028663E-4</v>
+        <v>0.99999998327942374</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
@@ -47472,15 +47480,15 @@
       </c>
       <c r="AU38" s="126" cm="1">
         <f t="array" ref="AU38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV38" s="126" cm="1">
         <f t="array" ref="AV38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW38" s="126" cm="1">
         <f t="array" ref="AW38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX38" s="126">
         <f>AV38-AW38</f>
@@ -47492,11 +47500,11 @@
       </c>
       <c r="AZ38" s="126">
         <f>AT38/AT42*1000+AU38/AU42*100+AY38/AY42*10+AV38/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA38" s="126">
         <f>AZ38/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB38" s="126" cm="1">
         <f t="array" ref="BB38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_win")*($X$7:$X$78))</f>
@@ -47504,15 +47512,15 @@
       </c>
       <c r="BC38" s="126" cm="1">
         <f t="array" ref="BC38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD38" s="126" cm="1">
         <f t="array" ref="BD38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE38" s="126" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF38" s="126">
         <f>BD38-BE38</f>
@@ -47524,11 +47532,11 @@
       </c>
       <c r="BH38" s="126">
         <f>BB38/BB42*1000+BC38/BC42*100+BG38/BG42*10+BD38/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI38" s="126">
         <f>BH38/BH42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BK38" s="141">
         <v>82</v>
@@ -47605,7 +47613,7 @@
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
@@ -47613,7 +47621,7 @@
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="31">
         <f>VLOOKUP(1,AD38:AN41,5,FALSE)</f>
@@ -47621,11 +47629,11 @@
       </c>
       <c r="O39" s="31" t="str">
         <f>VLOOKUP(1,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -47685,7 +47693,7 @@
       </c>
       <c r="AG39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_lose")</f>
@@ -47693,11 +47701,11 @@
       </c>
       <c r="AI39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE39,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE39,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL39" s="123">
         <f>AI39-AJ39</f>
@@ -47709,15 +47717,15 @@
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>0</v>
+        <v>5.9806451612903224</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>8.3021500000000003E-4</v>
+        <v>59806550.344916232</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -47725,7 +47733,7 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>8.2948593577903611E-4</v>
+        <v>0.99999998327860917</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
@@ -47737,15 +47745,15 @@
       </c>
       <c r="AU39" s="126" cm="1">
         <f t="array" ref="AU39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV39" s="126" cm="1">
         <f t="array" ref="AV39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW39" s="126" cm="1">
         <f t="array" ref="AW39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX39" s="126">
         <f>AV39-AW39</f>
@@ -47757,11 +47765,11 @@
       </c>
       <c r="AZ39" s="126">
         <f>AT39/AT42*1000+AU39/AU42*100+AY39/AY42*10+AV39/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA39" s="126">
         <f>AZ39/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB39" s="126" cm="1">
         <f t="array" ref="BB39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($X$7:$X$78))</f>
@@ -47769,15 +47777,15 @@
       </c>
       <c r="BC39" s="126" cm="1">
         <f t="array" ref="BC39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD39" s="126" cm="1">
         <f t="array" ref="BD39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE39" s="126" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF39" s="126">
         <f>BD39-BE39</f>
@@ -47789,11 +47797,11 @@
       </c>
       <c r="BH39" s="126">
         <f>BB39/BB42*1000+BC39/BC42*100+BG39/BG42*10+BD39/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI39" s="126">
         <f>BH39/BH42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
@@ -47860,7 +47868,7 @@
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="23">
         <f>VLOOKUP(2,AD38:AN41,3,FALSE)</f>
@@ -47868,7 +47876,7 @@
       </c>
       <c r="M40" s="23">
         <f>VLOOKUP(2,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="23">
         <f>VLOOKUP(2,AD38:AN41,5,FALSE)</f>
@@ -47876,11 +47884,11 @@
       </c>
       <c r="O40" s="23" t="str">
         <f>VLOOKUP(2,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P40" s="34">
         <f>L40*3+M40</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="123">
         <f>DATE(2026,6,20)+TIME(13,0,0)+gmt_delta</f>
@@ -47980,7 +47988,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>7.5671989240137219E-4</v>
+        <v>1.2663913617613456E-11</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -48201,7 +48209,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>7.4087382006895759E-4</v>
+        <v>1.2398725278822286E-11</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -48393,7 +48401,7 @@
       </c>
       <c r="AG42" s="123">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH42" s="123">
         <f t="shared" si="18"/>
@@ -48401,7 +48409,7 @@
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
@@ -48413,15 +48421,15 @@
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>1</v>
+        <v>6.9806451612903224</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>1.000878935</v>
+        <v>59806551.344964951</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -48429,15 +48437,15 @@
       </c>
       <c r="AU42" s="126">
         <f>MAX(AU38:AU41)-MIN(AU38:AU41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV42" s="126">
         <f>MAX(AV38:AV41)-MIN(AV38:AV41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW42" s="126">
         <f>MAX(AW38:AW41)-MIN(AW38:AW41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY42" s="126">
         <f>MAX(AY38:AY41)-MIN(AY38:AY41)+1</f>
@@ -48445,7 +48453,7 @@
       </c>
       <c r="AZ42" s="126">
         <f>MAX(AZ38:AZ41)+1</f>
-        <v>1</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BB42" s="126">
         <f>MAX(BB38:BB41)-MIN(BB38:BB41)+1</f>
@@ -48453,15 +48461,15 @@
       </c>
       <c r="BC42" s="126">
         <f>MAX(BC38:BC41)-MIN(BC38:BC41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD42" s="126">
         <f>MAX(BD38:BD41)-MIN(BD38:BD41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE42" s="126">
         <f>MAX(BE38:BE41)-MIN(BE38:BE41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG42" s="126">
         <f>MAX(BG38:BG41)-MIN(BG38:BG41)+1</f>
@@ -48469,7 +48477,7 @@
       </c>
       <c r="BH42" s="126">
         <f>MAX(BH38:BH41)+1</f>
-        <v>1</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BK42" s="141">
         <v>76</v>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7612EA-D857-45B2-9F00-4F766F3341ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0228E2A8-4687-468C-A561-6E8EC8F849A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="str" cm="1">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="str" cm="1">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42103,8 +42103,12 @@
         <f>AE34</f>
         <v>Ivory Coast</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="F15" s="19">
+        <v>1</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
       <c r="H15" s="80" t="str">
         <f>AE35</f>
         <v>Ecuador</v>
@@ -42143,11 +42147,11 @@
       </c>
       <c r="S15" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Ivory Coast_win</v>
       </c>
       <c r="T15" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Ecuador_lose</v>
       </c>
       <c r="U15" s="123">
         <f t="shared" si="8"/>
@@ -42177,9 +42181,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="123" t="str">
+      <c r="AB15" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD15" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR15))</f>
@@ -42305,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42579,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42841,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -42879,8 +42883,12 @@
         <f>AE40</f>
         <v>Sweden</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
+      <c r="F18" s="19">
+        <v>5</v>
+      </c>
+      <c r="G18" s="20">
+        <v>1</v>
+      </c>
       <c r="H18" s="80" t="str">
         <f>AE41</f>
         <v>Tunisia</v>
@@ -42919,11 +42927,11 @@
       </c>
       <c r="S18" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Sweden_win</v>
       </c>
       <c r="T18" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Tunisia_lose</v>
       </c>
       <c r="U18" s="123">
         <f t="shared" si="8"/>
@@ -42953,9 +42961,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB18" s="123" t="str">
+      <c r="AB18" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF18" s="123">
         <f t="shared" ref="AF18:AH18" si="13">MAX(AF14:AF17)-MIN(AF14:AF17)+1</f>
@@ -43041,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43145,7 +43153,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43419,7 +43427,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43688,7 +43696,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43938,7 +43946,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44198,7 +44206,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44225,7 +44233,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44442,7 +44450,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44787,7 +44795,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45051,7 +45059,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45322,7 +45330,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45583,7 +45591,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45793,7 +45801,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45900,7 +45908,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46172,7 +46180,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46432,7 +46440,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46447,14 +46455,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46484,15 +46492,15 @@
       </c>
       <c r="J34" s="33" t="str">
         <f>VLOOKUP(2,AD32:AN35,2,FALSE)</f>
-        <v>Ecuador</v>
+        <v>Ivory Coast</v>
       </c>
       <c r="K34" s="23">
         <f>L34+M34+N34</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="23">
         <f>VLOOKUP(2,AD32:AN35,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="23">
         <f>VLOOKUP(2,AD32:AN35,4,FALSE)</f>
@@ -46504,11 +46512,11 @@
       </c>
       <c r="O34" s="23" t="str">
         <f>VLOOKUP(2,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 0</v>
       </c>
       <c r="P34" s="34">
         <f>L34*3+M34</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" s="123">
         <f>DATE(2026,6,18)+TIME(14,0,0)+gmt_delta</f>
@@ -46556,7 +46564,7 @@
       </c>
       <c r="AD34" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR34))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE34" s="124" t="str">
         <f>VLOOKUP("Ivory Coast",T,lang,FALSE)</f>
@@ -46564,7 +46572,7 @@
       </c>
       <c r="AF34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_draw")</f>
@@ -46576,7 +46584,7 @@
       </c>
       <c r="AI34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE34,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE34,$F$7:$F$78)</f>
@@ -46584,23 +46592,23 @@
       </c>
       <c r="AL34" s="123">
         <f>AI34-AJ34</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM34" s="123">
         <f>AL34-AL36</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO34" s="123">
         <f>AN34/AN36*10+BA34</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>4.616151105384616</v>
+        <v>75000005.510381877</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -46608,7 +46616,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>6.1548672290480187E-8</v>
+        <v>0.9999999253833104</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -46674,7 +46682,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46705,11 +46713,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46739,11 +46747,11 @@
       </c>
       <c r="J35" s="33" t="str">
         <f>VLOOKUP(3,AD32:AN35,2,FALSE)</f>
-        <v>Ivory Coast</v>
+        <v>Ecuador</v>
       </c>
       <c r="K35" s="23">
         <f>L35+M35+N35</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="23">
         <f>VLOOKUP(3,AD32:AN35,3,FALSE)</f>
@@ -46755,11 +46763,11 @@
       </c>
       <c r="N35" s="23">
         <f>VLOOKUP(3,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="23" t="str">
         <f>VLOOKUP(3,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 1</v>
       </c>
       <c r="P35" s="34">
         <f>L35*3+M35</f>
@@ -46811,7 +46819,7 @@
       </c>
       <c r="AD35" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR35))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE35" s="124" t="str">
         <f>VLOOKUP("Ecuador",T,lang,FALSE)</f>
@@ -46827,7 +46835,7 @@
       </c>
       <c r="AH35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE35,$G$7:$G$78)</f>
@@ -46835,15 +46843,15 @@
       </c>
       <c r="AJ35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE35,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" s="123">
         <f>AI35-AJ35</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM35" s="123">
         <f>AL35-AL36</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
@@ -46855,7 +46863,7 @@
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>4.6161820053846156</v>
+        <v>3.846951236153846</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -46863,7 +46871,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>6.154908429041916E-8</v>
+        <v>5.1292675552864665E-8</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -46929,7 +46937,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47154,7 +47162,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47274,7 +47282,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47301,7 +47309,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47416,7 +47424,7 @@
       </c>
       <c r="AD38" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR38))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE38" s="124" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
@@ -47448,7 +47456,7 @@
       </c>
       <c r="AM38" s="123">
         <f>AL38-AL42</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
@@ -47456,11 +47464,11 @@
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>5.9806451612903224</v>
+        <v>3.4806451612903224</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>59806550.344964951</v>
+        <v>34806554.456076071</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -47468,7 +47476,7 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>0.99999998327942374</v>
+        <v>0.46408732639569511</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
@@ -47538,7 +47546,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47568,7 +47576,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47609,7 +47617,7 @@
       </c>
       <c r="J39" s="30" t="str">
         <f>VLOOKUP(1,AD38:AN41,2,FALSE)</f>
-        <v>Netherlands</v>
+        <v>Sweden</v>
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
@@ -47617,11 +47625,11 @@
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="31">
         <f>VLOOKUP(1,AD38:AN41,5,FALSE)</f>
@@ -47629,11 +47637,11 @@
       </c>
       <c r="O39" s="31" t="str">
         <f>VLOOKUP(1,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD38:AN41,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>5 - 1</v>
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -47681,7 +47689,7 @@
       </c>
       <c r="AD39" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR39))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE39" s="124" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
@@ -47713,7 +47721,7 @@
       </c>
       <c r="AM39" s="123">
         <f>AL39-AL42</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
@@ -47721,11 +47729,11 @@
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>5.9806451612903224</v>
+        <v>3.4806451612903224</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>59806550.344916232</v>
+        <v>34806554.456027351</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -47733,7 +47741,7 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>0.99999998327860917</v>
+        <v>0.46408732639504552</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
@@ -47803,7 +47811,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -47864,7 +47872,7 @@
       </c>
       <c r="J40" s="33" t="str">
         <f>VLOOKUP(2,AD38:AN41,2,FALSE)</f>
-        <v>Japan</v>
+        <v>Netherlands</v>
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
@@ -47936,7 +47944,7 @@
       </c>
       <c r="AD40" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR40))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE40" s="124" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
@@ -47944,7 +47952,7 @@
       </c>
       <c r="AF40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_draw")</f>
@@ -47956,31 +47964,31 @@
       </c>
       <c r="AI40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE40,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE40,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL40" s="123">
         <f>AI40-AJ40</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM40" s="123">
         <f>AL40-AL42</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN40" s="123">
         <f>AF40*3+AG40</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO40" s="123">
         <f>AN40/AN42*10+BA40</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP40" s="123">
         <f>AO40*10000000+BI40*100+AM40/AM42*10+AI40/AI42*1++IF(AQ40=0,ROW(),AQ40)/2000000</f>
-        <v>7.5738499999999996E-4</v>
+        <v>75000009.722979605</v>
       </c>
       <c r="AQ40" s="126">
         <f>VLOOKUP(AE40,db_fifarank,2,FALSE)</f>
@@ -47988,7 +47996,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>1.2663913617613456E-11</v>
+        <v>0.99999998666666856</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -48085,11 +48093,11 @@
       </c>
       <c r="J41" s="33" t="str">
         <f>VLOOKUP(3,AD38:AN41,2,FALSE)</f>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
       <c r="K41" s="23">
         <f>L41+M41+N41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="23">
         <f>VLOOKUP(3,AD38:AN41,3,FALSE)</f>
@@ -48097,7 +48105,7 @@
       </c>
       <c r="M41" s="23">
         <f>VLOOKUP(3,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="23">
         <f>VLOOKUP(3,AD38:AN41,5,FALSE)</f>
@@ -48105,11 +48113,11 @@
       </c>
       <c r="O41" s="23" t="str">
         <f>VLOOKUP(3,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P41" s="34">
         <f>L41*3+M41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="123">
         <f>DATE(2026,6,20)+TIME(6,0,0)+gmt_delta</f>
@@ -48173,19 +48181,19 @@
       </c>
       <c r="AH41" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE41 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE41,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE41,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL41" s="123">
         <f>AI41-AJ41</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM41" s="123">
         <f>AL41-AL42</f>
@@ -48201,7 +48209,7 @@
       </c>
       <c r="AP41" s="123">
         <f>AO41*10000000+BI41*100+AM41/AM42*10+AI41/AI42*1++IF(AQ41=0,ROW(),AQ41)/2000000</f>
-        <v>7.4152499999999993E-4</v>
+        <v>0.16740819166666665</v>
       </c>
       <c r="AQ41" s="126">
         <f>VLOOKUP(AE41,db_fifarank,2,FALSE)</f>
@@ -48209,7 +48217,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>1.2398725278822286E-11</v>
+        <v>2.2321089030907787E-9</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -48329,7 +48337,7 @@
       </c>
       <c r="K42" s="36">
         <f>L42+M42+N42</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="36">
         <f>VLOOKUP(4,AD38:AN41,3,FALSE)</f>
@@ -48341,11 +48349,11 @@
       </c>
       <c r="N42" s="36">
         <f>VLOOKUP(4,AD38:AN41,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="36" t="str">
         <f>VLOOKUP(4,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 5</v>
       </c>
       <c r="P42" s="37">
         <f>L42*3+M42</f>
@@ -48397,7 +48405,7 @@
       </c>
       <c r="AF42" s="123">
         <f t="shared" ref="AF42:AH42" si="18">MAX(AF38:AF41)-MIN(AF38:AF41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG42" s="123">
         <f t="shared" si="18"/>
@@ -48405,31 +48413,31 @@
       </c>
       <c r="AH42" s="123">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM42" s="123">
         <f>MAX(AM38:AM41)+1</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>6.9806451612903224</v>
+        <v>8.5</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>59806551.344964951</v>
+        <v>75000010.722979605</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -48479,7 +48487,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48572,7 +48580,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48828,7 +48836,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48843,14 +48851,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49087,7 +49095,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49100,11 +49108,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49324,7 +49332,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="141">
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49566,7 +49574,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="142"/>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49809,7 +49817,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49825,7 +49833,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49930,7 +49938,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49944,7 +49952,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50179,7 +50187,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50432,7 +50440,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50692,7 +50700,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50947,7 +50955,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51151,7 +51159,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51272,7 +51280,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51299,7 +51307,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51558,7 +51566,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52041,7 +52049,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52289,7 +52297,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52512,7 +52520,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52625,7 +52633,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52868,7 +52876,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53120,7 +53128,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53386,7 +53394,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53640,7 +53648,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53836,7 +53844,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53936,7 +53944,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54192,7 +54200,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54206,25 +54214,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54462,7 +54470,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54474,19 +54482,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54707,7 +54715,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54943,7 +54951,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56350,7 +56358,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56393,7 +56401,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>383.33408402333333</v>
+        <v>366.66741735666665</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -56424,7 +56432,7 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Morocco</v>
+        <v>Ⓕ Japan</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
@@ -56444,7 +56452,7 @@
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
@@ -56452,7 +56460,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -56495,7 +56503,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>5716.667394146667</v>
+        <v>5700.00072748</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -56526,7 +56534,7 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓒ Morocco</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
@@ -56554,7 +56562,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -56597,7 +56605,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>5716.667544601667</v>
+        <v>5700.0008779350001</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -56619,22 +56627,22 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,3,FALSE)</f>
@@ -56642,7 +56650,7 @@
       </c>
       <c r="M83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,5,FALSE)</f>
@@ -56650,11 +56658,11 @@
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
@@ -56723,16 +56731,16 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56772,11 +56780,11 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
-        <v>Ivory Coast</v>
+        <v>Ecuador</v>
       </c>
       <c r="AF84" s="123">
         <f t="shared" si="39"/>
@@ -56788,7 +56796,7 @@
       </c>
       <c r="AH84" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI84" s="123">
         <f t="shared" si="41"/>
@@ -56796,18 +56804,18 @@
       </c>
       <c r="AJ84" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK84" s="123" t="s">
         <v>3185</v>
       </c>
       <c r="AL84" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
@@ -56815,38 +56823,38 @@
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>666.66743315666668</v>
+        <v>333.33413072333332</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
-        <v>1532.98</v>
+        <v>1594.78</v>
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCE</v>
+        <v>BC</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Ivory Coast</v>
+        <v/>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓔ Ecuador</v>
       </c>
     </row>
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓖ Egypt</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56886,11 +56894,11 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
       <c r="AF85" s="123">
         <f t="shared" si="39"/>
@@ -56898,7 +56906,7 @@
       </c>
       <c r="AG85" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH85" s="123">
         <f t="shared" si="40"/>
@@ -56906,11 +56914,11 @@
       </c>
       <c r="AI85" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ85" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK85" s="123" t="s">
         <v>3186</v>
@@ -56925,42 +56933,42 @@
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>666.66742405166667</v>
+        <v>5733.3341635483339</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
-        <v>1514.77</v>
+        <v>1660.43</v>
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEF</v>
+        <v>BCF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
       <c r="AT85" s="130" t="str">
         <f>"Ⓕ "&amp;AE85</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓕ Japan</v>
       </c>
     </row>
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓘ Norway</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57000,7 +57008,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57051,7 +57059,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFG</v>
+        <v>BCFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57065,16 +57073,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57114,7 +57122,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -57165,7 +57173,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFG</v>
+        <v>BCFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57179,16 +57187,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57228,7 +57236,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -57279,7 +57287,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGI</v>
+        <v>BCFGI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57302,7 +57310,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓗ Saudi Arabia</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57342,7 +57350,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -57393,7 +57401,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGIJ</v>
+        <v>BCFGIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57416,11 +57424,11 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,3,FALSE)</f>
@@ -57432,11 +57440,11 @@
       </c>
       <c r="N90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -57456,7 +57464,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57507,11 +57515,11 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGIJ</v>
+        <v>BCFGIJK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>DR Congo</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
@@ -57530,7 +57538,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -57550,7 +57558,7 @@
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 1</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
@@ -57570,7 +57578,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -57621,7 +57629,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGIJL</v>
+        <v>BCFGIJKL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57684,7 +57692,7 @@
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
@@ -57860,11 +57868,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57880,31 +57908,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -58947,15 +58955,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BCEFGIJL</v>
+        <v>BCFGIJKL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3E</v>
+        <v>3I</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -58983,7 +58991,7 @@
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>
-        <v>3I</v>
+        <v>3K</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0228E2A8-4687-468C-A561-6E8EC8F849A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1E16B3-64B4-4CFF-8CD3-C8C0AEA41E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="str" cm="1">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="141" t="str" cm="1">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="131">
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="132"/>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="131">
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43153,7 +43153,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43218,8 +43218,12 @@
         <f>AE50</f>
         <v>Spain</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="20"/>
+      <c r="F20" s="19">
+        <v>0</v>
+      </c>
+      <c r="G20" s="20">
+        <v>0</v>
+      </c>
       <c r="H20" s="80" t="str">
         <f>AE51</f>
         <v>Cape Verde</v>
@@ -43258,15 +43262,15 @@
       </c>
       <c r="S20" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Spain_draw</v>
       </c>
       <c r="T20" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Cape Verde_draw</v>
       </c>
       <c r="U20" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="123">
         <f t="shared" si="3"/>
@@ -43278,7 +43282,7 @@
       </c>
       <c r="X20" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="123">
         <f t="shared" si="10"/>
@@ -43292,9 +43296,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="123" t="str">
+      <c r="AB20" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD20" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR20))</f>
@@ -43427,7 +43431,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43696,7 +43700,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43946,7 +43950,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44206,7 +44210,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44233,7 +44237,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44450,7 +44454,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44795,7 +44799,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45059,7 +45063,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45330,7 +45334,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45591,7 +45595,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45801,7 +45805,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45908,7 +45912,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46180,7 +46184,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46440,7 +46444,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46455,14 +46459,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46682,7 +46686,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46713,11 +46717,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46937,7 +46941,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47162,7 +47166,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47282,7 +47286,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47309,7 +47313,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47546,7 +47550,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47576,7 +47580,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47811,7 +47815,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48487,7 +48491,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48580,7 +48584,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="132"/>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48836,7 +48840,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48851,14 +48855,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49095,7 +49099,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49108,11 +49112,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49332,7 +49336,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49574,7 +49578,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49817,7 +49821,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49833,7 +49837,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49938,7 +49942,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49952,7 +49956,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50077,7 +50081,7 @@
       </c>
       <c r="AG50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_lose")</f>
@@ -50101,15 +50105,15 @@
       </c>
       <c r="AN50" s="123">
         <f>AF50*3+AG50</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO50" s="123">
         <f>AN50/AN54*10+BA50</f>
-        <v>0</v>
+        <v>5.9803921568627452</v>
       </c>
       <c r="AP50" s="123">
         <f>AO50*10000000+BI50*100+AM50/AM54*10+AI50/AI54*1++IF(AQ50=0,ROW(),AQ50)/2000000</f>
-        <v>9.3820000000000004E-4</v>
+        <v>59804019.608781338</v>
       </c>
       <c r="AQ50" s="126">
         <f>VLOOKUP(AE50,db_fifarank,2,FALSE)</f>
@@ -50117,7 +50121,7 @@
       </c>
       <c r="AR50" s="125">
         <f>AP50/AP54</f>
-        <v>9.3732060580763133E-4</v>
+        <v>0.9999999832787162</v>
       </c>
       <c r="AS50" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J51,"1H")</f>
@@ -50129,7 +50133,7 @@
       </c>
       <c r="AU50" s="126" cm="1">
         <f t="array" ref="AU50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV50" s="126" cm="1">
         <f t="array" ref="AV50">SUMPRODUCT(($E$7:$E$78=AE50)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -50149,11 +50153,11 @@
       </c>
       <c r="AZ50" s="126">
         <f>AT50/AT54*1000+AU50/AU54*100+AY50/AY54*10+AV50/AV54</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA50" s="126">
         <f>AZ50/AZ54</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB50" s="126" cm="1">
         <f t="array" ref="BB50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_win")*($X$7:$X$78))</f>
@@ -50161,7 +50165,7 @@
       </c>
       <c r="BC50" s="126" cm="1">
         <f t="array" ref="BC50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD50" s="126" cm="1">
         <f t="array" ref="BD50">SUMPRODUCT(($E$7:$E$78=AE50)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -50181,13 +50185,13 @@
       </c>
       <c r="BH50" s="126">
         <f>BB50/BB54*1000+BC50/BC54*100+BG50/BG54*10+BD50/BD54</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI50" s="126">
         <f>BH50/BH54</f>
-        <v>0</v>
-      </c>
-      <c r="BK50" s="131">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50250,7 +50254,7 @@
       </c>
       <c r="K51" s="31">
         <f>L51+M51+N51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="31">
         <f>VLOOKUP(1,AD50:AN53,3,FALSE)</f>
@@ -50258,7 +50262,7 @@
       </c>
       <c r="M51" s="31">
         <f>VLOOKUP(1,AD50:AN53,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="31">
         <f>VLOOKUP(1,AD50:AN53,5,FALSE)</f>
@@ -50270,7 +50274,7 @@
       </c>
       <c r="P51" s="32">
         <f>L51*3+M51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="123">
         <f>DATE(2026,6,23)+TIME(9,0,0)+gmt_delta</f>
@@ -50318,7 +50322,7 @@
       </c>
       <c r="AD51" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR51))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE51" s="124" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
@@ -50330,7 +50334,7 @@
       </c>
       <c r="AG51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_lose")</f>
@@ -50354,15 +50358,15 @@
       </c>
       <c r="AN51" s="123">
         <f>AF51*3+AG51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO51" s="123">
         <f>AN51/AN54*10+BA51</f>
-        <v>0</v>
+        <v>5.9803921568627452</v>
       </c>
       <c r="AP51" s="123">
         <f>AO51*10000000+BI51*100+AM51/AM54*10+AI51/AI54*1++IF(AQ51=0,ROW(),AQ51)/2000000</f>
-        <v>6.8306500000000006E-4</v>
+        <v>59804019.6085262</v>
       </c>
       <c r="AQ51" s="126">
         <f>VLOOKUP(AE51,db_fifarank,2,FALSE)</f>
@@ -50370,7 +50374,7 @@
       </c>
       <c r="AR51" s="125">
         <f>AP51/AP54</f>
-        <v>6.8242474910039407E-4</v>
+        <v>0.99999998327444994</v>
       </c>
       <c r="AS51" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J52,"2H")</f>
@@ -50382,7 +50386,7 @@
       </c>
       <c r="AU51" s="126" cm="1">
         <f t="array" ref="AU51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV51" s="126" cm="1">
         <f t="array" ref="AV51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -50402,11 +50406,11 @@
       </c>
       <c r="AZ51" s="126">
         <f>AT51/AT54*1000+AU51/AU54*100+AY51/AY54*10+AV51/AV54</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA51" s="126">
         <f>AZ51/AZ54</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB51" s="126" cm="1">
         <f t="array" ref="BB51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($X$7:$X$78))</f>
@@ -50414,7 +50418,7 @@
       </c>
       <c r="BC51" s="126" cm="1">
         <f t="array" ref="BC51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD51" s="126" cm="1">
         <f t="array" ref="BD51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -50434,13 +50438,13 @@
       </c>
       <c r="BH51" s="126">
         <f>BB51/BB54*1000+BC51/BC54*100+BG51/BG54*10+BD51/BD54</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI51" s="126">
         <f>BH51/BH54</f>
-        <v>0</v>
-      </c>
-      <c r="BK51" s="132"/>
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50503,11 +50507,11 @@
       </c>
       <c r="J52" s="33" t="str">
         <f>VLOOKUP(2,AD50:AN53,2,FALSE)</f>
-        <v>Uruguay</v>
+        <v>Cape Verde</v>
       </c>
       <c r="K52" s="23">
         <f>L52+M52+N52</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="23">
         <f>VLOOKUP(2,AD50:AN53,3,FALSE)</f>
@@ -50515,7 +50519,7 @@
       </c>
       <c r="M52" s="23">
         <f>VLOOKUP(2,AD50:AN53,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="23">
         <f>VLOOKUP(2,AD50:AN53,5,FALSE)</f>
@@ -50527,7 +50531,7 @@
       </c>
       <c r="P52" s="34">
         <f>L52*3+M52</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="123">
         <f>DATE(2026,6,23)+TIME(12,0,0)+gmt_delta</f>
@@ -50575,7 +50579,7 @@
       </c>
       <c r="AD52" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR52))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE52" s="124" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
@@ -50627,7 +50631,7 @@
       </c>
       <c r="AR52" s="125">
         <f>AP52/AP54</f>
-        <v>7.1004883218564344E-4</v>
+        <v>1.1884067204264892E-11</v>
       </c>
       <c r="AT52" s="126" cm="1">
         <f t="array" ref="AT52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($U$7:$U$78))</f>
@@ -50700,7 +50704,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50752,7 +50756,7 @@
       </c>
       <c r="J53" s="33" t="str">
         <f>VLOOKUP(3,AD50:AN53,2,FALSE)</f>
-        <v>Saudi Arabia</v>
+        <v>Uruguay</v>
       </c>
       <c r="K53" s="23">
         <f>L53+M53+N53</f>
@@ -50824,7 +50828,7 @@
       </c>
       <c r="AD53" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR53))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE53" s="124" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
@@ -50876,7 +50880,7 @@
       </c>
       <c r="AR53" s="125">
         <f>AP53/AP54</f>
-        <v>8.3575089850702075E-4</v>
+        <v>1.3987939129918085E-11</v>
       </c>
       <c r="AT53" s="126" cm="1">
         <f t="array" ref="AT53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($U$7:$U$78))</f>
@@ -50955,7 +50959,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51005,7 +51009,7 @@
       </c>
       <c r="J54" s="35" t="str">
         <f>VLOOKUP(4,AD50:AN53,2,FALSE)</f>
-        <v>Cape Verde</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="K54" s="36">
         <f>L54+M54+N54</f>
@@ -51081,7 +51085,7 @@
       </c>
       <c r="AG54" s="123">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH54" s="123">
         <f t="shared" si="25"/>
@@ -51101,15 +51105,15 @@
       </c>
       <c r="AN54" s="123">
         <f>MAX(AN50:AN53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO54" s="123">
         <f>MAX(AO50:AO53)+1</f>
-        <v>1</v>
+        <v>6.9803921568627452</v>
       </c>
       <c r="AP54" s="123">
         <f>MAX(AP50:AP53)+1</f>
-        <v>1.0009382</v>
+        <v>59804020.608781338</v>
       </c>
       <c r="AT54" s="126">
         <f>MAX(AT50:AT53)-MIN(AT50:AT53)+1</f>
@@ -51117,7 +51121,7 @@
       </c>
       <c r="AU54" s="126">
         <f>MAX(AU50:AU53)-MIN(AU50:AU53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV54" s="126">
         <f>MAX(AV50:AV53)-MIN(AV50:AV53)+1</f>
@@ -51133,7 +51137,7 @@
       </c>
       <c r="AZ54" s="126">
         <f>MAX(AZ50:AZ53)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="BB54" s="126">
         <f>MAX(BB50:BB53)-MIN(BB50:BB53)+1</f>
@@ -51141,7 +51145,7 @@
       </c>
       <c r="BC54" s="126">
         <f>MAX(BC50:BC53)-MIN(BC50:BC53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD54" s="126">
         <f>MAX(BD50:BD53)-MIN(BD50:BD53)+1</f>
@@ -51157,9 +51161,9 @@
       </c>
       <c r="BH54" s="126">
         <f>MAX(BH50:BH53)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK54" s="131">
+        <v>51</v>
+      </c>
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51280,7 +51284,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51307,7 +51311,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51566,7 +51570,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52049,7 +52053,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52297,7 +52301,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52520,7 +52524,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52633,7 +52637,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52876,7 +52880,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53128,7 +53132,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53394,7 +53398,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53648,7 +53652,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53844,7 +53848,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53944,7 +53948,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54200,7 +54204,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54214,25 +54218,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54470,7 +54474,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54482,19 +54486,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54715,7 +54719,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54951,7 +54955,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56627,13 +56631,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56731,16 +56735,16 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓗ Uruguay</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56845,16 +56849,16 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56959,16 +56963,16 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓖ Egypt</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57008,7 +57012,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57073,16 +57077,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓘ Norway</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57122,11 +57126,11 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
-        <v>Saudi Arabia</v>
+        <v>Uruguay</v>
       </c>
       <c r="AF87" s="123">
         <f t="shared" si="39"/>
@@ -57165,38 +57169,38 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>666.6673773816666</v>
+        <v>666.66750320166659</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
-        <v>1421.43</v>
+        <v>1673.07</v>
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFG</v>
+        <v>BCFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Uruguay</v>
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓗ Uruguay</v>
       </c>
     </row>
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57236,7 +57240,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -57287,7 +57291,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGI</v>
+        <v>BCFGHI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57310,7 +57314,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57350,7 +57354,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -57401,7 +57405,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGIJ</v>
+        <v>BCFGHIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57464,7 +57468,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57515,11 +57519,11 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGIJK</v>
+        <v>BCFGHIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>DR Congo</v>
+        <v/>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
@@ -57578,7 +57582,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -57629,7 +57633,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGIJKL</v>
+        <v>BCFGHIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57868,6 +57872,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57883,36 +57917,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -58955,15 +58959,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BCFGIJKL</v>
+        <v>BCFGHIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3I</v>
+        <v>3H</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -58991,7 +58995,7 @@
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>
-        <v>3K</v>
+        <v>3I</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1E16B3-64B4-4CFF-8CD3-C8C0AEA41E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7646990B-E30E-4F87-9D27-697A420E4C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="str" cm="1">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="str" cm="1">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43153,7 +43153,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43431,7 +43431,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43700,7 +43700,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43752,8 +43752,12 @@
         <f>AE44</f>
         <v>Belgium</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20"/>
+      <c r="F22" s="19">
+        <v>1</v>
+      </c>
+      <c r="G22" s="20">
+        <v>1</v>
+      </c>
       <c r="H22" s="80" t="str">
         <f>AE45</f>
         <v>Egypt</v>
@@ -43792,43 +43796,43 @@
       </c>
       <c r="S22" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Belgium_draw</v>
       </c>
       <c r="T22" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Egypt_draw</v>
       </c>
       <c r="U22" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB22" s="123" t="str">
+      <c r="AB22" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD22" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR22))</f>
@@ -43950,7 +43954,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44210,7 +44214,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44237,7 +44241,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44454,7 +44458,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44799,7 +44803,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45063,7 +45067,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45334,7 +45338,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45595,7 +45599,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45805,7 +45809,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45912,7 +45916,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46184,7 +46188,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46444,7 +46448,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46459,14 +46463,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46686,7 +46690,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46717,11 +46721,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46941,7 +46945,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47166,7 +47170,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47286,7 +47290,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47313,7 +47317,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47550,7 +47554,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47580,7 +47584,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47815,7 +47819,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48491,7 +48495,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48584,7 +48588,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48723,7 +48727,7 @@
       </c>
       <c r="AG44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_lose")</f>
@@ -48731,11 +48735,11 @@
       </c>
       <c r="AI44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE44,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE44,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL44" s="123">
         <f>AI44-AJ44</f>
@@ -48747,15 +48751,15 @@
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>8.6735499999999999E-4</v>
+        <v>59805923.801838219</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -48763,7 +48767,7 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>8.6660334725374266E-4</v>
+        <v>0.99999998327924866</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
@@ -48775,15 +48779,15 @@
       </c>
       <c r="AU44" s="126" cm="1">
         <f t="array" ref="AU44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" s="126" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW44" s="126" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" s="126">
         <f>AV44-AW44</f>
@@ -48795,11 +48799,11 @@
       </c>
       <c r="AZ44" s="126">
         <f>AT44/AT48*1000+AU44/AU48*100+AY44/AY48*10+AV44/AV48</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA44" s="126">
         <f>AZ44/AZ48</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB44" s="126" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($X$7:$X$78))</f>
@@ -48807,15 +48811,15 @@
       </c>
       <c r="BC44" s="126" cm="1">
         <f t="array" ref="BC44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD44" s="126" cm="1">
         <f t="array" ref="BD44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE44" s="126" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF44" s="126">
         <f>BD44-BE44</f>
@@ -48827,11 +48831,11 @@
       </c>
       <c r="BH44" s="126">
         <f>BB44/BB48*1000+BC44/BC48*100+BG44/BG48*10+BD44/BD48</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI44" s="126">
         <f>BH44/BH48</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK44" s="21"/>
       <c r="BL44" s="21"/>
@@ -48840,7 +48844,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48855,14 +48859,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -48896,7 +48900,7 @@
       </c>
       <c r="K45" s="31">
         <f>L45+M45+N45</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="31">
         <f>VLOOKUP(1,AD44:AN47,3,FALSE)</f>
@@ -48904,7 +48908,7 @@
       </c>
       <c r="M45" s="31">
         <f>VLOOKUP(1,AD44:AN47,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="31">
         <f>VLOOKUP(1,AD44:AN47,5,FALSE)</f>
@@ -48912,11 +48916,11 @@
       </c>
       <c r="O45" s="31" t="str">
         <f>VLOOKUP(1,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD44:AN47,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P45" s="32">
         <f>L45*3+M45</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="123">
         <f>DATE(2026,6,21)+TIME(8,0,0)+gmt_delta</f>
@@ -48964,7 +48968,7 @@
       </c>
       <c r="AD45" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR45))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE45" s="124" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
@@ -48976,7 +48980,7 @@
       </c>
       <c r="AG45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_lose")</f>
@@ -48984,11 +48988,11 @@
       </c>
       <c r="AI45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE45,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE45,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL45" s="123">
         <f>AI45-AJ45</f>
@@ -49000,15 +49004,15 @@
       </c>
       <c r="AN45" s="123">
         <f>AF45*3+AG45</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO45" s="123">
         <f>AN45/AN48*10+BA45</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP45" s="123">
         <f>AO45*10000000+BI45*100+AM45/AM48*10+AI45/AI48*1++IF(AQ45=0,ROW(),AQ45)/2000000</f>
-        <v>7.8162000000000001E-4</v>
+        <v>59805923.801752485</v>
       </c>
       <c r="AQ45" s="126">
         <f>VLOOKUP(AE45,db_fifarank,2,FALSE)</f>
@@ -49016,7 +49020,7 @@
       </c>
       <c r="AR45" s="125">
         <f>AP45/AP48</f>
-        <v>7.809426454917195E-4</v>
+        <v>0.99999998327781503</v>
       </c>
       <c r="AS45" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J46,"2G")</f>
@@ -49028,15 +49032,15 @@
       </c>
       <c r="AU45" s="126" cm="1">
         <f t="array" ref="AU45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV45" s="126" cm="1">
         <f t="array" ref="AV45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW45" s="126" cm="1">
         <f t="array" ref="AW45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX45" s="126">
         <f>AV45-AW45</f>
@@ -49048,11 +49052,11 @@
       </c>
       <c r="AZ45" s="126">
         <f>AT45/AT48*1000+AU45/AU48*100+AY45/AY48*10+AV45/AV48</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA45" s="126">
         <f>AZ45/AZ48</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB45" s="126" cm="1">
         <f t="array" ref="BB45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($X$7:$X$78))</f>
@@ -49060,15 +49064,15 @@
       </c>
       <c r="BC45" s="126" cm="1">
         <f t="array" ref="BC45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD45" s="126" cm="1">
         <f t="array" ref="BD45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE45" s="126" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF45" s="126">
         <f>BD45-BE45</f>
@@ -49080,11 +49084,11 @@
       </c>
       <c r="BH45" s="126">
         <f>BB45/BB48*1000+BC45/BC48*100+BG45/BG48*10+BD45/BD48</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI45" s="126">
         <f>BH45/BH48</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK45" s="21" t="str" cm="1">
         <f t="array" ref="BK45">INDEX(T,24+MONTH(BP45),lang) &amp; " " &amp; DAY(BP45) &amp; ", " &amp; YEAR(BP45) &amp; "   " &amp; (IF(HOUR(BP45)&lt;10,0,"")&amp;HOUR(BP45)) &amp; ":" &amp;  (IF(MINUTE(BP45)&lt;10,0,"")&amp;MINUTE(BP45))</f>
@@ -49099,7 +49103,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49112,11 +49116,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49146,11 +49150,11 @@
       </c>
       <c r="J46" s="33" t="str">
         <f>VLOOKUP(2,AD44:AN47,2,FALSE)</f>
-        <v>Iran</v>
+        <v>Egypt</v>
       </c>
       <c r="K46" s="23">
         <f>L46+M46+N46</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="23">
         <f>VLOOKUP(2,AD44:AN47,3,FALSE)</f>
@@ -49158,7 +49162,7 @@
       </c>
       <c r="M46" s="23">
         <f>VLOOKUP(2,AD44:AN47,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="23">
         <f>VLOOKUP(2,AD44:AN47,5,FALSE)</f>
@@ -49166,11 +49170,11 @@
       </c>
       <c r="O46" s="23" t="str">
         <f>VLOOKUP(2,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD44:AN47,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P46" s="34">
         <f>L46*3+M46</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="123">
         <f>DATE(2026,6,21)+TIME(14,0,0)+gmt_delta</f>
@@ -49218,7 +49222,7 @@
       </c>
       <c r="AD46" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR46))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE46" s="124" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
@@ -49270,7 +49274,7 @@
       </c>
       <c r="AR46" s="125">
         <f>AP46/AP48</f>
-        <v>8.0695008780659041E-4</v>
+        <v>1.3504514856614602E-11</v>
       </c>
       <c r="AT46" s="126" cm="1">
         <f t="array" ref="AT46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($U$7:$U$78))</f>
@@ -49336,7 +49340,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="141">
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49388,7 +49392,7 @@
       </c>
       <c r="J47" s="33" t="str">
         <f>VLOOKUP(3,AD44:AN47,2,FALSE)</f>
-        <v>Egypt</v>
+        <v>Iran</v>
       </c>
       <c r="K47" s="23">
         <f>L47+M47+N47</f>
@@ -49512,7 +49516,7 @@
       </c>
       <c r="AR47" s="125">
         <f>AP47/AP48</f>
-        <v>6.4022969357412996E-4</v>
+        <v>1.0714406676649276E-11</v>
       </c>
       <c r="AT47" s="126" cm="1">
         <f t="array" ref="AT47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($U$7:$U$78))</f>
@@ -49578,7 +49582,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="142"/>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49729,7 +49733,7 @@
       </c>
       <c r="AG48" s="123">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" s="123">
         <f t="shared" si="24"/>
@@ -49737,7 +49741,7 @@
       </c>
       <c r="AI48" s="123">
         <f>MAX(AI44:AI47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL48" s="123">
         <f>MIN(AL44:AL47)</f>
@@ -49749,15 +49753,15 @@
       </c>
       <c r="AN48" s="123">
         <f>MAX(AN44:AN47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO48" s="123">
         <f>MAX(AO44:AO47)+1</f>
-        <v>1</v>
+        <v>6.9805825242718447</v>
       </c>
       <c r="AP48" s="123">
         <f>MAX(AP44:AP47)+1</f>
-        <v>1.000867355</v>
+        <v>59805924.801838219</v>
       </c>
       <c r="AT48" s="126">
         <f>MAX(AT44:AT47)-MIN(AT44:AT47)+1</f>
@@ -49765,15 +49769,15 @@
       </c>
       <c r="AU48" s="126">
         <f>MAX(AU44:AU47)-MIN(AU44:AU47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV48" s="126">
         <f>MAX(AV44:AV47)-MIN(AV44:AV47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW48" s="126">
         <f>MAX(AW44:AW47)-MIN(AW44:AW47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY48" s="126">
         <f>MAX(AY44:AY47)-MIN(AY44:AY47)+1</f>
@@ -49781,7 +49785,7 @@
       </c>
       <c r="AZ48" s="126">
         <f>MAX(AZ44:AZ47)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB48" s="126">
         <f>MAX(BB44:BB47)-MIN(BB44:BB47)+1</f>
@@ -49789,15 +49793,15 @@
       </c>
       <c r="BC48" s="126">
         <f>MAX(BC44:BC47)-MIN(BC44:BC47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD48" s="126">
         <f>MAX(BD44:BD47)-MIN(BD44:BD47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE48" s="126">
         <f>MAX(BE44:BE47)-MIN(BE44:BE47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG48" s="126">
         <f>MAX(BG44:BG47)-MIN(BG44:BG47)+1</f>
@@ -49805,7 +49809,7 @@
       </c>
       <c r="BH48" s="126">
         <f>MAX(BH44:BH47)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
@@ -49821,7 +49825,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49837,7 +49841,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49942,7 +49946,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49956,7 +49960,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50191,7 +50195,7 @@
         <f>BH50/BH54</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50444,7 +50448,7 @@
         <f>BH51/BH54</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50704,7 +50708,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50959,7 +50963,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51163,7 +51167,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51284,7 +51288,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51311,7 +51315,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51570,7 +51574,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52053,7 +52057,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52301,7 +52305,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52524,7 +52528,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52637,7 +52641,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52880,7 +52884,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53132,7 +53136,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53398,7 +53402,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53652,7 +53656,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53848,7 +53852,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53948,7 +53952,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54204,7 +54208,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54218,25 +54222,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54474,7 +54478,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54486,19 +54490,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54719,7 +54723,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54955,7 +54959,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56631,13 +56635,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56735,11 +56739,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56849,16 +56853,16 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓖ Iran</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56963,16 +56967,16 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57012,11 +57016,11 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
-        <v>Egypt</v>
+        <v>Iran</v>
       </c>
       <c r="AF86" s="123">
         <f t="shared" si="39"/>
@@ -57055,11 +57059,11 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>666.66744828666663</v>
+        <v>666.66747431666658</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
-        <v>1563.24</v>
+        <v>1615.3</v>
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
@@ -57067,21 +57071,21 @@
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Egypt</v>
+        <v>Iran</v>
       </c>
       <c r="AT86" s="130" t="str">
         <f>"Ⓖ "&amp;AE86</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓖ Iran</v>
       </c>
     </row>
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57191,11 +57195,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57354,7 +57358,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -57872,11 +57876,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57892,31 +57916,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haavas/git/VM2026/fasit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D38062-D18D-074E-84EB-9E026F85BAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8A4FD8-E24C-024F-B03D-5F05D0F5E6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="2920" windowWidth="28800" windowHeight="15340" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="2920" windowWidth="28800" windowHeight="15340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="150" t="str" cm="1">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="152" t="str" cm="1">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44024,8 +44024,12 @@
         <f>AE56</f>
         <v>France</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="20"/>
+      <c r="F23" s="19">
+        <v>3</v>
+      </c>
+      <c r="G23" s="20">
+        <v>1</v>
+      </c>
       <c r="H23" s="80" t="str">
         <f>AE57</f>
         <v>Senegal</v>
@@ -44064,11 +44068,11 @@
       </c>
       <c r="S23" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>France_win</v>
       </c>
       <c r="T23" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Senegal_lose</v>
       </c>
       <c r="U23" s="123">
         <f t="shared" si="8"/>
@@ -44098,9 +44102,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="123" t="str">
+      <c r="AB23" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD23" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR23))</f>
@@ -44222,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44249,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44466,7 +44470,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44811,7 +44815,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45075,7 +45079,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45346,7 +45350,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45607,7 +45611,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45817,7 +45821,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45924,7 +45928,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46196,7 +46200,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46456,7 +46460,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46471,14 +46475,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -46698,7 +46702,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46729,11 +46733,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -46953,7 +46957,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47178,7 +47182,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47298,7 +47302,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47325,7 +47329,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47562,7 +47566,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47592,7 +47596,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47827,7 +47831,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48503,7 +48507,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48596,7 +48600,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48852,7 +48856,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48867,14 +48871,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49111,7 +49115,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49124,11 +49128,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -49348,7 +49352,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="141">
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49590,7 +49594,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="142"/>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49833,7 +49837,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49849,7 +49853,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49954,7 +49958,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49968,7 +49972,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50203,7 +50207,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50456,7 +50460,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50716,7 +50720,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50971,7 +50975,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51175,7 +51179,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51296,7 +51300,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51323,7 +51327,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51448,7 +51452,7 @@
       </c>
       <c r="AF56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_draw")</f>
@@ -51460,31 +51464,31 @@
       </c>
       <c r="AI56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE56,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE56,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL56" s="123">
         <f>AI56-AJ56</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM56" s="123">
         <f>AL56-AL60</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN56" s="123">
         <f>AF56*3+AG56</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO56" s="123">
         <f>AN56/AN60*10+BA56</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP56" s="123">
         <f>AO56*10000000+BI56*100+AM56/AM60*10+AI56/AI60*1++IF(AQ56=0,ROW(),AQ56)/2000000</f>
-        <v>9.3866000000000002E-4</v>
+        <v>75000008.750938654</v>
       </c>
       <c r="AQ56" s="126">
         <f>VLOOKUP(AE56,db_fifarank,2,FALSE)</f>
@@ -51492,7 +51496,7 @@
       </c>
       <c r="AR56" s="125">
         <f>AP56/AP60</f>
-        <v>9.3777974366581059E-4</v>
+        <v>0.99999998666666845</v>
       </c>
       <c r="AS56" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J57,"1I")</f>
@@ -51582,7 +51586,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -51629,11 +51633,11 @@
       </c>
       <c r="K57" s="31">
         <f>L57+M57+N57</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="31">
         <f>VLOOKUP(1,AD56:AN59,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="31">
         <f>VLOOKUP(1,AD56:AN59,4,FALSE)</f>
@@ -51645,11 +51649,11 @@
       </c>
       <c r="O57" s="31" t="str">
         <f>VLOOKUP(1,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>3 - 1</v>
       </c>
       <c r="P57" s="32">
         <f>L57*3+M57</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R57" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -51697,7 +51701,7 @@
       </c>
       <c r="AD57" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR57))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE57" s="124" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
@@ -51713,19 +51717,19 @@
       </c>
       <c r="AH57" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE57 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE57,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE57,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL57" s="123">
         <f>AI57-AJ57</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM57" s="123">
         <f>AL57-AL60</f>
@@ -51741,7 +51745,7 @@
       </c>
       <c r="AP57" s="123">
         <f>AO57*10000000+BI57*100+AM57/AM60*10+AI57/AI60*1++IF(AQ57=0,ROW(),AQ57)/2000000</f>
-        <v>8.4449500000000001E-4</v>
+        <v>0.250844495</v>
       </c>
       <c r="AQ57" s="126">
         <f>VLOOKUP(AE57,db_fifarank,2,FALSE)</f>
@@ -51749,7 +51753,7 @@
       </c>
       <c r="AR57" s="125">
         <f>AP57/AP60</f>
-        <v>8.4370304969537283E-4</v>
+        <v>3.3445928318277399E-9</v>
       </c>
       <c r="AS57" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J58,"2I")</f>
@@ -51875,7 +51879,7 @@
       <c r="I58" s="69"/>
       <c r="J58" s="33" t="str">
         <f>VLOOKUP(2,AD56:AN59,2,FALSE)</f>
-        <v>Senegal</v>
+        <v>Norway</v>
       </c>
       <c r="K58" s="23">
         <f>L58+M58+N58</f>
@@ -51947,7 +51951,7 @@
       </c>
       <c r="AD58" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR58))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE58" s="124" t="str">
         <f>VLOOKUP("Iraq",T,lang,FALSE)</f>
@@ -51979,7 +51983,7 @@
       </c>
       <c r="AM58" s="123">
         <f>AL58-AL60</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN58" s="123">
         <f>AF58*3+AG58</f>
@@ -51991,7 +51995,7 @@
       </c>
       <c r="AP58" s="123">
         <f>AO58*10000000+BI58*100+AM58/AM60*10+AI58/AI60*1++IF(AQ58=0,ROW(),AQ58)/2000000</f>
-        <v>7.2357000000000009E-4</v>
+        <v>4.0007235699999999</v>
       </c>
       <c r="AQ58" s="126">
         <f>VLOOKUP(AE58,db_fifarank,2,FALSE)</f>
@@ -51999,7 +52003,7 @@
       </c>
       <c r="AR58" s="125">
         <f>AP58/AP60</f>
-        <v>7.2289145071087577E-4</v>
+        <v>5.3342973998079103E-8</v>
       </c>
       <c r="AT58" s="126" cm="1">
         <f t="array" ref="AT58">SUMPRODUCT(($S$7:$S$78=AE58&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE58&amp;"_win")*($U$7:$U$78))</f>
@@ -52065,7 +52069,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52123,7 +52127,7 @@
       <c r="I59" s="69"/>
       <c r="J59" s="33" t="str">
         <f>VLOOKUP(3,AD56:AN59,2,FALSE)</f>
-        <v>Norway</v>
+        <v>Iraq</v>
       </c>
       <c r="K59" s="23">
         <f>L59+M59+N59</f>
@@ -52195,7 +52199,7 @@
       </c>
       <c r="AD59" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR59))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE59" s="124" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
@@ -52227,7 +52231,7 @@
       </c>
       <c r="AM59" s="123">
         <f>AL59-AL60</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN59" s="123">
         <f>AF59*3+AG59</f>
@@ -52239,7 +52243,7 @@
       </c>
       <c r="AP59" s="123">
         <f>AO59*10000000+BI59*100+AM59/AM60*10+AI59/AI60*1++IF(AQ59=0,ROW(),AQ59)/2000000</f>
-        <v>7.7547E-4</v>
+        <v>4.0007754699999998</v>
       </c>
       <c r="AQ59" s="126">
         <f>VLOOKUP(AE59,db_fifarank,2,FALSE)</f>
@@ -52247,7 +52251,7 @@
       </c>
       <c r="AR59" s="125">
         <f>AP59/AP60</f>
-        <v>7.7474277994217945E-4</v>
+        <v>5.3343665997989134E-8</v>
       </c>
       <c r="AT59" s="126" cm="1">
         <f t="array" ref="AT59">SUMPRODUCT(($S$7:$S$78=AE59&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE59&amp;"_win")*($U$7:$U$78))</f>
@@ -52313,7 +52317,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52375,11 +52379,11 @@
       <c r="I60" s="69"/>
       <c r="J60" s="35" t="str">
         <f>VLOOKUP(4,AD56:AN59,2,FALSE)</f>
-        <v>Iraq</v>
+        <v>Senegal</v>
       </c>
       <c r="K60" s="36">
         <f>L60+M60+N60</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="36">
         <f>VLOOKUP(4,AD56:AN59,3,FALSE)</f>
@@ -52391,11 +52395,11 @@
       </c>
       <c r="N60" s="36">
         <f>VLOOKUP(4,AD56:AN59,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" s="36" t="str">
         <f>VLOOKUP(4,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 3</v>
       </c>
       <c r="P60" s="37">
         <f>L60*3+M60</f>
@@ -52447,7 +52451,7 @@
       </c>
       <c r="AF60" s="123">
         <f t="shared" ref="AF60:AH60" si="27">MAX(AF56:AF59)-MIN(AF56:AF59)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG60" s="123">
         <f t="shared" si="27"/>
@@ -52455,31 +52459,31 @@
       </c>
       <c r="AH60" s="123">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI60" s="123">
         <f>MAX(AI56:AI59)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL60" s="123">
         <f>MIN(AL56:AL59)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM60" s="123">
         <f>MAX(AM56:AM59)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN60" s="123">
         <f>MAX(AN56:AN59)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO60" s="123">
         <f>MAX(AO56:AO59)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP60" s="123">
         <f>MAX(AP56:AP59)+1</f>
-        <v>1.0009386600000001</v>
+        <v>75000009.750938654</v>
       </c>
       <c r="AT60" s="126">
         <f>MAX(AT56:AT59)-MIN(AT56:AT59)+1</f>
@@ -52536,7 +52540,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52649,7 +52653,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52892,7 +52896,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53144,7 +53148,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53410,7 +53414,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53664,7 +53668,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53860,7 +53864,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53960,7 +53964,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54216,7 +54220,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54230,25 +54234,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -54486,7 +54490,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54498,19 +54502,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -54731,7 +54735,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54967,7 +54971,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56643,13 +56647,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56747,11 +56751,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56861,11 +56865,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -56975,11 +56979,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57089,16 +57093,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57203,16 +57207,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57252,11 +57256,11 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
-        <v>Norway</v>
+        <v>Iraq</v>
       </c>
       <c r="AF88" s="123">
         <f t="shared" si="39"/>
@@ -57295,23 +57299,23 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>666.66744213666664</v>
+        <v>666.66739023666662</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
-        <v>1550.94</v>
+        <v>1447.14</v>
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHI</v>
+        <v>BCFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Norway</v>
+        <v/>
       </c>
       <c r="AT88" s="130" t="str">
         <f>"Ⓘ "&amp;AE88</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓘ Iraq</v>
       </c>
     </row>
     <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -57326,7 +57330,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓘ Iraq</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57417,7 +57421,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHIJ</v>
+        <v>BCFGHJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57480,7 +57484,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57531,11 +57535,11 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHIJ</v>
+        <v>BCFGHJK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>DR Congo</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
@@ -57594,7 +57598,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -57645,7 +57649,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHIJL</v>
+        <v>BCFGHJKL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57884,11 +57888,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57904,31 +57928,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -58971,11 +58975,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BCFGHIJL</v>
+        <v>BCFGHJKL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -59007,7 +59011,7 @@
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>
-        <v>3I</v>
+        <v>3K</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haavas/git/VM2026/fasit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8A4FD8-E24C-024F-B03D-5F05D0F5E6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9271FDD6-2770-444D-8AEC-F635EAD88D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="2920" windowWidth="28800" windowHeight="15340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="str" cm="1">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="141" t="str" cm="1">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="131">
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="132"/>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="131">
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44288,8 +44288,12 @@
         <f>AE58</f>
         <v>Iraq</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="F24" s="19">
+        <v>1</v>
+      </c>
+      <c r="G24" s="20">
+        <v>3</v>
+      </c>
       <c r="H24" s="80" t="str">
         <f>AE59</f>
         <v>Norway</v>
@@ -44328,11 +44332,11 @@
       </c>
       <c r="S24" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Iraq_lose</v>
       </c>
       <c r="T24" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Norway_win</v>
       </c>
       <c r="U24" s="123">
         <f t="shared" si="8"/>
@@ -44362,9 +44366,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB24" s="123" t="str">
+      <c r="AB24" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF24" s="123">
         <f t="shared" ref="AF24:AH24" si="14">MAX(AF20:AF23)-MIN(AF20:AF23)+1</f>
@@ -44470,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44815,7 +44819,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45079,7 +45083,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45350,7 +45354,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45611,7 +45615,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45821,7 +45825,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45928,7 +45932,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46200,7 +46204,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46460,7 +46464,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46475,14 +46479,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -46702,7 +46706,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46733,11 +46737,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -46957,7 +46961,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47182,7 +47186,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47302,7 +47306,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47329,7 +47333,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47566,7 +47570,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47596,7 +47600,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47831,7 +47835,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48507,7 +48511,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48600,7 +48604,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="132"/>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48856,7 +48860,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48871,14 +48875,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49115,7 +49119,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49128,11 +49132,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -49352,7 +49356,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49594,7 +49598,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49837,7 +49841,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49853,7 +49857,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49958,7 +49962,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49972,7 +49976,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50207,7 +50211,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="131">
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50460,7 +50464,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="132"/>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50720,7 +50724,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50975,7 +50979,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51179,7 +51183,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="131">
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51300,7 +51304,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51327,7 +51331,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51586,7 +51590,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -51701,7 +51705,7 @@
       </c>
       <c r="AD57" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR57))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE57" s="124" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
@@ -51883,11 +51887,11 @@
       </c>
       <c r="K58" s="23">
         <f>L58+M58+N58</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="23">
         <f>VLOOKUP(2,AD56:AN59,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="23">
         <f>VLOOKUP(2,AD56:AN59,4,FALSE)</f>
@@ -51899,11 +51903,11 @@
       </c>
       <c r="O58" s="23" t="str">
         <f>VLOOKUP(2,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>3 - 1</v>
       </c>
       <c r="P58" s="34">
         <f>L58*3+M58</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R58" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -51951,7 +51955,7 @@
       </c>
       <c r="AD58" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR58))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE58" s="124" t="str">
         <f>VLOOKUP("Iraq",T,lang,FALSE)</f>
@@ -51967,23 +51971,23 @@
       </c>
       <c r="AH58" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE58 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE58,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE58,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL58" s="123">
         <f>AI58-AJ58</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM58" s="123">
         <f>AL58-AL60</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN58" s="123">
         <f>AF58*3+AG58</f>
@@ -51995,7 +51999,7 @@
       </c>
       <c r="AP58" s="123">
         <f>AO58*10000000+BI58*100+AM58/AM60*10+AI58/AI60*1++IF(AQ58=0,ROW(),AQ58)/2000000</f>
-        <v>4.0007235699999999</v>
+        <v>0.25072357000000001</v>
       </c>
       <c r="AQ58" s="126">
         <f>VLOOKUP(AE58,db_fifarank,2,FALSE)</f>
@@ -52003,7 +52007,7 @@
       </c>
       <c r="AR58" s="125">
         <f>AP58/AP60</f>
-        <v>5.3342973998079103E-8</v>
+        <v>3.3429804987040298E-9</v>
       </c>
       <c r="AT58" s="126" cm="1">
         <f t="array" ref="AT58">SUMPRODUCT(($S$7:$S$78=AE58&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE58&amp;"_win")*($U$7:$U$78))</f>
@@ -52069,7 +52073,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52127,11 +52131,11 @@
       <c r="I59" s="69"/>
       <c r="J59" s="33" t="str">
         <f>VLOOKUP(3,AD56:AN59,2,FALSE)</f>
-        <v>Iraq</v>
+        <v>Senegal</v>
       </c>
       <c r="K59" s="23">
         <f>L59+M59+N59</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="23">
         <f>VLOOKUP(3,AD56:AN59,3,FALSE)</f>
@@ -52143,11 +52147,11 @@
       </c>
       <c r="N59" s="23">
         <f>VLOOKUP(3,AD56:AN59,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="23" t="str">
         <f>VLOOKUP(3,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 3</v>
       </c>
       <c r="P59" s="34">
         <f>L59*3+M59</f>
@@ -52207,7 +52211,7 @@
       </c>
       <c r="AF59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_draw")</f>
@@ -52219,31 +52223,31 @@
       </c>
       <c r="AI59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE59,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE59,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL59" s="123">
         <f>AI59-AJ59</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM59" s="123">
         <f>AL59-AL60</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN59" s="123">
         <f>AF59*3+AG59</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO59" s="123">
         <f>AN59/AN60*10+BA59</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP59" s="123">
         <f>AO59*10000000+BI59*100+AM59/AM60*10+AI59/AI60*1++IF(AQ59=0,ROW(),AQ59)/2000000</f>
-        <v>4.0007754699999998</v>
+        <v>75000008.750775471</v>
       </c>
       <c r="AQ59" s="126">
         <f>VLOOKUP(AE59,db_fifarank,2,FALSE)</f>
@@ -52251,7 +52255,7 @@
       </c>
       <c r="AR59" s="125">
         <f>AP59/AP60</f>
-        <v>5.3343665997989134E-8</v>
+        <v>0.99999998666449263</v>
       </c>
       <c r="AT59" s="126" cm="1">
         <f t="array" ref="AT59">SUMPRODUCT(($S$7:$S$78=AE59&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE59&amp;"_win")*($U$7:$U$78))</f>
@@ -52317,7 +52321,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52379,7 +52383,7 @@
       <c r="I60" s="69"/>
       <c r="J60" s="35" t="str">
         <f>VLOOKUP(4,AD56:AN59,2,FALSE)</f>
-        <v>Senegal</v>
+        <v>Iraq</v>
       </c>
       <c r="K60" s="36">
         <f>L60+M60+N60</f>
@@ -52540,7 +52544,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52653,7 +52657,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52896,7 +52900,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53148,7 +53152,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53414,7 +53418,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53668,7 +53672,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53864,7 +53868,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53964,7 +53968,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54220,7 +54224,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54234,25 +54238,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -54490,7 +54494,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54502,19 +54506,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -54735,7 +54739,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54971,7 +54975,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56378,7 +56382,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56647,13 +56651,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56751,11 +56755,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56800,7 +56804,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56865,11 +56869,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -56979,11 +56983,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57093,11 +57097,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57207,11 +57211,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57256,11 +57260,11 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
-        <v>Iraq</v>
+        <v>Senegal</v>
       </c>
       <c r="AF88" s="123">
         <f t="shared" si="39"/>
@@ -57272,26 +57276,26 @@
       </c>
       <c r="AH88" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI88" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ88" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK88" s="123" t="s">
         <v>3189</v>
       </c>
       <c r="AL88" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -57299,11 +57303,11 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>666.66739023666662</v>
+        <v>33.334177828333331</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
-        <v>1447.14</v>
+        <v>1688.99</v>
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
@@ -57315,7 +57319,7 @@
       </c>
       <c r="AT88" s="130" t="str">
         <f>"Ⓘ "&amp;AE88</f>
-        <v>Ⓘ Iraq</v>
+        <v>Ⓘ Senegal</v>
       </c>
     </row>
     <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -57330,11 +57334,11 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Iraq</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,3,FALSE)</f>
@@ -57346,11 +57350,11 @@
       </c>
       <c r="N89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
@@ -57444,7 +57448,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -57464,7 +57468,7 @@
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 1</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -57558,7 +57562,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -57578,7 +57582,7 @@
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>1 - 3</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
@@ -57716,7 +57720,7 @@
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
@@ -57888,6 +57892,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57903,36 +57937,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8312EC39-E6B5-4F35-8101-4825631F7CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA14AB1-F0AE-49E6-B8EB-568D2B32C034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="str" cm="1">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="141" t="str" cm="1">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="131">
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="132"/>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="131">
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44474,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44827,7 +44827,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45091,7 +45091,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45157,8 +45157,12 @@
         <f>AE74</f>
         <v>England</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="F28" s="19">
+        <v>4</v>
+      </c>
+      <c r="G28" s="20">
+        <v>2</v>
+      </c>
       <c r="H28" s="80" t="str">
         <f>AE75</f>
         <v>Croatia</v>
@@ -45197,11 +45201,11 @@
       </c>
       <c r="S28" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>England_win</v>
       </c>
       <c r="T28" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Croatia_lose</v>
       </c>
       <c r="U28" s="123">
         <f t="shared" si="8"/>
@@ -45231,9 +45235,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="123" t="str">
+      <c r="AB28" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD28" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR28))</f>
@@ -45362,7 +45366,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45412,8 +45416,12 @@
         <f>AE68</f>
         <v>Portugal</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
+      <c r="F29" s="19">
+        <v>1</v>
+      </c>
+      <c r="G29" s="20">
+        <v>1</v>
+      </c>
       <c r="H29" s="80" t="str">
         <f>AE69</f>
         <v>DR Congo</v>
@@ -45452,43 +45460,43 @@
       </c>
       <c r="S29" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Portugal_draw</v>
       </c>
       <c r="T29" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>DR Congo_draw</v>
       </c>
       <c r="U29" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="123" t="str">
+      <c r="AB29" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD29" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR29))</f>
@@ -45623,7 +45631,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45833,7 +45841,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45940,7 +45948,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46212,7 +46220,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46472,7 +46480,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46487,14 +46495,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46714,7 +46722,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46745,11 +46753,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46969,7 +46977,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47194,7 +47202,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47314,7 +47322,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47341,7 +47349,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47578,7 +47586,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47608,7 +47616,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47843,7 +47851,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48519,7 +48527,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48612,7 +48620,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="132"/>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48868,7 +48876,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48883,14 +48891,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49127,7 +49135,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49140,11 +49148,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49364,7 +49372,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49606,7 +49614,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49849,7 +49857,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49865,7 +49873,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49970,7 +49978,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49984,7 +49992,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50219,7 +50227,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="131">
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50472,7 +50480,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="132"/>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50732,7 +50740,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50987,7 +50995,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51191,7 +51199,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="131">
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51312,7 +51320,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51339,7 +51347,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51598,7 +51606,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52081,7 +52089,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52329,7 +52337,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52552,7 +52560,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52665,7 +52673,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52908,7 +52916,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53160,7 +53168,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53426,7 +53434,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53680,7 +53688,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53876,7 +53884,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53976,7 +53984,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54115,7 +54123,7 @@
       </c>
       <c r="AG68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_lose")</f>
@@ -54123,11 +54131,11 @@
       </c>
       <c r="AI68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE68,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE68,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL68" s="123">
         <f>AI68-AJ68</f>
@@ -54139,15 +54147,15 @@
       </c>
       <c r="AN68" s="123">
         <f>AF68*3+AG68</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO68" s="123">
         <f>AN68/AN72*10+BA68</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP68" s="123">
         <f>AO68*10000000+BI68*100+AM68/AM72*10+AI68/AI72*1++IF(AQ68=0,ROW(),AQ68)/2000000</f>
-        <v>8.8191499999999993E-4</v>
+        <v>59805923.801852785</v>
       </c>
       <c r="AQ68" s="126">
         <f>VLOOKUP(AE68,db_fifarank,2,FALSE)</f>
@@ -54155,7 +54163,7 @@
       </c>
       <c r="AR68" s="125">
         <f>AP68/AP72</f>
-        <v>8.8113791125899203E-4</v>
+        <v>0.99999998327924866</v>
       </c>
       <c r="AS68" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J69,"1K")</f>
@@ -54167,15 +54175,15 @@
       </c>
       <c r="AU68" s="126" cm="1">
         <f t="array" ref="AU68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV68" s="126" cm="1">
         <f t="array" ref="AV68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW68" s="126" cm="1">
         <f t="array" ref="AW68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX68" s="126">
         <f>AV68-AW68</f>
@@ -54187,11 +54195,11 @@
       </c>
       <c r="AZ68" s="126">
         <f>AT68/AT72*1000+AU68/AU72*100+AY68/AY72*10+AV68/AV72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA68" s="126">
         <f>AZ68/AZ72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB68" s="126" cm="1">
         <f t="array" ref="BB68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_win")*($X$7:$X$78))</f>
@@ -54199,15 +54207,15 @@
       </c>
       <c r="BC68" s="126" cm="1">
         <f t="array" ref="BC68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD68" s="126" cm="1">
         <f t="array" ref="BD68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE68" s="126" cm="1">
         <f t="array" ref="BE68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF68" s="126">
         <f>BD68-BE68</f>
@@ -54219,11 +54227,11 @@
       </c>
       <c r="BH68" s="126">
         <f>BB68/BB72*1000+BC68/BC72*100+BG68/BG72*10+BD68/BD72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI68" s="126">
         <f>BH68/BH72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK68" s="21"/>
       <c r="BL68" s="21"/>
@@ -54232,7 +54240,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54246,25 +54254,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54299,7 +54307,7 @@
       </c>
       <c r="K69" s="31">
         <f>L69+M69+N69</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="31">
         <f>VLOOKUP(1,AD68:AN71,3,FALSE)</f>
@@ -54307,7 +54315,7 @@
       </c>
       <c r="M69" s="31">
         <f>VLOOKUP(1,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" s="31">
         <f>VLOOKUP(1,AD68:AN71,5,FALSE)</f>
@@ -54315,11 +54323,11 @@
       </c>
       <c r="O69" s="31" t="str">
         <f>VLOOKUP(1,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P69" s="32">
         <f>L69*3+M69</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -54367,7 +54375,7 @@
       </c>
       <c r="AD69" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR69))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE69" s="124" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
@@ -54379,7 +54387,7 @@
       </c>
       <c r="AG69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_lose")</f>
@@ -54387,11 +54395,11 @@
       </c>
       <c r="AI69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE69,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE69,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL69" s="123">
         <f>AI69-AJ69</f>
@@ -54403,15 +54411,15 @@
       </c>
       <c r="AN69" s="123">
         <f>AF69*3+AG69</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO69" s="123">
         <f>AN69/AN72*10+BA69</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP69" s="123">
         <f>AO69*10000000+BI69*100+AM69/AM72*10+AI69/AI72*1++IF(AQ69=0,ROW(),AQ69)/2000000</f>
-        <v>7.391749999999999E-4</v>
+        <v>59805923.801710039</v>
       </c>
       <c r="AQ69" s="126">
         <f>VLOOKUP(AE69,db_fifarank,2,FALSE)</f>
@@ -54419,7 +54427,7 @@
       </c>
       <c r="AR69" s="125">
         <f>AP69/AP72</f>
-        <v>7.385236848844451E-4</v>
+        <v>0.99999998327686179</v>
       </c>
       <c r="AS69" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J70,"2K")</f>
@@ -54431,15 +54439,15 @@
       </c>
       <c r="AU69" s="126" cm="1">
         <f t="array" ref="AU69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV69" s="126" cm="1">
         <f t="array" ref="AV69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW69" s="126" cm="1">
         <f t="array" ref="AW69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX69" s="126">
         <f>AV69-AW69</f>
@@ -54451,11 +54459,11 @@
       </c>
       <c r="AZ69" s="126">
         <f>AT69/AT72*1000+AU69/AU72*100+AY69/AY72*10+AV69/AV72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA69" s="126">
         <f>AZ69/AZ72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB69" s="126" cm="1">
         <f t="array" ref="BB69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_win")*($X$7:$X$78))</f>
@@ -54463,15 +54471,15 @@
       </c>
       <c r="BC69" s="126" cm="1">
         <f t="array" ref="BC69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD69" s="126" cm="1">
         <f t="array" ref="BD69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE69" s="126" cm="1">
         <f t="array" ref="BE69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF69" s="126">
         <f>BD69-BE69</f>
@@ -54483,11 +54491,11 @@
       </c>
       <c r="BH69" s="126">
         <f>BB69/BB72*1000+BC69/BC72*100+BG69/BG72*10+BD69/BD72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI69" s="126">
         <f>BH69/BH72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK69" s="21" t="str" cm="1">
         <f t="array" ref="BK69">INDEX(T,24+MONTH(BP69),lang) &amp; " " &amp; DAY(BP69) &amp; ", " &amp; YEAR(BP69) &amp; "   " &amp; (IF(HOUR(BP69)&lt;10,0,"")&amp;HOUR(BP69)) &amp; ":" &amp;  (IF(MINUTE(BP69)&lt;10,0,"")&amp;MINUTE(BP69))</f>
@@ -54502,7 +54510,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54514,19 +54522,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54557,11 +54565,11 @@
       <c r="I70" s="69"/>
       <c r="J70" s="33" t="str">
         <f>VLOOKUP(2,AD68:AN71,2,FALSE)</f>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="K70" s="23">
         <f>L70+M70+N70</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="23">
         <f>VLOOKUP(2,AD68:AN71,3,FALSE)</f>
@@ -54569,7 +54577,7 @@
       </c>
       <c r="M70" s="23">
         <f>VLOOKUP(2,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" s="23">
         <f>VLOOKUP(2,AD68:AN71,5,FALSE)</f>
@@ -54577,11 +54585,11 @@
       </c>
       <c r="O70" s="23" t="str">
         <f>VLOOKUP(2,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P70" s="34">
         <f>L70*3+M70</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -54681,7 +54689,7 @@
       </c>
       <c r="AR70" s="125">
         <f>AP70/AP72</f>
-        <v>7.3202441668655794E-4</v>
+        <v>1.2250792917716104E-11</v>
       </c>
       <c r="AT70" s="126" cm="1">
         <f t="array" ref="AT70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($U$7:$U$78))</f>
@@ -54747,7 +54755,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54793,7 +54801,7 @@
       <c r="I71" s="69"/>
       <c r="J71" s="33" t="str">
         <f>VLOOKUP(3,AD68:AN71,2,FALSE)</f>
-        <v>DR Congo</v>
+        <v>Colombia</v>
       </c>
       <c r="K71" s="23">
         <f>L71+M71+N71</f>
@@ -54865,7 +54873,7 @@
       </c>
       <c r="AD71" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR71))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE71" s="124" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
@@ -54917,7 +54925,7 @@
       </c>
       <c r="AR71" s="125">
         <f>AP71/AP72</f>
-        <v>8.4579907710691335E-4</v>
+        <v>1.4154868481755742E-11</v>
       </c>
       <c r="AT71" s="126" cm="1">
         <f t="array" ref="AT71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($U$7:$U$78))</f>
@@ -54983,7 +54991,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -55102,7 +55110,7 @@
       </c>
       <c r="AG72" s="123">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH72" s="123">
         <f t="shared" si="35"/>
@@ -55110,7 +55118,7 @@
       </c>
       <c r="AI72" s="123">
         <f>MAX(AI68:AI71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL72" s="123">
         <f>MIN(AL68:AL71)</f>
@@ -55122,15 +55130,15 @@
       </c>
       <c r="AN72" s="123">
         <f>MAX(AN68:AN71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO72" s="123">
         <f>MAX(AO68:AO71)+1</f>
-        <v>1</v>
+        <v>6.9805825242718447</v>
       </c>
       <c r="AP72" s="123">
         <f>MAX(AP68:AP71)+1</f>
-        <v>1.0008819149999999</v>
+        <v>59805924.801852785</v>
       </c>
       <c r="AT72" s="126">
         <f>MAX(AT68:AT71)-MIN(AT68:AT71)+1</f>
@@ -55138,15 +55146,15 @@
       </c>
       <c r="AU72" s="126">
         <f>MAX(AU68:AU71)-MIN(AU68:AU71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV72" s="126">
         <f>MAX(AV68:AV71)-MIN(AV68:AV71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW72" s="126">
         <f>MAX(AW68:AW71)-MIN(AW68:AW71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY72" s="126">
         <f>MAX(AY68:AY71)-MIN(AY68:AY71)+1</f>
@@ -55154,7 +55162,7 @@
       </c>
       <c r="AZ72" s="126">
         <f>MAX(AZ68:AZ71)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB72" s="126">
         <f>MAX(BB68:BB71)-MIN(BB68:BB71)+1</f>
@@ -55162,15 +55170,15 @@
       </c>
       <c r="BC72" s="126">
         <f>MAX(BC68:BC71)-MIN(BC68:BC71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD72" s="126">
         <f>MAX(BD68:BD71)-MIN(BD68:BD71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE72" s="126">
         <f>MAX(BE68:BE71)-MIN(BE68:BE71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG72" s="126">
         <f>MAX(BG68:BG71)-MIN(BG68:BG71)+1</f>
@@ -55178,7 +55186,7 @@
       </c>
       <c r="BH72" s="126">
         <f>MAX(BH68:BH71)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="73" spans="1:95" x14ac:dyDescent="0.25">
@@ -55369,7 +55377,7 @@
       </c>
       <c r="AF74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_draw")</f>
@@ -55381,31 +55389,31 @@
       </c>
       <c r="AI74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE74,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE74,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL74" s="123">
         <f>AI74-AJ74</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM74" s="123">
         <f>AL74-AL78</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN74" s="123">
         <f>AF74*3+AG74</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO74" s="123">
         <f>AN74/AN78*10+BA74</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP74" s="123">
         <f>AO74*10000000+BI74*100+AM74/AM78*10+AI74/AI78*1++IF(AQ74=0,ROW(),AQ74)/2000000</f>
-        <v>9.1298500000000006E-4</v>
+        <v>75000008.800912976</v>
       </c>
       <c r="AQ74" s="126">
         <f>VLOOKUP(AE74,db_fifarank,2,FALSE)</f>
@@ -55413,7 +55421,7 @@
       </c>
       <c r="AR74" s="125">
         <f>AP74/AP78</f>
-        <v>9.1215221870660421E-4</v>
+        <v>0.99999998666666845</v>
       </c>
       <c r="AS74" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J75,"1L")</f>
@@ -55517,11 +55525,11 @@
       </c>
       <c r="K75" s="31">
         <f>L75+M75+N75</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="31">
         <f>VLOOKUP(1,AD74:AN77,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="31">
         <f>VLOOKUP(1,AD74:AN77,4,FALSE)</f>
@@ -55533,11 +55541,11 @@
       </c>
       <c r="O75" s="31" t="str">
         <f>VLOOKUP(1,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>4 - 2</v>
       </c>
       <c r="P75" s="32">
         <f>L75*3+M75</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R75" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -55585,7 +55593,7 @@
       </c>
       <c r="AD75" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR75))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE75" s="124" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
@@ -55601,19 +55609,19 @@
       </c>
       <c r="AH75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE75,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE75,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL75" s="123">
         <f>AI75-AJ75</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM75" s="123">
         <f>AL75-AL78</f>
@@ -55629,7 +55637,7 @@
       </c>
       <c r="AP75" s="123">
         <f>AO75*10000000+BI75*100+AM75/AM78*10+AI75/AI78*1++IF(AQ75=0,ROW(),AQ75)/2000000</f>
-        <v>8.5853500000000001E-4</v>
+        <v>0.40085853500000002</v>
       </c>
       <c r="AQ75" s="126">
         <f>VLOOKUP(AE75,db_fifarank,2,FALSE)</f>
@@ -55637,7 +55645,7 @@
       </c>
       <c r="AR75" s="125">
         <f>AP75/AP78</f>
-        <v>8.5775188539491268E-4</v>
+        <v>5.3447797682170484E-9</v>
       </c>
       <c r="AS75" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J76,"2L")</f>
@@ -55737,7 +55745,7 @@
       <c r="I76" s="69"/>
       <c r="J76" s="33" t="str">
         <f>VLOOKUP(2,AD74:AN77,2,FALSE)</f>
-        <v>Croatia</v>
+        <v>Panama</v>
       </c>
       <c r="K76" s="23">
         <f>L76+M76+N76</f>
@@ -55809,7 +55817,7 @@
       </c>
       <c r="AD76" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR76))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE76" s="124" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
@@ -55841,7 +55849,7 @@
       </c>
       <c r="AM76" s="123">
         <f>AL76-AL78</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN76" s="123">
         <f>AF76*3+AG76</f>
@@ -55853,7 +55861,7 @@
       </c>
       <c r="AP76" s="123">
         <f>AO76*10000000+BI76*100+AM76/AM78*10+AI76/AI78*1++IF(AQ76=0,ROW(),AQ76)/2000000</f>
-        <v>6.7315499999999993E-4</v>
+        <v>4.0006731550000003</v>
       </c>
       <c r="AQ76" s="126">
         <f>VLOOKUP(AE76,db_fifarank,2,FALSE)</f>
@@ -55861,7 +55869,7 @@
       </c>
       <c r="AR76" s="125">
         <f>AP76/AP78</f>
-        <v>6.7254098017321647E-4</v>
+        <v>5.3342301762623238E-8</v>
       </c>
       <c r="AT76" s="126" cm="1">
         <f t="array" ref="AT76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($U$7:$U$78))</f>
@@ -55957,7 +55965,7 @@
       <c r="I77" s="69"/>
       <c r="J77" s="33" t="str">
         <f>VLOOKUP(3,AD74:AN77,2,FALSE)</f>
-        <v>Panama</v>
+        <v>Ghana</v>
       </c>
       <c r="K77" s="23">
         <f>L77+M77+N77</f>
@@ -56029,7 +56037,7 @@
       </c>
       <c r="AD77" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR77))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE77" s="124" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
@@ -56061,7 +56069,7 @@
       </c>
       <c r="AM77" s="123">
         <f>AL77-AL78</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN77" s="123">
         <f>AF77*3+AG77</f>
@@ -56073,7 +56081,7 @@
       </c>
       <c r="AP77" s="123">
         <f>AO77*10000000+BI77*100+AM77/AM78*10+AI77/AI78*1++IF(AQ77=0,ROW(),AQ77)/2000000</f>
-        <v>7.7032000000000001E-4</v>
+        <v>4.00077032</v>
       </c>
       <c r="AQ77" s="126">
         <f>VLOOKUP(AE77,db_fifarank,2,FALSE)</f>
@@ -56081,7 +56089,7 @@
       </c>
       <c r="AR77" s="125">
         <f>AP77/AP78</f>
-        <v>7.6961735090288596E-4</v>
+        <v>5.3343597295787265E-8</v>
       </c>
       <c r="AT77" s="126" cm="1">
         <f t="array" ref="AT77">SUMPRODUCT(($S$7:$S$78=AE77&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE77&amp;"_win")*($U$7:$U$78))</f>
@@ -56177,11 +56185,11 @@
       <c r="I78" s="69"/>
       <c r="J78" s="35" t="str">
         <f>VLOOKUP(4,AD74:AN77,2,FALSE)</f>
-        <v>Ghana</v>
+        <v>Croatia</v>
       </c>
       <c r="K78" s="36">
         <f>L78+M78+N78</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="36">
         <f>VLOOKUP(4,AD74:AN77,3,FALSE)</f>
@@ -56193,11 +56201,11 @@
       </c>
       <c r="N78" s="36">
         <f>VLOOKUP(4,AD74:AN77,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" s="36" t="str">
         <f>VLOOKUP(4,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 4</v>
       </c>
       <c r="P78" s="37">
         <f>L78*3+M78</f>
@@ -56249,7 +56257,7 @@
       </c>
       <c r="AF78" s="123">
         <f t="shared" ref="AF78:AH78" si="36">MAX(AF74:AF77)-MIN(AF74:AF77)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG78" s="123">
         <f t="shared" si="36"/>
@@ -56257,31 +56265,31 @@
       </c>
       <c r="AH78" s="123">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI78" s="123">
         <f>MAX(AI74:AI77)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL78" s="123">
         <f>MIN(AL74:AL77)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM78" s="123">
         <f>MAX(AM74:AM77)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN78" s="123">
         <f>MAX(AN74:AN77)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO78" s="123">
         <f>MAX(AO74:AO77)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP78" s="123">
         <f>MAX(AP74:AP77)+1</f>
-        <v>1.000912985</v>
+        <v>75000009.800912976</v>
       </c>
       <c r="AT78" s="126">
         <f>MAX(AT74:AT77)-MIN(AT74:AT77)+1</f>
@@ -56659,13 +56667,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56763,11 +56771,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56877,11 +56885,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -56991,16 +56999,16 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓚ Colombia</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57105,16 +57113,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓛ Ghana</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57219,11 +57227,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57496,11 +57504,11 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
-        <v>DR Congo</v>
+        <v>Colombia</v>
       </c>
       <c r="AF90" s="123">
         <f t="shared" si="39"/>
@@ -57539,11 +57547,11 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>666.66740584166666</v>
+        <v>666.66751321166657</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
-        <v>1478.35</v>
+        <v>1693.09</v>
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
@@ -57551,11 +57559,11 @@
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>DR Congo</v>
+        <v>Colombia</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓚ Colombia</v>
       </c>
     </row>
     <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57610,11 +57618,11 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
-        <v>Panama</v>
+        <v>Ghana</v>
       </c>
       <c r="AF91" s="123">
         <f t="shared" si="39"/>
@@ -57653,11 +57661,11 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>666.66743698666664</v>
+        <v>666.66733982166659</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
-        <v>1540.64</v>
+        <v>1346.31</v>
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
@@ -57665,11 +57673,11 @@
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Panama</v>
+        <v>Ghana</v>
       </c>
       <c r="AT91" s="130" t="str">
         <f>"Ⓛ "&amp;AE91</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓛ Ghana</v>
       </c>
     </row>
     <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57900,6 +57908,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57915,36 +57953,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA14AB1-F0AE-49E6-B8EB-568D2B32C034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0A3F42-F085-480C-9D6C-1FC783BF04E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="str" cm="1">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="str" cm="1">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44474,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44827,7 +44827,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -44889,8 +44889,12 @@
         <f>AE76</f>
         <v>Ghana</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="F27" s="19">
+        <v>1</v>
+      </c>
+      <c r="G27" s="20">
+        <v>0</v>
+      </c>
       <c r="H27" s="80" t="str">
         <f>AE77</f>
         <v>Panama</v>
@@ -44929,11 +44933,11 @@
       </c>
       <c r="S27" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Ghana_win</v>
       </c>
       <c r="T27" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Panama_lose</v>
       </c>
       <c r="U27" s="123">
         <f t="shared" si="8"/>
@@ -44963,9 +44967,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="123" t="str">
+      <c r="AB27" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD27" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR27))</f>
@@ -45091,7 +45095,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45366,7 +45370,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45631,7 +45635,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45679,8 +45683,12 @@
         <f>AE70</f>
         <v>Uzbekistan</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="F30" s="19">
+        <v>1</v>
+      </c>
+      <c r="G30" s="20">
+        <v>3</v>
+      </c>
       <c r="H30" s="80" t="str">
         <f>AE71</f>
         <v>Colombia</v>
@@ -45719,11 +45727,11 @@
       </c>
       <c r="S30" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Uzbekistan_lose</v>
       </c>
       <c r="T30" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Colombia_win</v>
       </c>
       <c r="U30" s="123">
         <f t="shared" si="8"/>
@@ -45753,9 +45761,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="123" t="str">
+      <c r="AB30" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF30" s="123">
         <f t="shared" ref="AF30:AH30" si="15">MAX(AF26:AF29)-MIN(AF26:AF29)+1</f>
@@ -45841,7 +45849,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45948,7 +45956,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46220,7 +46228,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46480,7 +46488,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46495,14 +46503,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46722,7 +46730,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46753,11 +46761,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46977,7 +46985,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47202,7 +47210,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47322,7 +47330,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47349,7 +47357,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47586,7 +47594,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47616,7 +47624,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47851,7 +47859,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48527,7 +48535,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48620,7 +48628,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48876,7 +48884,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48891,14 +48899,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49135,7 +49143,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49148,11 +49156,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49372,7 +49380,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="141">
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49614,7 +49622,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="142"/>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49857,7 +49865,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49873,7 +49881,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49978,7 +49986,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -49992,7 +50000,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50227,7 +50235,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50480,7 +50488,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50740,7 +50748,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50995,7 +51003,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51199,7 +51207,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51320,7 +51328,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51347,7 +51355,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51606,7 +51614,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52089,7 +52097,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52337,7 +52345,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52560,7 +52568,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52673,7 +52681,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52916,7 +52924,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53168,7 +53176,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53434,7 +53442,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53688,7 +53696,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53884,7 +53892,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53984,7 +53992,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54111,7 +54119,7 @@
       </c>
       <c r="AD68" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR68))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE68" s="124" t="str">
         <f>VLOOKUP("Portugal",T,lang,FALSE)</f>
@@ -54143,7 +54151,7 @@
       </c>
       <c r="AM68" s="123">
         <f>AL68-AL72</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN68" s="123">
         <f>AF68*3+AG68</f>
@@ -54151,11 +54159,11 @@
       </c>
       <c r="AO68" s="123">
         <f>AN68/AN72*10+BA68</f>
-        <v>5.9805825242718447</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP68" s="123">
         <f>AO68*10000000+BI68*100+AM68/AM72*10+AI68/AI72*1++IF(AQ68=0,ROW(),AQ68)/2000000</f>
-        <v>59805923.801852785</v>
+        <v>34805927.551852785</v>
       </c>
       <c r="AQ68" s="126">
         <f>VLOOKUP(AE68,db_fifarank,2,FALSE)</f>
@@ -54163,7 +54171,7 @@
       </c>
       <c r="AR68" s="125">
         <f>AP68/AP72</f>
-        <v>0.99999998327924866</v>
+        <v>0.46407897368919898</v>
       </c>
       <c r="AS68" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J69,"1K")</f>
@@ -54240,7 +54248,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54254,25 +54262,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54303,7 +54311,7 @@
       <c r="I69" s="69"/>
       <c r="J69" s="30" t="str">
         <f>VLOOKUP(1,AD68:AN71,2,FALSE)</f>
-        <v>Portugal</v>
+        <v>Colombia</v>
       </c>
       <c r="K69" s="31">
         <f>L69+M69+N69</f>
@@ -54311,11 +54319,11 @@
       </c>
       <c r="L69" s="31">
         <f>VLOOKUP(1,AD68:AN71,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="31">
         <f>VLOOKUP(1,AD68:AN71,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" s="31">
         <f>VLOOKUP(1,AD68:AN71,5,FALSE)</f>
@@ -54323,11 +54331,11 @@
       </c>
       <c r="O69" s="31" t="str">
         <f>VLOOKUP(1,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD68:AN71,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>3 - 1</v>
       </c>
       <c r="P69" s="32">
         <f>L69*3+M69</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R69" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -54375,7 +54383,7 @@
       </c>
       <c r="AD69" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR69))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE69" s="124" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
@@ -54407,7 +54415,7 @@
       </c>
       <c r="AM69" s="123">
         <f>AL69-AL72</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN69" s="123">
         <f>AF69*3+AG69</f>
@@ -54415,11 +54423,11 @@
       </c>
       <c r="AO69" s="123">
         <f>AN69/AN72*10+BA69</f>
-        <v>5.9805825242718447</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP69" s="123">
         <f>AO69*10000000+BI69*100+AM69/AM72*10+AI69/AI72*1++IF(AQ69=0,ROW(),AQ69)/2000000</f>
-        <v>59805923.801710039</v>
+        <v>34805927.551710039</v>
       </c>
       <c r="AQ69" s="126">
         <f>VLOOKUP(AE69,db_fifarank,2,FALSE)</f>
@@ -54427,7 +54435,7 @@
       </c>
       <c r="AR69" s="125">
         <f>AP69/AP72</f>
-        <v>0.99999998327686179</v>
+        <v>0.46407897368729573</v>
       </c>
       <c r="AS69" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J70,"2K")</f>
@@ -54510,7 +54518,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54522,19 +54530,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54565,7 +54573,7 @@
       <c r="I70" s="69"/>
       <c r="J70" s="33" t="str">
         <f>VLOOKUP(2,AD68:AN71,2,FALSE)</f>
-        <v>DR Congo</v>
+        <v>Portugal</v>
       </c>
       <c r="K70" s="23">
         <f>L70+M70+N70</f>
@@ -54653,19 +54661,19 @@
       </c>
       <c r="AH70" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE70 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE70,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE70,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL70" s="123">
         <f>AI70-AJ70</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM70" s="123">
         <f>AL70-AL72</f>
@@ -54681,7 +54689,7 @@
       </c>
       <c r="AP70" s="123">
         <f>AO70*10000000+BI70*100+AM70/AM72*10+AI70/AI72*1++IF(AQ70=0,ROW(),AQ70)/2000000</f>
-        <v>7.3266999999999994E-4</v>
+        <v>0.25073266999999999</v>
       </c>
       <c r="AQ70" s="126">
         <f>VLOOKUP(AE70,db_fifarank,2,FALSE)</f>
@@ -54689,7 +54697,7 @@
       </c>
       <c r="AR70" s="125">
         <f>AP70/AP72</f>
-        <v>1.2250792917716104E-11</v>
+        <v>3.3431018320256936E-9</v>
       </c>
       <c r="AT70" s="126" cm="1">
         <f t="array" ref="AT70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($U$7:$U$78))</f>
@@ -54755,7 +54763,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54801,11 +54809,11 @@
       <c r="I71" s="69"/>
       <c r="J71" s="33" t="str">
         <f>VLOOKUP(3,AD68:AN71,2,FALSE)</f>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="K71" s="23">
         <f>L71+M71+N71</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="23">
         <f>VLOOKUP(3,AD68:AN71,3,FALSE)</f>
@@ -54813,7 +54821,7 @@
       </c>
       <c r="M71" s="23">
         <f>VLOOKUP(3,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" s="23">
         <f>VLOOKUP(3,AD68:AN71,5,FALSE)</f>
@@ -54821,11 +54829,11 @@
       </c>
       <c r="O71" s="23" t="str">
         <f>VLOOKUP(3,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P71" s="34">
         <f>L71*3+M71</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="123">
         <f>DATE(2026,6,26)+TIME(13,0,0)+gmt_delta</f>
@@ -54873,7 +54881,7 @@
       </c>
       <c r="AD71" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR71))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE71" s="124" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
@@ -54881,7 +54889,7 @@
       </c>
       <c r="AF71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_draw")</f>
@@ -54893,31 +54901,31 @@
       </c>
       <c r="AI71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE71,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE71,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL71" s="123">
         <f>AI71-AJ71</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM71" s="123">
         <f>AL71-AL72</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN71" s="123">
         <f>AF71*3+AG71</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO71" s="123">
         <f>AN71/AN72*10+BA71</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP71" s="123">
         <f>AO71*10000000+BI71*100+AM71/AM72*10+AI71/AI72*1++IF(AQ71=0,ROW(),AQ71)/2000000</f>
-        <v>8.4654499999999998E-4</v>
+        <v>75000008.75084655</v>
       </c>
       <c r="AQ71" s="126">
         <f>VLOOKUP(AE71,db_fifarank,2,FALSE)</f>
@@ -54925,7 +54933,7 @@
       </c>
       <c r="AR71" s="125">
         <f>AP71/AP72</f>
-        <v>1.4154868481755742E-11</v>
+        <v>0.99999998666666845</v>
       </c>
       <c r="AT71" s="126" cm="1">
         <f t="array" ref="AT71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($U$7:$U$78))</f>
@@ -54991,7 +54999,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -55038,7 +55046,7 @@
       </c>
       <c r="K72" s="36">
         <f>L72+M72+N72</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="36">
         <f>VLOOKUP(4,AD68:AN71,3,FALSE)</f>
@@ -55050,11 +55058,11 @@
       </c>
       <c r="N72" s="36">
         <f>VLOOKUP(4,AD68:AN71,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" s="36" t="str">
         <f>VLOOKUP(4,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 3</v>
       </c>
       <c r="P72" s="37">
         <f>L72*3+M72</f>
@@ -55106,7 +55114,7 @@
       </c>
       <c r="AF72" s="123">
         <f t="shared" ref="AF72:AH72" si="35">MAX(AF68:AF71)-MIN(AF68:AF71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG72" s="123">
         <f t="shared" si="35"/>
@@ -55114,31 +55122,31 @@
       </c>
       <c r="AH72" s="123">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI72" s="123">
         <f>MAX(AI68:AI71)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL72" s="123">
         <f>MIN(AL68:AL71)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM72" s="123">
         <f>MAX(AM68:AM71)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN72" s="123">
         <f>MAX(AN68:AN71)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO72" s="123">
         <f>MAX(AO68:AO71)+1</f>
-        <v>6.9805825242718447</v>
+        <v>8.5</v>
       </c>
       <c r="AP72" s="123">
         <f>MAX(AP68:AP71)+1</f>
-        <v>59805924.801852785</v>
+        <v>75000009.75084655</v>
       </c>
       <c r="AT72" s="126">
         <f>MAX(AT68:AT71)-MIN(AT68:AT71)+1</f>
@@ -55745,15 +55753,15 @@
       <c r="I76" s="69"/>
       <c r="J76" s="33" t="str">
         <f>VLOOKUP(2,AD74:AN77,2,FALSE)</f>
-        <v>Panama</v>
+        <v>Ghana</v>
       </c>
       <c r="K76" s="23">
         <f>L76+M76+N76</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="23">
         <f>VLOOKUP(2,AD74:AN77,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="23">
         <f>VLOOKUP(2,AD74:AN77,4,FALSE)</f>
@@ -55765,11 +55773,11 @@
       </c>
       <c r="O76" s="23" t="str">
         <f>VLOOKUP(2,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 0</v>
       </c>
       <c r="P76" s="34">
         <f>L76*3+M76</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R76" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -55817,7 +55825,7 @@
       </c>
       <c r="AD76" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR76))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE76" s="124" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
@@ -55825,7 +55833,7 @@
       </c>
       <c r="AF76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_draw")</f>
@@ -55837,7 +55845,7 @@
       </c>
       <c r="AI76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE76,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE76,$F$7:$F$78)</f>
@@ -55845,23 +55853,23 @@
       </c>
       <c r="AL76" s="123">
         <f>AI76-AJ76</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM76" s="123">
         <f>AL76-AL78</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN76" s="123">
         <f>AF76*3+AG76</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO76" s="123">
         <f>AN76/AN78*10+BA76</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP76" s="123">
         <f>AO76*10000000+BI76*100+AM76/AM78*10+AI76/AI78*1++IF(AQ76=0,ROW(),AQ76)/2000000</f>
-        <v>4.0006731550000003</v>
+        <v>75000006.200673163</v>
       </c>
       <c r="AQ76" s="126">
         <f>VLOOKUP(AE76,db_fifarank,2,FALSE)</f>
@@ -55869,7 +55877,7 @@
       </c>
       <c r="AR76" s="125">
         <f>AP76/AP78</f>
-        <v>5.3342301762623238E-8</v>
+        <v>0.9999999519968088</v>
       </c>
       <c r="AT76" s="126" cm="1">
         <f t="array" ref="AT76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($U$7:$U$78))</f>
@@ -55965,11 +55973,11 @@
       <c r="I77" s="69"/>
       <c r="J77" s="33" t="str">
         <f>VLOOKUP(3,AD74:AN77,2,FALSE)</f>
-        <v>Ghana</v>
+        <v>Panama</v>
       </c>
       <c r="K77" s="23">
         <f>L77+M77+N77</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="23">
         <f>VLOOKUP(3,AD74:AN77,3,FALSE)</f>
@@ -55981,11 +55989,11 @@
       </c>
       <c r="N77" s="23">
         <f>VLOOKUP(3,AD74:AN77,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" s="23" t="str">
         <f>VLOOKUP(3,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 1</v>
       </c>
       <c r="P77" s="34">
         <f>L77*3+M77</f>
@@ -56037,7 +56045,7 @@
       </c>
       <c r="AD77" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR77))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE77" s="124" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
@@ -56053,7 +56061,7 @@
       </c>
       <c r="AH77" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE77 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE77,$G$7:$G$78)</f>
@@ -56061,15 +56069,15 @@
       </c>
       <c r="AJ77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE77,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL77" s="123">
         <f>AI77-AJ77</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM77" s="123">
         <f>AL77-AL78</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN77" s="123">
         <f>AF77*3+AG77</f>
@@ -56081,7 +56089,7 @@
       </c>
       <c r="AP77" s="123">
         <f>AO77*10000000+BI77*100+AM77/AM78*10+AI77/AI78*1++IF(AQ77=0,ROW(),AQ77)/2000000</f>
-        <v>4.00077032</v>
+        <v>2.00077032</v>
       </c>
       <c r="AQ77" s="126">
         <f>VLOOKUP(AE77,db_fifarank,2,FALSE)</f>
@@ -56089,7 +56097,7 @@
       </c>
       <c r="AR77" s="125">
         <f>AP77/AP78</f>
-        <v>5.3343597295787265E-8</v>
+        <v>2.6676934113889205E-8</v>
       </c>
       <c r="AT77" s="126" cm="1">
         <f t="array" ref="AT77">SUMPRODUCT(($S$7:$S$78=AE77&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE77&amp;"_win")*($U$7:$U$78))</f>
@@ -56398,7 +56406,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56500,7 +56508,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -56667,13 +56675,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56771,16 +56779,16 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56820,7 +56828,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56871,11 +56879,11 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABC</v>
+        <v>ABCE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Ecuador</v>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
@@ -56885,16 +56893,16 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Spain</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56914,7 +56922,7 @@
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
@@ -56985,7 +56993,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCF</v>
+        <v>ABCEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56999,20 +57007,20 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ Colombia</v>
+        <v>Ⓗ Spain</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
@@ -57020,7 +57028,7 @@
       </c>
       <c r="M86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
@@ -57032,7 +57040,7 @@
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" s="123">
         <f>DATE(2026,12,4)+TIME(8,0,0)+gmt_delta</f>
@@ -57099,7 +57107,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFG</v>
+        <v>ABCEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57113,20 +57121,20 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Ghana</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,3,FALSE)</f>
@@ -57138,11 +57146,11 @@
       </c>
       <c r="N87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
@@ -57162,7 +57170,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -57213,7 +57221,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGH</v>
+        <v>ABCEFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57227,16 +57235,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57256,7 +57264,7 @@
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 1</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
@@ -57327,7 +57335,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGH</v>
+        <v>ABCEFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57350,7 +57358,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57441,7 +57449,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGH</v>
+        <v>ABCEFGH</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57504,11 +57512,11 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="AF90" s="123">
         <f t="shared" si="39"/>
@@ -57516,7 +57524,7 @@
       </c>
       <c r="AG90" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH90" s="123">
         <f t="shared" si="40"/>
@@ -57524,11 +57532,11 @@
       </c>
       <c r="AI90" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ90" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK90" s="123" t="s">
         <v>3191</v>
@@ -57543,27 +57551,27 @@
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>666.66751321166657</v>
+        <v>5700.0007391749996</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
-        <v>1693.09</v>
+        <v>1478.35</v>
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGHK</v>
+        <v>ABCEFGHK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
-        <v>Ⓚ Colombia</v>
+        <v>Ⓚ DR Congo</v>
       </c>
     </row>
     <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57618,11 +57626,11 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
-        <v>Ghana</v>
+        <v>Panama</v>
       </c>
       <c r="AF91" s="123">
         <f t="shared" si="39"/>
@@ -57634,7 +57642,7 @@
       </c>
       <c r="AH91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,5,FALSE)</f>
@@ -57642,18 +57650,18 @@
       </c>
       <c r="AJ91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK91" s="123" t="s">
         <v>3192</v>
       </c>
       <c r="AL91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57661,23 +57669,23 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>666.66733982166659</v>
+        <v>333.33410365333333</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
-        <v>1346.31</v>
+        <v>1540.64</v>
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGHKL</v>
+        <v>ABCEFGHK</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Ghana</v>
+        <v/>
       </c>
       <c r="AT91" s="130" t="str">
         <f>"Ⓛ "&amp;AE91</f>
-        <v>Ⓛ Ghana</v>
+        <v>Ⓛ Panama</v>
       </c>
     </row>
     <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57908,11 +57916,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57928,31 +57956,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -58995,11 +59003,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ABCFGHKL</v>
+        <v>ABCEFGHK</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -59027,7 +59035,7 @@
       </c>
       <c r="J3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,8,FALSE)</f>
-        <v>3L</v>
+        <v>3E</v>
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haavas\git\VM2026\fasit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A71133-A3E6-461B-9315-DAE7F4FC0512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBD9F3F-2C05-4304-85E6-31F2CD5A1440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="17180" windowHeight="18490" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -22542,13 +22542,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP157"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="42" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>207</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>245</v>
       </c>
@@ -23444,7 +23444,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -23572,7 +23572,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>312</v>
       </c>
@@ -23700,7 +23700,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>341</v>
       </c>
@@ -23828,7 +23828,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>370</v>
       </c>
@@ -23956,7 +23956,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>393</v>
       </c>
@@ -24084,7 +24084,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>342</v>
       </c>
@@ -24212,7 +24212,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>433</v>
       </c>
@@ -24340,7 +24340,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>471</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>498</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>527</v>
       </c>
@@ -24724,7 +24724,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>558</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>592</v>
       </c>
@@ -24980,7 +24980,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>626</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>660</v>
       </c>
@@ -25236,7 +25236,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>693</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>725</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>750</v>
       </c>
@@ -25620,7 +25620,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>559</v>
       </c>
@@ -25748,7 +25748,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>794</v>
       </c>
@@ -25876,7 +25876,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>818</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>843</v>
       </c>
@@ -26132,7 +26132,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>871</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>898</v>
       </c>
@@ -26388,7 +26388,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>925</v>
       </c>
@@ -26516,7 +26516,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>949</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>973</v>
       </c>
@@ -26772,7 +26772,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>997</v>
       </c>
@@ -26900,7 +26900,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1024</v>
       </c>
@@ -27028,7 +27028,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1058</v>
       </c>
@@ -27156,7 +27156,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1077</v>
       </c>
@@ -27284,7 +27284,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1093</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1113</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1148</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1180</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1198</v>
       </c>
@@ -27924,7 +27924,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1237</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1264</v>
       </c>
@@ -28180,7 +28180,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1285</v>
       </c>
@@ -28308,7 +28308,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1323</v>
       </c>
@@ -28436,7 +28436,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1349</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1384</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1419</v>
       </c>
@@ -28820,7 +28820,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1449</v>
       </c>
@@ -28948,7 +28948,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1479</v>
       </c>
@@ -29076,7 +29076,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1508</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1544</v>
       </c>
@@ -29332,7 +29332,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1565</v>
       </c>
@@ -29460,7 +29460,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1604</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1633</v>
       </c>
@@ -29716,7 +29716,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1662</v>
       </c>
@@ -29844,7 +29844,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1677</v>
       </c>
@@ -29972,7 +29972,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1703</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1739</v>
       </c>
@@ -30228,7 +30228,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1770</v>
       </c>
@@ -30356,7 +30356,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1798</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1836</v>
       </c>
@@ -30612,7 +30612,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1858</v>
       </c>
@@ -30740,7 +30740,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1883</v>
       </c>
@@ -30868,7 +30868,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1900</v>
       </c>
@@ -30996,7 +30996,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1920</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1958</v>
       </c>
@@ -31252,7 +31252,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1995</v>
       </c>
@@ -31380,7 +31380,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2033</v>
       </c>
@@ -31508,7 +31508,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2072</v>
       </c>
@@ -31636,7 +31636,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2090</v>
       </c>
@@ -31764,7 +31764,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2126</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2146</v>
       </c>
@@ -32020,7 +32020,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2183</v>
       </c>
@@ -32148,7 +32148,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2201</v>
       </c>
@@ -32276,7 +32276,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>2240</v>
       </c>
@@ -32404,7 +32404,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2274</v>
       </c>
@@ -32532,7 +32532,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2304</v>
       </c>
@@ -32660,7 +32660,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>2340</v>
       </c>
@@ -32788,7 +32788,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>2375</v>
       </c>
@@ -32916,7 +32916,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>2395</v>
       </c>
@@ -33044,7 +33044,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>2426</v>
       </c>
@@ -33172,7 +33172,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>2458</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>2493</v>
       </c>
@@ -33428,7 +33428,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>2524</v>
       </c>
@@ -33556,7 +33556,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>2549</v>
       </c>
@@ -33684,7 +33684,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>2573</v>
       </c>
@@ -33812,7 +33812,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>2600</v>
       </c>
@@ -33940,7 +33940,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>2616</v>
       </c>
@@ -34068,7 +34068,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>2622</v>
       </c>
@@ -34196,7 +34196,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>2628</v>
       </c>
@@ -34324,7 +34324,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>2634</v>
       </c>
@@ -34452,7 +34452,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>2640</v>
       </c>
@@ -34580,7 +34580,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>2648</v>
       </c>
@@ -34708,7 +34708,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>2656</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>2663</v>
       </c>
@@ -34964,7 +34964,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>2670</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2677</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2684</v>
       </c>
@@ -35348,7 +35348,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>2691</v>
       </c>
@@ -35476,7 +35476,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>2698</v>
       </c>
@@ -35604,7 +35604,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>2706</v>
       </c>
@@ -35732,7 +35732,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>2714</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>2721</v>
       </c>
@@ -35988,7 +35988,7 @@
         <v>2726</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2727</v>
       </c>
@@ -36116,7 +36116,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2747</v>
       </c>
@@ -36244,7 +36244,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>2767</v>
       </c>
@@ -36372,7 +36372,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>2787</v>
       </c>
@@ -36500,7 +36500,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>2807</v>
       </c>
@@ -36628,7 +36628,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>2827</v>
       </c>
@@ -36756,7 +36756,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>2847</v>
       </c>
@@ -36884,7 +36884,7 @@
         <v>2866</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>2867</v>
       </c>
@@ -37012,7 +37012,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>2887</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>2907</v>
       </c>
@@ -37268,7 +37268,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2927</v>
       </c>
@@ -37396,7 +37396,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>2947</v>
       </c>
@@ -37524,7 +37524,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>2967</v>
       </c>
@@ -37652,7 +37652,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2987</v>
       </c>
@@ -37780,7 +37780,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2977</v>
       </c>
@@ -37908,7 +37908,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>2997</v>
       </c>
@@ -38036,7 +38036,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>3033</v>
       </c>
@@ -38164,43 +38164,43 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>3074</v>
       </c>
@@ -38337,22 +38337,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA72"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.1796875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="10"/>
-    <col min="5" max="5" width="1.1796875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="10"/>
-    <col min="7" max="7" width="27.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="1.1796875" style="10" customWidth="1"/>
-    <col min="10" max="16384" width="9.1796875" style="10"/>
+    <col min="1" max="1" width="1.140625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="10"/>
+    <col min="5" max="5" width="1.140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="10"/>
+    <col min="7" max="7" width="27.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="1.140625" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:27" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="39" t="s">
         <v>3115</v>
       </c>
@@ -38364,7 +38364,7 @@
       <c r="G2" s="40"/>
       <c r="H2" s="41"/>
     </row>
-    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="42"/>
       <c r="C3" s="43"/>
       <c r="D3" s="44"/>
@@ -38372,7 +38372,7 @@
       <c r="G3" s="43"/>
       <c r="H3" s="44"/>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
         <v>3117</v>
       </c>
@@ -38384,7 +38384,7 @@
       <c r="G4" s="45"/>
       <c r="H4" s="44"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B5" s="42"/>
       <c r="C5" s="43"/>
       <c r="D5" s="44"/>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="H5" s="44"/>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
         <v>3120</v>
       </c>
@@ -38412,7 +38412,7 @@
       </c>
       <c r="H6" s="44"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="54"/>
       <c r="C7" s="43"/>
       <c r="D7" s="44"/>
@@ -38428,7 +38428,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
         <v>3126</v>
       </c>
@@ -38444,7 +38444,7 @@
       </c>
       <c r="H8" s="44"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="54"/>
       <c r="C9" s="43"/>
       <c r="D9" s="44"/>
@@ -38456,7 +38456,7 @@
       </c>
       <c r="H9" s="44"/>
     </row>
-    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
         <v>3132</v>
       </c>
@@ -38468,7 +38468,7 @@
       <c r="G10" s="50"/>
       <c r="H10" s="44"/>
     </row>
-    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="54"/>
       <c r="C11" s="43"/>
       <c r="D11" s="44"/>
@@ -38476,7 +38476,7 @@
       <c r="G11" s="52"/>
       <c r="H11" s="53"/>
     </row>
-    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="54" t="s">
         <v>3134</v>
       </c>
@@ -38497,7 +38497,7 @@
       <c r="P12" s="76"/>
       <c r="Q12" s="76"/>
     </row>
-    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="54"/>
       <c r="C13" s="43"/>
       <c r="D13" s="44"/>
@@ -38514,7 +38514,7 @@
       <c r="P13" s="76"/>
       <c r="Q13" s="76"/>
     </row>
-    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="54" t="s">
         <v>3135</v>
       </c>
@@ -38535,7 +38535,7 @@
       <c r="P14" s="76"/>
       <c r="Q14" s="76"/>
     </row>
-    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="51"/>
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
@@ -38560,7 +38560,7 @@
       <c r="P15" s="76"/>
       <c r="Q15" s="76"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="F16" s="118" t="s">
         <v>3137</v>
       </c>
@@ -38579,7 +38579,7 @@
       <c r="P16" s="76"/>
       <c r="Q16" s="76"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
       <c r="C17" s="56"/>
       <c r="D17" s="57"/>
@@ -38598,7 +38598,7 @@
       <c r="P17" s="76"/>
       <c r="Q17" s="76"/>
     </row>
-    <row r="18" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="42"/>
       <c r="C18" s="58" t="s">
         <v>3131</v>
@@ -38623,7 +38623,7 @@
       <c r="P18" s="76"/>
       <c r="Q18" s="76"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="59" t="str">
         <f>VLOOKUP("France",T,lang,FALSE)</f>
         <v>France</v>
@@ -38651,7 +38651,7 @@
       <c r="P19" s="76"/>
       <c r="Q19" s="76"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="59" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
         <v>Spain</v>
@@ -38679,7 +38679,7 @@
       <c r="P20" s="76"/>
       <c r="Q20" s="76"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="59" t="str">
         <f>VLOOKUP("Argentina",T,lang,FALSE)</f>
         <v>Argentina</v>
@@ -38707,7 +38707,7 @@
       <c r="P21" s="76"/>
       <c r="Q21" s="76"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="59" t="str">
         <f>VLOOKUP("England",T,lang,FALSE)</f>
         <v>England</v>
@@ -38735,7 +38735,7 @@
       <c r="P22" s="76"/>
       <c r="Q22" s="76"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="59" t="str">
         <f>VLOOKUP("Portugal",T,lang,FALSE)</f>
         <v>Portugal</v>
@@ -38763,7 +38763,7 @@
       <c r="P23" s="76"/>
       <c r="Q23" s="76"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="59" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
         <v>Brazil</v>
@@ -38791,7 +38791,7 @@
       <c r="P24" s="76"/>
       <c r="Q24" s="76"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="59" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
         <v>Netherlands</v>
@@ -38819,7 +38819,7 @@
       <c r="P25" s="76"/>
       <c r="Q25" s="76"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="59" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
         <v>Morocco</v>
@@ -38847,7 +38847,7 @@
       <c r="P26" s="76"/>
       <c r="Q26" s="76"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="59" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
         <v>Belgium</v>
@@ -38875,7 +38875,7 @@
       <c r="P27" s="76"/>
       <c r="Q27" s="76"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="59" t="str">
         <f>VLOOKUP("Germany",T,lang,FALSE)</f>
         <v>Germany</v>
@@ -38903,7 +38903,7 @@
       <c r="P28" s="76"/>
       <c r="Q28" s="76"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="59" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
         <v>Croatia</v>
@@ -38931,7 +38931,7 @@
       <c r="P29" s="76"/>
       <c r="Q29" s="76"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="59" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
         <v>Colombia</v>
@@ -38959,7 +38959,7 @@
       <c r="P30" s="76"/>
       <c r="Q30" s="76"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="59" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
         <v>Senegal</v>
@@ -38987,7 +38987,7 @@
       <c r="P31" s="76"/>
       <c r="Q31" s="76"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="59" t="str">
         <f>VLOOKUP("Mexico",T,lang,FALSE)</f>
         <v>Mexico</v>
@@ -39015,7 +39015,7 @@
       <c r="P32" s="76"/>
       <c r="Q32" s="76"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="59" t="str">
         <f>VLOOKUP("United States",T,lang,FALSE)</f>
         <v>United States</v>
@@ -39043,7 +39043,7 @@
       <c r="P33" s="76"/>
       <c r="Q33" s="76"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="59" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
         <v>Uruguay</v>
@@ -39071,7 +39071,7 @@
       <c r="P34" s="76"/>
       <c r="Q34" s="76"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="59" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
         <v>Japan</v>
@@ -39099,7 +39099,7 @@
       <c r="P35" s="76"/>
       <c r="Q35" s="76"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B36" s="59" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
         <v>Switzerland</v>
@@ -39127,7 +39127,7 @@
       <c r="P36" s="76"/>
       <c r="Q36" s="76"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="59" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
         <v>Iran</v>
@@ -39155,7 +39155,7 @@
       <c r="P37" s="76"/>
       <c r="Q37" s="76"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B38" s="59" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
         <v>Turkey</v>
@@ -39183,7 +39183,7 @@
       <c r="P38" s="76"/>
       <c r="Q38" s="76"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B39" s="59" t="str">
         <f>VLOOKUP("Ecuador",T,lang,FALSE)</f>
         <v>Ecuador</v>
@@ -39211,7 +39211,7 @@
       <c r="P39" s="76"/>
       <c r="Q39" s="76"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="59" t="str">
         <f>VLOOKUP("Austria",T,lang,FALSE)</f>
         <v>Austria</v>
@@ -39239,7 +39239,7 @@
       <c r="P40" s="76"/>
       <c r="Q40" s="76"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" s="59" t="str">
         <f>VLOOKUP("Korea Republic",T,lang,FALSE)</f>
         <v>Korea Republic</v>
@@ -39267,7 +39267,7 @@
       <c r="P41" s="76"/>
       <c r="Q41" s="76"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" s="59" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
         <v>Australia</v>
@@ -39295,7 +39295,7 @@
       <c r="P42" s="76"/>
       <c r="Q42" s="76"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="59" t="str">
         <f>VLOOKUP("Algeria",T,lang,FALSE)</f>
         <v>Algeria</v>
@@ -39319,7 +39319,7 @@
       <c r="P43" s="76"/>
       <c r="Q43" s="76"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44" s="59" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
         <v>Egypt</v>
@@ -39347,7 +39347,7 @@
       <c r="P44" s="76"/>
       <c r="Q44" s="76"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="59" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
         <v>Canada</v>
@@ -39375,7 +39375,7 @@
       <c r="P45" s="76"/>
       <c r="Q45" s="76"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B46" s="59" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
         <v>Norway</v>
@@ -39403,7 +39403,7 @@
       <c r="P46" s="76"/>
       <c r="Q46" s="76"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B47" s="59" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
         <v>Panama</v>
@@ -39431,7 +39431,7 @@
       <c r="P47" s="76"/>
       <c r="Q47" s="76"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B48" s="59" t="str">
         <f>VLOOKUP("Ivory Coast",T,lang,FALSE)</f>
         <v>Ivory Coast</v>
@@ -39455,7 +39455,7 @@
       <c r="P48" s="76"/>
       <c r="Q48" s="76"/>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="59" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
         <v>Sweden</v>
@@ -39479,7 +39479,7 @@
       <c r="P49" s="76"/>
       <c r="Q49" s="76"/>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="59" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
         <v>Paraguay</v>
@@ -39503,7 +39503,7 @@
       <c r="P50" s="76"/>
       <c r="Q50" s="76"/>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="59" t="str">
         <f>VLOOKUP("Czech Republic",T,lang,FALSE)</f>
         <v>Czech Republic</v>
@@ -39527,7 +39527,7 @@
       <c r="P51" s="76"/>
       <c r="Q51" s="76"/>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="59" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
         <v>Scotland</v>
@@ -39551,7 +39551,7 @@
       <c r="P52" s="76"/>
       <c r="Q52" s="76"/>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="59" t="str">
         <f>VLOOKUP("Tunisia",T,lang,FALSE)</f>
         <v>Tunisia</v>
@@ -39575,7 +39575,7 @@
       <c r="P53" s="76"/>
       <c r="Q53" s="76"/>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="59" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
         <v>DR Congo</v>
@@ -39599,7 +39599,7 @@
       <c r="P54" s="76"/>
       <c r="Q54" s="76"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="59" t="str">
         <f>VLOOKUP("Uzbekistan",T,lang,FALSE)</f>
         <v>Uzbekistan</v>
@@ -39623,7 +39623,7 @@
       <c r="P55" s="76"/>
       <c r="Q55" s="76"/>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="59" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
         <v>Qatar</v>
@@ -39647,7 +39647,7 @@
       <c r="P56" s="76"/>
       <c r="Q56" s="76"/>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="59" t="str">
         <f>VLOOKUP("Iraq",T,lang,FALSE)</f>
         <v>Iraq</v>
@@ -39671,7 +39671,7 @@
       <c r="P57" s="76"/>
       <c r="Q57" s="76"/>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="59" t="str">
         <f>VLOOKUP("South Africa",T,lang,FALSE)</f>
         <v>South Africa</v>
@@ -39695,7 +39695,7 @@
       <c r="P58" s="76"/>
       <c r="Q58" s="76"/>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="59" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
         <v>Saudi Arabia</v>
@@ -39719,7 +39719,7 @@
       <c r="P59" s="76"/>
       <c r="Q59" s="76"/>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="59" t="str">
         <f>VLOOKUP("Jordan",T,lang,FALSE)</f>
         <v>Jordan</v>
@@ -39743,7 +39743,7 @@
       <c r="P60" s="76"/>
       <c r="Q60" s="76"/>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="59" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
         <v>Bosnia and Herzegovina</v>
@@ -39767,7 +39767,7 @@
       <c r="P61" s="76"/>
       <c r="Q61" s="76"/>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="59" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
         <v>Cape Verde</v>
@@ -39791,7 +39791,7 @@
       <c r="P62" s="76"/>
       <c r="Q62" s="76"/>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="59" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
         <v>Ghana</v>
@@ -39815,7 +39815,7 @@
       <c r="P63" s="76"/>
       <c r="Q63" s="76"/>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="59" t="str">
         <f>VLOOKUP("Curaçao",T,lang,FALSE)</f>
         <v>Curaçao</v>
@@ -39839,7 +39839,7 @@
       <c r="P64" s="76"/>
       <c r="Q64" s="76"/>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="59" t="str">
         <f>VLOOKUP("Haiti",T,lang,FALSE)</f>
         <v>Haiti</v>
@@ -39866,7 +39866,7 @@
       <c r="P65" s="76"/>
       <c r="Q65" s="76"/>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B66" s="59" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
         <v>New Zealand</v>
@@ -39888,7 +39888,7 @@
       <c r="P66" s="76"/>
       <c r="Q66" s="76"/>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" s="51"/>
       <c r="C67" s="52"/>
       <c r="D67" s="53"/>
@@ -39905,7 +39905,7 @@
       <c r="P67" s="76"/>
       <c r="Q67" s="76"/>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F68" s="76"/>
       <c r="G68" s="76"/>
       <c r="H68" s="76"/>
@@ -39919,7 +39919,7 @@
       <c r="P68" s="76"/>
       <c r="Q68" s="76"/>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F69" s="76"/>
       <c r="G69" s="76"/>
       <c r="H69" s="76"/>
@@ -39933,7 +39933,7 @@
       <c r="P69" s="76"/>
       <c r="Q69" s="76"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F70" s="76"/>
       <c r="G70" s="76"/>
       <c r="H70" s="76"/>
@@ -39947,7 +39947,7 @@
       <c r="P70" s="76"/>
       <c r="Q70" s="76"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F71" s="76"/>
       <c r="G71" s="76"/>
       <c r="H71" s="76"/>
@@ -39961,7 +39961,7 @@
       <c r="P71" s="76"/>
       <c r="Q71" s="76"/>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F72" s="76"/>
       <c r="G72" s="76"/>
       <c r="H72" s="76"/>
@@ -40011,81 +40011,81 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CR111"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22.453125" style="5" customWidth="1"/>
-    <col min="6" max="7" width="4.26953125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="22.453125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="3.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="8" customWidth="1"/>
-    <col min="11" max="14" width="5.453125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="7.7265625" style="9" customWidth="1"/>
-    <col min="16" max="16" width="6.7265625" style="9" customWidth="1"/>
-    <col min="17" max="17" width="3.453125" style="68" customWidth="1"/>
-    <col min="18" max="18" width="15.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" style="5" customWidth="1"/>
+    <col min="6" max="7" width="4.28515625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="3.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="8" customWidth="1"/>
+    <col min="11" max="14" width="5.42578125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="7.7109375" style="9" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" style="9" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="68" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="19" max="20" width="16" style="127" hidden="1" customWidth="1"/>
     <col min="21" max="28" width="4" style="123" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="4.26953125" style="124" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.453125" style="123" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="13.453125" style="124" hidden="1" customWidth="1"/>
-    <col min="32" max="36" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" style="124" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="5.42578125" style="123" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="124" hidden="1" customWidth="1"/>
+    <col min="32" max="36" width="5.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="37" max="39" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="5.42578125" style="123" hidden="1" customWidth="1"/>
     <col min="41" max="42" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="7.1796875" style="125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="7.140625" style="125" hidden="1" customWidth="1"/>
     <col min="44" max="44" width="10" style="125" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="15.26953125" style="125" hidden="1" customWidth="1"/>
-    <col min="46" max="50" width="4.7265625" style="126" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="9.1796875" style="125" hidden="1" customWidth="1"/>
-    <col min="52" max="61" width="9.1796875" style="126" hidden="1" customWidth="1"/>
-    <col min="62" max="62" width="9.1796875" style="112" hidden="1" customWidth="1"/>
-    <col min="63" max="63" width="3.26953125" style="2" customWidth="1"/>
-    <col min="64" max="64" width="19.7265625" style="2" customWidth="1"/>
+    <col min="45" max="45" width="15.28515625" style="125" hidden="1" customWidth="1"/>
+    <col min="46" max="50" width="4.7109375" style="126" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="125" hidden="1" customWidth="1"/>
+    <col min="52" max="61" width="9.140625" style="126" hidden="1" customWidth="1"/>
+    <col min="62" max="62" width="9.140625" style="112" hidden="1" customWidth="1"/>
+    <col min="63" max="63" width="3.28515625" style="2" customWidth="1"/>
+    <col min="64" max="64" width="19.7109375" style="2" customWidth="1"/>
     <col min="65" max="67" width="3" style="2" customWidth="1"/>
     <col min="68" max="69" width="2" style="111" customWidth="1"/>
-    <col min="70" max="70" width="3.26953125" style="2" customWidth="1"/>
-    <col min="71" max="71" width="19.7265625" style="2" customWidth="1"/>
+    <col min="70" max="70" width="3.28515625" style="2" customWidth="1"/>
+    <col min="71" max="71" width="19.7109375" style="2" customWidth="1"/>
     <col min="72" max="74" width="3" style="2" customWidth="1"/>
     <col min="75" max="76" width="2" style="111" customWidth="1"/>
     <col min="77" max="77" width="4" style="2" customWidth="1"/>
-    <col min="78" max="78" width="19.7265625" style="2" customWidth="1"/>
+    <col min="78" max="78" width="19.7109375" style="2" customWidth="1"/>
     <col min="79" max="81" width="3" style="2" customWidth="1"/>
     <col min="82" max="83" width="2" style="111" customWidth="1"/>
-    <col min="84" max="84" width="3.81640625" style="2" customWidth="1"/>
-    <col min="85" max="85" width="19.7265625" style="2" customWidth="1"/>
+    <col min="84" max="84" width="3.85546875" style="2" customWidth="1"/>
+    <col min="85" max="85" width="19.7109375" style="2" customWidth="1"/>
     <col min="86" max="88" width="3" style="2" customWidth="1"/>
     <col min="89" max="90" width="2" style="111" customWidth="1"/>
-    <col min="91" max="91" width="3.7265625" style="2" customWidth="1"/>
-    <col min="92" max="92" width="19.7265625" style="2" customWidth="1"/>
+    <col min="91" max="91" width="3.7109375" style="2" customWidth="1"/>
+    <col min="92" max="92" width="19.7109375" style="2" customWidth="1"/>
     <col min="93" max="95" width="3" style="2" customWidth="1"/>
     <col min="96" max="96" width="2" style="111" customWidth="1"/>
-    <col min="97" max="16384" width="9.1796875" style="2"/>
+    <col min="97" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:95" ht="46" x14ac:dyDescent="0.35">
-      <c r="A1" s="150" t="str" cm="1">
+    <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40101,7 +40101,7 @@
       <c r="AW1" s="125"/>
       <c r="AX1" s="125"/>
     </row>
-    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="S2" s="123"/>
       <c r="T2" s="123"/>
       <c r="AC2" s="123"/>
@@ -40117,7 +40117,7 @@
       <c r="AW2" s="125"/>
       <c r="AX2" s="125"/>
     </row>
-    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40152,45 +40152,45 @@
       <c r="AW3" s="125"/>
       <c r="AX3" s="125"/>
     </row>
-    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A5" s="152" t="str" cm="1">
+    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:95" x14ac:dyDescent="0.25">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
-    </row>
-    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
+    </row>
+    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,39 +40300,39 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
-    </row>
-    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
+    </row>
+    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -40407,28 +40407,28 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
-    </row>
-    <row r="8" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
+    </row>
+    <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>2</v>
       </c>
@@ -40675,7 +40675,7 @@
       <c r="CP8" s="21"/>
       <c r="CQ8" s="21"/>
     </row>
-    <row r="9" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>3</v>
       </c>
@@ -40940,7 +40940,7 @@
       <c r="CP9" s="21"/>
       <c r="CQ9" s="21"/>
     </row>
-    <row r="10" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>4</v>
       </c>
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41203,7 +41203,7 @@
       <c r="CP10" s="21"/>
       <c r="CQ10" s="21"/>
     </row>
-    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>5</v>
       </c>
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41470,7 +41470,7 @@
       <c r="CP11" s="21"/>
       <c r="CQ11" s="21"/>
     </row>
-    <row r="12" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>6</v>
       </c>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41697,7 +41697,7 @@
       <c r="CP12" s="21"/>
       <c r="CQ12" s="21"/>
     </row>
-    <row r="13" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>7</v>
       </c>
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -41816,7 +41816,7 @@
       <c r="CP13" s="21"/>
       <c r="CQ13" s="21"/>
     </row>
-    <row r="14" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>8</v>
       </c>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42083,7 +42083,7 @@
       <c r="CP14" s="21"/>
       <c r="CQ14" s="21"/>
     </row>
-    <row r="15" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>9</v>
       </c>
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42347,7 +42347,7 @@
       <c r="CH15" s="21"/>
       <c r="CI15" s="21"/>
     </row>
-    <row r="16" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>10</v>
       </c>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42603,7 +42603,7 @@
       <c r="CH16" s="21"/>
       <c r="CI16" s="21"/>
     </row>
-    <row r="17" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>11</v>
       </c>
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -42863,7 +42863,7 @@
       <c r="CH17" s="21"/>
       <c r="CI17" s="21"/>
     </row>
-    <row r="18" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>12</v>
       </c>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43083,7 +43083,7 @@
       <c r="CH18" s="21"/>
       <c r="CI18" s="21"/>
     </row>
-    <row r="19" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>13</v>
       </c>
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43202,7 +43202,7 @@
       <c r="CP19" s="21"/>
       <c r="CQ19" s="21"/>
     </row>
-    <row r="20" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>14</v>
       </c>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43469,7 +43469,7 @@
       <c r="CP20" s="21"/>
       <c r="CQ20" s="21"/>
     </row>
-    <row r="21" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>15</v>
       </c>
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43740,7 +43740,7 @@
       <c r="CP21" s="21"/>
       <c r="CQ21" s="21"/>
     </row>
-    <row r="22" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>16</v>
       </c>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44004,7 +44004,7 @@
         <v>46217.791666666672</v>
       </c>
     </row>
-    <row r="23" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>17</v>
       </c>
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44268,7 +44268,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>18</v>
       </c>
@@ -44474,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44487,7 +44487,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>19</v>
       </c>
@@ -44601,7 +44601,7 @@
       <c r="CP25" s="21"/>
       <c r="CQ25" s="21"/>
     </row>
-    <row r="26" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>20</v>
       </c>
@@ -44713,7 +44713,7 @@
       </c>
       <c r="AF26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_draw")</f>
@@ -44725,7 +44725,7 @@
       </c>
       <c r="AI26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE26,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE26,$F$7:$F$78)</f>
@@ -44733,23 +44733,23 @@
       </c>
       <c r="AL26" s="123">
         <f>AI26-AJ26</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM26" s="123">
         <f>AL26-AL30</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN26" s="123">
         <f>AF26*3+AG26</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO26" s="123">
         <f>AN26/AN30*10+BA26</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP26" s="123">
         <f>AO26*10000000+BI26*100+AM26/AM30*10+AI26/AI30*1++IF(AQ26=0,ROW(),AQ26)/2000000</f>
-        <v>75000009.37226513</v>
+        <v>85714295.461154029</v>
       </c>
       <c r="AQ26" s="126">
         <f>VLOOKUP(AE26,db_fifarank,2,FALSE)</f>
@@ -44757,7 +44757,7 @@
       </c>
       <c r="AR26" s="125">
         <f>AP26/AP30</f>
-        <v>0.99999998666666856</v>
+        <v>0.99999998833333481</v>
       </c>
       <c r="AS26" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J27,"1D")</f>
@@ -44827,7 +44827,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -44869,7 +44869,7 @@
       <c r="CP26" s="21"/>
       <c r="CQ26" s="21"/>
     </row>
-    <row r="27" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>21</v>
       </c>
@@ -44905,11 +44905,11 @@
       </c>
       <c r="K27" s="31">
         <f>L27+M27+N27</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="31">
         <f>VLOOKUP(1,AD26:AN29,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="31">
         <f>VLOOKUP(1,AD26:AN29,4,FALSE)</f>
@@ -44921,11 +44921,11 @@
       </c>
       <c r="O27" s="31" t="str">
         <f>VLOOKUP(1,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD26:AN29,7,FALSE)</f>
-        <v>4 - 1</v>
+        <v>6 - 1</v>
       </c>
       <c r="P27" s="32">
         <f>L27*3+M27</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R27" s="123">
         <f>DATE(2026,6,17)+TIME(12,0,0)+gmt_delta</f>
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AP27" s="123">
         <f>AO27*10000000+BI27*100+AM27/AM30*10+AI27/AI30*1++IF(AQ27=0,ROW(),AQ27)/2000000</f>
-        <v>0.20075175000000001</v>
+        <v>0.14360889285714284</v>
       </c>
       <c r="AQ27" s="126">
         <f>VLOOKUP(AE27,db_fifarank,2,FALSE)</f>
@@ -45025,7 +45025,7 @@
       </c>
       <c r="AR27" s="125">
         <f>AP27/AP30</f>
-        <v>2.6766896298222066E-9</v>
+        <v>1.6754368732668397E-9</v>
       </c>
       <c r="AS27" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J28,"2D")</f>
@@ -45095,7 +45095,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45141,7 +45141,7 @@
       <c r="CP27" s="21"/>
       <c r="CQ27" s="21"/>
     </row>
-    <row r="28" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>22</v>
       </c>
@@ -45177,7 +45177,7 @@
       </c>
       <c r="K28" s="23">
         <f>L28+M28+N28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="23">
         <f>VLOOKUP(2,AD26:AN29,3,FALSE)</f>
@@ -45189,11 +45189,11 @@
       </c>
       <c r="N28" s="23">
         <f>VLOOKUP(2,AD26:AN29,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="23" t="str">
         <f>VLOOKUP(2,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD26:AN29,7,FALSE)</f>
-        <v>2 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P28" s="34">
         <f>L28*3+M28</f>
@@ -45261,7 +45261,7 @@
       </c>
       <c r="AH28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE28,$G$7:$G$78)</f>
@@ -45269,15 +45269,15 @@
       </c>
       <c r="AJ28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE28,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL28" s="123">
         <f>AI28-AJ28</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM28" s="123">
         <f>AL28-AL30</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN28" s="123">
         <f>AF28*3+AG28</f>
@@ -45285,11 +45285,11 @@
       </c>
       <c r="AO28" s="123">
         <f>AN28/AN30*10+BA28</f>
-        <v>7.5</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP28" s="123">
         <f>AO28*10000000+BI28*100+AM28/AM30*10+AI28/AI30*1++IF(AQ28=0,ROW(),AQ28)/2000000</f>
-        <v>75000007.543647483</v>
+        <v>42857146.476980813</v>
       </c>
       <c r="AQ28" s="126">
         <f>VLOOKUP(AE28,db_fifarank,2,FALSE)</f>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="AR28" s="125">
         <f>AP28/AP30</f>
-        <v>0.99999996228510324</v>
+        <v>0.4999999795413802</v>
       </c>
       <c r="AT28" s="126" cm="1">
         <f t="array" ref="AT28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($U$7:$U$78))</f>
@@ -45370,7 +45370,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45400,7 +45400,7 @@
       <c r="CK28" s="114"/>
       <c r="CL28" s="112"/>
     </row>
-    <row r="29" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>23</v>
       </c>
@@ -45548,7 +45548,7 @@
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>1.4293709485714283</v>
+        <v>1.1119106311111111</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -45556,7 +45556,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>1.9058276678585728E-8</v>
+        <v>1.2972289069829002E-8</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -45635,7 +45635,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45663,7 +45663,7 @@
       <c r="CK29" s="114"/>
       <c r="CL29" s="112"/>
     </row>
-    <row r="30" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>24</v>
       </c>
@@ -45767,7 +45767,7 @@
       </c>
       <c r="AF30" s="123">
         <f t="shared" ref="AF30:AH30" si="15">MAX(AF26:AF29)-MIN(AF26:AF29)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG30" s="123">
         <f t="shared" si="15"/>
@@ -45779,7 +45779,7 @@
       </c>
       <c r="AI30" s="123">
         <f>MAX(AI26:AI29)+1</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL30" s="123">
         <f>MIN(AL26:AL29)</f>
@@ -45787,19 +45787,19 @@
       </c>
       <c r="AM30" s="123">
         <f>MAX(AM26:AM29)+1</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN30" s="123">
         <f>MAX(AN26:AN29)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO30" s="123">
         <f>MAX(AO26:AO29)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP30" s="123">
         <f>MAX(AP26:AP29)+1</f>
-        <v>75000010.37226513</v>
+        <v>85714296.461154029</v>
       </c>
       <c r="AT30" s="126">
         <f>MAX(AT26:AT29)-MIN(AT26:AT29)+1</f>
@@ -45849,7 +45849,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45886,7 +45886,7 @@
       <c r="CK30" s="114"/>
       <c r="CL30" s="112"/>
     </row>
-    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>25</v>
       </c>
@@ -45960,7 +45960,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -45996,7 +45996,7 @@
       <c r="CK31" s="114"/>
       <c r="CL31" s="112"/>
     </row>
-    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>26</v>
       </c>
@@ -46236,7 +46236,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46254,7 +46254,7 @@
       <c r="CK32" s="114"/>
       <c r="CL32" s="112"/>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>27</v>
       </c>
@@ -46500,7 +46500,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46515,16 +46515,16 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
-    </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
+    </row>
+    <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>28</v>
       </c>
@@ -46746,7 +46746,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46777,13 +46777,13 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
-    </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
+    </row>
+    <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>29</v>
       </c>
@@ -47001,7 +47001,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47037,7 +47037,7 @@
       <c r="CK35" s="114"/>
       <c r="CL35" s="112"/>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>30</v>
       </c>
@@ -47226,7 +47226,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47263,7 +47263,7 @@
         <v>46222.791666666672</v>
       </c>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>31</v>
       </c>
@@ -47283,8 +47283,12 @@
         <f>AE26</f>
         <v>United States</v>
       </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="20"/>
+      <c r="F37" s="19">
+        <v>2</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
       <c r="H37" s="80" t="str">
         <f>AE28</f>
         <v>Australia</v>
@@ -47295,11 +47299,11 @@
       </c>
       <c r="S37" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>United States_win</v>
       </c>
       <c r="T37" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Australia_lose</v>
       </c>
       <c r="U37" s="123">
         <f t="shared" si="8"/>
@@ -47329,9 +47333,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="123" t="str">
+      <c r="AB37" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BK37" s="21" t="str" cm="1">
         <f t="array" ref="BK37">INDEX(T,24+MONTH(BP37),lang) &amp; " " &amp; DAY(BP37) &amp; ", " &amp; YEAR(BP37) &amp; "   " &amp; (IF(HOUR(BP37)&lt;10,0,"")&amp;HOUR(BP37)) &amp; ":" &amp;  (IF(MINUTE(BP37)&lt;10,0,"")&amp;MINUTE(BP37))</f>
@@ -47346,7 +47350,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47373,7 +47377,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47388,7 +47392,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>32</v>
       </c>
@@ -47610,7 +47614,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47640,7 +47644,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47653,7 +47657,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>33</v>
       </c>
@@ -47875,7 +47879,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -47908,7 +47912,7 @@
       <c r="CP39" s="21"/>
       <c r="CQ39" s="21"/>
     </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>34</v>
       </c>
@@ -48129,7 +48133,7 @@
       <c r="CK40" s="114"/>
       <c r="CL40" s="112"/>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>35</v>
       </c>
@@ -48369,7 +48373,7 @@
       <c r="CK41" s="114"/>
       <c r="CL41" s="112"/>
     </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>36</v>
       </c>
@@ -48551,7 +48555,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48574,7 +48578,7 @@
       <c r="BW42" s="112"/>
       <c r="CK42" s="114"/>
     </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <v>37</v>
       </c>
@@ -48644,7 +48648,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48671,7 +48675,7 @@
       </c>
       <c r="CK43" s="114"/>
     </row>
-    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <v>38</v>
       </c>
@@ -48900,7 +48904,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48915,16 +48919,16 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
-    </row>
-    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
+    </row>
+    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <v>39</v>
       </c>
@@ -49159,7 +49163,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49172,13 +49176,13 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
-    </row>
-    <row r="46" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
+    </row>
+    <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <v>40</v>
       </c>
@@ -49396,7 +49400,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="141">
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49420,7 +49424,7 @@
       <c r="CK46" s="114"/>
       <c r="CL46" s="112"/>
     </row>
-    <row r="47" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <v>41</v>
       </c>
@@ -49638,7 +49642,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="142"/>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49685,7 +49689,7 @@
         <v>46221.875</v>
       </c>
     </row>
-    <row r="48" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <v>42</v>
       </c>
@@ -49881,7 +49885,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49897,7 +49901,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -49912,7 +49916,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <v>43</v>
       </c>
@@ -50002,7 +50006,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50016,7 +50020,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50029,7 +50033,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
         <v>44</v>
       </c>
@@ -50251,7 +50255,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50282,7 +50286,7 @@
       <c r="CK50" s="114"/>
       <c r="CL50" s="112"/>
     </row>
-    <row r="51" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <v>45</v>
       </c>
@@ -50504,7 +50508,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50539,7 +50543,7 @@
       <c r="CK51" s="114"/>
       <c r="CL51" s="112"/>
     </row>
-    <row r="52" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <v>46</v>
       </c>
@@ -50764,7 +50768,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50788,7 +50792,7 @@
       <c r="CK52" s="114"/>
       <c r="CL52" s="112"/>
     </row>
-    <row r="53" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>47</v>
       </c>
@@ -51019,7 +51023,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51041,7 +51045,7 @@
       <c r="CK53" s="114"/>
       <c r="CL53" s="112"/>
     </row>
-    <row r="54" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>48</v>
       </c>
@@ -51223,7 +51227,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51266,7 +51270,7 @@
       </c>
       <c r="CL54" s="112"/>
     </row>
-    <row r="55" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>49</v>
       </c>
@@ -51344,7 +51348,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51371,7 +51375,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51387,7 +51391,7 @@
       </c>
       <c r="CL55" s="112"/>
     </row>
-    <row r="56" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>50</v>
       </c>
@@ -51630,7 +51634,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -51644,7 +51648,7 @@
       </c>
       <c r="CL56" s="112"/>
     </row>
-    <row r="57" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>51</v>
       </c>
@@ -51894,7 +51898,7 @@
       <c r="CC57" s="21"/>
       <c r="CD57" s="114"/>
     </row>
-    <row r="58" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
         <v>52</v>
       </c>
@@ -52113,7 +52117,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52142,7 +52146,7 @@
       <c r="CC58" s="21"/>
       <c r="CD58" s="114"/>
     </row>
-    <row r="59" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <v>53</v>
       </c>
@@ -52361,7 +52365,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52394,7 +52398,7 @@
       <c r="CC59" s="21"/>
       <c r="CD59" s="114"/>
     </row>
-    <row r="60" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <v>54</v>
       </c>
@@ -52584,7 +52588,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52606,7 +52610,7 @@
       <c r="CC60" s="21"/>
       <c r="CD60" s="114"/>
     </row>
-    <row r="61" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <v>55</v>
       </c>
@@ -52697,7 +52701,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52717,7 +52721,7 @@
       <c r="CC61" s="21"/>
       <c r="CD61" s="114"/>
     </row>
-    <row r="62" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
         <v>56</v>
       </c>
@@ -52940,7 +52944,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -52969,7 +52973,7 @@
       <c r="CC62" s="21"/>
       <c r="CD62" s="114"/>
     </row>
-    <row r="63" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <v>57</v>
       </c>
@@ -53192,7 +53196,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53225,7 +53229,7 @@
         <v>46215.041666666672</v>
       </c>
     </row>
-    <row r="64" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
         <v>58</v>
       </c>
@@ -53458,7 +53462,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53473,7 +53477,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
         <v>59</v>
       </c>
@@ -53712,7 +53716,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53725,7 +53729,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A66" s="16">
         <v>60</v>
       </c>
@@ -53908,7 +53912,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -53930,7 +53934,7 @@
       <c r="BV66" s="21"/>
       <c r="BW66" s="114"/>
     </row>
-    <row r="67" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <v>61</v>
       </c>
@@ -54008,7 +54012,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54034,7 +54038,7 @@
         <v>46210.833333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
         <v>62</v>
       </c>
@@ -54264,7 +54268,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54278,27 +54282,27 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
-    </row>
-    <row r="69" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
+    </row>
+    <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <v>63</v>
       </c>
@@ -54534,7 +54538,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54546,21 +54550,21 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
-    </row>
-    <row r="70" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
+    </row>
+    <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <v>64</v>
       </c>
@@ -54779,7 +54783,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -54796,7 +54800,7 @@
       <c r="BQ70" s="112"/>
       <c r="BW70" s="112"/>
     </row>
-    <row r="71" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <v>65</v>
       </c>
@@ -55015,7 +55019,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -55029,7 +55033,7 @@
       </c>
       <c r="BQ71" s="112"/>
     </row>
-    <row r="72" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A72" s="16">
         <v>66</v>
       </c>
@@ -55213,7 +55217,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="73" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A73" s="16">
         <v>67</v>
       </c>
@@ -55292,7 +55296,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A74" s="16">
         <v>68</v>
       </c>
@@ -55516,7 +55520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A75" s="16">
         <v>69</v>
       </c>
@@ -55740,7 +55744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A76" s="16">
         <v>70</v>
       </c>
@@ -55960,7 +55964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A77" s="16">
         <v>71</v>
       </c>
@@ -56180,7 +56184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A78" s="16">
         <v>72</v>
       </c>
@@ -56364,7 +56368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A79" s="73"/>
       <c r="B79" s="73"/>
       <c r="C79" s="73"/>
@@ -56382,7 +56386,7 @@
       <c r="O79" s="70"/>
       <c r="P79" s="70"/>
     </row>
-    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="73"/>
       <c r="B80" s="73"/>
       <c r="C80" s="73"/>
@@ -56484,7 +56488,7 @@
         <v>Ⓐ Czech Republic</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="73"/>
       <c r="B81" s="73"/>
       <c r="C81" s="73"/>
@@ -56586,7 +56590,7 @@
         <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="73"/>
       <c r="B82" s="73"/>
       <c r="C82" s="73"/>
@@ -56688,16 +56692,16 @@
         <v>Ⓒ Morocco</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56792,14 +56796,14 @@
         <v>Ⓓ Turkey</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56906,14 +56910,14 @@
         <v>Ⓔ Ecuador</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -57020,14 +57024,14 @@
         <v>Ⓕ Japan</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57134,14 +57138,14 @@
         <v>Ⓖ Belgium</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57248,14 +57252,14 @@
         <v>Ⓗ Spain</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57362,7 +57366,7 @@
         <v>Ⓘ Senegal</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="73"/>
       <c r="B89" s="73"/>
       <c r="C89" s="73"/>
@@ -57476,7 +57480,7 @@
         <v>Ⓙ Jordan</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="73"/>
       <c r="B90" s="73"/>
       <c r="C90" s="73"/>
@@ -57590,7 +57594,7 @@
         <v>Ⓚ DR Congo</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="73"/>
       <c r="B91" s="73"/>
       <c r="C91" s="73"/>
@@ -57704,7 +57708,7 @@
         <v>Ⓛ Panama</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="73"/>
       <c r="B92" s="73"/>
       <c r="C92" s="73"/>
@@ -57779,7 +57783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A93" s="73"/>
       <c r="B93" s="73"/>
       <c r="C93" s="73"/>
@@ -57797,7 +57801,7 @@
       <c r="O93" s="70"/>
       <c r="P93" s="70"/>
     </row>
-    <row r="95" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:46" x14ac:dyDescent="0.25">
       <c r="R95" s="123">
         <f>DATE(2026,12,9)+TIME(8,0,0)+gmt_delta</f>
         <v>46365.791666666672</v>
@@ -57811,7 +57815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R96" s="123">
         <f>DATE(2026,12,9)+TIME(4,0,0)+gmt_delta</f>
         <v>46365.625</v>
@@ -57825,7 +57829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R97" s="123">
         <f>DATE(2026,12,10)+TIME(8,0,0)+gmt_delta</f>
         <v>46366.791666666672</v>
@@ -57839,7 +57843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="98" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R98" s="123">
         <f>DATE(2026,12,10)+TIME(4,0,0)+gmt_delta</f>
         <v>46366.625</v>
@@ -57853,7 +57857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="102" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R102" s="123">
         <f>DATE(2026,12,13)+TIME(8,0,0)+gmt_delta</f>
         <v>46369.791666666672</v>
@@ -57879,7 +57883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="103" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R103" s="123">
         <f>DATE(2026,12,14)+TIME(8,0,0)+gmt_delta</f>
         <v>46370.791666666672</v>
@@ -57905,7 +57909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="107" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R107" s="123">
         <f>DATE(2026,12,17)+TIME(8,0,0)+gmt_delta</f>
         <v>46373.791666666672</v>
@@ -57915,7 +57919,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="18:29" x14ac:dyDescent="0.35">
+    <row r="111" spans="18:29" x14ac:dyDescent="0.25">
       <c r="R111" s="123">
         <f>DATE(2026,12,18)+TIME(8,0,0)+gmt_delta</f>
         <v>46374.791666666672</v>
@@ -57932,11 +57936,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57952,31 +57976,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -59001,22 +59005,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A2A316-429C-49FB-9962-F944380EA825}">
   <dimension ref="B1:K500"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.453125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="81"/>
-    <col min="3" max="3" width="13.7265625" style="81" customWidth="1"/>
-    <col min="4" max="11" width="9.453125" style="81" customWidth="1"/>
-    <col min="12" max="16384" width="9.1796875" style="82"/>
+    <col min="1" max="1" width="2.42578125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="81"/>
+    <col min="3" max="3" width="13.7109375" style="81" customWidth="1"/>
+    <col min="4" max="11" width="9.42578125" style="81" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="82"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B2" s="108" t="s">
         <v>3193</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
         <v>423</v>
@@ -59058,7 +59062,7 @@
         <v>3K</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="84" t="s">
         <v>3194</v>
       </c>
@@ -59088,7 +59092,7 @@
         <v>3202</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="88">
         <v>1</v>
       </c>
@@ -59120,7 +59124,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="88">
         <v>2</v>
       </c>
@@ -59152,7 +59156,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="88">
         <v>3</v>
       </c>
@@ -59184,7 +59188,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="88">
         <v>4</v>
       </c>
@@ -59216,7 +59220,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="88">
         <v>5</v>
       </c>
@@ -59248,7 +59252,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="88">
         <v>6</v>
       </c>
@@ -59280,7 +59284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="88">
         <v>7</v>
       </c>
@@ -59312,7 +59316,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="88">
         <v>8</v>
       </c>
@@ -59344,7 +59348,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="88">
         <v>9</v>
       </c>
@@ -59376,7 +59380,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="88">
         <v>10</v>
       </c>
@@ -59408,7 +59412,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="88">
         <v>11</v>
       </c>
@@ -59440,7 +59444,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="88">
         <v>12</v>
       </c>
@@ -59472,7 +59476,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="88">
         <v>13</v>
       </c>
@@ -59504,7 +59508,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="88">
         <v>14</v>
       </c>
@@ -59536,7 +59540,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="88">
         <v>15</v>
       </c>
@@ -59568,7 +59572,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="88">
         <v>16</v>
       </c>
@@ -59600,7 +59604,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="88">
         <v>17</v>
       </c>
@@ -59632,7 +59636,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="88">
         <v>18</v>
       </c>
@@ -59664,7 +59668,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="88">
         <v>19</v>
       </c>
@@ -59696,7 +59700,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="88">
         <v>20</v>
       </c>
@@ -59728,7 +59732,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="88">
         <v>21</v>
       </c>
@@ -59760,7 +59764,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="88">
         <v>22</v>
       </c>
@@ -59792,7 +59796,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="88">
         <v>23</v>
       </c>
@@ -59824,7 +59828,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="88">
         <v>24</v>
       </c>
@@ -59856,7 +59860,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="88">
         <v>25</v>
       </c>
@@ -59888,7 +59892,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="88">
         <v>26</v>
       </c>
@@ -59920,7 +59924,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="88">
         <v>27</v>
       </c>
@@ -59952,7 +59956,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="88">
         <v>28</v>
       </c>
@@ -59984,7 +59988,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="88">
         <v>29</v>
       </c>
@@ -60016,7 +60020,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="88">
         <v>30</v>
       </c>
@@ -60048,7 +60052,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="88">
         <v>31</v>
       </c>
@@ -60080,7 +60084,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="88">
         <v>32</v>
       </c>
@@ -60112,7 +60116,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="88">
         <v>33</v>
       </c>
@@ -60144,7 +60148,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="88">
         <v>34</v>
       </c>
@@ -60176,7 +60180,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="88">
         <v>35</v>
       </c>
@@ -60208,7 +60212,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="88">
         <v>36</v>
       </c>
@@ -60240,7 +60244,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="88">
         <v>37</v>
       </c>
@@ -60272,7 +60276,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="88">
         <v>38</v>
       </c>
@@ -60304,7 +60308,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="88">
         <v>39</v>
       </c>
@@ -60336,7 +60340,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="88">
         <v>40</v>
       </c>
@@ -60368,7 +60372,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="88">
         <v>41</v>
       </c>
@@ -60400,7 +60404,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="88">
         <v>42</v>
       </c>
@@ -60432,7 +60436,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="88">
         <v>43</v>
       </c>
@@ -60464,7 +60468,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="88">
         <v>44</v>
       </c>
@@ -60496,7 +60500,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="88">
         <v>45</v>
       </c>
@@ -60528,7 +60532,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="88">
         <v>46</v>
       </c>
@@ -60560,7 +60564,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="88">
         <v>47</v>
       </c>
@@ -60592,7 +60596,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" s="88">
         <v>48</v>
       </c>
@@ -60624,7 +60628,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" s="88">
         <v>49</v>
       </c>
@@ -60656,7 +60660,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" s="88">
         <v>50</v>
       </c>
@@ -60688,7 +60692,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="88">
         <v>51</v>
       </c>
@@ -60720,7 +60724,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" s="88">
         <v>52</v>
       </c>
@@ -60752,7 +60756,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="88">
         <v>53</v>
       </c>
@@ -60784,7 +60788,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="88">
         <v>54</v>
       </c>
@@ -60816,7 +60820,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="88">
         <v>55</v>
       </c>
@@ -60848,7 +60852,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="88">
         <v>56</v>
       </c>
@@ -60880,7 +60884,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="88">
         <v>57</v>
       </c>
@@ -60912,7 +60916,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="88">
         <v>58</v>
       </c>
@@ -60944,7 +60948,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="88">
         <v>59</v>
       </c>
@@ -60976,7 +60980,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="88">
         <v>60</v>
       </c>
@@ -61008,7 +61012,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="88">
         <v>61</v>
       </c>
@@ -61040,7 +61044,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" s="88">
         <v>62</v>
       </c>
@@ -61072,7 +61076,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" s="88">
         <v>63</v>
       </c>
@@ -61104,7 +61108,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" s="88">
         <v>64</v>
       </c>
@@ -61136,7 +61140,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" s="88">
         <v>65</v>
       </c>
@@ -61168,7 +61172,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" s="88">
         <v>66</v>
       </c>
@@ -61200,7 +61204,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" s="88">
         <v>67</v>
       </c>
@@ -61232,7 +61236,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" s="88">
         <v>68</v>
       </c>
@@ -61264,7 +61268,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" s="88">
         <v>69</v>
       </c>
@@ -61296,7 +61300,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" s="88">
         <v>70</v>
       </c>
@@ -61328,7 +61332,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" s="88">
         <v>71</v>
       </c>
@@ -61360,7 +61364,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" s="88">
         <v>72</v>
       </c>
@@ -61392,7 +61396,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" s="88">
         <v>73</v>
       </c>
@@ -61424,7 +61428,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="88">
         <v>74</v>
       </c>
@@ -61456,7 +61460,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" s="88">
         <v>75</v>
       </c>
@@ -61488,7 +61492,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" s="88">
         <v>76</v>
       </c>
@@ -61520,7 +61524,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" s="88">
         <v>77</v>
       </c>
@@ -61552,7 +61556,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" s="88">
         <v>78</v>
       </c>
@@ -61584,7 +61588,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" s="88">
         <v>79</v>
       </c>
@@ -61616,7 +61620,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" s="88">
         <v>80</v>
       </c>
@@ -61648,7 +61652,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" s="88">
         <v>81</v>
       </c>
@@ -61680,7 +61684,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" s="88">
         <v>82</v>
       </c>
@@ -61712,7 +61716,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" s="88">
         <v>83</v>
       </c>
@@ -61744,7 +61748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" s="88">
         <v>84</v>
       </c>
@@ -61776,7 +61780,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" s="88">
         <v>85</v>
       </c>
@@ -61808,7 +61812,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" s="88">
         <v>86</v>
       </c>
@@ -61840,7 +61844,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" s="88">
         <v>87</v>
       </c>
@@ -61872,7 +61876,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" s="88">
         <v>88</v>
       </c>
@@ -61904,7 +61908,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" s="88">
         <v>89</v>
       </c>
@@ -61936,7 +61940,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" s="88">
         <v>90</v>
       </c>
@@ -61968,7 +61972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" s="88">
         <v>91</v>
       </c>
@@ -62000,7 +62004,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" s="88">
         <v>92</v>
       </c>
@@ -62032,7 +62036,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" s="88">
         <v>93</v>
       </c>
@@ -62064,7 +62068,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" s="88">
         <v>94</v>
       </c>
@@ -62096,7 +62100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" s="88">
         <v>95</v>
       </c>
@@ -62128,7 +62132,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="88">
         <v>96</v>
       </c>
@@ -62160,7 +62164,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" s="88">
         <v>97</v>
       </c>
@@ -62192,7 +62196,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" s="88">
         <v>98</v>
       </c>
@@ -62224,7 +62228,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" s="88">
         <v>99</v>
       </c>
@@ -62256,7 +62260,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" s="88">
         <v>100</v>
       </c>
@@ -62288,7 +62292,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" s="88">
         <v>101</v>
       </c>
@@ -62320,7 +62324,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" s="88">
         <v>102</v>
       </c>
@@ -62352,7 +62356,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" s="88">
         <v>103</v>
       </c>
@@ -62384,7 +62388,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" s="88">
         <v>104</v>
       </c>
@@ -62416,7 +62420,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" s="88">
         <v>105</v>
       </c>
@@ -62448,7 +62452,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" s="88">
         <v>106</v>
       </c>
@@ -62480,7 +62484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" s="88">
         <v>107</v>
       </c>
@@ -62512,7 +62516,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" s="88">
         <v>108</v>
       </c>
@@ -62544,7 +62548,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" s="88">
         <v>109</v>
       </c>
@@ -62576,7 +62580,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" s="88">
         <v>110</v>
       </c>
@@ -62608,7 +62612,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" s="88">
         <v>111</v>
       </c>
@@ -62640,7 +62644,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" s="88">
         <v>112</v>
       </c>
@@ -62672,7 +62676,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" s="88">
         <v>113</v>
       </c>
@@ -62704,7 +62708,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" s="88">
         <v>114</v>
       </c>
@@ -62736,7 +62740,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" s="88">
         <v>115</v>
       </c>
@@ -62768,7 +62772,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" s="88">
         <v>116</v>
       </c>
@@ -62800,7 +62804,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" s="88">
         <v>117</v>
       </c>
@@ -62832,7 +62836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" s="88">
         <v>118</v>
       </c>
@@ -62864,7 +62868,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" s="88">
         <v>119</v>
       </c>
@@ -62896,7 +62900,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" s="88">
         <v>120</v>
       </c>
@@ -62928,7 +62932,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" s="88">
         <v>121</v>
       </c>
@@ -62960,7 +62964,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" s="88">
         <v>122</v>
       </c>
@@ -62992,7 +62996,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" s="88">
         <v>123</v>
       </c>
@@ -63024,7 +63028,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" s="88">
         <v>124</v>
       </c>
@@ -63056,7 +63060,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" s="88">
         <v>125</v>
       </c>
@@ -63088,7 +63092,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" s="88">
         <v>126</v>
       </c>
@@ -63120,7 +63124,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" s="88">
         <v>127</v>
       </c>
@@ -63152,7 +63156,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" s="88">
         <v>128</v>
       </c>
@@ -63184,7 +63188,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" s="88">
         <v>129</v>
       </c>
@@ -63216,7 +63220,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" s="88">
         <v>130</v>
       </c>
@@ -63248,7 +63252,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" s="88">
         <v>131</v>
       </c>
@@ -63280,7 +63284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" s="88">
         <v>132</v>
       </c>
@@ -63312,7 +63316,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" s="88">
         <v>133</v>
       </c>
@@ -63344,7 +63348,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" s="88">
         <v>134</v>
       </c>
@@ -63376,7 +63380,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" s="88">
         <v>135</v>
       </c>
@@ -63408,7 +63412,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" s="88">
         <v>136</v>
       </c>
@@ -63440,7 +63444,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" s="88">
         <v>137</v>
       </c>
@@ -63472,7 +63476,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" s="88">
         <v>138</v>
       </c>
@@ -63504,7 +63508,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" s="88">
         <v>139</v>
       </c>
@@ -63536,7 +63540,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" s="88">
         <v>140</v>
       </c>
@@ -63568,7 +63572,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" s="88">
         <v>141</v>
       </c>
@@ -63600,7 +63604,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" s="88">
         <v>142</v>
       </c>
@@ -63632,7 +63636,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" s="88">
         <v>143</v>
       </c>
@@ -63664,7 +63668,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" s="88">
         <v>144</v>
       </c>
@@ -63696,7 +63700,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" s="88">
         <v>145</v>
       </c>
@@ -63728,7 +63732,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" s="88">
         <v>146</v>
       </c>
@@ -63760,7 +63764,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" s="88">
         <v>147</v>
       </c>
@@ -63792,7 +63796,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" s="88">
         <v>148</v>
       </c>
@@ -63824,7 +63828,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" s="88">
         <v>149</v>
       </c>
@@ -63856,7 +63860,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" s="88">
         <v>150</v>
       </c>
@@ -63888,7 +63892,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" s="88">
         <v>151</v>
       </c>
@@ -63920,7 +63924,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" s="88">
         <v>152</v>
       </c>
@@ -63952,7 +63956,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" s="88">
         <v>153</v>
       </c>
@@ -63984,7 +63988,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" s="88">
         <v>154</v>
       </c>
@@ -64016,7 +64020,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" s="88">
         <v>155</v>
       </c>
@@ -64048,7 +64052,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" s="88">
         <v>156</v>
       </c>
@@ -64080,7 +64084,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" s="88">
         <v>157</v>
       </c>
@@ -64112,7 +64116,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" s="88">
         <v>158</v>
       </c>
@@ -64144,7 +64148,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" s="88">
         <v>159</v>
       </c>
@@ -64176,7 +64180,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" s="88">
         <v>160</v>
       </c>
@@ -64208,7 +64212,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" s="88">
         <v>161</v>
       </c>
@@ -64240,7 +64244,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" s="88">
         <v>162</v>
       </c>
@@ -64272,7 +64276,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" s="88">
         <v>163</v>
       </c>
@@ -64304,7 +64308,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" s="88">
         <v>164</v>
       </c>
@@ -64336,7 +64340,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B170" s="88">
         <v>165</v>
       </c>
@@ -64368,7 +64372,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" s="88">
         <v>166</v>
       </c>
@@ -64400,7 +64404,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" s="88">
         <v>167</v>
       </c>
@@ -64432,7 +64436,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" s="88">
         <v>168</v>
       </c>
@@ -64464,7 +64468,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" s="88">
         <v>169</v>
       </c>
@@ -64496,7 +64500,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" s="88">
         <v>170</v>
       </c>
@@ -64528,7 +64532,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" s="88">
         <v>171</v>
       </c>
@@ -64560,7 +64564,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" s="88">
         <v>172</v>
       </c>
@@ -64592,7 +64596,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" s="88">
         <v>173</v>
       </c>
@@ -64624,7 +64628,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" s="88">
         <v>174</v>
       </c>
@@ -64656,7 +64660,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" s="88">
         <v>175</v>
       </c>
@@ -64688,7 +64692,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" s="88">
         <v>176</v>
       </c>
@@ -64720,7 +64724,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" s="88">
         <v>177</v>
       </c>
@@ -64752,7 +64756,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" s="88">
         <v>178</v>
       </c>
@@ -64784,7 +64788,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" s="88">
         <v>179</v>
       </c>
@@ -64816,7 +64820,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" s="88">
         <v>180</v>
       </c>
@@ -64848,7 +64852,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" s="88">
         <v>181</v>
       </c>
@@ -64880,7 +64884,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" s="88">
         <v>182</v>
       </c>
@@ -64912,7 +64916,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" s="88">
         <v>183</v>
       </c>
@@ -64944,7 +64948,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" s="88">
         <v>184</v>
       </c>
@@ -64976,7 +64980,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" s="88">
         <v>185</v>
       </c>
@@ -65008,7 +65012,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" s="88">
         <v>186</v>
       </c>
@@ -65040,7 +65044,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" s="88">
         <v>187</v>
       </c>
@@ -65072,7 +65076,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" s="88">
         <v>188</v>
       </c>
@@ -65104,7 +65108,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" s="88">
         <v>189</v>
       </c>
@@ -65136,7 +65140,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" s="88">
         <v>190</v>
       </c>
@@ -65168,7 +65172,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" s="88">
         <v>191</v>
       </c>
@@ -65200,7 +65204,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" s="88">
         <v>192</v>
       </c>
@@ -65232,7 +65236,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" s="88">
         <v>193</v>
       </c>
@@ -65264,7 +65268,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" s="88">
         <v>194</v>
       </c>
@@ -65296,7 +65300,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" s="88">
         <v>195</v>
       </c>
@@ -65328,7 +65332,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" s="88">
         <v>196</v>
       </c>
@@ -65360,7 +65364,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" s="88">
         <v>197</v>
       </c>
@@ -65392,7 +65396,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" s="88">
         <v>198</v>
       </c>
@@ -65424,7 +65428,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" s="88">
         <v>199</v>
       </c>
@@ -65456,7 +65460,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" s="88">
         <v>200</v>
       </c>
@@ -65488,7 +65492,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" s="88">
         <v>201</v>
       </c>
@@ -65520,7 +65524,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" s="88">
         <v>202</v>
       </c>
@@ -65552,7 +65556,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" s="88">
         <v>203</v>
       </c>
@@ -65584,7 +65588,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" s="88">
         <v>204</v>
       </c>
@@ -65616,7 +65620,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" s="88">
         <v>205</v>
       </c>
@@ -65648,7 +65652,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211" s="88">
         <v>206</v>
       </c>
@@ -65680,7 +65684,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" s="88">
         <v>207</v>
       </c>
@@ -65712,7 +65716,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" s="88">
         <v>208</v>
       </c>
@@ -65744,7 +65748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" s="88">
         <v>209</v>
       </c>
@@ -65776,7 +65780,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" s="88">
         <v>210</v>
       </c>
@@ -65808,7 +65812,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" s="88">
         <v>211</v>
       </c>
@@ -65840,7 +65844,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" s="88">
         <v>212</v>
       </c>
@@ -65872,7 +65876,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" s="88">
         <v>213</v>
       </c>
@@ -65904,7 +65908,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" s="88">
         <v>214</v>
       </c>
@@ -65936,7 +65940,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" s="88">
         <v>215</v>
       </c>
@@ -65968,7 +65972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" s="88">
         <v>216</v>
       </c>
@@ -66000,7 +66004,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" s="88">
         <v>217</v>
       </c>
@@ -66032,7 +66036,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" s="88">
         <v>218</v>
       </c>
@@ -66064,7 +66068,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" s="88">
         <v>219</v>
       </c>
@@ -66096,7 +66100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" s="88">
         <v>220</v>
       </c>
@@ -66128,7 +66132,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226" s="88">
         <v>221</v>
       </c>
@@ -66160,7 +66164,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" s="88">
         <v>222</v>
       </c>
@@ -66192,7 +66196,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" s="88">
         <v>223</v>
       </c>
@@ -66224,7 +66228,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" s="88">
         <v>224</v>
       </c>
@@ -66256,7 +66260,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" s="88">
         <v>225</v>
       </c>
@@ -66288,7 +66292,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" s="88">
         <v>226</v>
       </c>
@@ -66320,7 +66324,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" s="88">
         <v>227</v>
       </c>
@@ -66352,7 +66356,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" s="88">
         <v>228</v>
       </c>
@@ -66384,7 +66388,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" s="88">
         <v>229</v>
       </c>
@@ -66416,7 +66420,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" s="88">
         <v>230</v>
       </c>
@@ -66448,7 +66452,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" s="88">
         <v>231</v>
       </c>
@@ -66480,7 +66484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" s="88">
         <v>232</v>
       </c>
@@ -66512,7 +66516,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" s="88">
         <v>233</v>
       </c>
@@ -66544,7 +66548,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" s="88">
         <v>234</v>
       </c>
@@ -66576,7 +66580,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" s="88">
         <v>235</v>
       </c>
@@ -66608,7 +66612,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" s="88">
         <v>236</v>
       </c>
@@ -66640,7 +66644,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" s="88">
         <v>237</v>
       </c>
@@ -66672,7 +66676,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" s="88">
         <v>238</v>
       </c>
@@ -66704,7 +66708,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" s="88">
         <v>239</v>
       </c>
@@ -66736,7 +66740,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" s="88">
         <v>240</v>
       </c>
@@ -66768,7 +66772,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" s="88">
         <v>241</v>
       </c>
@@ -66800,7 +66804,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247" s="88">
         <v>242</v>
       </c>
@@ -66832,7 +66836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" s="88">
         <v>243</v>
       </c>
@@ -66864,7 +66868,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" s="88">
         <v>244</v>
       </c>
@@ -66896,7 +66900,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="250" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" s="88">
         <v>245</v>
       </c>
@@ -66928,7 +66932,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="251" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" s="88">
         <v>246</v>
       </c>
@@ -66960,7 +66964,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="252" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" s="88">
         <v>247</v>
       </c>
@@ -66992,7 +66996,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="253" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" s="88">
         <v>248</v>
       </c>
@@ -67024,7 +67028,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="254" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" s="88">
         <v>249</v>
       </c>
@@ -67056,7 +67060,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="255" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255" s="88">
         <v>250</v>
       </c>
@@ -67088,7 +67092,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="256" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B256" s="88">
         <v>251</v>
       </c>
@@ -67120,7 +67124,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="257" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" s="88">
         <v>252</v>
       </c>
@@ -67152,7 +67156,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" s="88">
         <v>253</v>
       </c>
@@ -67184,7 +67188,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="259" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" s="88">
         <v>254</v>
       </c>
@@ -67216,7 +67220,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260" s="88">
         <v>255</v>
       </c>
@@ -67248,7 +67252,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" s="88">
         <v>256</v>
       </c>
@@ -67280,7 +67284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262" s="88">
         <v>257</v>
       </c>
@@ -67312,7 +67316,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" s="88">
         <v>258</v>
       </c>
@@ -67344,7 +67348,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" s="88">
         <v>259</v>
       </c>
@@ -67376,7 +67380,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" s="88">
         <v>260</v>
       </c>
@@ -67408,7 +67412,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="266" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" s="88">
         <v>261</v>
       </c>
@@ -67440,7 +67444,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" s="88">
         <v>262</v>
       </c>
@@ -67472,7 +67476,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="268" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" s="88">
         <v>263</v>
       </c>
@@ -67504,7 +67508,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" s="88">
         <v>264</v>
       </c>
@@ -67536,7 +67540,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" s="88">
         <v>265</v>
       </c>
@@ -67568,7 +67572,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" s="88">
         <v>266</v>
       </c>
@@ -67600,7 +67604,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="272" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" s="88">
         <v>267</v>
       </c>
@@ -67632,7 +67636,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="273" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" s="88">
         <v>268</v>
       </c>
@@ -67664,7 +67668,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="274" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" s="88">
         <v>269</v>
       </c>
@@ -67696,7 +67700,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="275" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" s="88">
         <v>270</v>
       </c>
@@ -67728,7 +67732,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="276" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" s="88">
         <v>271</v>
       </c>
@@ -67760,7 +67764,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="277" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" s="88">
         <v>272</v>
       </c>
@@ -67792,7 +67796,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="278" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" s="88">
         <v>273</v>
       </c>
@@ -67824,7 +67828,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="279" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" s="88">
         <v>274</v>
       </c>
@@ -67856,7 +67860,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="280" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" s="88">
         <v>275</v>
       </c>
@@ -67888,7 +67892,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="281" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" s="88">
         <v>276</v>
       </c>
@@ -67920,7 +67924,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="282" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" s="88">
         <v>277</v>
       </c>
@@ -67952,7 +67956,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="283" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" s="88">
         <v>278</v>
       </c>
@@ -67984,7 +67988,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="284" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284" s="88">
         <v>279</v>
       </c>
@@ -68016,7 +68020,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="285" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" s="88">
         <v>280</v>
       </c>
@@ -68048,7 +68052,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="286" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" s="88">
         <v>281</v>
       </c>
@@ -68080,7 +68084,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287" s="88">
         <v>282</v>
       </c>
@@ -68112,7 +68116,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="288" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" s="88">
         <v>283</v>
       </c>
@@ -68144,7 +68148,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" s="88">
         <v>284</v>
       </c>
@@ -68176,7 +68180,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" s="88">
         <v>285</v>
       </c>
@@ -68208,7 +68212,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" s="88">
         <v>286</v>
       </c>
@@ -68240,7 +68244,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" s="88">
         <v>287</v>
       </c>
@@ -68272,7 +68276,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B293" s="88">
         <v>288</v>
       </c>
@@ -68304,7 +68308,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" s="88">
         <v>289</v>
       </c>
@@ -68336,7 +68340,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" s="88">
         <v>290</v>
       </c>
@@ -68368,7 +68372,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="296" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296" s="88">
         <v>291</v>
       </c>
@@ -68400,7 +68404,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297" s="88">
         <v>292</v>
       </c>
@@ -68432,7 +68436,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298" s="88">
         <v>293</v>
       </c>
@@ -68464,7 +68468,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299" s="88">
         <v>294</v>
       </c>
@@ -68496,7 +68500,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300" s="88">
         <v>295</v>
       </c>
@@ -68528,7 +68532,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="301" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B301" s="88">
         <v>296</v>
       </c>
@@ -68560,7 +68564,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="302" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B302" s="88">
         <v>297</v>
       </c>
@@ -68592,7 +68596,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B303" s="88">
         <v>298</v>
       </c>
@@ -68624,7 +68628,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="304" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B304" s="88">
         <v>299</v>
       </c>
@@ -68656,7 +68660,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B305" s="88">
         <v>300</v>
       </c>
@@ -68688,7 +68692,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B306" s="88">
         <v>301</v>
       </c>
@@ -68720,7 +68724,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B307" s="88">
         <v>302</v>
       </c>
@@ -68752,7 +68756,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B308" s="88">
         <v>303</v>
       </c>
@@ -68784,7 +68788,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B309" s="88">
         <v>304</v>
       </c>
@@ -68816,7 +68820,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B310" s="88">
         <v>305</v>
       </c>
@@ -68848,7 +68852,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="311" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B311" s="88">
         <v>306</v>
       </c>
@@ -68880,7 +68884,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="312" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B312" s="88">
         <v>307</v>
       </c>
@@ -68912,7 +68916,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B313" s="88">
         <v>308</v>
       </c>
@@ -68944,7 +68948,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B314" s="88">
         <v>309</v>
       </c>
@@ -68976,7 +68980,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B315" s="88">
         <v>310</v>
       </c>
@@ -69008,7 +69012,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B316" s="88">
         <v>311</v>
       </c>
@@ -69040,7 +69044,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B317" s="88">
         <v>312</v>
       </c>
@@ -69072,7 +69076,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="318" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B318" s="88">
         <v>313</v>
       </c>
@@ -69104,7 +69108,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="319" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B319" s="88">
         <v>314</v>
       </c>
@@ -69136,7 +69140,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B320" s="88">
         <v>315</v>
       </c>
@@ -69168,7 +69172,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="321" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B321" s="88">
         <v>316</v>
       </c>
@@ -69200,7 +69204,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="322" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B322" s="88">
         <v>317</v>
       </c>
@@ -69232,7 +69236,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="323" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B323" s="88">
         <v>318</v>
       </c>
@@ -69264,7 +69268,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="324" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B324" s="88">
         <v>319</v>
       </c>
@@ -69296,7 +69300,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" s="88">
         <v>320</v>
       </c>
@@ -69328,7 +69332,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="326" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B326" s="88">
         <v>321</v>
       </c>
@@ -69360,7 +69364,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="327" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B327" s="88">
         <v>322</v>
       </c>
@@ -69392,7 +69396,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="328" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B328" s="88">
         <v>323</v>
       </c>
@@ -69424,7 +69428,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="329" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B329" s="88">
         <v>324</v>
       </c>
@@ -69456,7 +69460,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="330" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B330" s="88">
         <v>325</v>
       </c>
@@ -69488,7 +69492,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="331" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B331" s="88">
         <v>326</v>
       </c>
@@ -69520,7 +69524,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="332" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B332" s="88">
         <v>327</v>
       </c>
@@ -69552,7 +69556,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="333" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B333" s="88">
         <v>328</v>
       </c>
@@ -69584,7 +69588,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="334" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B334" s="88">
         <v>329</v>
       </c>
@@ -69616,7 +69620,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="335" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B335" s="88">
         <v>330</v>
       </c>
@@ -69648,7 +69652,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" s="88">
         <v>331</v>
       </c>
@@ -69680,7 +69684,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="337" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B337" s="88">
         <v>332</v>
       </c>
@@ -69712,7 +69716,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" s="88">
         <v>333</v>
       </c>
@@ -69744,7 +69748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="339" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B339" s="88">
         <v>334</v>
       </c>
@@ -69776,7 +69780,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="340" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B340" s="88">
         <v>335</v>
       </c>
@@ -69808,7 +69812,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="341" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B341" s="88">
         <v>336</v>
       </c>
@@ -69840,7 +69844,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="342" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B342" s="88">
         <v>337</v>
       </c>
@@ -69872,7 +69876,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="343" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="343" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B343" s="88">
         <v>338</v>
       </c>
@@ -69904,7 +69908,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="344" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="344" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B344" s="88">
         <v>339</v>
       </c>
@@ -69936,7 +69940,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="345" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B345" s="88">
         <v>340</v>
       </c>
@@ -69968,7 +69972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="346" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B346" s="88">
         <v>341</v>
       </c>
@@ -70000,7 +70004,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="347" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B347" s="88">
         <v>342</v>
       </c>
@@ -70032,7 +70036,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="348" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B348" s="88">
         <v>343</v>
       </c>
@@ -70064,7 +70068,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="349" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B349" s="88">
         <v>344</v>
       </c>
@@ -70096,7 +70100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="350" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B350" s="88">
         <v>345</v>
       </c>
@@ -70128,7 +70132,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="351" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B351" s="88">
         <v>346</v>
       </c>
@@ -70160,7 +70164,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="352" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B352" s="88">
         <v>347</v>
       </c>
@@ -70192,7 +70196,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="353" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="353" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B353" s="88">
         <v>348</v>
       </c>
@@ -70224,7 +70228,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" s="88">
         <v>349</v>
       </c>
@@ -70256,7 +70260,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="355" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B355" s="88">
         <v>350</v>
       </c>
@@ -70288,7 +70292,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" s="88">
         <v>351</v>
       </c>
@@ -70320,7 +70324,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="357" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B357" s="88">
         <v>352</v>
       </c>
@@ -70352,7 +70356,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="358" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B358" s="88">
         <v>353</v>
       </c>
@@ -70384,7 +70388,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="359" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B359" s="88">
         <v>354</v>
       </c>
@@ -70416,7 +70420,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="360" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B360" s="88">
         <v>355</v>
       </c>
@@ -70448,7 +70452,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="361" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="361" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B361" s="88">
         <v>356</v>
       </c>
@@ -70480,7 +70484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="362" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B362" s="88">
         <v>357</v>
       </c>
@@ -70512,7 +70516,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="363" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="363" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B363" s="88">
         <v>358</v>
       </c>
@@ -70544,7 +70548,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="364" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B364" s="88">
         <v>359</v>
       </c>
@@ -70576,7 +70580,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="365" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B365" s="88">
         <v>360</v>
       </c>
@@ -70608,7 +70612,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="366" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B366" s="88">
         <v>361</v>
       </c>
@@ -70640,7 +70644,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="367" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B367" s="88">
         <v>362</v>
       </c>
@@ -70672,7 +70676,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="368" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B368" s="88">
         <v>363</v>
       </c>
@@ -70704,7 +70708,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="369" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B369" s="88">
         <v>364</v>
       </c>
@@ -70736,7 +70740,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="370" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B370" s="88">
         <v>365</v>
       </c>
@@ -70768,7 +70772,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="371" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="371" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B371" s="88">
         <v>366</v>
       </c>
@@ -70800,7 +70804,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" s="88">
         <v>367</v>
       </c>
@@ -70832,7 +70836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="373" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="373" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B373" s="88">
         <v>368</v>
       </c>
@@ -70864,7 +70868,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="374" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="374" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B374" s="88">
         <v>369</v>
       </c>
@@ -70896,7 +70900,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B375" s="88">
         <v>370</v>
       </c>
@@ -70928,7 +70932,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B376" s="88">
         <v>371</v>
       </c>
@@ -70960,7 +70964,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="377" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B377" s="88">
         <v>372</v>
       </c>
@@ -70992,7 +70996,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="378" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B378" s="88">
         <v>373</v>
       </c>
@@ -71024,7 +71028,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="379" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B379" s="88">
         <v>374</v>
       </c>
@@ -71056,7 +71060,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="380" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B380" s="88">
         <v>375</v>
       </c>
@@ -71088,7 +71092,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="381" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B381" s="88">
         <v>376</v>
       </c>
@@ -71120,7 +71124,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" s="88">
         <v>377</v>
       </c>
@@ -71152,7 +71156,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="383" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="383" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B383" s="88">
         <v>378</v>
       </c>
@@ -71184,7 +71188,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="384" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="384" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B384" s="88">
         <v>379</v>
       </c>
@@ -71216,7 +71220,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="385" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B385" s="88">
         <v>380</v>
       </c>
@@ -71248,7 +71252,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="386" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B386" s="88">
         <v>381</v>
       </c>
@@ -71280,7 +71284,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="387" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B387" s="88">
         <v>382</v>
       </c>
@@ -71312,7 +71316,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="388" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B388" s="88">
         <v>383</v>
       </c>
@@ -71344,7 +71348,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="389" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B389" s="88">
         <v>384</v>
       </c>
@@ -71376,7 +71380,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="390" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B390" s="88">
         <v>385</v>
       </c>
@@ -71408,7 +71412,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="391" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B391" s="88">
         <v>386</v>
       </c>
@@ -71440,7 +71444,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="392" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B392" s="88">
         <v>387</v>
       </c>
@@ -71472,7 +71476,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="393" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B393" s="88">
         <v>388</v>
       </c>
@@ -71504,7 +71508,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="394" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B394" s="88">
         <v>389</v>
       </c>
@@ -71536,7 +71540,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="395" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B395" s="88">
         <v>390</v>
       </c>
@@ -71568,7 +71572,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B396" s="88">
         <v>391</v>
       </c>
@@ -71600,7 +71604,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B397" s="88">
         <v>392</v>
       </c>
@@ -71632,7 +71636,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B398" s="88">
         <v>393</v>
       </c>
@@ -71664,7 +71668,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="399" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B399" s="88">
         <v>394</v>
       </c>
@@ -71696,7 +71700,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B400" s="88">
         <v>395</v>
       </c>
@@ -71728,7 +71732,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="401" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B401" s="88">
         <v>396</v>
       </c>
@@ -71760,7 +71764,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="402" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="402" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B402" s="88">
         <v>397</v>
       </c>
@@ -71792,7 +71796,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="403" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B403" s="88">
         <v>398</v>
       </c>
@@ -71824,7 +71828,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="404" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B404" s="88">
         <v>399</v>
       </c>
@@ -71856,7 +71860,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="405" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="405" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B405" s="88">
         <v>400</v>
       </c>
@@ -71888,7 +71892,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="406" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B406" s="88">
         <v>401</v>
       </c>
@@ -71920,7 +71924,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="407" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="407" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B407" s="88">
         <v>402</v>
       </c>
@@ -71952,7 +71956,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="408" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="408" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B408" s="88">
         <v>403</v>
       </c>
@@ -71984,7 +71988,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="409" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="409" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B409" s="88">
         <v>404</v>
       </c>
@@ -72016,7 +72020,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="410" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B410" s="88">
         <v>405</v>
       </c>
@@ -72048,7 +72052,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="411" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="411" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B411" s="88">
         <v>406</v>
       </c>
@@ -72080,7 +72084,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="412" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B412" s="88">
         <v>407</v>
       </c>
@@ -72112,7 +72116,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="413" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B413" s="88">
         <v>408</v>
       </c>
@@ -72144,7 +72148,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="414" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="414" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B414" s="88">
         <v>409</v>
       </c>
@@ -72176,7 +72180,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="415" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="415" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B415" s="88">
         <v>410</v>
       </c>
@@ -72208,7 +72212,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="416" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="416" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B416" s="88">
         <v>411</v>
       </c>
@@ -72240,7 +72244,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="417" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B417" s="88">
         <v>412</v>
       </c>
@@ -72272,7 +72276,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="418" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B418" s="88">
         <v>413</v>
       </c>
@@ -72304,7 +72308,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="419" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B419" s="88">
         <v>414</v>
       </c>
@@ -72336,7 +72340,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="420" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B420" s="88">
         <v>415</v>
       </c>
@@ -72368,7 +72372,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B421" s="88">
         <v>416</v>
       </c>
@@ -72400,7 +72404,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B422" s="88">
         <v>417</v>
       </c>
@@ -72432,7 +72436,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B423" s="88">
         <v>418</v>
       </c>
@@ -72464,7 +72468,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B424" s="88">
         <v>419</v>
       </c>
@@ -72496,7 +72500,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B425" s="88">
         <v>420</v>
       </c>
@@ -72528,7 +72532,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B426" s="88">
         <v>421</v>
       </c>
@@ -72560,7 +72564,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B427" s="88">
         <v>422</v>
       </c>
@@ -72592,7 +72596,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B428" s="88">
         <v>423</v>
       </c>
@@ -72624,7 +72628,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B429" s="88">
         <v>424</v>
       </c>
@@ -72656,7 +72660,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B430" s="88">
         <v>425</v>
       </c>
@@ -72688,7 +72692,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B431" s="88">
         <v>426</v>
       </c>
@@ -72720,7 +72724,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B432" s="88">
         <v>427</v>
       </c>
@@ -72752,7 +72756,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B433" s="88">
         <v>428</v>
       </c>
@@ -72784,7 +72788,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B434" s="88">
         <v>429</v>
       </c>
@@ -72816,7 +72820,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B435" s="88">
         <v>430</v>
       </c>
@@ -72848,7 +72852,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B436" s="88">
         <v>431</v>
       </c>
@@ -72880,7 +72884,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B437" s="88">
         <v>432</v>
       </c>
@@ -72912,7 +72916,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B438" s="88">
         <v>433</v>
       </c>
@@ -72944,7 +72948,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B439" s="88">
         <v>434</v>
       </c>
@@ -72976,7 +72980,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B440" s="88">
         <v>435</v>
       </c>
@@ -73008,7 +73012,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B441" s="88">
         <v>436</v>
       </c>
@@ -73040,7 +73044,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B442" s="88">
         <v>437</v>
       </c>
@@ -73072,7 +73076,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B443" s="88">
         <v>438</v>
       </c>
@@ -73104,7 +73108,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B444" s="88">
         <v>439</v>
       </c>
@@ -73136,7 +73140,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B445" s="88">
         <v>440</v>
       </c>
@@ -73168,7 +73172,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="446" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="446" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B446" s="88">
         <v>441</v>
       </c>
@@ -73200,7 +73204,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="447" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B447" s="88">
         <v>442</v>
       </c>
@@ -73232,7 +73236,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B448" s="88">
         <v>443</v>
       </c>
@@ -73264,7 +73268,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="449" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="449" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B449" s="88">
         <v>444</v>
       </c>
@@ -73296,7 +73300,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="450" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B450" s="88">
         <v>445</v>
       </c>
@@ -73328,7 +73332,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="451" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B451" s="88">
         <v>446</v>
       </c>
@@ -73360,7 +73364,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="452" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B452" s="88">
         <v>447</v>
       </c>
@@ -73392,7 +73396,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B453" s="88">
         <v>448</v>
       </c>
@@ -73424,7 +73428,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="454" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B454" s="88">
         <v>449</v>
       </c>
@@ -73456,7 +73460,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="455" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B455" s="88">
         <v>450</v>
       </c>
@@ -73488,7 +73492,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="456" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B456" s="88">
         <v>451</v>
       </c>
@@ -73520,7 +73524,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="457" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B457" s="88">
         <v>452</v>
       </c>
@@ -73552,7 +73556,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="458" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B458" s="88">
         <v>453</v>
       </c>
@@ -73584,7 +73588,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="459" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B459" s="88">
         <v>454</v>
       </c>
@@ -73616,7 +73620,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="460" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B460" s="88">
         <v>455</v>
       </c>
@@ -73648,7 +73652,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B461" s="88">
         <v>456</v>
       </c>
@@ -73680,7 +73684,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="462" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B462" s="88">
         <v>457</v>
       </c>
@@ -73712,7 +73716,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="463" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B463" s="88">
         <v>458</v>
       </c>
@@ -73744,7 +73748,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="464" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B464" s="88">
         <v>459</v>
       </c>
@@ -73776,7 +73780,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B465" s="88">
         <v>460</v>
       </c>
@@ -73808,7 +73812,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B466" s="88">
         <v>461</v>
       </c>
@@ -73840,7 +73844,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B467" s="88">
         <v>462</v>
       </c>
@@ -73872,7 +73876,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B468" s="88">
         <v>463</v>
       </c>
@@ -73904,7 +73908,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B469" s="88">
         <v>464</v>
       </c>
@@ -73936,7 +73940,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B470" s="88">
         <v>465</v>
       </c>
@@ -73968,7 +73972,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B471" s="88">
         <v>466</v>
       </c>
@@ -74000,7 +74004,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B472" s="88">
         <v>467</v>
       </c>
@@ -74032,7 +74036,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B473" s="88">
         <v>468</v>
       </c>
@@ -74064,7 +74068,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B474" s="88">
         <v>469</v>
       </c>
@@ -74096,7 +74100,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B475" s="88">
         <v>470</v>
       </c>
@@ -74128,7 +74132,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B476" s="88">
         <v>471</v>
       </c>
@@ -74160,7 +74164,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B477" s="88">
         <v>472</v>
       </c>
@@ -74192,7 +74196,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B478" s="88">
         <v>473</v>
       </c>
@@ -74224,7 +74228,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B479" s="88">
         <v>474</v>
       </c>
@@ -74256,7 +74260,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B480" s="88">
         <v>475</v>
       </c>
@@ -74288,7 +74292,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="481" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B481" s="88">
         <v>476</v>
       </c>
@@ -74320,7 +74324,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="482" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="482" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B482" s="88">
         <v>477</v>
       </c>
@@ -74352,7 +74356,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="483" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="483" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B483" s="88">
         <v>478</v>
       </c>
@@ -74384,7 +74388,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="484" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="484" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B484" s="88">
         <v>479</v>
       </c>
@@ -74416,7 +74420,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="485" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="485" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B485" s="88">
         <v>480</v>
       </c>
@@ -74448,7 +74452,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="486" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="486" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B486" s="88">
         <v>481</v>
       </c>
@@ -74480,7 +74484,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B487" s="88">
         <v>482</v>
       </c>
@@ -74512,7 +74516,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="488" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B488" s="88">
         <v>483</v>
       </c>
@@ -74544,7 +74548,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="489" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="489" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B489" s="88">
         <v>484</v>
       </c>
@@ -74576,7 +74580,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="490" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B490" s="88">
         <v>485</v>
       </c>
@@ -74608,7 +74612,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="491" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B491" s="88">
         <v>486</v>
       </c>
@@ -74640,7 +74644,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B492" s="88">
         <v>487</v>
       </c>
@@ -74672,7 +74676,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="493" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B493" s="88">
         <v>488</v>
       </c>
@@ -74704,7 +74708,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="494" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B494" s="88">
         <v>489</v>
       </c>
@@ -74736,7 +74740,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="495" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B495" s="88">
         <v>490</v>
       </c>
@@ -74768,7 +74772,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="496" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B496" s="88">
         <v>491</v>
       </c>
@@ -74800,7 +74804,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="497" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="497" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B497" s="88">
         <v>492</v>
       </c>
@@ -74832,7 +74836,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="498" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="498" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B498" s="88">
         <v>493</v>
       </c>
@@ -74864,7 +74868,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="499" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="499" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B499" s="88">
         <v>494</v>
       </c>
@@ -74896,7 +74900,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="500" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B500" s="90">
         <v>495</v>
       </c>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBD9F3F-2C05-4304-85E6-31F2CD5A1440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846A0B87-853F-453E-B4E4-B120E115E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42675,27 +42675,27 @@
       </c>
       <c r="U17" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="123">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W17" s="123">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="123">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="123">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="123">
         <f t="shared" si="5"/>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="AD20" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR20))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20" s="124" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
@@ -43314,7 +43314,7 @@
       </c>
       <c r="AF20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_draw")</f>
@@ -43326,7 +43326,7 @@
       </c>
       <c r="AI20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE20,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE20,$F$7:$F$78)</f>
@@ -43334,23 +43334,23 @@
       </c>
       <c r="AL20" s="123">
         <f>AI20-AJ20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM20" s="123">
         <f>AL20-AL24</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN20" s="123">
         <f>AF20*3+AG20</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO20" s="123">
         <f>AN20/AN24*10+BA20</f>
-        <v>3.4805825242718447</v>
+        <v>8.9805825242718456</v>
       </c>
       <c r="AP20" s="123">
         <f>AO20*10000000+BI20*100+AM20/AM24*10+AI20/AI24*1++IF(AQ20=0,ROW(),AQ20)/2000000</f>
-        <v>34805927.13518478</v>
+        <v>89805932.851851463</v>
       </c>
       <c r="AQ20" s="126">
         <f>VLOOKUP(AE20,db_fifarank,2,FALSE)</f>
@@ -43358,7 +43358,7 @@
       </c>
       <c r="AR20" s="125">
         <f>AP20/AP24</f>
-        <v>0.46407897793145042</v>
+        <v>0.99999998886487829</v>
       </c>
       <c r="AS20" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J21,"1C")</f>
@@ -43501,11 +43501,11 @@
       </c>
       <c r="J21" s="30" t="str">
         <f>VLOOKUP(1,AD20:AN23,2,FALSE)</f>
-        <v>Scotland</v>
+        <v>Brazil</v>
       </c>
       <c r="K21" s="31">
         <f>L21+M21+N21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="31">
         <f>VLOOKUP(1,AD20:AN23,3,FALSE)</f>
@@ -43513,7 +43513,7 @@
       </c>
       <c r="M21" s="31">
         <f>VLOOKUP(1,AD20:AN23,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="31">
         <f>VLOOKUP(1,AD20:AN23,5,FALSE)</f>
@@ -43521,11 +43521,11 @@
       </c>
       <c r="O21" s="31" t="str">
         <f>VLOOKUP(1,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD20:AN23,7,FALSE)</f>
-        <v>1 - 0</v>
+        <v>4 - 1</v>
       </c>
       <c r="P21" s="32">
         <f>L21*3+M21</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" s="123">
         <f>DATE(2026,6,15)+TIME(14,0,0)+gmt_delta</f>
@@ -43573,7 +43573,7 @@
       </c>
       <c r="AD21" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR21))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE21" s="124" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AF21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_draw")</f>
@@ -43593,7 +43593,7 @@
       </c>
       <c r="AI21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE21,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE21,$F$7:$F$78)</f>
@@ -43601,23 +43601,23 @@
       </c>
       <c r="AL21" s="123">
         <f>AI21-AJ21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" s="123">
         <f>AL21-AL24</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN21" s="123">
         <f>AF21*3+AG21</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO21" s="123">
         <f>AN21/AN24*10+BA21</f>
-        <v>3.4805825242718447</v>
+        <v>8.9805825242718456</v>
       </c>
       <c r="AP21" s="123">
         <f>AO21*10000000+BI21*100+AM21/AM24*10+AI21/AI24*1++IF(AQ21=0,ROW(),AQ21)/2000000</f>
-        <v>34805927.135182135</v>
+        <v>89805929.95184882</v>
       </c>
       <c r="AQ21" s="126">
         <f>VLOOKUP(AE21,db_fifarank,2,FALSE)</f>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="AR21" s="125">
         <f>AP21/AP24</f>
-        <v>0.46407897793141517</v>
+        <v>0.99999995657299601</v>
       </c>
       <c r="AS21" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J22,"2C")</f>
@@ -43772,15 +43772,15 @@
       </c>
       <c r="J22" s="33" t="str">
         <f>VLOOKUP(2,AD20:AN23,2,FALSE)</f>
-        <v>Brazil</v>
+        <v>Morocco</v>
       </c>
       <c r="K22" s="23">
         <f>L22+M22+N22</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="23">
         <f>VLOOKUP(2,AD20:AN23,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="23">
         <f>VLOOKUP(2,AD20:AN23,4,FALSE)</f>
@@ -43792,11 +43792,11 @@
       </c>
       <c r="O22" s="23" t="str">
         <f>VLOOKUP(2,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD20:AN23,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 1</v>
       </c>
       <c r="P22" s="34">
         <f>L22*3+M22</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R22" s="123">
         <f>DATE(2026,6,15)+TIME(8,0,0)+gmt_delta</f>
@@ -43860,7 +43860,7 @@
       </c>
       <c r="AH22" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE22 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE22,$G$7:$G$78)</f>
@@ -43868,11 +43868,11 @@
       </c>
       <c r="AJ22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE22,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL22" s="123">
         <f>AI22-AJ22</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AM22" s="123">
         <f>AL22-AL24</f>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="AR22" s="125">
         <f>AP22/AP24</f>
-        <v>8.6113990622283044E-12</v>
+        <v>7.1916740052548863E-12</v>
       </c>
       <c r="AT22" s="126" cm="1">
         <f t="array" ref="AT22">SUMPRODUCT(($S$7:$S$78=AE22&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE22&amp;"_win")*($U$7:$U$78))</f>
@@ -44036,23 +44036,23 @@
       </c>
       <c r="J23" s="33" t="str">
         <f>VLOOKUP(3,AD20:AN23,2,FALSE)</f>
-        <v>Morocco</v>
+        <v>Scotland</v>
       </c>
       <c r="K23" s="23">
         <f>L23+M23+N23</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="23">
         <f>VLOOKUP(3,AD20:AN23,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="23">
         <f>VLOOKUP(3,AD20:AN23,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="23">
         <f>VLOOKUP(3,AD20:AN23,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="23" t="str">
         <f>VLOOKUP(3,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD20:AN23,7,FALSE)</f>
@@ -44060,7 +44060,7 @@
       </c>
       <c r="P23" s="34">
         <f>L23*3+M23</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R23" s="123">
         <f>DATE(2026,6,16)+TIME(8,0,0)+gmt_delta</f>
@@ -44108,7 +44108,7 @@
       </c>
       <c r="AD23" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR23))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE23" s="124" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
@@ -44124,7 +44124,7 @@
       </c>
       <c r="AH23" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE23 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE23,$G$7:$G$78)</f>
@@ -44132,15 +44132,15 @@
       </c>
       <c r="AJ23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE23,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL23" s="123">
         <f>AI23-AJ23</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" s="123">
         <f>AL23-AL24</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN23" s="123">
         <f>AF23*3+AG23</f>
@@ -44148,11 +44148,11 @@
       </c>
       <c r="AO23" s="123">
         <f>AN23/AN24*10+BA23</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AP23" s="123">
         <f>AO23*10000000+BI23*100+AM23/AM24*10+AI23/AI24*1++IF(AQ23=0,ROW(),AQ23)/2000000</f>
-        <v>75000007.167415842</v>
+        <v>60000005.200749181</v>
       </c>
       <c r="AQ23" s="126">
         <f>VLOOKUP(AE23,db_fifarank,2,FALSE)</f>
@@ -44160,7 +44160,7 @@
       </c>
       <c r="AR23" s="125">
         <f>AP23/AP24</f>
-        <v>0.99999998666666812</v>
+        <v>0.66810735802523147</v>
       </c>
       <c r="AT23" s="126" cm="1">
         <f t="array" ref="AT23">SUMPRODUCT(($S$7:$S$78=AE23&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE23&amp;"_win")*($U$7:$U$78))</f>
@@ -44304,7 +44304,7 @@
       </c>
       <c r="K24" s="36">
         <f>L24+M24+N24</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="36">
         <f>VLOOKUP(4,AD20:AN23,3,FALSE)</f>
@@ -44316,11 +44316,11 @@
       </c>
       <c r="N24" s="36">
         <f>VLOOKUP(4,AD20:AN23,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="36" t="str">
         <f>VLOOKUP(4,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD20:AN23,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>0 - 4</v>
       </c>
       <c r="P24" s="37">
         <f>L24*3+M24</f>
@@ -44380,31 +44380,31 @@
       </c>
       <c r="AH24" s="123">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI24" s="123">
         <f>MAX(AI20:AI23)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL24" s="123">
         <f>MIN(AL20:AL23)</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AM24" s="123">
         <f>MAX(AM20:AM23)+1</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN24" s="123">
         <f>MAX(AN20:AN23)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO24" s="123">
         <f>MAX(AO20:AO23)+1</f>
-        <v>8.5</v>
+        <v>9.9805825242718456</v>
       </c>
       <c r="AP24" s="123">
         <f>MAX(AP20:AP23)+1</f>
-        <v>75000008.167415842</v>
+        <v>89805933.851851463</v>
       </c>
       <c r="AT24" s="126">
         <f>MAX(AT20:AT23)-MIN(AT20:AT23)+1</f>
@@ -44973,7 +44973,7 @@
       </c>
       <c r="AD27" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR27))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE27" s="124" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
@@ -44981,7 +44981,7 @@
       </c>
       <c r="AF27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_draw")</f>
@@ -44993,7 +44993,7 @@
       </c>
       <c r="AI27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE27,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE27,$F$7:$F$78)</f>
@@ -45001,23 +45001,23 @@
       </c>
       <c r="AL27" s="123">
         <f>AI27-AJ27</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AM27" s="123">
         <f>AL27-AL30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" s="123">
         <f>AF27*3+AG27</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO27" s="123">
         <f>AN27/AN30*10+BA27</f>
-        <v>0</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP27" s="123">
         <f>AO27*10000000+BI27*100+AM27/AM30*10+AI27/AI30*1++IF(AQ27=0,ROW(),AQ27)/2000000</f>
-        <v>0.14360889285714284</v>
+        <v>42857144.254720002</v>
       </c>
       <c r="AQ27" s="126">
         <f>VLOOKUP(AE27,db_fifarank,2,FALSE)</f>
@@ -45025,7 +45025,7 @@
       </c>
       <c r="AR27" s="125">
         <f>AP27/AP30</f>
-        <v>1.6754368732668397E-9</v>
+        <v>0.49999995361500732</v>
       </c>
       <c r="AS27" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J28,"2D")</f>
@@ -45432,15 +45432,15 @@
       </c>
       <c r="J29" s="33" t="str">
         <f>VLOOKUP(3,AD26:AN29,2,FALSE)</f>
-        <v>Turkey</v>
+        <v>Paraguay</v>
       </c>
       <c r="K29" s="23">
         <f>L29+M29+N29</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="23">
         <f>VLOOKUP(3,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="23">
         <f>VLOOKUP(3,AD26:AN29,4,FALSE)</f>
@@ -45452,11 +45452,11 @@
       </c>
       <c r="O29" s="23" t="str">
         <f>VLOOKUP(3,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD26:AN29,7,FALSE)</f>
-        <v>0 - 2</v>
+        <v>2 - 4</v>
       </c>
       <c r="P29" s="34">
         <f>L29*3+M29</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" s="123">
         <f>DATE(2026,6,17)+TIME(6,0,0)+gmt_delta</f>
@@ -45504,7 +45504,7 @@
       </c>
       <c r="AD29" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR29))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE29" s="124" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
@@ -45520,7 +45520,7 @@
       </c>
       <c r="AH29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE29,$G$7:$G$78)</f>
@@ -45528,15 +45528,15 @@
       </c>
       <c r="AJ29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE29,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL29" s="123">
         <f>AI29-AJ29</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM29" s="123">
         <f>AL29-AL30</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN29" s="123">
         <f>AF29*3+AG29</f>
@@ -45548,7 +45548,7 @@
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>1.1119106311111111</v>
+        <v>7.9951999999999996E-4</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -45556,7 +45556,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>1.2972289069829002E-8</v>
+        <v>9.3277321638210582E-12</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -45695,11 +45695,11 @@
       </c>
       <c r="J30" s="35" t="str">
         <f>VLOOKUP(4,AD26:AN29,2,FALSE)</f>
-        <v>Paraguay</v>
+        <v>Turkey</v>
       </c>
       <c r="K30" s="36">
         <f>L30+M30+N30</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="36">
         <f>VLOOKUP(4,AD26:AN29,3,FALSE)</f>
@@ -45711,11 +45711,11 @@
       </c>
       <c r="N30" s="36">
         <f>VLOOKUP(4,AD26:AN29,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="36" t="str">
         <f>VLOOKUP(4,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD26:AN29,7,FALSE)</f>
-        <v>1 - 4</v>
+        <v>0 - 3</v>
       </c>
       <c r="P30" s="37">
         <f>L30*3+M30</f>
@@ -45775,7 +45775,7 @@
       </c>
       <c r="AH30" s="123">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" s="123">
         <f>MAX(AI26:AI29)+1</f>
@@ -46803,8 +46803,12 @@
         <f>AE20</f>
         <v>Brazil</v>
       </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="20"/>
+      <c r="F35" s="19">
+        <v>3</v>
+      </c>
+      <c r="G35" s="20">
+        <v>0</v>
+      </c>
       <c r="H35" s="80" t="str">
         <f>AE22</f>
         <v>Haiti</v>
@@ -46843,11 +46847,11 @@
       </c>
       <c r="S35" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Brazil_win</v>
       </c>
       <c r="T35" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Haiti_lose</v>
       </c>
       <c r="U35" s="123">
         <f t="shared" si="8"/>
@@ -46877,9 +46881,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="123" t="str">
+      <c r="AB35" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD35" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR35))</f>
@@ -47057,8 +47061,12 @@
         <f>AE23</f>
         <v>Scotland</v>
       </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="20"/>
+      <c r="F36" s="19">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
+        <v>1</v>
+      </c>
       <c r="H36" s="80" t="str">
         <f>AE21</f>
         <v>Morocco</v>
@@ -47097,11 +47105,11 @@
       </c>
       <c r="S36" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Scotland_lose</v>
       </c>
       <c r="T36" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Morocco_win</v>
       </c>
       <c r="U36" s="123">
         <f t="shared" si="8"/>
@@ -47131,9 +47139,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="123" t="str">
+      <c r="AB36" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF36" s="123">
         <f t="shared" ref="AF36:AH36" si="16">MAX(AF32:AF35)-MIN(AF32:AF35)+1</f>
@@ -47412,8 +47420,12 @@
         <f>AE29</f>
         <v>Turkey</v>
       </c>
-      <c r="F38" s="19"/>
-      <c r="G38" s="20"/>
+      <c r="F38" s="19">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20">
+        <v>1</v>
+      </c>
       <c r="H38" s="80" t="str">
         <f>AE27</f>
         <v>Paraguay</v>
@@ -47452,11 +47464,11 @@
       </c>
       <c r="S38" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Turkey_lose</v>
       </c>
       <c r="T38" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Paraguay_win</v>
       </c>
       <c r="U38" s="123">
         <f t="shared" si="8"/>
@@ -47486,13 +47498,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB38" s="123" t="str">
+      <c r="AB38" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD38" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR38))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE38" s="124" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
@@ -47500,7 +47512,7 @@
       </c>
       <c r="AF38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_draw")</f>
@@ -47512,31 +47524,31 @@
       </c>
       <c r="AI38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE38,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE38,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL38" s="123">
         <f>AI38-AJ38</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM38" s="123">
         <f>AL38-AL42</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>3.4806451612903224</v>
+        <v>8</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>34806554.456076071</v>
+        <v>80000009.764767826</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -47544,7 +47556,7 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>0.46408732639569511</v>
+        <v>0.99999998750000163</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
@@ -47556,15 +47568,15 @@
       </c>
       <c r="AU38" s="126" cm="1">
         <f t="array" ref="AU38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV38" s="126" cm="1">
         <f t="array" ref="AV38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW38" s="126" cm="1">
         <f t="array" ref="AW38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX38" s="126">
         <f>AV38-AW38</f>
@@ -47576,11 +47588,11 @@
       </c>
       <c r="AZ38" s="126">
         <f>AT38/AT42*1000+AU38/AU42*100+AY38/AY42*10+AV38/AV42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BA38" s="126">
         <f>AZ38/AZ42</f>
-        <v>0.98064516129032253</v>
+        <v>0</v>
       </c>
       <c r="BB38" s="126" cm="1">
         <f t="array" ref="BB38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_win")*($X$7:$X$78))</f>
@@ -47588,15 +47600,15 @@
       </c>
       <c r="BC38" s="126" cm="1">
         <f t="array" ref="BC38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD38" s="126" cm="1">
         <f t="array" ref="BD38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE38" s="126" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF38" s="126">
         <f>BD38-BE38</f>
@@ -47608,11 +47620,11 @@
       </c>
       <c r="BH38" s="126">
         <f>BB38/BB42*1000+BC38/BC42*100+BG38/BG42*10+BD38/BD42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="126">
         <f>BH38/BH42</f>
-        <v>0.98064516129032253</v>
+        <v>0</v>
       </c>
       <c r="BK38" s="131">
         <v>82</v>
@@ -47685,11 +47697,11 @@
       </c>
       <c r="J39" s="30" t="str">
         <f>VLOOKUP(1,AD38:AN41,2,FALSE)</f>
-        <v>Sweden</v>
+        <v>Netherlands</v>
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
@@ -47697,7 +47709,7 @@
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="31">
         <f>VLOOKUP(1,AD38:AN41,5,FALSE)</f>
@@ -47705,11 +47717,11 @@
       </c>
       <c r="O39" s="31" t="str">
         <f>VLOOKUP(1,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD38:AN41,7,FALSE)</f>
-        <v>5 - 1</v>
+        <v>7 - 3</v>
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -47797,11 +47809,11 @@
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>3.4806451612903224</v>
+        <v>2</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>34806554.456027351</v>
+        <v>20000004.695274659</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -47809,7 +47821,7 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>0.46408732639504552</v>
+        <v>0.25000002505103042</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
@@ -47821,15 +47833,15 @@
       </c>
       <c r="AU39" s="126" cm="1">
         <f t="array" ref="AU39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV39" s="126" cm="1">
         <f t="array" ref="AV39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW39" s="126" cm="1">
         <f t="array" ref="AW39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX39" s="126">
         <f>AV39-AW39</f>
@@ -47841,11 +47853,11 @@
       </c>
       <c r="AZ39" s="126">
         <f>AT39/AT42*1000+AU39/AU42*100+AY39/AY42*10+AV39/AV42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BA39" s="126">
         <f>AZ39/AZ42</f>
-        <v>0.98064516129032253</v>
+        <v>0</v>
       </c>
       <c r="BB39" s="126" cm="1">
         <f t="array" ref="BB39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($X$7:$X$78))</f>
@@ -47853,15 +47865,15 @@
       </c>
       <c r="BC39" s="126" cm="1">
         <f t="array" ref="BC39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD39" s="126" cm="1">
         <f t="array" ref="BD39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE39" s="126" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF39" s="126">
         <f>BD39-BE39</f>
@@ -47873,11 +47885,11 @@
       </c>
       <c r="BH39" s="126">
         <f>BB39/BB42*1000+BC39/BC42*100+BG39/BG42*10+BD39/BD42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="126">
         <f>BH39/BH42</f>
-        <v>0.98064516129032253</v>
+        <v>0</v>
       </c>
       <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
@@ -47940,31 +47952,31 @@
       </c>
       <c r="J40" s="33" t="str">
         <f>VLOOKUP(2,AD38:AN41,2,FALSE)</f>
-        <v>Netherlands</v>
+        <v>Sweden</v>
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="23">
         <f>VLOOKUP(2,AD38:AN41,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="23">
         <f>VLOOKUP(2,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" s="23">
         <f>VLOOKUP(2,AD38:AN41,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="23" t="str">
         <f>VLOOKUP(2,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD38:AN41,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>6 - 6</v>
       </c>
       <c r="P40" s="34">
         <f>L40*3+M40</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R40" s="123">
         <f>DATE(2026,6,20)+TIME(13,0,0)+gmt_delta</f>
@@ -48012,7 +48024,7 @@
       </c>
       <c r="AD40" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR40))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE40" s="124" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
@@ -48028,23 +48040,23 @@
       </c>
       <c r="AH40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE40,$G$7:$G$78)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE40,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AL40" s="123">
         <f>AI40-AJ40</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM40" s="123">
         <f>AL40-AL42</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AN40" s="123">
         <f>AF40*3+AG40</f>
@@ -48052,11 +48064,11 @@
       </c>
       <c r="AO40" s="123">
         <f>AN40/AN42*10+BA40</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AP40" s="123">
         <f>AO40*10000000+BI40*100+AM40/AM42*10+AI40/AI42*1++IF(AQ40=0,ROW(),AQ40)/2000000</f>
-        <v>75000009.722979605</v>
+        <v>60000005.195201829</v>
       </c>
       <c r="AQ40" s="126">
         <f>VLOOKUP(AE40,db_fifarank,2,FALSE)</f>
@@ -48064,7 +48076,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>0.99999998666666856</v>
+        <v>0.74999996402032931</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -48153,8 +48165,12 @@
         <f>AE38</f>
         <v>Netherlands</v>
       </c>
-      <c r="F41" s="19"/>
-      <c r="G41" s="20"/>
+      <c r="F41" s="19">
+        <v>5</v>
+      </c>
+      <c r="G41" s="20">
+        <v>1</v>
+      </c>
       <c r="H41" s="80" t="str">
         <f>AE40</f>
         <v>Sweden</v>
@@ -48193,11 +48209,11 @@
       </c>
       <c r="S41" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Netherlands_win</v>
       </c>
       <c r="T41" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Sweden_lose</v>
       </c>
       <c r="U41" s="123">
         <f t="shared" si="8"/>
@@ -48227,9 +48243,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB41" s="123" t="str">
+      <c r="AB41" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD41" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR41))</f>
@@ -48277,7 +48293,7 @@
       </c>
       <c r="AP41" s="123">
         <f>AO41*10000000+BI41*100+AM41/AM42*10+AI41/AI42*1++IF(AQ41=0,ROW(),AQ41)/2000000</f>
-        <v>0.16740819166666665</v>
+        <v>0.12574152499999999</v>
       </c>
       <c r="AQ41" s="126">
         <f>VLOOKUP(AE41,db_fifarank,2,FALSE)</f>
@@ -48285,7 +48301,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>2.2321089030907787E-9</v>
+        <v>1.5717688510034155E-9</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -48485,7 +48501,7 @@
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
@@ -48497,15 +48513,15 @@
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>75000010.722979605</v>
+        <v>80000010.764767826</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -48513,15 +48529,15 @@
       </c>
       <c r="AU42" s="126">
         <f>MAX(AU38:AU41)-MIN(AU38:AU41)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV42" s="126">
         <f>MAX(AV38:AV41)-MIN(AV38:AV41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW42" s="126">
         <f>MAX(AW38:AW41)-MIN(AW38:AW41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY42" s="126">
         <f>MAX(AY38:AY41)-MIN(AY38:AY41)+1</f>
@@ -48529,7 +48545,7 @@
       </c>
       <c r="AZ42" s="126">
         <f>MAX(AZ38:AZ41)+1</f>
-        <v>51.666666666666664</v>
+        <v>1</v>
       </c>
       <c r="BB42" s="126">
         <f>MAX(BB38:BB41)-MIN(BB38:BB41)+1</f>
@@ -48537,15 +48553,15 @@
       </c>
       <c r="BC42" s="126">
         <f>MAX(BC38:BC41)-MIN(BC38:BC41)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD42" s="126">
         <f>MAX(BD38:BD41)-MIN(BD38:BD41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE42" s="126">
         <f>MAX(BE38:BE41)-MIN(BE38:BE41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BG42" s="126">
         <f>MAX(BG38:BG41)-MIN(BG38:BG41)+1</f>
@@ -48553,7 +48569,7 @@
       </c>
       <c r="BH42" s="126">
         <f>MAX(BH38:BH41)+1</f>
-        <v>51.666666666666664</v>
+        <v>1</v>
       </c>
       <c r="BK42" s="131">
         <v>76</v>
@@ -56426,7 +56442,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56469,7 +56485,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>5566.6674173566671</v>
+        <v>3066.6674173566666</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -56500,35 +56516,35 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Japan</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>1 - 1</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -56571,7 +56587,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>5066.6673595866669</v>
+        <v>2566.6673595866664</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -56602,51 +56618,51 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Morocco</v>
+        <v>Ⓓ Paraguay</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 4</v>
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
-        <v>Morocco</v>
+        <v>Scotland</v>
       </c>
       <c r="AF82" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG82" s="123">
         <f t="shared" ref="AG82:AG91" si="49">VLOOKUP($AE82,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH82" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI82" s="123">
         <f t="shared" si="41"/>
@@ -56669,15 +56685,15 @@
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>5783.3342112683331</v>
+        <v>8283.3340825083342</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
-        <v>1755.87</v>
+        <v>1498.35</v>
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
@@ -56685,11 +56701,11 @@
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Morocco</v>
+        <v>Scotland</v>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
-        <v>Ⓒ Morocco</v>
+        <v>Ⓒ Scotland</v>
       </c>
     </row>
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -56706,7 +56722,7 @@
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓕ Japan</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
@@ -56726,7 +56742,7 @@
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
@@ -56734,15 +56750,15 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
-        <v>Turkey</v>
+        <v>Paraguay</v>
       </c>
       <c r="AF83" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" s="123">
         <f t="shared" si="49"/>
@@ -56754,11 +56770,11 @@
       </c>
       <c r="AI83" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ83" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK83" s="123" t="s">
         <v>3184</v>
@@ -56773,27 +56789,27 @@
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>250.00079951999999</v>
+        <v>7816.6674184166668</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
-        <v>1599.04</v>
+        <v>1503.5</v>
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABC</v>
+        <v>ABCD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Paraguay</v>
       </c>
       <c r="AT83" s="130" t="str">
         <f>"Ⓓ "&amp;AE83</f>
-        <v>Ⓓ Turkey</v>
+        <v>Ⓓ Paraguay</v>
       </c>
     </row>
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -56808,7 +56824,7 @@
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓖ Belgium</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56848,7 +56864,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56899,11 +56915,11 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCE</v>
+        <v>ABCD</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Ecuador</v>
+        <v/>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
@@ -56922,7 +56938,7 @@
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Spain</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56942,7 +56958,7 @@
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
@@ -56962,7 +56978,7 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
@@ -57005,7 +57021,7 @@
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>5816.6674968816669</v>
+        <v>3316.6674968816665</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -57013,7 +57029,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCEF</v>
+        <v>ABCDF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57036,11 +57052,11 @@
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓗ Spain</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
@@ -57052,11 +57068,11 @@
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>0 - 0</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
@@ -57076,7 +57092,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57119,7 +57135,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>5783.3342006883331</v>
+        <v>3283.3342006883336</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57127,7 +57143,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCEFG</v>
+        <v>ABCDFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57150,7 +57166,7 @@
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Bosnia and Herzegovina</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57170,7 +57186,7 @@
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 5</v>
+        <v>2 - 3</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
@@ -57190,7 +57206,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -57233,7 +57249,7 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>5750.0009381999998</v>
+        <v>3250.0009381999998</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
@@ -57241,7 +57257,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCEFGH</v>
+        <v>ABCDFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57264,11 +57280,11 @@
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,3,FALSE)</f>
@@ -57276,7 +57292,7 @@
       </c>
       <c r="M88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,5,FALSE)</f>
@@ -57284,11 +57300,11 @@
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 5</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="123">
         <f>DATE(2026,12,5)+TIME(4,0,0)+gmt_delta</f>
@@ -57304,7 +57320,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -57355,7 +57371,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCEFGH</v>
+        <v>ABCDFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57378,7 +57394,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57418,7 +57434,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -57469,7 +57485,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCEFGH</v>
+        <v>ABCDFGH</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57492,7 +57508,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Senegal</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -57512,7 +57528,7 @@
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>0 - 1</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -57532,7 +57548,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57575,7 +57591,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>5783.3340725083326</v>
+        <v>3283.3340725083335</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -57583,7 +57599,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCEFGHK</v>
+        <v>ABCDFGHK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57606,7 +57622,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Jordan</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -57646,7 +57662,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -57697,7 +57713,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCEFGHK</v>
+        <v>ABCDFGHK</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57720,7 +57736,7 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Turkey</v>
+        <v>Ⓙ Jordan</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
@@ -57740,7 +57756,7 @@
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 2</v>
+        <v>1 - 3</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
@@ -57748,7 +57764,7 @@
       </c>
       <c r="AF92" s="123">
         <f>MAX(AF80:AF91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG92" s="123">
         <f>MAX(AG80:AG91)+1</f>
@@ -57776,7 +57792,7 @@
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
@@ -59023,11 +59039,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ABCEFGHK</v>
+        <v>ABCDFGHK</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -59055,7 +59071,7 @@
       </c>
       <c r="J3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,8,FALSE)</f>
-        <v>3E</v>
+        <v>3D</v>
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846A0B87-853F-453E-B4E4-B120E115E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D96CB73-D0D8-4EB8-BA59-1F902786D4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="str" cm="1">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="141" t="str" cm="1">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="131">
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="132"/>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="131">
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44474,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44827,7 +44827,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45095,7 +45095,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45370,7 +45370,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45635,7 +45635,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45849,7 +45849,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45960,7 +45960,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46108,7 +46108,7 @@
       </c>
       <c r="AF32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_draw")</f>
@@ -46120,31 +46120,31 @@
       </c>
       <c r="AI32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE32,$G$7:$G$78)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE32,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL32" s="123">
         <f>AI32-AJ32</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM32" s="123">
         <f>AL32-AL36</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN32" s="123">
         <f>AF32*3+AG32</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO32" s="123">
         <f>AN32/AN36*10+BA32</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP32" s="123">
         <f>AO32*10000000+BI32*100+AM32/AM36*10+AI32/AI36*1++IF(AQ32=0,ROW(),AQ32)/2000000</f>
-        <v>75000010.106634423</v>
+        <v>85714295.900865197</v>
       </c>
       <c r="AQ32" s="126">
         <f>VLOOKUP(AE32,db_fifarank,2,FALSE)</f>
@@ -46152,7 +46152,7 @@
       </c>
       <c r="AR32" s="125">
         <f>AP32/AP36</f>
-        <v>0.99999998666666867</v>
+        <v>0.99999998833333481</v>
       </c>
       <c r="AS32" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J33,"1E")</f>
@@ -46236,7 +46236,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46290,11 +46290,11 @@
       </c>
       <c r="K33" s="31">
         <f>L33+M33+N33</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="31">
         <f>VLOOKUP(1,AD32:AN35,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="31">
         <f>VLOOKUP(1,AD32:AN35,4,FALSE)</f>
@@ -46306,11 +46306,11 @@
       </c>
       <c r="O33" s="31" t="str">
         <f>VLOOKUP(1,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD32:AN35,7,FALSE)</f>
-        <v>7 - 1</v>
+        <v>9 - 2</v>
       </c>
       <c r="P33" s="32">
         <f>L33*3+M33</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R33" s="123">
         <f>DATE(2026,6,18)+TIME(11,0,0)+gmt_delta</f>
@@ -46402,7 +46402,7 @@
       </c>
       <c r="AP33" s="123">
         <f>AO33*10000000+BI33*100+AM33/AM36*10+AI33/AI36*1++IF(AQ33=0,ROW(),AQ33)/2000000</f>
-        <v>0.125647325</v>
+        <v>0.10064732500000001</v>
       </c>
       <c r="AQ33" s="126">
         <f>VLOOKUP(AE33,db_fifarank,2,FALSE)</f>
@@ -46410,7 +46410,7 @@
       </c>
       <c r="AR33" s="125">
         <f>AP33/AP36</f>
-        <v>1.6752974185744538E-9</v>
+        <v>1.1742186384192819E-9</v>
       </c>
       <c r="AS33" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J34,"2E")</f>
@@ -46500,7 +46500,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46515,14 +46515,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46560,7 +46560,7 @@
       </c>
       <c r="K34" s="23">
         <f>L34+M34+N34</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="23">
         <f>VLOOKUP(2,AD32:AN35,3,FALSE)</f>
@@ -46572,11 +46572,11 @@
       </c>
       <c r="N34" s="23">
         <f>VLOOKUP(2,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="23" t="str">
         <f>VLOOKUP(2,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD32:AN35,7,FALSE)</f>
-        <v>1 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P34" s="34">
         <f>L34*3+M34</f>
@@ -46644,23 +46644,23 @@
       </c>
       <c r="AH34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE34,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE34,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL34" s="123">
         <f>AI34-AJ34</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM34" s="123">
         <f>AL34-AL36</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
@@ -46668,11 +46668,11 @@
       </c>
       <c r="AO34" s="123">
         <f>AN34/AN36*10+BA34</f>
-        <v>7.5</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>75000005.510381877</v>
+        <v>42857147.343623638</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -46680,7 +46680,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>0.9999999253833104</v>
+        <v>0.49999998708723048</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -46746,7 +46746,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46777,11 +46777,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -46931,7 +46931,7 @@
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>3.846951236153846</v>
+        <v>3.5722259614285714</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -46939,7 +46939,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>5.1292675552864665E-8</v>
+        <v>4.1675964110866009E-8</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -47005,7 +47005,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47145,7 +47145,7 @@
       </c>
       <c r="AF36" s="123">
         <f t="shared" ref="AF36:AH36" si="16">MAX(AF32:AF35)-MIN(AF32:AF35)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG36" s="123">
         <f t="shared" si="16"/>
@@ -47157,7 +47157,7 @@
       </c>
       <c r="AI36" s="123">
         <f>MAX(AI32:AI35)+1</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL36" s="123">
         <f>MIN(AL32:AL35)</f>
@@ -47165,19 +47165,19 @@
       </c>
       <c r="AM36" s="123">
         <f>MAX(AM32:AM35)+1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN36" s="123">
         <f>MAX(AN32:AN35)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO36" s="123">
         <f>MAX(AO32:AO35)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP36" s="123">
         <f>MAX(AP32:AP35)+1</f>
-        <v>75000011.106634423</v>
+        <v>85714296.900865197</v>
       </c>
       <c r="AT36" s="126">
         <f>MAX(AT32:AT35)-MIN(AT32:AT35)+1</f>
@@ -47234,7 +47234,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47358,7 +47358,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47385,7 +47385,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47626,7 +47626,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47656,7 +47656,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47689,8 +47689,12 @@
         <f>AE32</f>
         <v>Germany</v>
       </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="20"/>
+      <c r="F39" s="19">
+        <v>2</v>
+      </c>
+      <c r="G39" s="20">
+        <v>1</v>
+      </c>
       <c r="H39" s="80" t="str">
         <f>AE34</f>
         <v>Ivory Coast</v>
@@ -47729,11 +47733,11 @@
       </c>
       <c r="S39" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Germany_win</v>
       </c>
       <c r="T39" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Ivory Coast_lose</v>
       </c>
       <c r="U39" s="123">
         <f t="shared" si="8"/>
@@ -47763,9 +47767,9 @@
         <f t="shared" ref="AA39:AA70" si="17">IF(OR(E39=my_team,H39=my_team),1,IF(INT(MATCH(E39,$AE$8:$AE$78,0)/6)=$AA$6,1,0))</f>
         <v>0</v>
       </c>
-      <c r="AB39" s="123" t="str">
+      <c r="AB39" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD39" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR39))</f>
@@ -47891,7 +47895,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48571,7 +48575,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48664,7 +48668,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="132"/>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48920,7 +48924,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48935,14 +48939,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49179,7 +49183,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49192,11 +49196,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49416,7 +49420,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49658,7 +49662,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49901,7 +49905,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49917,7 +49921,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50022,7 +50026,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50036,7 +50040,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50271,7 +50275,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="131">
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50524,7 +50528,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="132"/>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50784,7 +50788,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51039,7 +51043,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51243,7 +51247,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="131">
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51364,7 +51368,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51391,7 +51395,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51650,7 +51654,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52133,7 +52137,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52381,7 +52385,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52604,7 +52608,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52717,7 +52721,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52960,7 +52964,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53212,7 +53216,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53478,7 +53482,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53732,7 +53736,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53928,7 +53932,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54028,7 +54032,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54284,7 +54288,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54298,25 +54302,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54554,7 +54558,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54566,19 +54570,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54799,7 +54803,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55035,7 +55039,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56711,13 +56715,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56815,11 +56819,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -56929,11 +56933,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -57043,11 +57047,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57157,11 +57161,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57271,11 +57275,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57952,6 +57956,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57967,36 +58001,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D96CB73-D0D8-4EB8-BA59-1F902786D4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D60778-0CC0-47C3-8C64-B9F512B57544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42675,27 +42675,27 @@
       </c>
       <c r="U17" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="123">
         <f t="shared" si="5"/>
@@ -43274,7 +43274,7 @@
       </c>
       <c r="U20" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="123">
         <f t="shared" si="3"/>
@@ -43286,7 +43286,7 @@
       </c>
       <c r="X20" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="123">
         <f t="shared" si="10"/>
@@ -46370,7 +46370,7 @@
       </c>
       <c r="AG33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_lose")</f>
@@ -46394,15 +46394,15 @@
       </c>
       <c r="AN33" s="123">
         <f>AF33*3+AG33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" s="123">
         <f>AN33/AN36*10+BA33</f>
-        <v>0</v>
+        <v>2.4089635854341735</v>
       </c>
       <c r="AP33" s="123">
         <f>AO33*10000000+BI33*100+AM33/AM36*10+AI33/AI36*1++IF(AQ33=0,ROW(),AQ33)/2000000</f>
-        <v>0.10064732500000001</v>
+        <v>24089733.994204748</v>
       </c>
       <c r="AQ33" s="126">
         <f>VLOOKUP(AE33,db_fifarank,2,FALSE)</f>
@@ -46410,7 +46410,7 @@
       </c>
       <c r="AR33" s="125">
         <f>AP33/AP36</f>
-        <v>1.1742186384192819E-9</v>
+        <v>0.28104685991960332</v>
       </c>
       <c r="AS33" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J34,"2E")</f>
@@ -46422,7 +46422,7 @@
       </c>
       <c r="AU33" s="126" cm="1">
         <f t="array" ref="AU33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV33" s="126" cm="1">
         <f t="array" ref="AV33">SUMPRODUCT(($E$7:$E$78=AE33)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -46442,11 +46442,11 @@
       </c>
       <c r="AZ33" s="126">
         <f>AT33/AT36*1000+AU33/AU36*100+AY33/AY36*10+AV33/AV36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA33" s="126">
         <f>AZ33/AZ36</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB33" s="126" cm="1">
         <f t="array" ref="BB33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_win")*($X$7:$X$78))</f>
@@ -46454,7 +46454,7 @@
       </c>
       <c r="BC33" s="126" cm="1">
         <f t="array" ref="BC33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD33" s="126" cm="1">
         <f t="array" ref="BD33">SUMPRODUCT(($E$7:$E$78=AE33)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -46474,11 +46474,11 @@
       </c>
       <c r="BH33" s="126">
         <f>BB33/BB36*1000+BC33/BC36*100+BG33/BG36*10+BD33/BD36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI33" s="126">
         <f>BH33/BH36</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BK33" s="21" t="str" cm="1">
         <f t="array" ref="BK33">INDEX(T,24+MONTH(BP33),lang) &amp; " " &amp; DAY(BP33) &amp; ", " &amp; YEAR(BP33) &amp; "   " &amp; (IF(HOUR(BP33)&lt;10,0,"")&amp;HOUR(BP33)) &amp; ":" &amp;  (IF(MINUTE(BP33)&lt;10,0,"")&amp;MINUTE(BP33))</f>
@@ -46819,7 +46819,7 @@
       </c>
       <c r="K35" s="23">
         <f>L35+M35+N35</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="23">
         <f>VLOOKUP(3,AD32:AN35,3,FALSE)</f>
@@ -46827,7 +46827,7 @@
       </c>
       <c r="M35" s="23">
         <f>VLOOKUP(3,AD32:AN35,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="23">
         <f>VLOOKUP(3,AD32:AN35,5,FALSE)</f>
@@ -46839,7 +46839,7 @@
       </c>
       <c r="P35" s="34">
         <f>L35*3+M35</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="123">
         <f>DATE(2026,6,19)+TIME(13,30,0)+gmt_delta</f>
@@ -46899,7 +46899,7 @@
       </c>
       <c r="AG35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_lose")</f>
@@ -46923,15 +46923,15 @@
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO35" s="123">
         <f>AN35/AN36*10+BA35</f>
-        <v>0</v>
+        <v>2.4089635854341735</v>
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>3.5722259614285714</v>
+        <v>24089737.465783384</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -46939,7 +46939,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>4.1675964110866009E-8</v>
+        <v>0.28104690042134878</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -46947,7 +46947,7 @@
       </c>
       <c r="AU35" s="126" cm="1">
         <f t="array" ref="AU35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV35" s="126" cm="1">
         <f t="array" ref="AV35">SUMPRODUCT(($E$7:$E$78=AE35)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE35)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -46967,11 +46967,11 @@
       </c>
       <c r="AZ35" s="126">
         <f>AT35/AT36*1000+AU35/AU36*100+AY35/AY36*10+AV35/AV36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA35" s="126">
         <f>AZ35/AZ36</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB35" s="126" cm="1">
         <f t="array" ref="BB35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($X$7:$X$78))</f>
@@ -46979,7 +46979,7 @@
       </c>
       <c r="BC35" s="126" cm="1">
         <f t="array" ref="BC35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD35" s="126" cm="1">
         <f t="array" ref="BD35">SUMPRODUCT(($E$7:$E$78=AE35)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE35)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -46999,11 +46999,11 @@
       </c>
       <c r="BH35" s="126">
         <f>BB35/BB36*1000+BC35/BC36*100+BG35/BG36*10+BD35/BD36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI35" s="126">
         <f>BH35/BH36</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
@@ -47077,7 +47077,7 @@
       </c>
       <c r="K36" s="36">
         <f>L36+M36+N36</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="36">
         <f>VLOOKUP(4,AD32:AN35,3,FALSE)</f>
@@ -47085,7 +47085,7 @@
       </c>
       <c r="M36" s="36">
         <f>VLOOKUP(4,AD32:AN35,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="36">
         <f>VLOOKUP(4,AD32:AN35,5,FALSE)</f>
@@ -47097,7 +47097,7 @@
       </c>
       <c r="P36" s="37">
         <f>L36*3+M36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="123">
         <f>DATE(2026,6,19)+TIME(11,0,0)+gmt_delta</f>
@@ -47149,7 +47149,7 @@
       </c>
       <c r="AG36" s="123">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH36" s="123">
         <f t="shared" si="16"/>
@@ -47185,7 +47185,7 @@
       </c>
       <c r="AU36" s="126">
         <f>MAX(AU32:AU35)-MIN(AU32:AU35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV36" s="126">
         <f>MAX(AV32:AV35)-MIN(AV32:AV35)+1</f>
@@ -47201,7 +47201,7 @@
       </c>
       <c r="AZ36" s="126">
         <f>MAX(AZ32:AZ35)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="BB36" s="126">
         <f>MAX(BB32:BB35)-MIN(BB32:BB35)+1</f>
@@ -47209,7 +47209,7 @@
       </c>
       <c r="BC36" s="126">
         <f>MAX(BC32:BC35)-MIN(BC32:BC35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD36" s="126">
         <f>MAX(BD32:BD35)-MIN(BD32:BD35)+1</f>
@@ -47225,7 +47225,7 @@
       </c>
       <c r="BH36" s="126">
         <f>MAX(BH32:BH35)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="BK36" s="21"/>
       <c r="BL36" s="21"/>
@@ -47536,7 +47536,7 @@
       </c>
       <c r="AM38" s="123">
         <f>AL38-AL42</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
@@ -47544,11 +47544,11 @@
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>8</v>
+        <v>8.9806451612903224</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>80000009.764767826</v>
+        <v>89806559.784067512</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -47556,7 +47556,7 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>0.99999998750000163</v>
+        <v>0.99999998886495611</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
@@ -47568,15 +47568,15 @@
       </c>
       <c r="AU38" s="126" cm="1">
         <f t="array" ref="AU38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV38" s="126" cm="1">
         <f t="array" ref="AV38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW38" s="126" cm="1">
         <f t="array" ref="AW38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX38" s="126">
         <f>AV38-AW38</f>
@@ -47588,11 +47588,11 @@
       </c>
       <c r="AZ38" s="126">
         <f>AT38/AT42*1000+AU38/AU42*100+AY38/AY42*10+AV38/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA38" s="126">
         <f>AZ38/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB38" s="126" cm="1">
         <f t="array" ref="BB38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_win")*($X$7:$X$78))</f>
@@ -47600,15 +47600,15 @@
       </c>
       <c r="BC38" s="126" cm="1">
         <f t="array" ref="BC38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD38" s="126" cm="1">
         <f t="array" ref="BD38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE38" s="126" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF38" s="126">
         <f>BD38-BE38</f>
@@ -47620,11 +47620,11 @@
       </c>
       <c r="BH38" s="126">
         <f>BB38/BB42*1000+BC38/BC42*100+BG38/BG42*10+BD38/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI38" s="126">
         <f>BH38/BH42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BK38" s="141">
         <v>82</v>
@@ -47773,7 +47773,7 @@
       </c>
       <c r="AD39" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR39))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE39" s="124" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
@@ -47781,7 +47781,7 @@
       </c>
       <c r="AF39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_draw")</f>
@@ -47793,7 +47793,7 @@
       </c>
       <c r="AI39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE39,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE39,$F$7:$F$78)</f>
@@ -47801,23 +47801,23 @@
       </c>
       <c r="AL39" s="123">
         <f>AI39-AJ39</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM39" s="123">
         <f>AL39-AL42</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>2</v>
+        <v>8.9806451612903224</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>20000004.695274659</v>
+        <v>89806559.6590188</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -47825,7 +47825,7 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>0.25000002505103042</v>
+        <v>0.99999998747253316</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
@@ -47837,15 +47837,15 @@
       </c>
       <c r="AU39" s="126" cm="1">
         <f t="array" ref="AU39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV39" s="126" cm="1">
         <f t="array" ref="AV39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW39" s="126" cm="1">
         <f t="array" ref="AW39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX39" s="126">
         <f>AV39-AW39</f>
@@ -47857,11 +47857,11 @@
       </c>
       <c r="AZ39" s="126">
         <f>AT39/AT42*1000+AU39/AU42*100+AY39/AY42*10+AV39/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA39" s="126">
         <f>AZ39/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB39" s="126" cm="1">
         <f t="array" ref="BB39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($X$7:$X$78))</f>
@@ -47869,15 +47869,15 @@
       </c>
       <c r="BC39" s="126" cm="1">
         <f t="array" ref="BC39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD39" s="126" cm="1">
         <f t="array" ref="BD39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE39" s="126" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF39" s="126">
         <f>BD39-BE39</f>
@@ -47889,11 +47889,11 @@
       </c>
       <c r="BH39" s="126">
         <f>BB39/BB42*1000+BC39/BC42*100+BG39/BG42*10+BD39/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI39" s="126">
         <f>BH39/BH42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
@@ -47948,15 +47948,19 @@
         <f>AE35</f>
         <v>Ecuador</v>
       </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="20"/>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20">
+        <v>0</v>
+      </c>
       <c r="H40" s="80" t="str">
         <f>AE33</f>
         <v>Curaçao</v>
       </c>
       <c r="J40" s="33" t="str">
         <f>VLOOKUP(2,AD38:AN41,2,FALSE)</f>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
@@ -47968,19 +47972,19 @@
       </c>
       <c r="M40" s="23">
         <f>VLOOKUP(2,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="23">
         <f>VLOOKUP(2,AD38:AN41,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="23" t="str">
         <f>VLOOKUP(2,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD38:AN41,7,FALSE)</f>
-        <v>6 - 6</v>
+        <v>6 - 2</v>
       </c>
       <c r="P40" s="34">
         <f>L40*3+M40</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R40" s="123">
         <f>DATE(2026,6,20)+TIME(13,0,0)+gmt_delta</f>
@@ -47988,15 +47992,15 @@
       </c>
       <c r="S40" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Ecuador_draw</v>
       </c>
       <c r="T40" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Curaçao_draw</v>
       </c>
       <c r="U40" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="123">
         <f t="shared" si="3"/>
@@ -48008,7 +48012,7 @@
       </c>
       <c r="X40" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="123">
         <f t="shared" si="10"/>
@@ -48022,13 +48026,13 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB40" s="123" t="str">
+      <c r="AB40" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD40" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR40))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE40" s="124" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
@@ -48060,7 +48064,7 @@
       </c>
       <c r="AM40" s="123">
         <f>AL40-AL42</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN40" s="123">
         <f>AF40*3+AG40</f>
@@ -48072,7 +48076,7 @@
       </c>
       <c r="AP40" s="123">
         <f>AO40*10000000+BI40*100+AM40/AM42*10+AI40/AI42*1++IF(AQ40=0,ROW(),AQ40)/2000000</f>
-        <v>60000005.195201829</v>
+        <v>60000006.904603533</v>
       </c>
       <c r="AQ40" s="126">
         <f>VLOOKUP(AE40,db_fifarank,2,FALSE)</f>
@@ -48080,7 +48084,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>0.74999996402032931</v>
+        <v>0.66810271299519663</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -48181,31 +48185,31 @@
       </c>
       <c r="J41" s="33" t="str">
         <f>VLOOKUP(3,AD38:AN41,2,FALSE)</f>
-        <v>Japan</v>
+        <v>Sweden</v>
       </c>
       <c r="K41" s="23">
         <f>L41+M41+N41</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="23">
         <f>VLOOKUP(3,AD38:AN41,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="23">
         <f>VLOOKUP(3,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="23">
         <f>VLOOKUP(3,AD38:AN41,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="23" t="str">
         <f>VLOOKUP(3,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD38:AN41,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>6 - 6</v>
       </c>
       <c r="P41" s="34">
         <f>L41*3+M41</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R41" s="123">
         <f>DATE(2026,6,20)+TIME(6,0,0)+gmt_delta</f>
@@ -48269,7 +48273,7 @@
       </c>
       <c r="AH41" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE41 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE41,$G$7:$G$78)</f>
@@ -48277,11 +48281,11 @@
       </c>
       <c r="AJ41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE41,$F$7:$F$78)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AL41" s="123">
         <f>AI41-AJ41</f>
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="AM41" s="123">
         <f>AL41-AL42</f>
@@ -48305,7 +48309,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>1.5717688510034155E-9</v>
+        <v>1.4001374053543276E-9</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -48413,8 +48417,12 @@
         <f>AE41</f>
         <v>Tunisia</v>
       </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="20"/>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20">
+        <v>4</v>
+      </c>
       <c r="H42" s="80" t="str">
         <f>AE39</f>
         <v>Japan</v>
@@ -48425,7 +48433,7 @@
       </c>
       <c r="K42" s="36">
         <f>L42+M42+N42</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="36">
         <f>VLOOKUP(4,AD38:AN41,3,FALSE)</f>
@@ -48437,11 +48445,11 @@
       </c>
       <c r="N42" s="36">
         <f>VLOOKUP(4,AD38:AN41,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="36" t="str">
         <f>VLOOKUP(4,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD38:AN41,7,FALSE)</f>
-        <v>1 - 5</v>
+        <v>1 - 9</v>
       </c>
       <c r="P42" s="37">
         <f>L42*3+M42</f>
@@ -48453,11 +48461,11 @@
       </c>
       <c r="S42" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Tunisia_lose</v>
       </c>
       <c r="T42" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Japan_win</v>
       </c>
       <c r="U42" s="123">
         <f t="shared" si="8"/>
@@ -48487,9 +48495,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="123" t="str">
+      <c r="AB42" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF42" s="123">
         <f t="shared" ref="AF42:AH42" si="18">MAX(AF38:AF41)-MIN(AF38:AF41)+1</f>
@@ -48501,7 +48509,7 @@
       </c>
       <c r="AH42" s="123">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
@@ -48509,11 +48517,11 @@
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="AM42" s="123">
         <f>MAX(AM38:AM41)+1</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
@@ -48521,11 +48529,11 @@
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>9</v>
+        <v>9.9806451612903224</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>80000010.764767826</v>
+        <v>89806560.784067512</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -48533,15 +48541,15 @@
       </c>
       <c r="AU42" s="126">
         <f>MAX(AU38:AU41)-MIN(AU38:AU41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV42" s="126">
         <f>MAX(AV38:AV41)-MIN(AV38:AV41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW42" s="126">
         <f>MAX(AW38:AW41)-MIN(AW38:AW41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY42" s="126">
         <f>MAX(AY38:AY41)-MIN(AY38:AY41)+1</f>
@@ -48549,7 +48557,7 @@
       </c>
       <c r="AZ42" s="126">
         <f>MAX(AZ38:AZ41)+1</f>
-        <v>1</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BB42" s="126">
         <f>MAX(BB38:BB41)-MIN(BB38:BB41)+1</f>
@@ -48557,15 +48565,15 @@
       </c>
       <c r="BC42" s="126">
         <f>MAX(BC38:BC41)-MIN(BC38:BC41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD42" s="126">
         <f>MAX(BD38:BD41)-MIN(BD38:BD41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE42" s="126">
         <f>MAX(BE38:BE41)-MIN(BE38:BE41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG42" s="126">
         <f>MAX(BG38:BG41)-MIN(BG38:BG41)+1</f>
@@ -48573,7 +48581,7 @@
       </c>
       <c r="BH42" s="126">
         <f>MAX(BH38:BH41)+1</f>
-        <v>1</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BK42" s="141">
         <v>76</v>
@@ -48715,8 +48723,12 @@
         <f>AE50</f>
         <v>Spain</v>
       </c>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="F44" s="19">
+        <v>4</v>
+      </c>
+      <c r="G44" s="20">
+        <v>0</v>
+      </c>
       <c r="H44" s="80" t="str">
         <f>AE52</f>
         <v>Saudi Arabia</v>
@@ -48755,11 +48767,11 @@
       </c>
       <c r="S44" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Spain_win</v>
       </c>
       <c r="T44" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Saudi Arabia_lose</v>
       </c>
       <c r="U44" s="123">
         <f t="shared" si="8"/>
@@ -48789,9 +48801,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB44" s="123" t="str">
+      <c r="AB44" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD44" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR44))</f>
@@ -50153,7 +50165,7 @@
       </c>
       <c r="AD50" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR50))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE50" s="124" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
@@ -50161,7 +50173,7 @@
       </c>
       <c r="AF50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_draw")</f>
@@ -50173,7 +50185,7 @@
       </c>
       <c r="AI50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE50,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE50,$F$7:$F$78)</f>
@@ -50181,23 +50193,23 @@
       </c>
       <c r="AL50" s="123">
         <f>AI50-AJ50</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM50" s="123">
         <f>AL50-AL54</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN50" s="123">
         <f>AF50*3+AG50</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO50" s="123">
         <f>AN50/AN54*10+BA50</f>
-        <v>5.985221674876847</v>
+        <v>8</v>
       </c>
       <c r="AP50" s="123">
         <f>AO50*10000000+BI50*100+AM50/AM54*10+AI50/AI54*1++IF(AQ50=0,ROW(),AQ50)/2000000</f>
-        <v>59852315.27187416</v>
+        <v>80000009.689827099</v>
       </c>
       <c r="AQ50" s="126">
         <f>VLOOKUP(AE50,db_fifarank,2,FALSE)</f>
@@ -50205,7 +50217,7 @@
       </c>
       <c r="AR50" s="125">
         <f>AP50/AP54</f>
-        <v>0.99917759969584252</v>
+        <v>0.99999998750000163</v>
       </c>
       <c r="AS50" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J51,"1H")</f>
@@ -50217,7 +50229,7 @@
       </c>
       <c r="AU50" s="126" cm="1">
         <f t="array" ref="AU50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV50" s="126" cm="1">
         <f t="array" ref="AV50">SUMPRODUCT(($E$7:$E$78=AE50)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -50237,11 +50249,11 @@
       </c>
       <c r="AZ50" s="126">
         <f>AT50/AT54*1000+AU50/AU54*100+AY50/AY54*10+AV50/AV54</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BA50" s="126">
         <f>AZ50/AZ54</f>
-        <v>0.98522167487684731</v>
+        <v>0</v>
       </c>
       <c r="BB50" s="126" cm="1">
         <f t="array" ref="BB50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_win")*($X$7:$X$78))</f>
@@ -50249,7 +50261,7 @@
       </c>
       <c r="BC50" s="126" cm="1">
         <f t="array" ref="BC50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD50" s="126" cm="1">
         <f t="array" ref="BD50">SUMPRODUCT(($E$7:$E$78=AE50)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -50269,11 +50281,11 @@
       </c>
       <c r="BH50" s="126">
         <f>BB50/BB54*1000+BC50/BC54*100+BG50/BG54*10+BD50/BD54</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BI50" s="126">
         <f>BH50/BH54</f>
-        <v>0.98522167487684731</v>
+        <v>0</v>
       </c>
       <c r="BK50" s="141">
         <v>79</v>
@@ -50334,15 +50346,15 @@
       </c>
       <c r="J51" s="30" t="str">
         <f>VLOOKUP(1,AD50:AN53,2,FALSE)</f>
-        <v>Uruguay</v>
+        <v>Spain</v>
       </c>
       <c r="K51" s="31">
         <f>L51+M51+N51</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="31">
         <f>VLOOKUP(1,AD50:AN53,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="31">
         <f>VLOOKUP(1,AD50:AN53,4,FALSE)</f>
@@ -50354,11 +50366,11 @@
       </c>
       <c r="O51" s="31" t="str">
         <f>VLOOKUP(1,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD50:AN53,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>4 - 0</v>
       </c>
       <c r="P51" s="32">
         <f>L51*3+M51</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R51" s="123">
         <f>DATE(2026,6,23)+TIME(9,0,0)+gmt_delta</f>
@@ -50438,7 +50450,7 @@
       </c>
       <c r="AM51" s="123">
         <f>AL51-AL54</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN51" s="123">
         <f>AF51*3+AG51</f>
@@ -50446,11 +50458,11 @@
       </c>
       <c r="AO51" s="123">
         <f>AN51/AN54*10+BA51</f>
-        <v>5.985221674876847</v>
+        <v>2</v>
       </c>
       <c r="AP51" s="123">
         <f>AO51*10000000+BI51*100+AM51/AM54*10+AI51/AI54*1++IF(AQ51=0,ROW(),AQ51)/2000000</f>
-        <v>59852315.271619022</v>
+        <v>20000004.44512751</v>
       </c>
       <c r="AQ51" s="126">
         <f>VLOOKUP(AE51,db_fifarank,2,FALSE)</f>
@@ -50458,7 +50470,7 @@
       </c>
       <c r="AR51" s="125">
         <f>AP51/AP54</f>
-        <v>0.99917759969158326</v>
+        <v>0.25000002215838124</v>
       </c>
       <c r="AS51" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J52,"2H")</f>
@@ -50470,7 +50482,7 @@
       </c>
       <c r="AU51" s="126" cm="1">
         <f t="array" ref="AU51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV51" s="126" cm="1">
         <f t="array" ref="AV51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -50490,11 +50502,11 @@
       </c>
       <c r="AZ51" s="126">
         <f>AT51/AT54*1000+AU51/AU54*100+AY51/AY54*10+AV51/AV54</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BA51" s="126">
         <f>AZ51/AZ54</f>
-        <v>0.98522167487684731</v>
+        <v>0</v>
       </c>
       <c r="BB51" s="126" cm="1">
         <f t="array" ref="BB51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($X$7:$X$78))</f>
@@ -50502,7 +50514,7 @@
       </c>
       <c r="BC51" s="126" cm="1">
         <f t="array" ref="BC51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD51" s="126" cm="1">
         <f t="array" ref="BD51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -50522,11 +50534,11 @@
       </c>
       <c r="BH51" s="126">
         <f>BB51/BB54*1000+BC51/BC54*100+BG51/BG54*10+BD51/BD54</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BI51" s="126">
         <f>BH51/BH54</f>
-        <v>0.98522167487684731</v>
+        <v>0</v>
       </c>
       <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
@@ -50591,7 +50603,7 @@
       </c>
       <c r="J52" s="33" t="str">
         <f>VLOOKUP(2,AD50:AN53,2,FALSE)</f>
-        <v>Saudi Arabia</v>
+        <v>Uruguay</v>
       </c>
       <c r="K52" s="23">
         <f>L52+M52+N52</f>
@@ -50663,7 +50675,7 @@
       </c>
       <c r="AD52" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR52))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE52" s="124" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
@@ -50679,7 +50691,7 @@
       </c>
       <c r="AH52" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE52 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE52,$G$7:$G$78)</f>
@@ -50687,11 +50699,11 @@
       </c>
       <c r="AJ52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE52,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL52" s="123">
         <f>AI52-AJ52</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM52" s="123">
         <f>AL52-AL54</f>
@@ -50703,11 +50715,11 @@
       </c>
       <c r="AO52" s="123">
         <f>AN52/AN54*10+BA52</f>
-        <v>5.9901477832512313</v>
+        <v>2.9805825242718447</v>
       </c>
       <c r="AP52" s="123">
         <f>AO52*10000000+BI52*100+AM52/AM54*10+AI52/AI54*1++IF(AQ52=0,ROW(),AQ52)/2000000</f>
-        <v>59901577.348001353</v>
+        <v>29805923.501681589</v>
       </c>
       <c r="AQ52" s="126">
         <f>VLOOKUP(AE52,db_fifarank,2,FALSE)</f>
@@ -50715,7 +50727,7 @@
       </c>
       <c r="AR52" s="125">
         <f>AP52/AP54</f>
-        <v>0.99999998330384865</v>
+        <v>0.37257399398662516</v>
       </c>
       <c r="AT52" s="126" cm="1">
         <f t="array" ref="AT52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($U$7:$U$78))</f>
@@ -50743,11 +50755,11 @@
       </c>
       <c r="AZ52" s="126">
         <f>AT52/AT54*1000+AU52/AU54*100+AY52/AY54*10+AV52/AV54</f>
-        <v>100.5</v>
+        <v>50.5</v>
       </c>
       <c r="BA52" s="126">
         <f>AZ52/AZ54</f>
-        <v>0.99014778325123154</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB52" s="126" cm="1">
         <f t="array" ref="BB52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($X$7:$X$78))</f>
@@ -50775,11 +50787,11 @@
       </c>
       <c r="BH52" s="126">
         <f>BB52/BB54*1000+BC52/BC54*100+BG52/BG54*10+BD52/BD54</f>
-        <v>100.5</v>
+        <v>50.5</v>
       </c>
       <c r="BI52" s="126">
         <f>BH52/BH54</f>
-        <v>0.99014778325123154</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK52" s="21"/>
       <c r="BL52" s="21"/>
@@ -50840,11 +50852,11 @@
       </c>
       <c r="J53" s="33" t="str">
         <f>VLOOKUP(3,AD50:AN53,2,FALSE)</f>
-        <v>Spain</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="K53" s="23">
         <f>L53+M53+N53</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="23">
         <f>VLOOKUP(3,AD50:AN53,3,FALSE)</f>
@@ -50856,11 +50868,11 @@
       </c>
       <c r="N53" s="23">
         <f>VLOOKUP(3,AD50:AN53,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="23" t="str">
         <f>VLOOKUP(3,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD50:AN53,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 5</v>
       </c>
       <c r="P53" s="34">
         <f>L53*3+M53</f>
@@ -50912,7 +50924,7 @@
       </c>
       <c r="AD53" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR53))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE53" s="124" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
@@ -50944,7 +50956,7 @@
       </c>
       <c r="AM53" s="123">
         <f>AL53-AL54</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN53" s="123">
         <f>AF53*3+AG53</f>
@@ -50952,11 +50964,11 @@
       </c>
       <c r="AO53" s="123">
         <f>AN53/AN54*10+BA53</f>
-        <v>5.9901477832512313</v>
+        <v>2.9805825242718447</v>
       </c>
       <c r="AP53" s="123">
         <f>AO53*10000000+BI53*100+AM53/AM54*10+AI53/AI54*1++IF(AQ53=0,ROW(),AQ53)/2000000</f>
-        <v>59901577.348127171</v>
+        <v>29805927.946251854</v>
       </c>
       <c r="AQ53" s="126">
         <f>VLOOKUP(AE53,db_fifarank,2,FALSE)</f>
@@ -50964,7 +50976,7 @@
       </c>
       <c r="AR53" s="125">
         <f>AP53/AP54</f>
-        <v>0.99999998330594908</v>
+        <v>0.37257404954374601</v>
       </c>
       <c r="AT53" s="126" cm="1">
         <f t="array" ref="AT53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($U$7:$U$78))</f>
@@ -50992,11 +51004,11 @@
       </c>
       <c r="AZ53" s="126">
         <f>AT53/AT54*1000+AU53/AU54*100+AY53/AY54*10+AV53/AV54</f>
-        <v>100.5</v>
+        <v>50.5</v>
       </c>
       <c r="BA53" s="126">
         <f>AZ53/AZ54</f>
-        <v>0.99014778325123154</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB53" s="126" cm="1">
         <f t="array" ref="BB53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($X$7:$X$78))</f>
@@ -51024,11 +51036,11 @@
       </c>
       <c r="BH53" s="126">
         <f>BB53/BB54*1000+BC53/BC54*100+BG53/BG54*10+BD53/BD54</f>
-        <v>100.5</v>
+        <v>50.5</v>
       </c>
       <c r="BI53" s="126">
         <f>BH53/BH54</f>
-        <v>0.99014778325123154</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK53" s="21" t="str" cm="1">
         <f t="array" ref="BK53">INDEX(T,24+MONTH(BP53),lang) &amp; " " &amp; DAY(BP53) &amp; ", " &amp; YEAR(BP53) &amp; "   " &amp; (IF(HOUR(BP53)&lt;10,0,"")&amp;HOUR(BP53)) &amp; ":" &amp;  (IF(MINUTE(BP53)&lt;10,0,"")&amp;MINUTE(BP53))</f>
@@ -51165,7 +51177,7 @@
       </c>
       <c r="AF54" s="123">
         <f t="shared" ref="AF54:AH54" si="25">MAX(AF50:AF53)-MIN(AF50:AF53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG54" s="123">
         <f t="shared" si="25"/>
@@ -51173,31 +51185,31 @@
       </c>
       <c r="AH54" s="123">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI54" s="123">
         <f>MAX(AI50:AI53)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL54" s="123">
         <f>MIN(AL50:AL53)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM54" s="123">
         <f>MAX(AM50:AM53)+1</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN54" s="123">
         <f>MAX(AN50:AN53)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO54" s="123">
         <f>MAX(AO50:AO53)+1</f>
-        <v>6.9901477832512313</v>
+        <v>9</v>
       </c>
       <c r="AP54" s="123">
         <f>MAX(AP50:AP53)+1</f>
-        <v>59901578.348127171</v>
+        <v>80000010.689827099</v>
       </c>
       <c r="AT54" s="126">
         <f>MAX(AT50:AT53)-MIN(AT50:AT53)+1</f>
@@ -51205,7 +51217,7 @@
       </c>
       <c r="AU54" s="126">
         <f>MAX(AU50:AU53)-MIN(AU50:AU53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV54" s="126">
         <f>MAX(AV50:AV53)-MIN(AV50:AV53)+1</f>
@@ -51221,7 +51233,7 @@
       </c>
       <c r="AZ54" s="126">
         <f>MAX(AZ50:AZ53)+1</f>
-        <v>101.5</v>
+        <v>51.5</v>
       </c>
       <c r="BB54" s="126">
         <f>MAX(BB50:BB53)-MIN(BB50:BB53)+1</f>
@@ -51229,7 +51241,7 @@
       </c>
       <c r="BC54" s="126">
         <f>MAX(BC50:BC53)-MIN(BC50:BC53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD54" s="126">
         <f>MAX(BD50:BD53)-MIN(BD50:BD53)+1</f>
@@ -51245,7 +51257,7 @@
       </c>
       <c r="BH54" s="126">
         <f>MAX(BH50:BH53)+1</f>
-        <v>101.5</v>
+        <v>51.5</v>
       </c>
       <c r="BK54" s="141">
         <v>80</v>
@@ -56446,7 +56458,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56481,7 +56493,7 @@
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,10,FALSE)</f>
@@ -56489,7 +56501,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>3066.6674173566666</v>
+        <v>3128.5721792614286</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -56520,7 +56532,7 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓕ Sweden</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
@@ -56540,7 +56552,7 @@
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>6 - 6</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
@@ -56583,7 +56595,7 @@
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
@@ -56591,7 +56603,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>2566.6673595866664</v>
+        <v>2728.5721214914283</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -56622,7 +56634,7 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Paraguay</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
@@ -56642,7 +56654,7 @@
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>1 - 1</v>
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
@@ -56650,7 +56662,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -56685,7 +56697,7 @@
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
@@ -56693,7 +56705,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>8283.3340825083342</v>
+        <v>8314.286463460714</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -56726,35 +56738,35 @@
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Japan</v>
+        <v>Ⓓ Paraguay</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>2 - 4</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
@@ -56789,7 +56801,7 @@
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
@@ -56797,7 +56809,7 @@
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>7816.6674184166668</v>
+        <v>7928.5721803214283</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
@@ -56868,7 +56880,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56880,7 +56892,7 @@
       </c>
       <c r="AG84" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH84" s="123">
         <f t="shared" si="40"/>
@@ -56903,15 +56915,15 @@
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>500.00079739</v>
+        <v>3100.0007973900001</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -56919,11 +56931,11 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCD</v>
+        <v>ABCDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Ecuador</v>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
@@ -56982,31 +56994,31 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
-        <v>Japan</v>
+        <v>Sweden</v>
       </c>
       <c r="AF85" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG85" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH85" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI85" s="123">
         <f t="shared" si="41"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ85" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK85" s="123" t="s">
         <v>3186</v>
@@ -57017,31 +57029,31 @@
       </c>
       <c r="AM85" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>3316.6674968816665</v>
+        <v>8385.715043099286</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
-        <v>1660.43</v>
+        <v>1514.77</v>
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDF</v>
+        <v>ABCDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Japan</v>
+        <v>Sweden</v>
       </c>
       <c r="AT85" s="130" t="str">
         <f>"Ⓕ "&amp;AE85</f>
-        <v>Ⓕ Japan</v>
+        <v>Ⓕ Sweden</v>
       </c>
     </row>
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57056,11 +57068,11 @@
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Spain</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
@@ -57072,11 +57084,11 @@
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 3</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
@@ -57131,7 +57143,7 @@
       </c>
       <c r="AM86" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
@@ -57139,7 +57151,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>3283.3342006883336</v>
+        <v>3314.2865816407143</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57147,7 +57159,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDFG</v>
+        <v>ABCDEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57170,7 +57182,7 @@
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57190,7 +57202,7 @@
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>0 - 1</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
@@ -57210,11 +57222,11 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
-        <v>Spain</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="AF87" s="123">
         <f t="shared" si="39"/>
@@ -57226,26 +57238,26 @@
       </c>
       <c r="AH87" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI87" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ87" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK87" s="123" t="s">
         <v>3188</v>
       </c>
       <c r="AL87" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
@@ -57253,23 +57265,23 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>3250.0009381999998</v>
+        <v>2514.2864250007142</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
-        <v>1876.4</v>
+        <v>1421.43</v>
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDFGH</v>
+        <v>ABCDEFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Spain</v>
+        <v/>
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
-        <v>Ⓗ Spain</v>
+        <v>Ⓗ Saudi Arabia</v>
       </c>
     </row>
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57359,7 +57371,7 @@
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -57367,7 +57379,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>283.33417782833334</v>
+        <v>414.2865587807143</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -57375,7 +57387,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDFGH</v>
+        <v>ABCDEFG</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57398,11 +57410,11 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓗ Saudi Arabia</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,3,FALSE)</f>
@@ -57410,7 +57422,7 @@
       </c>
       <c r="M89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,5,FALSE)</f>
@@ -57418,11 +57430,11 @@
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>1 - 5</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="123">
         <f>DATE(2026,12,5)+TIME(8,0,0)+gmt_delta</f>
@@ -57473,7 +57485,7 @@
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -57481,7 +57493,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>283.33402905833333</v>
+        <v>414.28641001071429</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -57489,7 +57501,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDFGH</v>
+        <v>ABCDEFG</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57587,7 +57599,7 @@
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
@@ -57595,7 +57607,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>3283.3340725083335</v>
+        <v>3314.2864534607143</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -57603,7 +57615,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDFGHK</v>
+        <v>ABCDEFGK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57701,7 +57713,7 @@
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57709,7 +57721,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>500.00077032000002</v>
+        <v>600.00077032000002</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -57717,7 +57729,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDFGHK</v>
+        <v>ABCDEFGK</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57780,19 +57792,19 @@
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
@@ -59043,15 +59055,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ABCDFGHK</v>
+        <v>ABCDEFGK</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3H</v>
+        <v>3C</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -59063,7 +59075,7 @@
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
-        <v>3C</v>
+        <v>3D</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
@@ -59075,7 +59087,7 @@
       </c>
       <c r="J3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,8,FALSE)</f>
-        <v>3D</v>
+        <v>3E</v>
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D60778-0CC0-47C3-8C64-B9F512B57544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A64261-95E4-4A63-A469-E60C38406F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="2910" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="str" cm="1">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="str" cm="1">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43541,27 +43541,27 @@
       </c>
       <c r="U21" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="123">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W21" s="123">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X21" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="123">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="123">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="123">
         <f t="shared" si="5"/>
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43812,27 +43812,27 @@
       </c>
       <c r="U22" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="123">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="123">
         <f t="shared" si="5"/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44474,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44827,7 +44827,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45095,7 +45095,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45370,7 +45370,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45635,7 +45635,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45849,7 +45849,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45960,7 +45960,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46236,7 +46236,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46500,7 +46500,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46515,14 +46515,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46746,7 +46746,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46777,11 +46777,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -47005,7 +47005,7 @@
         <f>BH35/BH36</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47234,7 +47234,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47358,7 +47358,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47385,7 +47385,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47626,7 +47626,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47656,7 +47656,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47895,7 +47895,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48583,7 +48583,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48676,7 +48676,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48807,7 +48807,7 @@
       </c>
       <c r="AD44" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR44))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE44" s="124" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
@@ -48819,7 +48819,7 @@
       </c>
       <c r="AG44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_lose")</f>
@@ -48843,15 +48843,15 @@
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>5.9852941176470589</v>
+        <v>7.6470588235294112</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>59853040.040083036</v>
+        <v>76470686.608710483</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -48859,7 +48859,7 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>0.9991816403290853</v>
+        <v>0.99999998256490596</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
@@ -48875,11 +48875,11 @@
       </c>
       <c r="AV44" s="126" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW44" s="126" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX44" s="126">
         <f>AV44-AW44</f>
@@ -48891,11 +48891,11 @@
       </c>
       <c r="AZ44" s="126">
         <f>AT44/AT48*1000+AU44/AU48*100+AY44/AY48*10+AV44/AV48</f>
-        <v>100.5</v>
+        <v>50</v>
       </c>
       <c r="BA44" s="126">
         <f>AZ44/AZ48</f>
-        <v>0.98529411764705888</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB44" s="126" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($X$7:$X$78))</f>
@@ -48907,11 +48907,11 @@
       </c>
       <c r="BD44" s="126" cm="1">
         <f t="array" ref="BD44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE44" s="126" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF44" s="126">
         <f>BD44-BE44</f>
@@ -48923,11 +48923,11 @@
       </c>
       <c r="BH44" s="126">
         <f>BB44/BB48*1000+BC44/BC48*100+BG44/BG48*10+BD44/BD48</f>
-        <v>100.5</v>
+        <v>50</v>
       </c>
       <c r="BI44" s="126">
         <f>BH44/BH48</f>
-        <v>0.98529411764705888</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BK44" s="21"/>
       <c r="BL44" s="21"/>
@@ -48936,7 +48936,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="141">
+      <c r="BR44" s="131">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48951,14 +48951,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="144" t="str" cm="1">
+      <c r="CM44" s="133" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="145"/>
-      <c r="CO44" s="145"/>
-      <c r="CP44" s="145"/>
-      <c r="CQ44" s="146"/>
+      <c r="CN44" s="134"/>
+      <c r="CO44" s="134"/>
+      <c r="CP44" s="134"/>
+      <c r="CQ44" s="135"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -48980,8 +48980,12 @@
         <f>AE44</f>
         <v>Belgium</v>
       </c>
-      <c r="F45" s="19"/>
-      <c r="G45" s="20"/>
+      <c r="F45" s="19">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20">
+        <v>0</v>
+      </c>
       <c r="H45" s="80" t="str">
         <f>AE46</f>
         <v>Iran</v>
@@ -48992,7 +48996,7 @@
       </c>
       <c r="K45" s="31">
         <f>L45+M45+N45</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="31">
         <f>VLOOKUP(1,AD44:AN47,3,FALSE)</f>
@@ -49000,7 +49004,7 @@
       </c>
       <c r="M45" s="31">
         <f>VLOOKUP(1,AD44:AN47,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" s="31">
         <f>VLOOKUP(1,AD44:AN47,5,FALSE)</f>
@@ -49012,7 +49016,7 @@
       </c>
       <c r="P45" s="32">
         <f>L45*3+M45</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45" s="123">
         <f>DATE(2026,6,21)+TIME(8,0,0)+gmt_delta</f>
@@ -49020,15 +49024,15 @@
       </c>
       <c r="S45" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Belgium_draw</v>
       </c>
       <c r="T45" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Iran_draw</v>
       </c>
       <c r="U45" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="123">
         <f t="shared" si="3"/>
@@ -49040,7 +49044,7 @@
       </c>
       <c r="X45" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" s="123">
         <f t="shared" si="10"/>
@@ -49054,9 +49058,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB45" s="123" t="str">
+      <c r="AB45" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD45" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR45))</f>
@@ -49100,11 +49104,11 @@
       </c>
       <c r="AO45" s="123">
         <f>AN45/AN48*10+BA45</f>
-        <v>5.9852941176470589</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="AP45" s="123">
         <f>AO45*10000000+BI45*100+AM45/AM48*10+AI45/AI48*1++IF(AQ45=0,ROW(),AQ45)/2000000</f>
-        <v>59853040.039997302</v>
+        <v>33333333.667448286</v>
       </c>
       <c r="AQ45" s="126">
         <f>VLOOKUP(AE45,db_fifarank,2,FALSE)</f>
@@ -49112,7 +49116,7 @@
       </c>
       <c r="AR45" s="125">
         <f>AP45/AP48</f>
-        <v>0.99918164032765411</v>
+        <v>0.43589687191956777</v>
       </c>
       <c r="AS45" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J46,"2G")</f>
@@ -49124,15 +49128,15 @@
       </c>
       <c r="AU45" s="126" cm="1">
         <f t="array" ref="AU45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV45" s="126" cm="1">
         <f t="array" ref="AV45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW45" s="126" cm="1">
         <f t="array" ref="AW45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX45" s="126">
         <f>AV45-AW45</f>
@@ -49144,11 +49148,11 @@
       </c>
       <c r="AZ45" s="126">
         <f>AT45/AT48*1000+AU45/AU48*100+AY45/AY48*10+AV45/AV48</f>
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="BA45" s="126">
         <f>AZ45/AZ48</f>
-        <v>0.98529411764705888</v>
+        <v>0</v>
       </c>
       <c r="BB45" s="126" cm="1">
         <f t="array" ref="BB45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($X$7:$X$78))</f>
@@ -49156,15 +49160,15 @@
       </c>
       <c r="BC45" s="126" cm="1">
         <f t="array" ref="BC45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD45" s="126" cm="1">
         <f t="array" ref="BD45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE45" s="126" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF45" s="126">
         <f>BD45-BE45</f>
@@ -49176,11 +49180,11 @@
       </c>
       <c r="BH45" s="126">
         <f>BB45/BB48*1000+BC45/BC48*100+BG45/BG48*10+BD45/BD48</f>
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="BI45" s="126">
         <f>BH45/BH48</f>
-        <v>0.98529411764705888</v>
+        <v>0</v>
       </c>
       <c r="BK45" s="21" t="str" cm="1">
         <f t="array" ref="BK45">INDEX(T,24+MONTH(BP45),lang) &amp; " " &amp; DAY(BP45) &amp; ", " &amp; YEAR(BP45) &amp; "   " &amp; (IF(HOUR(BP45)&lt;10,0,"")&amp;HOUR(BP45)) &amp; ":" &amp;  (IF(MINUTE(BP45)&lt;10,0,"")&amp;MINUTE(BP45))</f>
@@ -49195,7 +49199,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="142"/>
+      <c r="BR45" s="132"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49208,11 +49212,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="147"/>
-      <c r="CN45" s="148"/>
-      <c r="CO45" s="148"/>
-      <c r="CP45" s="148"/>
-      <c r="CQ45" s="149"/>
+      <c r="CM45" s="136"/>
+      <c r="CN45" s="137"/>
+      <c r="CO45" s="137"/>
+      <c r="CP45" s="137"/>
+      <c r="CQ45" s="138"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49242,11 +49246,11 @@
       </c>
       <c r="J46" s="33" t="str">
         <f>VLOOKUP(2,AD44:AN47,2,FALSE)</f>
-        <v>New Zealand</v>
+        <v>Belgium</v>
       </c>
       <c r="K46" s="23">
         <f>L46+M46+N46</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="23">
         <f>VLOOKUP(2,AD44:AN47,3,FALSE)</f>
@@ -49254,7 +49258,7 @@
       </c>
       <c r="M46" s="23">
         <f>VLOOKUP(2,AD44:AN47,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N46" s="23">
         <f>VLOOKUP(2,AD44:AN47,5,FALSE)</f>
@@ -49262,11 +49266,11 @@
       </c>
       <c r="O46" s="23" t="str">
         <f>VLOOKUP(2,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD44:AN47,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>1 - 1</v>
       </c>
       <c r="P46" s="34">
         <f>L46*3+M46</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46" s="123">
         <f>DATE(2026,6,21)+TIME(14,0,0)+gmt_delta</f>
@@ -49326,7 +49330,7 @@
       </c>
       <c r="AG46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_lose")</f>
@@ -49350,15 +49354,15 @@
       </c>
       <c r="AN46" s="123">
         <f>AF46*3+AG46</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO46" s="123">
         <f>AN46/AN48*10+BA46</f>
-        <v>5.9901960784313726</v>
+        <v>7.6470588235294112</v>
       </c>
       <c r="AP46" s="123">
         <f>AO46*10000000+BI46*100+AM46/AM48*10+AI46/AI48*1++IF(AQ46=0,ROW(),AQ46)/2000000</f>
-        <v>59902060.47139588</v>
+        <v>76470686.941984117</v>
       </c>
       <c r="AQ46" s="126">
         <f>VLOOKUP(AE46,db_fifarank,2,FALSE)</f>
@@ -49366,7 +49370,7 @@
       </c>
       <c r="AR46" s="125">
         <f>AP46/AP48</f>
-        <v>0.99999998330608375</v>
+        <v>0.999999986923094</v>
       </c>
       <c r="AT46" s="126" cm="1">
         <f t="array" ref="AT46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($U$7:$U$78))</f>
@@ -49378,11 +49382,11 @@
       </c>
       <c r="AV46" s="126" cm="1">
         <f t="array" ref="AV46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW46" s="126" cm="1">
         <f t="array" ref="AW46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX46" s="126">
         <f>AV46-AW46</f>
@@ -49394,11 +49398,11 @@
       </c>
       <c r="AZ46" s="126">
         <f>AT46/AT48*1000+AU46/AU48*100+AY46/AY48*10+AV46/AV48</f>
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="BA46" s="126">
         <f>AZ46/AZ48</f>
-        <v>0.99019607843137258</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB46" s="126" cm="1">
         <f t="array" ref="BB46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($X$7:$X$78))</f>
@@ -49410,11 +49414,11 @@
       </c>
       <c r="BD46" s="126" cm="1">
         <f t="array" ref="BD46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE46" s="126" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF46" s="126">
         <f>BD46-BE46</f>
@@ -49426,13 +49430,13 @@
       </c>
       <c r="BH46" s="126">
         <f>BB46/BB48*1000+BC46/BC48*100+BG46/BG48*10+BD46/BD48</f>
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="BI46" s="126">
         <f>BH46/BH48</f>
-        <v>0.99019607843137258</v>
-      </c>
-      <c r="BK46" s="141">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="BK46" s="131">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49484,7 +49488,7 @@
       </c>
       <c r="J47" s="33" t="str">
         <f>VLOOKUP(3,AD44:AN47,2,FALSE)</f>
-        <v>Belgium</v>
+        <v>New Zealand</v>
       </c>
       <c r="K47" s="23">
         <f>L47+M47+N47</f>
@@ -49504,7 +49508,7 @@
       </c>
       <c r="O47" s="23" t="str">
         <f>VLOOKUP(3,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD44:AN47,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P47" s="34">
         <f>L47*3+M47</f>
@@ -49556,7 +49560,7 @@
       </c>
       <c r="AD47" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR47))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE47" s="124" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
@@ -49596,11 +49600,11 @@
       </c>
       <c r="AO47" s="123">
         <f>AN47/AN48*10+BA47</f>
-        <v>5.9901960784313726</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="AP47" s="123">
         <f>AO47*10000000+BI47*100+AM47/AM48*10+AI47/AI48*1++IF(AQ47=0,ROW(),AQ47)/2000000</f>
-        <v>59902060.471229017</v>
+        <v>33333334.000640783</v>
       </c>
       <c r="AQ47" s="126">
         <f>VLOOKUP(AE47,db_fifarank,2,FALSE)</f>
@@ -49608,7 +49612,7 @@
       </c>
       <c r="AR47" s="125">
         <f>AP47/AP48</f>
-        <v>0.99999998330329809</v>
+        <v>0.43589687627669477</v>
       </c>
       <c r="AT47" s="126" cm="1">
         <f t="array" ref="AT47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($U$7:$U$78))</f>
@@ -49616,15 +49620,15 @@
       </c>
       <c r="AU47" s="126" cm="1">
         <f t="array" ref="AU47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV47" s="126" cm="1">
         <f t="array" ref="AV47">SUMPRODUCT(($E$7:$E$78=AE47)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW47" s="126" cm="1">
         <f t="array" ref="AW47">SUMPRODUCT(($E$7:$E$78=AE47)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX47" s="126">
         <f>AV47-AW47</f>
@@ -49636,11 +49640,11 @@
       </c>
       <c r="AZ47" s="126">
         <f>AT47/AT48*1000+AU47/AU48*100+AY47/AY48*10+AV47/AV48</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BA47" s="126">
         <f>AZ47/AZ48</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BB47" s="126" cm="1">
         <f t="array" ref="BB47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($X$7:$X$78))</f>
@@ -49648,15 +49652,15 @@
       </c>
       <c r="BC47" s="126" cm="1">
         <f t="array" ref="BC47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD47" s="126" cm="1">
         <f t="array" ref="BD47">SUMPRODUCT(($E$7:$E$78=AE47)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE47" s="126" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(($E$7:$E$78=AE47)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF47" s="126">
         <f>BD47-BE47</f>
@@ -49668,13 +49672,13 @@
       </c>
       <c r="BH47" s="126">
         <f>BB47/BB48*1000+BC47/BC48*100+BG47/BG48*10+BD47/BD48</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BI47" s="126">
         <f>BH47/BH48</f>
-        <v>0.99019607843137258</v>
-      </c>
-      <c r="BK47" s="142"/>
+        <v>0</v>
+      </c>
+      <c r="BK47" s="132"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49825,7 +49829,7 @@
       </c>
       <c r="AG48" s="123">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" s="123">
         <f t="shared" si="24"/>
@@ -49845,15 +49849,15 @@
       </c>
       <c r="AN48" s="123">
         <f>MAX(AN44:AN47)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO48" s="123">
         <f>MAX(AO44:AO47)+1</f>
-        <v>6.9901960784313726</v>
+        <v>8.6470588235294112</v>
       </c>
       <c r="AP48" s="123">
         <f>MAX(AP44:AP47)+1</f>
-        <v>59902061.47139588</v>
+        <v>76470687.941984117</v>
       </c>
       <c r="AT48" s="126">
         <f>MAX(AT44:AT47)-MIN(AT44:AT47)+1</f>
@@ -49861,15 +49865,15 @@
       </c>
       <c r="AU48" s="126">
         <f>MAX(AU44:AU47)-MIN(AU44:AU47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV48" s="126">
         <f>MAX(AV44:AV47)-MIN(AV44:AV47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW48" s="126">
         <f>MAX(AW44:AW47)-MIN(AW44:AW47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY48" s="126">
         <f>MAX(AY44:AY47)-MIN(AY44:AY47)+1</f>
@@ -49877,7 +49881,7 @@
       </c>
       <c r="AZ48" s="126">
         <f>MAX(AZ44:AZ47)+1</f>
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="BB48" s="126">
         <f>MAX(BB44:BB47)-MIN(BB44:BB47)+1</f>
@@ -49885,15 +49889,15 @@
       </c>
       <c r="BC48" s="126">
         <f>MAX(BC44:BC47)-MIN(BC44:BC47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD48" s="126">
         <f>MAX(BD44:BD47)-MIN(BD44:BD47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE48" s="126">
         <f>MAX(BE44:BE47)-MIN(BE44:BE47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG48" s="126">
         <f>MAX(BG44:BG47)-MIN(BG44:BG47)+1</f>
@@ -49901,7 +49905,7 @@
       </c>
       <c r="BH48" s="126">
         <f>MAX(BH44:BH47)+1</f>
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
@@ -49917,7 +49921,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="141">
+      <c r="BY48" s="131">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49933,7 +49937,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="141">
+      <c r="CM48" s="131">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50038,7 +50042,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="142"/>
+      <c r="BY49" s="132"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50052,7 +50056,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="142"/>
+      <c r="CM49" s="132"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50287,7 +50291,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="141">
+      <c r="BK50" s="131">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50540,7 +50544,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="142"/>
+      <c r="BK51" s="132"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50800,7 +50804,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="141">
+      <c r="BR52" s="131">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51055,7 +51059,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="142"/>
+      <c r="BR53" s="132"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51259,7 +51263,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK54" s="141">
+      <c r="BK54" s="131">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51380,7 +51384,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="142"/>
+      <c r="BK55" s="132"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51407,7 +51411,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="141">
+      <c r="CF55" s="131">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51666,7 +51670,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="142"/>
+      <c r="CF56" s="132"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52149,7 +52153,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="141">
+      <c r="BK58" s="131">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52397,7 +52401,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="142"/>
+      <c r="BK59" s="132"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52620,7 +52624,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="141">
+      <c r="BR60" s="131">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52733,7 +52737,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="142"/>
+      <c r="BR61" s="132"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52976,7 +52980,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="141">
+      <c r="BK62" s="131">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53228,7 +53232,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="142"/>
+      <c r="BK63" s="132"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53494,7 +53498,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="141">
+      <c r="BY64" s="131">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53748,7 +53752,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="142"/>
+      <c r="BY65" s="132"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53944,7 +53948,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="141">
+      <c r="BK66" s="131">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54044,7 +54048,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="142"/>
+      <c r="BK67" s="132"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54300,7 +54304,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="141">
+      <c r="BR68" s="131">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54314,25 +54318,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="143" t="str">
+      <c r="CE68" s="163" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="143"/>
-      <c r="CG68" s="143"/>
-      <c r="CH68" s="143"/>
-      <c r="CI68" s="143"/>
-      <c r="CJ68" s="143"/>
-      <c r="CK68" s="131" t="str">
+      <c r="CF68" s="163"/>
+      <c r="CG68" s="163"/>
+      <c r="CH68" s="163"/>
+      <c r="CI68" s="163"/>
+      <c r="CJ68" s="163"/>
+      <c r="CK68" s="153" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="131"/>
-      <c r="CM68" s="131"/>
-      <c r="CN68" s="131"/>
-      <c r="CO68" s="131"/>
-      <c r="CP68" s="131"/>
-      <c r="CQ68" s="131"/>
+      <c r="CL68" s="153"/>
+      <c r="CM68" s="153"/>
+      <c r="CN68" s="153"/>
+      <c r="CO68" s="153"/>
+      <c r="CP68" s="153"/>
+      <c r="CQ68" s="153"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54570,7 +54574,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="142"/>
+      <c r="BR69" s="132"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54582,19 +54586,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="143"/>
-      <c r="CF69" s="143"/>
-      <c r="CG69" s="143"/>
-      <c r="CH69" s="143"/>
-      <c r="CI69" s="143"/>
-      <c r="CJ69" s="143"/>
-      <c r="CK69" s="131"/>
-      <c r="CL69" s="131"/>
-      <c r="CM69" s="131"/>
-      <c r="CN69" s="131"/>
-      <c r="CO69" s="131"/>
-      <c r="CP69" s="131"/>
-      <c r="CQ69" s="131"/>
+      <c r="CE69" s="163"/>
+      <c r="CF69" s="163"/>
+      <c r="CG69" s="163"/>
+      <c r="CH69" s="163"/>
+      <c r="CI69" s="163"/>
+      <c r="CJ69" s="163"/>
+      <c r="CK69" s="153"/>
+      <c r="CL69" s="153"/>
+      <c r="CM69" s="153"/>
+      <c r="CN69" s="153"/>
+      <c r="CO69" s="153"/>
+      <c r="CP69" s="153"/>
+      <c r="CQ69" s="153"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54815,7 +54819,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="141">
+      <c r="BK70" s="131">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55051,7 +55055,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="142"/>
+      <c r="BK71" s="132"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56727,13 +56731,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="132" t="s">
+      <c r="C83" s="154" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="133"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="134"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="155"/>
+      <c r="G83" s="156"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56831,16 +56835,16 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
-      <c r="E84" s="136"/>
-      <c r="F84" s="136"/>
-      <c r="G84" s="137"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="159"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓖ New Zealand</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56860,7 +56864,7 @@
       </c>
       <c r="O84" s="100" t="str">
         <f>VLOOKUP(4,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(4,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
@@ -56945,11 +56949,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="135"/>
-      <c r="D85" s="136"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="137"/>
+      <c r="C85" s="157"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="159"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -57059,11 +57063,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="135"/>
-      <c r="D86" s="136"/>
-      <c r="E86" s="136"/>
-      <c r="F86" s="136"/>
-      <c r="G86" s="137"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="158"/>
+      <c r="G86" s="159"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57112,7 +57116,7 @@
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
-        <v>Belgium</v>
+        <v>New Zealand</v>
       </c>
       <c r="AF86" s="123">
         <f t="shared" si="39"/>
@@ -57128,11 +57132,11 @@
       </c>
       <c r="AI86" s="123">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ86" s="123">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK86" s="123" t="s">
         <v>3187</v>
@@ -57151,11 +57155,11 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>3314.2865816407143</v>
+        <v>3328.5720693564285</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
-        <v>1734.71</v>
+        <v>1281.57</v>
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
@@ -57163,21 +57167,21 @@
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Belgium</v>
+        <v>New Zealand</v>
       </c>
       <c r="AT86" s="130" t="str">
         <f>"Ⓖ "&amp;AE86</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓖ New Zealand</v>
       </c>
     </row>
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="136"/>
-      <c r="E87" s="136"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="137"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="158"/>
+      <c r="G87" s="159"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57287,11 +57291,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="140"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="162"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -57968,11 +57972,31 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -57988,31 +58012,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A64261-95E4-4A63-A469-E60C38406F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47B0EA0-916B-4CF1-B76E-33FF931A991F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,12 +13157,56 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13243,50 +13287,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="str" cm="1">
+      <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="140" t="str">
+      <c r="O3" s="151" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="140"/>
+      <c r="P3" s="151"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="141" t="str" cm="1">
+      <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="J5" s="147" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
+      <c r="J5" s="158" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="149"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="152"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="133" t="s">
+      <c r="BK6" s="144" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="134"/>
-      <c r="BM6" s="134"/>
-      <c r="BN6" s="134"/>
-      <c r="BO6" s="135"/>
-      <c r="BR6" s="133" t="str" cm="1">
+      <c r="BL6" s="145"/>
+      <c r="BM6" s="145"/>
+      <c r="BN6" s="145"/>
+      <c r="BO6" s="146"/>
+      <c r="BR6" s="144" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="134"/>
-      <c r="BT6" s="134"/>
-      <c r="BU6" s="134"/>
-      <c r="BV6" s="135"/>
-      <c r="BY6" s="133" t="str" cm="1">
+      <c r="BS6" s="145"/>
+      <c r="BT6" s="145"/>
+      <c r="BU6" s="145"/>
+      <c r="BV6" s="146"/>
+      <c r="BY6" s="144" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="134"/>
-      <c r="CA6" s="134"/>
-      <c r="CB6" s="134"/>
-      <c r="CC6" s="135"/>
-      <c r="CF6" s="133" t="str" cm="1">
+      <c r="BZ6" s="145"/>
+      <c r="CA6" s="145"/>
+      <c r="CB6" s="145"/>
+      <c r="CC6" s="146"/>
+      <c r="CF6" s="144" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="134"/>
-      <c r="CH6" s="134"/>
-      <c r="CI6" s="134"/>
-      <c r="CJ6" s="135"/>
+      <c r="CG6" s="145"/>
+      <c r="CH6" s="145"/>
+      <c r="CI6" s="145"/>
+      <c r="CJ6" s="146"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="136"/>
-      <c r="BL7" s="137"/>
-      <c r="BM7" s="137"/>
-      <c r="BN7" s="137"/>
-      <c r="BO7" s="138"/>
-      <c r="BR7" s="136"/>
-      <c r="BS7" s="137"/>
-      <c r="BT7" s="137"/>
-      <c r="BU7" s="137"/>
-      <c r="BV7" s="138"/>
-      <c r="BY7" s="136"/>
-      <c r="BZ7" s="137"/>
-      <c r="CA7" s="137"/>
-      <c r="CB7" s="137"/>
-      <c r="CC7" s="138"/>
-      <c r="CF7" s="136"/>
-      <c r="CG7" s="137"/>
-      <c r="CH7" s="137"/>
-      <c r="CI7" s="137"/>
-      <c r="CJ7" s="138"/>
+      <c r="BK7" s="147"/>
+      <c r="BL7" s="148"/>
+      <c r="BM7" s="148"/>
+      <c r="BN7" s="148"/>
+      <c r="BO7" s="149"/>
+      <c r="BR7" s="147"/>
+      <c r="BS7" s="148"/>
+      <c r="BT7" s="148"/>
+      <c r="BU7" s="148"/>
+      <c r="BV7" s="149"/>
+      <c r="BY7" s="147"/>
+      <c r="BZ7" s="148"/>
+      <c r="CA7" s="148"/>
+      <c r="CB7" s="148"/>
+      <c r="CC7" s="149"/>
+      <c r="CF7" s="147"/>
+      <c r="CG7" s="148"/>
+      <c r="CH7" s="148"/>
+      <c r="CI7" s="148"/>
+      <c r="CJ7" s="149"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="131">
+      <c r="BK10" s="141">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK11" s="132"/>
+      <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="131">
+      <c r="BR12" s="141">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="132"/>
+      <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="131">
+      <c r="BK14" s="141">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="132"/>
+      <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="131">
+      <c r="BY16" s="141">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="132"/>
+      <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="131">
+      <c r="BK18" s="141">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43127,27 +43127,27 @@
       </c>
       <c r="U19" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="123">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="123">
         <f t="shared" si="5"/>
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="132"/>
+      <c r="BK19" s="142"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="131">
+      <c r="BR20" s="141">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="132"/>
+      <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="131">
+      <c r="BK22" s="141">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="132"/>
+      <c r="BK23" s="142"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="131">
+      <c r="CF23" s="141">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44474,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="132"/>
+      <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44827,7 +44827,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="131">
+      <c r="BK26" s="141">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45095,7 +45095,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="132"/>
+      <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45370,7 +45370,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="131">
+      <c r="BR28" s="141">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45635,7 +45635,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="132"/>
+      <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45849,7 +45849,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="131">
+      <c r="BK30" s="141">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45960,7 +45960,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK31" s="132"/>
+      <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46236,7 +46236,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="131">
+      <c r="BY32" s="141">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46500,7 +46500,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="132"/>
+      <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46515,14 +46515,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="133" t="str" cm="1">
+      <c r="CM33" s="144" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="134"/>
-      <c r="CO33" s="134"/>
-      <c r="CP33" s="134"/>
-      <c r="CQ33" s="135"/>
+      <c r="CN33" s="145"/>
+      <c r="CO33" s="145"/>
+      <c r="CP33" s="145"/>
+      <c r="CQ33" s="146"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46746,7 +46746,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="131">
+      <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46777,11 +46777,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="136"/>
-      <c r="CN34" s="137"/>
-      <c r="CO34" s="137"/>
-      <c r="CP34" s="137"/>
-      <c r="CQ34" s="138"/>
+      <c r="CM34" s="147"/>
+      <c r="CN34" s="148"/>
+      <c r="CO34" s="148"/>
+      <c r="CP34" s="148"/>
+      <c r="CQ34" s="149"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -47005,7 +47005,7 @@
         <f>BH35/BH36</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK35" s="132"/>
+      <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47234,7 +47234,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="131">
+      <c r="BR36" s="141">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47358,7 +47358,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="132"/>
+      <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47385,7 +47385,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="131">
+      <c r="CM37" s="141">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47626,7 +47626,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="131">
+      <c r="BK38" s="141">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47656,7 +47656,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="132"/>
+      <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47895,7 +47895,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="132"/>
+      <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48583,7 +48583,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="131">
+      <c r="BK42" s="141">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48626,8 +48626,12 @@
         <f>AE53</f>
         <v>Uruguay</v>
       </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="20"/>
+      <c r="F43" s="19">
+        <v>2</v>
+      </c>
+      <c r="G43" s="20">
+        <v>2</v>
+      </c>
       <c r="H43" s="80" t="str">
         <f>AE51</f>
         <v>Cape Verde</v>
@@ -48638,45 +48642,45 @@
       </c>
       <c r="S43" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Uruguay_draw</v>
       </c>
       <c r="T43" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Cape Verde_draw</v>
       </c>
       <c r="U43" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA43" s="123">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB43" s="123" t="str">
+      <c r="AB43" s="123">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BK43" s="132"/>
+        <v>0</v>
+      </c>
+      <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48936,7 +48940,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="131">
+      <c r="BR44" s="141">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -48951,14 +48955,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="133" t="str" cm="1">
+      <c r="CM44" s="144" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="134"/>
-      <c r="CO44" s="134"/>
-      <c r="CP44" s="134"/>
-      <c r="CQ44" s="135"/>
+      <c r="CN44" s="145"/>
+      <c r="CO44" s="145"/>
+      <c r="CP44" s="145"/>
+      <c r="CQ44" s="146"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
@@ -49199,7 +49203,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="132"/>
+      <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49212,11 +49216,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="136"/>
-      <c r="CN45" s="137"/>
-      <c r="CO45" s="137"/>
-      <c r="CP45" s="137"/>
-      <c r="CQ45" s="138"/>
+      <c r="CM45" s="147"/>
+      <c r="CN45" s="148"/>
+      <c r="CO45" s="148"/>
+      <c r="CP45" s="148"/>
+      <c r="CQ45" s="149"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
@@ -49436,7 +49440,7 @@
         <f>BH46/BH48</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK46" s="131">
+      <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -49678,7 +49682,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="132"/>
+      <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -49921,7 +49925,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="131">
+      <c r="BY48" s="141">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -49937,7 +49941,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="131">
+      <c r="CM48" s="141">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50042,7 +50046,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="132"/>
+      <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50056,7 +50060,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="132"/>
+      <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50291,7 +50295,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="131">
+      <c r="BK50" s="141">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -50422,7 +50426,7 @@
       </c>
       <c r="AD51" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR51))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE51" s="124" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
@@ -50434,7 +50438,7 @@
       </c>
       <c r="AG51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_lose")</f>
@@ -50442,11 +50446,11 @@
       </c>
       <c r="AI51" s="123">
         <f>SUMIF($E$7:$E$78,$AE51,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE51,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ51" s="123">
         <f>SUMIF($E$7:$E$78,$AE51,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE51,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL51" s="123">
         <f>AI51-AJ51</f>
@@ -50458,15 +50462,15 @@
       </c>
       <c r="AN51" s="123">
         <f>AF51*3+AG51</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO51" s="123">
         <f>AN51/AN54*10+BA51</f>
-        <v>2</v>
+        <v>4.9806451612903224</v>
       </c>
       <c r="AP51" s="123">
         <f>AO51*10000000+BI51*100+AM51/AM54*10+AI51/AI54*1++IF(AQ51=0,ROW(),AQ51)/2000000</f>
-        <v>20000004.44512751</v>
+        <v>49806554.522546858</v>
       </c>
       <c r="AQ51" s="126">
         <f>VLOOKUP(AE51,db_fifarank,2,FALSE)</f>
@@ -50474,7 +50478,7 @@
       </c>
       <c r="AR51" s="125">
         <f>AP51/AP54</f>
-        <v>0.25000002215838124</v>
+        <v>0.62258184834068175</v>
       </c>
       <c r="AS51" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J52,"2H")</f>
@@ -50486,15 +50490,15 @@
       </c>
       <c r="AU51" s="126" cm="1">
         <f t="array" ref="AU51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV51" s="126" cm="1">
         <f t="array" ref="AV51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW51" s="126" cm="1">
         <f t="array" ref="AW51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX51" s="126">
         <f>AV51-AW51</f>
@@ -50506,11 +50510,11 @@
       </c>
       <c r="AZ51" s="126">
         <f>AT51/AT54*1000+AU51/AU54*100+AY51/AY54*10+AV51/AV54</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA51" s="126">
         <f>AZ51/AZ54</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB51" s="126" cm="1">
         <f t="array" ref="BB51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($X$7:$X$78))</f>
@@ -50518,15 +50522,15 @@
       </c>
       <c r="BC51" s="126" cm="1">
         <f t="array" ref="BC51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD51" s="126" cm="1">
         <f t="array" ref="BD51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE51" s="126" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF51" s="126">
         <f>BD51-BE51</f>
@@ -50538,13 +50542,13 @@
       </c>
       <c r="BH51" s="126">
         <f>BB51/BB54*1000+BC51/BC54*100+BG51/BG54*10+BD51/BD54</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI51" s="126">
         <f>BH51/BH54</f>
-        <v>0</v>
-      </c>
-      <c r="BK51" s="132"/>
+        <v>0.98064516129032253</v>
+      </c>
+      <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -50611,7 +50615,7 @@
       </c>
       <c r="K52" s="23">
         <f>L52+M52+N52</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="23">
         <f>VLOOKUP(2,AD50:AN53,3,FALSE)</f>
@@ -50619,7 +50623,7 @@
       </c>
       <c r="M52" s="23">
         <f>VLOOKUP(2,AD50:AN53,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52" s="23">
         <f>VLOOKUP(2,AD50:AN53,5,FALSE)</f>
@@ -50627,11 +50631,11 @@
       </c>
       <c r="O52" s="23" t="str">
         <f>VLOOKUP(2,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD50:AN53,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>3 - 3</v>
       </c>
       <c r="P52" s="34">
         <f>L52*3+M52</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52" s="123">
         <f>DATE(2026,6,23)+TIME(12,0,0)+gmt_delta</f>
@@ -50679,7 +50683,7 @@
       </c>
       <c r="AD52" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR52))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE52" s="124" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
@@ -50719,11 +50723,11 @@
       </c>
       <c r="AO52" s="123">
         <f>AN52/AN54*10+BA52</f>
-        <v>2.9805825242718447</v>
+        <v>2</v>
       </c>
       <c r="AP52" s="123">
         <f>AO52*10000000+BI52*100+AM52/AM54*10+AI52/AI54*1++IF(AQ52=0,ROW(),AQ52)/2000000</f>
-        <v>29805923.501681589</v>
+        <v>20000000.200710714</v>
       </c>
       <c r="AQ52" s="126">
         <f>VLOOKUP(AE52,db_fifarank,2,FALSE)</f>
@@ -50731,7 +50735,7 @@
       </c>
       <c r="AR52" s="125">
         <f>AP52/AP54</f>
-        <v>0.37257399398662516</v>
+        <v>0.24999996910317837</v>
       </c>
       <c r="AT52" s="126" cm="1">
         <f t="array" ref="AT52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($U$7:$U$78))</f>
@@ -50739,15 +50743,15 @@
       </c>
       <c r="AU52" s="126" cm="1">
         <f t="array" ref="AU52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV52" s="126" cm="1">
         <f t="array" ref="AV52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW52" s="126" cm="1">
         <f t="array" ref="AW52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX52" s="126">
         <f>AV52-AW52</f>
@@ -50759,11 +50763,11 @@
       </c>
       <c r="AZ52" s="126">
         <f>AT52/AT54*1000+AU52/AU54*100+AY52/AY54*10+AV52/AV54</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BA52" s="126">
         <f>AZ52/AZ54</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BB52" s="126" cm="1">
         <f t="array" ref="BB52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($X$7:$X$78))</f>
@@ -50771,15 +50775,15 @@
       </c>
       <c r="BC52" s="126" cm="1">
         <f t="array" ref="BC52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD52" s="126" cm="1">
         <f t="array" ref="BD52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE52" s="126" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF52" s="126">
         <f>BD52-BE52</f>
@@ -50791,11 +50795,11 @@
       </c>
       <c r="BH52" s="126">
         <f>BB52/BB54*1000+BC52/BC54*100+BG52/BG54*10+BD52/BD54</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BI52" s="126">
         <f>BH52/BH54</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BK52" s="21"/>
       <c r="BL52" s="21"/>
@@ -50804,7 +50808,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="131">
+      <c r="BR52" s="141">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -50856,7 +50860,7 @@
       </c>
       <c r="J53" s="33" t="str">
         <f>VLOOKUP(3,AD50:AN53,2,FALSE)</f>
-        <v>Saudi Arabia</v>
+        <v>Cape Verde</v>
       </c>
       <c r="K53" s="23">
         <f>L53+M53+N53</f>
@@ -50868,19 +50872,19 @@
       </c>
       <c r="M53" s="23">
         <f>VLOOKUP(3,AD50:AN53,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53" s="23">
         <f>VLOOKUP(3,AD50:AN53,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="23" t="str">
         <f>VLOOKUP(3,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD50:AN53,7,FALSE)</f>
-        <v>1 - 5</v>
+        <v>2 - 2</v>
       </c>
       <c r="P53" s="34">
         <f>L53*3+M53</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53" s="123">
         <f>DATE(2026,6,23)+TIME(6,0,0)+gmt_delta</f>
@@ -50940,7 +50944,7 @@
       </c>
       <c r="AG53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_lose")</f>
@@ -50948,11 +50952,11 @@
       </c>
       <c r="AI53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE53,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE53,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL53" s="123">
         <f>AI53-AJ53</f>
@@ -50964,15 +50968,15 @@
       </c>
       <c r="AN53" s="123">
         <f>AF53*3+AG53</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO53" s="123">
         <f>AN53/AN54*10+BA53</f>
-        <v>2.9805825242718447</v>
+        <v>4.9806451612903224</v>
       </c>
       <c r="AP53" s="123">
         <f>AO53*10000000+BI53*100+AM53/AM54*10+AI53/AI54*1++IF(AQ53=0,ROW(),AQ53)/2000000</f>
-        <v>29805927.946251854</v>
+        <v>49806554.722700335</v>
       </c>
       <c r="AQ53" s="126">
         <f>VLOOKUP(AE53,db_fifarank,2,FALSE)</f>
@@ -50980,7 +50984,7 @@
       </c>
       <c r="AR53" s="125">
         <f>AP53/AP54</f>
-        <v>0.37257404954374601</v>
+        <v>0.62258185084259998</v>
       </c>
       <c r="AT53" s="126" cm="1">
         <f t="array" ref="AT53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($U$7:$U$78))</f>
@@ -50992,11 +50996,11 @@
       </c>
       <c r="AV53" s="126" cm="1">
         <f t="array" ref="AV53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW53" s="126" cm="1">
         <f t="array" ref="AW53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX53" s="126">
         <f>AV53-AW53</f>
@@ -51008,11 +51012,11 @@
       </c>
       <c r="AZ53" s="126">
         <f>AT53/AT54*1000+AU53/AU54*100+AY53/AY54*10+AV53/AV54</f>
-        <v>50.5</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA53" s="126">
         <f>AZ53/AZ54</f>
-        <v>0.98058252427184467</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB53" s="126" cm="1">
         <f t="array" ref="BB53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($X$7:$X$78))</f>
@@ -51024,11 +51028,11 @@
       </c>
       <c r="BD53" s="126" cm="1">
         <f t="array" ref="BD53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE53" s="126" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF53" s="126">
         <f>BD53-BE53</f>
@@ -51040,11 +51044,11 @@
       </c>
       <c r="BH53" s="126">
         <f>BB53/BB54*1000+BC53/BC54*100+BG53/BG54*10+BD53/BD54</f>
-        <v>50.5</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI53" s="126">
         <f>BH53/BH54</f>
-        <v>0.98058252427184467</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BK53" s="21" t="str" cm="1">
         <f t="array" ref="BK53">INDEX(T,24+MONTH(BP53),lang) &amp; " " &amp; DAY(BP53) &amp; ", " &amp; YEAR(BP53) &amp; "   " &amp; (IF(HOUR(BP53)&lt;10,0,"")&amp;HOUR(BP53)) &amp; ":" &amp;  (IF(MINUTE(BP53)&lt;10,0,"")&amp;MINUTE(BP53))</f>
@@ -51059,7 +51063,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="132"/>
+      <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51109,11 +51113,11 @@
       </c>
       <c r="J54" s="35" t="str">
         <f>VLOOKUP(4,AD50:AN53,2,FALSE)</f>
-        <v>Cape Verde</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="K54" s="36">
         <f>L54+M54+N54</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="36">
         <f>VLOOKUP(4,AD50:AN53,3,FALSE)</f>
@@ -51125,11 +51129,11 @@
       </c>
       <c r="N54" s="36">
         <f>VLOOKUP(4,AD50:AN53,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="36" t="str">
         <f>VLOOKUP(4,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD50:AN53,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 5</v>
       </c>
       <c r="P54" s="37">
         <f>L54*3+M54</f>
@@ -51185,7 +51189,7 @@
       </c>
       <c r="AG54" s="123">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH54" s="123">
         <f t="shared" si="25"/>
@@ -51225,11 +51229,11 @@
       </c>
       <c r="AV54" s="126">
         <f>MAX(AV50:AV53)-MIN(AV50:AV53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW54" s="126">
         <f>MAX(AW50:AW53)-MIN(AW50:AW53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY54" s="126">
         <f>MAX(AY50:AY53)-MIN(AY50:AY53)+1</f>
@@ -51237,7 +51241,7 @@
       </c>
       <c r="AZ54" s="126">
         <f>MAX(AZ50:AZ53)+1</f>
-        <v>51.5</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BB54" s="126">
         <f>MAX(BB50:BB53)-MIN(BB50:BB53)+1</f>
@@ -51249,11 +51253,11 @@
       </c>
       <c r="BD54" s="126">
         <f>MAX(BD50:BD53)-MIN(BD50:BD53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE54" s="126">
         <f>MAX(BE50:BE53)-MIN(BE50:BE53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG54" s="126">
         <f>MAX(BG50:BG53)-MIN(BG50:BG53)+1</f>
@@ -51261,9 +51265,9 @@
       </c>
       <c r="BH54" s="126">
         <f>MAX(BH50:BH53)+1</f>
-        <v>51.5</v>
-      </c>
-      <c r="BK54" s="131">
+        <v>51.666666666666664</v>
+      </c>
+      <c r="BK54" s="141">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -51384,7 +51388,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="132"/>
+      <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -51411,7 +51415,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="131">
+      <c r="CF55" s="141">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -51670,7 +51674,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="132"/>
+      <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52153,7 +52157,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="131">
+      <c r="BK58" s="141">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52401,7 +52405,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="132"/>
+      <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -52624,7 +52628,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="131">
+      <c r="BR60" s="141">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -52737,7 +52741,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="132"/>
+      <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -52980,7 +52984,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="131">
+      <c r="BK62" s="141">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53232,7 +53236,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="132"/>
+      <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -53498,7 +53502,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="131">
+      <c r="BY64" s="141">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -53752,7 +53756,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="132"/>
+      <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -53948,7 +53952,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="131">
+      <c r="BK66" s="141">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54048,7 +54052,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="132"/>
+      <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54304,7 +54308,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="131">
+      <c r="BR68" s="141">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -54318,25 +54322,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="163" t="str">
+      <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="163"/>
-      <c r="CG68" s="163"/>
-      <c r="CH68" s="163"/>
-      <c r="CI68" s="163"/>
-      <c r="CJ68" s="163"/>
-      <c r="CK68" s="153" t="str">
+      <c r="CF68" s="143"/>
+      <c r="CG68" s="143"/>
+      <c r="CH68" s="143"/>
+      <c r="CI68" s="143"/>
+      <c r="CJ68" s="143"/>
+      <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="153"/>
-      <c r="CM68" s="153"/>
-      <c r="CN68" s="153"/>
-      <c r="CO68" s="153"/>
-      <c r="CP68" s="153"/>
-      <c r="CQ68" s="153"/>
+      <c r="CL68" s="131"/>
+      <c r="CM68" s="131"/>
+      <c r="CN68" s="131"/>
+      <c r="CO68" s="131"/>
+      <c r="CP68" s="131"/>
+      <c r="CQ68" s="131"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
@@ -54574,7 +54578,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="132"/>
+      <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -54586,19 +54590,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="163"/>
-      <c r="CF69" s="163"/>
-      <c r="CG69" s="163"/>
-      <c r="CH69" s="163"/>
-      <c r="CI69" s="163"/>
-      <c r="CJ69" s="163"/>
-      <c r="CK69" s="153"/>
-      <c r="CL69" s="153"/>
-      <c r="CM69" s="153"/>
-      <c r="CN69" s="153"/>
-      <c r="CO69" s="153"/>
-      <c r="CP69" s="153"/>
-      <c r="CQ69" s="153"/>
+      <c r="CE69" s="143"/>
+      <c r="CF69" s="143"/>
+      <c r="CG69" s="143"/>
+      <c r="CH69" s="143"/>
+      <c r="CI69" s="143"/>
+      <c r="CJ69" s="143"/>
+      <c r="CK69" s="131"/>
+      <c r="CL69" s="131"/>
+      <c r="CM69" s="131"/>
+      <c r="CN69" s="131"/>
+      <c r="CO69" s="131"/>
+      <c r="CP69" s="131"/>
+      <c r="CQ69" s="131"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
@@ -54819,7 +54823,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="131">
+      <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55055,7 +55059,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="132"/>
+      <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -56462,7 +56466,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56497,7 +56501,7 @@
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,10,FALSE)</f>
@@ -56505,7 +56509,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>3128.5721792614286</v>
+        <v>3028.5721792614286</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -56564,7 +56568,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -56599,7 +56603,7 @@
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
@@ -56607,7 +56611,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>2728.5721214914283</v>
+        <v>2528.5721214914283</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -56615,11 +56619,11 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>AB</v>
+        <v>A</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
-        <v>Bosnia and Herzegovina</v>
+        <v/>
       </c>
       <c r="AT81" s="130" t="str">
         <f>"Ⓑ "&amp;AE81</f>
@@ -56701,7 +56705,7 @@
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
@@ -56709,7 +56713,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>8314.286463460714</v>
+        <v>8264.286463460714</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -56717,7 +56721,7 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>ABC</v>
+        <v>AC</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56731,13 +56735,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="154" t="s">
+      <c r="C83" s="132" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-      <c r="F83" s="155"/>
-      <c r="G83" s="156"/>
+      <c r="D83" s="133"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="134"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -56805,7 +56809,7 @@
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
@@ -56813,7 +56817,7 @@
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>7928.5721803214283</v>
+        <v>7778.5721803214283</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
@@ -56821,7 +56825,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCD</v>
+        <v>ACD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56835,20 +56839,20 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="157"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="159"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="137"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ New Zealand</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,3,FALSE)</f>
@@ -56856,7 +56860,7 @@
       </c>
       <c r="M84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,5,FALSE)</f>
@@ -56868,7 +56872,7 @@
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R84" s="123">
         <f>DATE(2026,12,3)+TIME(4,0,0)+gmt_delta</f>
@@ -56884,7 +56888,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56919,7 +56923,7 @@
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
@@ -56927,7 +56931,7 @@
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>3100.0007973900001</v>
+        <v>3000.0007973900001</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -56935,7 +56939,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDE</v>
+        <v>ACDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56949,16 +56953,16 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="157"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="159"/>
+      <c r="C85" s="135"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="137"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓖ New Zealand</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -56978,7 +56982,7 @@
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
@@ -57033,7 +57037,7 @@
       </c>
       <c r="AM85" s="123">
         <f t="shared" si="44"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
@@ -57041,7 +57045,7 @@
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>8385.715043099286</v>
+        <v>8335.715043099286</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -57049,7 +57053,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDEF</v>
+        <v>ACDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57063,20 +57067,20 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="157"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="159"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="137"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
@@ -57088,11 +57092,11 @@
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>1 - 1</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
@@ -57112,7 +57116,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57147,7 +57151,7 @@
       </c>
       <c r="AM86" s="123">
         <f t="shared" si="44"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
@@ -57155,7 +57159,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>3328.5720693564285</v>
+        <v>3278.5720693564285</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57163,7 +57167,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDEFG</v>
+        <v>ACDEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57177,16 +57181,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="157"/>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="159"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="136"/>
+      <c r="E87" s="136"/>
+      <c r="F87" s="136"/>
+      <c r="G87" s="137"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57206,7 +57210,7 @@
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 3</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
@@ -57226,11 +57230,11 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
-        <v>Saudi Arabia</v>
+        <v>Cape Verde</v>
       </c>
       <c r="AF87" s="123">
         <f t="shared" si="39"/>
@@ -57238,69 +57242,69 @@
       </c>
       <c r="AG87" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH87" s="123">
         <f t="shared" si="40"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI87" s="123">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ87" s="123">
         <f t="shared" si="42"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK87" s="123" t="s">
         <v>3188</v>
       </c>
       <c r="AL87" s="123">
         <f t="shared" si="43"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>2514.2864250007142</v>
+        <v>5778.5721116364284</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
-        <v>1421.43</v>
+        <v>1366.13</v>
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDEFG</v>
+        <v>ACDEFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Cape Verde</v>
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
     </row>
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="162"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="140"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Bosnia and Herzegovina</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -57320,7 +57324,7 @@
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 5</v>
+        <v>0 - 1</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
@@ -57375,7 +57379,7 @@
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -57383,7 +57387,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>414.2865587807143</v>
+        <v>264.2865587807143</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -57391,7 +57395,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDEFG</v>
+        <v>ACDEFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57414,7 +57418,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -57434,7 +57438,7 @@
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 5</v>
+        <v>2 - 5</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
@@ -57489,7 +57493,7 @@
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -57497,7 +57501,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>414.28641001071429</v>
+        <v>264.28641001071429</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -57505,7 +57509,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDEFG</v>
+        <v>ACDEFGH</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57568,7 +57572,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -57603,7 +57607,7 @@
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
@@ -57611,7 +57615,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>3314.2864534607143</v>
+        <v>3264.2864534607143</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -57619,7 +57623,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDEFGK</v>
+        <v>ACDEFGHK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57717,7 +57721,7 @@
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57725,7 +57729,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>600.00077032000002</v>
+        <v>500.00077032000002</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -57733,7 +57737,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCDEFGK</v>
+        <v>ACDEFGHK</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57788,7 +57792,7 @@
       </c>
       <c r="AG92" s="123">
         <f>MAX(AG80:AG91)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
@@ -57804,11 +57808,11 @@
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
@@ -57972,6 +57976,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -57987,36 +58021,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -59059,15 +59063,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>492</v>
+        <v>283</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ABCDEFGK</v>
+        <v>ACDEFGHK</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3C</v>
+        <v>3H</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -59075,11 +59079,11 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3B</v>
+        <v>3E</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
-        <v>3D</v>
+        <v>3C</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
@@ -59091,7 +59095,7 @@
       </c>
       <c r="J3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,8,FALSE)</f>
-        <v>3E</v>
+        <v>3D</v>
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>

--- a/fasit/world_cup_2026_fasit.xlsx
+++ b/fasit/world_cup_2026_fasit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hs\git\VM2026\fasit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47B0EA0-916B-4CF1-B76E-33FF931A991F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7B8906-5403-4878-85EF-36BB85DECFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13157,56 +13157,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13287,6 +13243,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40067,25 +40067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="str" cm="1">
+      <c r="A1" s="139" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40132,11 +40132,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="151" t="str">
+      <c r="O3" s="140" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="151"/>
+      <c r="P3" s="140"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -40154,43 +40154,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="str" cm="1">
+      <c r="A5" s="141" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
-      <c r="J5" s="158" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="J5" s="147" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="159"/>
-      <c r="P5" s="160"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="163"/>
+      <c r="A6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="152"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -40300,37 +40300,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="144" t="s">
+      <c r="BK6" s="133" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="145"/>
-      <c r="BM6" s="145"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BR6" s="144" t="str" cm="1">
+      <c r="BL6" s="134"/>
+      <c r="BM6" s="134"/>
+      <c r="BN6" s="134"/>
+      <c r="BO6" s="135"/>
+      <c r="BR6" s="133" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="145"/>
-      <c r="BT6" s="145"/>
-      <c r="BU6" s="145"/>
-      <c r="BV6" s="146"/>
-      <c r="BY6" s="144" t="str" cm="1">
+      <c r="BS6" s="134"/>
+      <c r="BT6" s="134"/>
+      <c r="BU6" s="134"/>
+      <c r="BV6" s="135"/>
+      <c r="BY6" s="133" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="145"/>
-      <c r="CA6" s="145"/>
-      <c r="CB6" s="145"/>
-      <c r="CC6" s="146"/>
-      <c r="CF6" s="144" t="str" cm="1">
+      <c r="BZ6" s="134"/>
+      <c r="CA6" s="134"/>
+      <c r="CB6" s="134"/>
+      <c r="CC6" s="135"/>
+      <c r="CF6" s="133" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="145"/>
-      <c r="CH6" s="145"/>
-      <c r="CI6" s="145"/>
-      <c r="CJ6" s="146"/>
+      <c r="CG6" s="134"/>
+      <c r="CH6" s="134"/>
+      <c r="CI6" s="134"/>
+      <c r="CJ6" s="135"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -40407,26 +40407,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="147"/>
-      <c r="BL7" s="148"/>
-      <c r="BM7" s="148"/>
-      <c r="BN7" s="148"/>
-      <c r="BO7" s="149"/>
-      <c r="BR7" s="147"/>
-      <c r="BS7" s="148"/>
-      <c r="BT7" s="148"/>
-      <c r="BU7" s="148"/>
-      <c r="BV7" s="149"/>
-      <c r="BY7" s="147"/>
-      <c r="BZ7" s="148"/>
-      <c r="CA7" s="148"/>
-      <c r="CB7" s="148"/>
-      <c r="CC7" s="149"/>
-      <c r="CF7" s="147"/>
-      <c r="CG7" s="148"/>
-      <c r="CH7" s="148"/>
-      <c r="CI7" s="148"/>
-      <c r="CJ7" s="149"/>
+      <c r="BK7" s="136"/>
+      <c r="BL7" s="137"/>
+      <c r="BM7" s="137"/>
+      <c r="BN7" s="137"/>
+      <c r="BO7" s="138"/>
+      <c r="BR7" s="136"/>
+      <c r="BS7" s="137"/>
+      <c r="BT7" s="137"/>
+      <c r="BU7" s="137"/>
+      <c r="BV7" s="138"/>
+      <c r="BY7" s="136"/>
+      <c r="BZ7" s="137"/>
+      <c r="CA7" s="137"/>
+      <c r="CB7" s="137"/>
+      <c r="CC7" s="138"/>
+      <c r="CF7" s="136"/>
+      <c r="CG7" s="137"/>
+      <c r="CH7" s="137"/>
+      <c r="CI7" s="137"/>
+      <c r="CJ7" s="138"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -41162,7 +41162,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="141">
+      <c r="BK10" s="131">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -41425,7 +41425,7 @@
         <f>BH11/BH12</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK11" s="142"/>
+      <c r="BK11" s="132"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -41663,7 +41663,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="141">
+      <c r="BR12" s="131">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -41784,7 +41784,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="142"/>
+      <c r="BR13" s="132"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42042,7 +42042,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="141">
+      <c r="BK14" s="131">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42309,7 +42309,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="142"/>
+      <c r="BK15" s="132"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -42583,7 +42583,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="141">
+      <c r="BY16" s="131">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -42845,7 +42845,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="142"/>
+      <c r="BY17" s="132"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43049,7 +43049,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="141">
+      <c r="BK18" s="131">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43157,7 +43157,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="142"/>
+      <c r="BK19" s="132"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -43435,7 +43435,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="141">
+      <c r="BR20" s="131">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -43708,7 +43708,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="142"/>
+      <c r="BR21" s="132"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -43962,7 +43962,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="141">
+      <c r="BK22" s="131">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44226,7 +44226,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="142"/>
+      <c r="BK23" s="132"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -44253,7 +44253,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="141">
+      <c r="CF23" s="131">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -44474,7 +44474,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="142"/>
+      <c r="CF24" s="132"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -44827,7 +44827,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="141">
+      <c r="BK26" s="131">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45095,7 +45095,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="142"/>
+      <c r="BK27" s="132"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45370,7 +45370,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="141">
+      <c r="BR28" s="131">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -45635,7 +45635,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="142"/>
+      <c r="BR29" s="132"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -45849,7 +45849,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="141">
+      <c r="BK30" s="131">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -45960,7 +45960,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK31" s="142"/>
+      <c r="BK31" s="132"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46236,7 +46236,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="141">
+      <c r="BY32" s="131">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -46500,7 +46500,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="142"/>
+      <c r="BY33" s="132"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -46515,14 +46515,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="144" t="str" cm="1">
+      <c r="CM33" s="133" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="145"/>
-      <c r="CO33" s="145"/>
-      <c r="CP33" s="145"/>
-      <c r="CQ33" s="146"/>
+      <c r="CN33" s="134"/>
+      <c r="CO33" s="134"/>
+      <c r="CP33" s="134"/>
+      <c r="CQ33" s="135"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -46746,7 +46746,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="141">
+      <c r="BK34" s="131">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -46777,11 +46777,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="147"/>
-      <c r="CN34" s="148"/>
-      <c r="CO34" s="148"/>
-      <c r="CP34" s="148"/>
-      <c r="CQ34" s="149"/>
+      <c r="CM34" s="136"/>
+      <c r="CN34" s="137"/>
+      <c r="CO34" s="137"/>
+      <c r="CP34" s="137"/>
+      <c r="CQ34" s="138"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -47005,7 +47005,7 @@
         <f>BH35/BH36</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK35" s="142"/>
+      <c r="BK35" s="132"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47234,7 +47234,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="141">
+      <c r="BR36" s="131">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -47358,7 +47358,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="142"/>
+      <c r="BR37" s="132"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -47385,7 +47385,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="141">
+      <c r="CM37" s="131">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -47626,7 +47626,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="141">
+      <c r="BK38" s="131">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -47656,7 +47656,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="142"/>
+      <c r="CM38" s="132"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -47895,7 +47895,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="142"/>
+      <c r="BK39" s="132"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48583,7 +48583,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="141">
+      <c r="BK42" s="131">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -48680,7 +48680,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="142"/>
+      <c r="BK43" s="132"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -48811,7 +48811,7 @@
       </c>
       <c r="AD44" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR44))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE44" s="124" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
@@ -48843,7 +48843,7 @@
       </c>
       <c r="AM44" s="123">
         <f>AL44-AL48</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
@@ -48851,11 +48851,11 @@
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>7.6470588235294112</v>
+        <v>4.9803921568627452</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>76470686.608710483</v>
+        <v>49804023.808710493</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -48863,7 +48863,7 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>0.99999998256490596</v>
+        <v>0.62255022134039661</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
@@ -48940,7 +48940,7 @@
      